--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD COMBUSTIVEL/DASHBOARD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="329" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D82B8A67-AE72-4A2A-AE15-832CB1E81081}"/>
+  <xr:revisionPtr revIDLastSave="641" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5571D5BF-7362-4C43-BC82-CBB6A8D3CA90}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7943" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8066" uniqueCount="335">
   <si>
     <t>Data</t>
   </si>
@@ -1039,6 +1039,12 @@
   <si>
     <t>EDENEY</t>
   </si>
+  <si>
+    <t>POSTO ITAJAO</t>
+  </si>
+  <si>
+    <t>POSTO SOARES</t>
+  </si>
 </sst>
 </file>
 
@@ -1179,7 +1185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1235,7 +1241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1245,7 +1251,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1597,7 +1602,18 @@
     <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="33" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+    </row>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="30" t="s">
         <v>0</v>
@@ -70047,19 +70063,33 @@
       </c>
     </row>
     <row r="2131" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2131" s="18"/>
+      <c r="B2131" s="18">
+        <v>45938</v>
+      </c>
       <c r="C2131" s="1"/>
       <c r="D2131" s="1"/>
       <c r="E2131" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2131" s="1"/>
-      <c r="G2131" s="10"/>
-      <c r="H2131" s="3"/>
-      <c r="I2131" s="12"/>
-      <c r="J2131" s="7"/>
-      <c r="K2131" s="7"/>
+      <c r="F2131" s="1">
+        <v>46.94</v>
+      </c>
+      <c r="G2131" s="10">
+        <v>300</v>
+      </c>
+      <c r="H2131" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2131" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2131" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2131" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2132" s="18">
@@ -70352,124 +70382,236 @@
       </c>
     </row>
     <row r="2142" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2142" s="18"/>
+      <c r="B2142" s="18">
+        <v>45937</v>
+      </c>
       <c r="C2142" s="1"/>
       <c r="D2142" s="1"/>
       <c r="E2142" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2142" s="1"/>
-      <c r="G2142" s="10"/>
-      <c r="H2142" s="3"/>
-      <c r="I2142" s="12"/>
-      <c r="J2142" s="7"/>
-      <c r="K2142" s="7"/>
+      <c r="F2142" s="1">
+        <v>135.13999999999999</v>
+      </c>
+      <c r="G2142" s="10">
+        <v>850.03</v>
+      </c>
+      <c r="H2142" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2142" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2142" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2142" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2143" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2143" s="18"/>
+      <c r="B2143" s="18">
+        <v>45931</v>
+      </c>
       <c r="C2143" s="1"/>
       <c r="D2143" s="1"/>
       <c r="E2143" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2143" s="1"/>
-      <c r="G2143" s="10"/>
-      <c r="H2143" s="3"/>
-      <c r="I2143" s="12"/>
-      <c r="J2143" s="7"/>
-      <c r="K2143" s="7"/>
+      <c r="F2143" s="1">
+        <v>195.1</v>
+      </c>
+      <c r="G2143" s="10">
+        <v>1227.21</v>
+      </c>
+      <c r="H2143" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2143" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2143" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2143" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2144" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2144" s="18"/>
+      <c r="B2144" s="18">
+        <v>45931</v>
+      </c>
       <c r="C2144" s="1"/>
       <c r="D2144" s="1"/>
       <c r="E2144" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2144" s="1"/>
-      <c r="G2144" s="10"/>
-      <c r="H2144" s="3"/>
-      <c r="I2144" s="12"/>
-      <c r="J2144" s="7"/>
-      <c r="K2144" s="7"/>
+      <c r="F2144" s="1">
+        <v>50.084000000000003</v>
+      </c>
+      <c r="G2144" s="10">
+        <v>300</v>
+      </c>
+      <c r="H2144" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2144" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2144" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="K2144" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2145" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2145" s="18"/>
+      <c r="B2145" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2145" s="1"/>
       <c r="D2145" s="1"/>
       <c r="E2145" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2145" s="1"/>
-      <c r="G2145" s="10"/>
-      <c r="H2145" s="3"/>
-      <c r="I2145" s="12"/>
-      <c r="J2145" s="7"/>
-      <c r="K2145" s="7"/>
+      <c r="F2145" s="1">
+        <v>78.239999999999995</v>
+      </c>
+      <c r="G2145" s="10">
+        <v>500</v>
+      </c>
+      <c r="H2145" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2145" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2145" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K2145" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2146" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2146" s="18"/>
+      <c r="B2146" s="18">
+        <v>45938</v>
+      </c>
       <c r="C2146" s="1"/>
       <c r="D2146" s="1"/>
       <c r="E2146" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2146" s="1"/>
-      <c r="G2146" s="10"/>
-      <c r="H2146" s="3"/>
-      <c r="I2146" s="12"/>
-      <c r="J2146" s="7"/>
-      <c r="K2146" s="7"/>
+      <c r="F2146" s="1">
+        <v>144.86000000000001</v>
+      </c>
+      <c r="G2146" s="10">
+        <v>911.21</v>
+      </c>
+      <c r="H2146" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2146" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2146" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2146" s="7" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2147" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2147" s="18"/>
+      <c r="B2147" s="18">
+        <v>45941</v>
+      </c>
       <c r="C2147" s="1"/>
       <c r="D2147" s="1"/>
       <c r="E2147" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2147" s="1"/>
-      <c r="G2147" s="10"/>
-      <c r="H2147" s="3"/>
-      <c r="I2147" s="12"/>
-      <c r="J2147" s="7"/>
-      <c r="K2147" s="7"/>
+      <c r="F2147" s="1">
+        <v>99.17</v>
+      </c>
+      <c r="G2147" s="10">
+        <v>600</v>
+      </c>
+      <c r="H2147" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2147" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2147" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2147" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2148" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2148" s="18"/>
+      <c r="B2148" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2148" s="1"/>
       <c r="D2148" s="1"/>
       <c r="E2148" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2148" s="1"/>
-      <c r="G2148" s="10"/>
-      <c r="H2148" s="3"/>
-      <c r="I2148" s="12"/>
-      <c r="J2148" s="7"/>
-      <c r="K2148" s="7"/>
+      <c r="F2148" s="1">
+        <v>153.18100000000001</v>
+      </c>
+      <c r="G2148" s="10">
+        <v>891.51</v>
+      </c>
+      <c r="H2148" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2148" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2148" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2148" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2149" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2149" s="18"/>
+      <c r="B2149" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2149" s="1"/>
       <c r="D2149" s="1"/>
       <c r="E2149" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2149" s="1"/>
-      <c r="G2149" s="10"/>
-      <c r="H2149" s="3"/>
-      <c r="I2149" s="12"/>
-      <c r="J2149" s="7"/>
-      <c r="K2149" s="7"/>
+      <c r="F2149" s="1">
+        <v>147</v>
+      </c>
+      <c r="G2149" s="10">
+        <v>968.73</v>
+      </c>
+      <c r="H2149" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2149" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2149" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2149" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2150" s="18">
@@ -70501,124 +70643,236 @@
       </c>
     </row>
     <row r="2151" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2151" s="18"/>
+      <c r="B2151" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2151" s="1"/>
       <c r="D2151" s="1"/>
       <c r="E2151" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2151" s="1"/>
-      <c r="G2151" s="10"/>
-      <c r="H2151" s="3"/>
-      <c r="I2151" s="12"/>
-      <c r="J2151" s="7"/>
-      <c r="K2151" s="7"/>
+      <c r="F2151" s="1">
+        <v>35.726999999999997</v>
+      </c>
+      <c r="G2151" s="10">
+        <v>207.93</v>
+      </c>
+      <c r="H2151" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2151" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2151" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2151" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2152" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2152" s="18"/>
+      <c r="B2152" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2152" s="1"/>
       <c r="D2152" s="1"/>
       <c r="E2152" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2152" s="1"/>
-      <c r="G2152" s="10"/>
-      <c r="H2152" s="3"/>
-      <c r="I2152" s="12"/>
-      <c r="J2152" s="7"/>
-      <c r="K2152" s="7"/>
+      <c r="F2152" s="1">
+        <v>160.53</v>
+      </c>
+      <c r="G2152" s="10">
+        <v>1021</v>
+      </c>
+      <c r="H2152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2152" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2152" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2152" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2153" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2153" s="18"/>
+      <c r="B2153" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2153" s="1"/>
       <c r="D2153" s="1"/>
       <c r="E2153" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2153" s="1"/>
-      <c r="G2153" s="10"/>
-      <c r="H2153" s="3"/>
-      <c r="I2153" s="12"/>
-      <c r="J2153" s="7"/>
-      <c r="K2153" s="7"/>
+      <c r="F2153" s="1">
+        <v>165.83</v>
+      </c>
+      <c r="G2153" s="10">
+        <v>965.13</v>
+      </c>
+      <c r="H2153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2153" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2153" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2153" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2154" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2154" s="18"/>
+      <c r="B2154" s="18">
+        <v>45929</v>
+      </c>
       <c r="C2154" s="1"/>
       <c r="D2154" s="1"/>
       <c r="E2154" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2154" s="1"/>
-      <c r="G2154" s="10"/>
-      <c r="H2154" s="3"/>
-      <c r="I2154" s="12"/>
-      <c r="J2154" s="7"/>
-      <c r="K2154" s="7"/>
+      <c r="F2154" s="1">
+        <v>151.453</v>
+      </c>
+      <c r="G2154" s="10">
+        <v>881.45</v>
+      </c>
+      <c r="H2154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2154" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2154" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2154" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2155" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2155" s="18"/>
+      <c r="B2155" s="18">
+        <v>45938</v>
+      </c>
       <c r="C2155" s="1"/>
       <c r="D2155" s="1"/>
       <c r="E2155" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2155" s="1"/>
-      <c r="G2155" s="10"/>
-      <c r="H2155" s="3"/>
-      <c r="I2155" s="12"/>
-      <c r="J2155" s="7"/>
-      <c r="K2155" s="7"/>
+      <c r="F2155" s="1">
+        <v>154.06100000000001</v>
+      </c>
+      <c r="G2155" s="10">
+        <v>1015.26</v>
+      </c>
+      <c r="H2155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2155" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2155" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="K2155" s="7" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="2156" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2156" s="18"/>
+      <c r="B2156" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2156" s="1"/>
       <c r="D2156" s="1"/>
       <c r="E2156" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2156" s="1"/>
-      <c r="G2156" s="10"/>
-      <c r="H2156" s="3"/>
-      <c r="I2156" s="12"/>
-      <c r="J2156" s="7"/>
-      <c r="K2156" s="7"/>
+      <c r="F2156" s="1">
+        <v>125.348</v>
+      </c>
+      <c r="G2156" s="10">
+        <v>729</v>
+      </c>
+      <c r="H2156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2156" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2156" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2156" s="7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="2157" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2157" s="18"/>
+      <c r="B2157" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2157" s="1"/>
       <c r="D2157" s="1"/>
       <c r="E2157" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2157" s="1"/>
-      <c r="G2157" s="10"/>
-      <c r="H2157" s="3"/>
-      <c r="I2157" s="12"/>
-      <c r="J2157" s="7"/>
-      <c r="K2157" s="7"/>
+      <c r="F2157" s="1">
+        <v>82.78</v>
+      </c>
+      <c r="G2157" s="10">
+        <v>500</v>
+      </c>
+      <c r="H2157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2157" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2157" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2157" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2158" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2158" s="18"/>
+      <c r="B2158" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2158" s="1"/>
       <c r="D2158" s="1"/>
       <c r="E2158" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2158" s="1"/>
-      <c r="G2158" s="10"/>
-      <c r="H2158" s="3"/>
-      <c r="I2158" s="12"/>
-      <c r="J2158" s="7"/>
-      <c r="K2158" s="7"/>
+      <c r="F2158" s="1">
+        <v>117.745</v>
+      </c>
+      <c r="G2158" s="10">
+        <v>685.27</v>
+      </c>
+      <c r="H2158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2158" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2158" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2158" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2159" s="18">
@@ -70650,19 +70904,33 @@
       </c>
     </row>
     <row r="2160" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2160" s="18"/>
+      <c r="B2160" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2160" s="1"/>
       <c r="D2160" s="1"/>
       <c r="E2160" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2160" s="1"/>
-      <c r="G2160" s="10"/>
-      <c r="H2160" s="3"/>
-      <c r="I2160" s="12"/>
-      <c r="J2160" s="7"/>
-      <c r="K2160" s="7"/>
+      <c r="F2160" s="1">
+        <v>162.72999999999999</v>
+      </c>
+      <c r="G2160" s="10">
+        <v>1046.4000000000001</v>
+      </c>
+      <c r="H2160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2160" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2160" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2160" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2161" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2161" s="18">
@@ -70694,34 +70962,62 @@
       </c>
     </row>
     <row r="2162" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2162" s="18"/>
+      <c r="B2162" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2162" s="1"/>
       <c r="D2162" s="1"/>
       <c r="E2162" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2162" s="1"/>
-      <c r="G2162" s="10"/>
-      <c r="H2162" s="3"/>
-      <c r="I2162" s="12"/>
-      <c r="J2162" s="7"/>
-      <c r="K2162" s="7"/>
+      <c r="F2162" s="1">
+        <v>168.53800000000001</v>
+      </c>
+      <c r="G2162" s="10">
+        <v>980.89</v>
+      </c>
+      <c r="H2162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2162" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2162" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2162" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2163" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2163" s="18"/>
+      <c r="B2163" s="18">
+        <v>45929</v>
+      </c>
       <c r="C2163" s="1"/>
       <c r="D2163" s="1"/>
       <c r="E2163" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2163" s="1"/>
-      <c r="G2163" s="10"/>
-      <c r="H2163" s="3"/>
-      <c r="I2163" s="12"/>
-      <c r="J2163" s="7"/>
-      <c r="K2163" s="7"/>
+      <c r="F2163" s="1">
+        <v>53.39</v>
+      </c>
+      <c r="G2163" s="10">
+        <v>325.14999999999998</v>
+      </c>
+      <c r="H2163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2163" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2163" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2163" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2164" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2164" s="18">
@@ -70753,34 +71049,62 @@
       </c>
     </row>
     <row r="2165" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2165" s="18"/>
+      <c r="B2165" s="18">
+        <v>45936</v>
+      </c>
       <c r="C2165" s="1"/>
       <c r="D2165" s="1"/>
       <c r="E2165" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2165" s="1"/>
-      <c r="G2165" s="10"/>
-      <c r="H2165" s="3"/>
-      <c r="I2165" s="12"/>
-      <c r="J2165" s="7"/>
-      <c r="K2165" s="7"/>
+      <c r="F2165" s="1">
+        <v>82.58</v>
+      </c>
+      <c r="G2165" s="10">
+        <v>502.91</v>
+      </c>
+      <c r="H2165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2165" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2165" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2165" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2166" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2166" s="18"/>
+      <c r="B2166" s="18">
+        <v>45924</v>
+      </c>
       <c r="C2166" s="1"/>
       <c r="D2166" s="1"/>
       <c r="E2166" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2166" s="1"/>
-      <c r="G2166" s="10"/>
-      <c r="H2166" s="3"/>
-      <c r="I2166" s="12"/>
-      <c r="J2166" s="7"/>
-      <c r="K2166" s="7"/>
+      <c r="F2166" s="1">
+        <v>137.321</v>
+      </c>
+      <c r="G2166" s="10">
+        <v>836.28</v>
+      </c>
+      <c r="H2166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2166" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2166" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2166" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2167" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2167" s="18">
@@ -70838,49 +71162,91 @@
       </c>
     </row>
     <row r="2169" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2169" s="18"/>
+      <c r="B2169" s="18">
+        <v>45930</v>
+      </c>
       <c r="C2169" s="1"/>
       <c r="D2169" s="1"/>
       <c r="E2169" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2169" s="1"/>
-      <c r="G2169" s="10"/>
-      <c r="H2169" s="3"/>
-      <c r="I2169" s="12"/>
-      <c r="J2169" s="7"/>
-      <c r="K2169" s="7"/>
+      <c r="F2169" s="1">
+        <v>68</v>
+      </c>
+      <c r="G2169" s="10">
+        <v>719.96</v>
+      </c>
+      <c r="H2169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2169" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2169" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2169" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2170" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2170" s="18"/>
+      <c r="B2170" s="18">
+        <v>45930</v>
+      </c>
       <c r="C2170" s="1"/>
       <c r="D2170" s="1"/>
       <c r="E2170" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2170" s="1"/>
-      <c r="G2170" s="10"/>
-      <c r="H2170" s="3"/>
-      <c r="I2170" s="12"/>
-      <c r="J2170" s="7"/>
-      <c r="K2170" s="7"/>
+      <c r="F2170" s="1">
+        <v>137.321</v>
+      </c>
+      <c r="G2170" s="10">
+        <v>836.28</v>
+      </c>
+      <c r="H2170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2170" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2170" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2170" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2171" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2171" s="18"/>
+      <c r="B2171" s="18">
+        <v>45930</v>
+      </c>
       <c r="C2171" s="1"/>
       <c r="D2171" s="1"/>
       <c r="E2171" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="F2171" s="1"/>
-      <c r="G2171" s="10"/>
-      <c r="H2171" s="3"/>
-      <c r="I2171" s="12"/>
-      <c r="J2171" s="7"/>
-      <c r="K2171" s="7"/>
+      <c r="F2171" s="1">
+        <v>133.28</v>
+      </c>
+      <c r="G2171" s="10">
+        <v>838.35</v>
+      </c>
+      <c r="H2171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2171" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2171" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2171" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2172" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2172" s="18">
@@ -71171,13 +71537,31 @@
       </c>
     </row>
     <row r="2181" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2181" s="17"/>
+      <c r="B2181" s="17">
+        <v>45937</v>
+      </c>
       <c r="E2181" s="1">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="G2181" s="13"/>
-      <c r="I2181" s="12"/>
+      <c r="F2181" s="2">
+        <v>134.22800000000001</v>
+      </c>
+      <c r="G2181" s="13">
+        <v>781.2</v>
+      </c>
+      <c r="H2181" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2181" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2181" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2181" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2182" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2182" s="17">
@@ -71407,19 +71791,33 @@
       </c>
     </row>
     <row r="2189" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2189" s="18"/>
+      <c r="B2189" s="18">
+        <v>45932</v>
+      </c>
       <c r="C2189" s="1"/>
       <c r="D2189" s="1"/>
       <c r="E2189" s="1">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="F2189" s="1"/>
-      <c r="G2189" s="10"/>
-      <c r="H2189" s="3"/>
-      <c r="I2189" s="12"/>
-      <c r="J2189" s="7"/>
-      <c r="K2189" s="7"/>
+      <c r="F2189" s="1">
+        <v>140</v>
+      </c>
+      <c r="G2189" s="10">
+        <v>824.6</v>
+      </c>
+      <c r="H2189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2189" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2189" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="K2189" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2190" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2190" s="18">
@@ -71451,19 +71849,33 @@
       </c>
     </row>
     <row r="2191" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2191" s="18"/>
+      <c r="B2191" s="18">
+        <v>45943</v>
+      </c>
       <c r="C2191" s="1"/>
       <c r="D2191" s="1"/>
       <c r="E2191" s="1">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="F2191" s="1"/>
-      <c r="G2191" s="10"/>
-      <c r="H2191" s="3"/>
-      <c r="I2191" s="12"/>
-      <c r="J2191" s="7"/>
-      <c r="K2191" s="7"/>
+      <c r="F2191" s="1">
+        <v>120.73699999999999</v>
+      </c>
+      <c r="G2191" s="10">
+        <v>702.68</v>
+      </c>
+      <c r="H2191" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2191" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2191" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2191" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2192" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2192" s="18">
@@ -77579,94 +77991,178 @@
       </c>
     </row>
     <row r="2376" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2376" s="18"/>
+      <c r="B2376" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2376" s="1"/>
       <c r="D2376" s="1"/>
       <c r="E2376" s="1">
         <f>D2376-C2376</f>
         <v>0</v>
       </c>
-      <c r="F2376" s="1"/>
-      <c r="G2376" s="10"/>
-      <c r="H2376" s="3"/>
-      <c r="I2376" s="12"/>
-      <c r="J2376" s="7"/>
-      <c r="K2376" s="7"/>
+      <c r="F2376" s="1">
+        <v>508.02699999999999</v>
+      </c>
+      <c r="G2376" s="10">
+        <v>2956.72</v>
+      </c>
+      <c r="H2376" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2376" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2376" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2376" s="7" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="2377" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2377" s="18"/>
+      <c r="B2377" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2377" s="1"/>
       <c r="D2377" s="1"/>
       <c r="E2377" s="1">
         <f>D2377-C2377</f>
         <v>0</v>
       </c>
-      <c r="F2377" s="1"/>
-      <c r="G2377" s="10"/>
-      <c r="H2377" s="3"/>
-      <c r="I2377" s="12"/>
-      <c r="J2377" s="7"/>
-      <c r="K2377" s="7"/>
+      <c r="F2377" s="1">
+        <v>101.80200000000001</v>
+      </c>
+      <c r="G2377" s="10">
+        <v>592.48</v>
+      </c>
+      <c r="H2377" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2377" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2377" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2377" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2378" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2378" s="18"/>
+      <c r="B2378" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2378" s="1"/>
       <c r="D2378" s="1"/>
       <c r="E2378" s="1">
         <f>D2378-C2378</f>
         <v>0</v>
       </c>
-      <c r="F2378" s="1"/>
-      <c r="G2378" s="10"/>
-      <c r="H2378" s="3"/>
-      <c r="I2378" s="12"/>
-      <c r="J2378" s="7"/>
-      <c r="K2378" s="7"/>
+      <c r="F2378" s="1">
+        <v>127.41</v>
+      </c>
+      <c r="G2378" s="10">
+        <v>814.15</v>
+      </c>
+      <c r="H2378" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2378" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2378" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K2378" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2379" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2379" s="18"/>
+      <c r="B2379" s="18">
+        <v>45924</v>
+      </c>
       <c r="C2379" s="1"/>
       <c r="D2379" s="1"/>
       <c r="E2379" s="1">
         <f>D2379-C2379</f>
         <v>0</v>
       </c>
-      <c r="F2379" s="1"/>
-      <c r="G2379" s="10"/>
-      <c r="H2379" s="3"/>
-      <c r="I2379" s="12"/>
-      <c r="J2379" s="7"/>
-      <c r="K2379" s="7"/>
+      <c r="F2379" s="1">
+        <v>12.39</v>
+      </c>
+      <c r="G2379" s="10">
+        <v>70.5</v>
+      </c>
+      <c r="H2379" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2379" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2379" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2379" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2380" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2380" s="18"/>
+      <c r="B2380" s="18">
+        <v>45938</v>
+      </c>
       <c r="C2380" s="1"/>
       <c r="D2380" s="1"/>
       <c r="E2380" s="1">
         <f>D2380-C2380</f>
         <v>0</v>
       </c>
-      <c r="F2380" s="1"/>
-      <c r="G2380" s="10"/>
-      <c r="H2380" s="3"/>
-      <c r="I2380" s="12"/>
-      <c r="J2380" s="7"/>
-      <c r="K2380" s="7"/>
+      <c r="F2380" s="1">
+        <v>199.68</v>
+      </c>
+      <c r="G2380" s="10">
+        <v>1248.03</v>
+      </c>
+      <c r="H2380" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2380" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2380" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="K2380" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2381" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2381" s="18"/>
+      <c r="B2381" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2381" s="1"/>
       <c r="D2381" s="1"/>
       <c r="E2381" s="1">
         <f t="shared" ref="E2381:E2444" si="42">D2381-C2381</f>
         <v>0</v>
       </c>
-      <c r="F2381" s="1"/>
-      <c r="G2381" s="10"/>
-      <c r="H2381" s="3"/>
-      <c r="I2381" s="12"/>
-      <c r="J2381" s="7"/>
-      <c r="K2381" s="7"/>
+      <c r="F2381" s="1">
+        <v>62.360999999999997</v>
+      </c>
+      <c r="G2381" s="10">
+        <v>362.94</v>
+      </c>
+      <c r="H2381" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2381" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2381" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2381" s="7" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2382" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2382" s="18">
@@ -77727,34 +78223,62 @@
       </c>
     </row>
     <row r="2384" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2384" s="18"/>
+      <c r="B2384" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2384" s="1"/>
       <c r="D2384" s="1"/>
       <c r="E2384" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2384" s="1"/>
-      <c r="G2384" s="10"/>
-      <c r="H2384" s="3"/>
-      <c r="I2384" s="12"/>
-      <c r="J2384" s="7"/>
-      <c r="K2384" s="7"/>
+      <c r="F2384" s="1">
+        <v>49.673000000000002</v>
+      </c>
+      <c r="G2384" s="10">
+        <v>289.10000000000002</v>
+      </c>
+      <c r="H2384" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2384" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2384" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2384" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2385" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2385" s="18"/>
+      <c r="B2385" s="18">
+        <v>45936</v>
+      </c>
       <c r="C2385" s="1"/>
       <c r="D2385" s="1"/>
       <c r="E2385" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2385" s="1"/>
-      <c r="G2385" s="10"/>
-      <c r="H2385" s="3"/>
-      <c r="I2385" s="12"/>
-      <c r="J2385" s="7"/>
-      <c r="K2385" s="7"/>
+      <c r="F2385" s="1">
+        <v>189.96700000000001</v>
+      </c>
+      <c r="G2385" s="10">
+        <v>1105.6099999999999</v>
+      </c>
+      <c r="H2385" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2385" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2385" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2385" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2386" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2386" s="18">
@@ -77786,19 +78310,33 @@
       </c>
     </row>
     <row r="2387" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2387" s="18"/>
+      <c r="B2387" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2387" s="1"/>
       <c r="D2387" s="1"/>
       <c r="E2387" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2387" s="1"/>
-      <c r="G2387" s="10"/>
-      <c r="H2387" s="3"/>
-      <c r="I2387" s="12"/>
-      <c r="J2387" s="7"/>
-      <c r="K2387" s="7"/>
+      <c r="F2387" s="1">
+        <v>158.68</v>
+      </c>
+      <c r="G2387" s="10">
+        <v>998.14</v>
+      </c>
+      <c r="H2387" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2387" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2387" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2387" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2388" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2388" s="18">
@@ -77830,19 +78368,33 @@
       </c>
     </row>
     <row r="2389" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2389" s="18"/>
+      <c r="B2389" s="18">
+        <v>45924</v>
+      </c>
       <c r="C2389" s="1"/>
       <c r="D2389" s="1"/>
       <c r="E2389" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2389" s="1"/>
-      <c r="G2389" s="10"/>
-      <c r="H2389" s="3"/>
-      <c r="I2389" s="12"/>
-      <c r="J2389" s="7"/>
-      <c r="K2389" s="7"/>
+      <c r="F2389" s="1">
+        <v>22.91</v>
+      </c>
+      <c r="G2389" s="10">
+        <v>1395.59</v>
+      </c>
+      <c r="H2389" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2389" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2389" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2389" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2390" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2390" s="18">
@@ -77932,49 +78484,91 @@
       </c>
     </row>
     <row r="2393" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2393" s="18"/>
+      <c r="B2393" s="18">
+        <v>45943</v>
+      </c>
       <c r="C2393" s="1"/>
       <c r="D2393" s="1"/>
       <c r="E2393" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2393" s="1"/>
-      <c r="G2393" s="10"/>
-      <c r="H2393" s="3"/>
-      <c r="I2393" s="12"/>
-      <c r="J2393" s="7"/>
-      <c r="K2393" s="7"/>
+      <c r="F2393" s="1">
+        <v>197.18</v>
+      </c>
+      <c r="G2393" s="10">
+        <v>1240.27</v>
+      </c>
+      <c r="H2393" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2393" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2393" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2393" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2394" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2394" s="18"/>
+      <c r="B2394" s="18">
+        <v>45936</v>
+      </c>
       <c r="C2394" s="1"/>
       <c r="D2394" s="1"/>
       <c r="E2394" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2394" s="1"/>
-      <c r="G2394" s="10"/>
-      <c r="H2394" s="3"/>
-      <c r="I2394" s="12"/>
-      <c r="J2394" s="7"/>
-      <c r="K2394" s="7"/>
+      <c r="F2394" s="1">
+        <v>212.91</v>
+      </c>
+      <c r="G2394" s="10">
+        <v>1339.21</v>
+      </c>
+      <c r="H2394" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2394" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2394" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2394" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2395" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2395" s="18"/>
+      <c r="B2395" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2395" s="1"/>
       <c r="D2395" s="1"/>
       <c r="E2395" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2395" s="1"/>
-      <c r="G2395" s="10"/>
-      <c r="H2395" s="3"/>
-      <c r="I2395" s="12"/>
-      <c r="J2395" s="7"/>
-      <c r="K2395" s="7"/>
+      <c r="F2395" s="1">
+        <v>135.13</v>
+      </c>
+      <c r="G2395" s="10">
+        <v>816.19</v>
+      </c>
+      <c r="H2395" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2395" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2395" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K2395" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2396" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2396" s="18"/>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="641" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5571D5BF-7362-4C43-BC82-CBB6A8D3CA90}"/>
+  <xr:revisionPtr revIDLastSave="764" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CECC443E-7596-4BE7-941F-214DFCA73E83}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8066" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8104" uniqueCount="337">
   <si>
     <t>Data</t>
   </si>
@@ -1045,6 +1045,12 @@
   <si>
     <t>POSTO SOARES</t>
   </si>
+  <si>
+    <t>Diesel s10</t>
+  </si>
+  <si>
+    <t>POSTO RABELO</t>
+  </si>
 </sst>
 </file>
 
@@ -78571,94 +78577,176 @@
       </c>
     </row>
     <row r="2396" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2396" s="18"/>
+      <c r="B2396" s="18">
+        <v>45939</v>
+      </c>
       <c r="C2396" s="1"/>
       <c r="D2396" s="1"/>
       <c r="E2396" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2396" s="1"/>
-      <c r="G2396" s="10"/>
-      <c r="H2396" s="3"/>
-      <c r="I2396" s="12"/>
-      <c r="J2396" s="7"/>
-      <c r="K2396" s="7"/>
+      <c r="F2396" s="1">
+        <v>344.37</v>
+      </c>
+      <c r="G2396" s="10">
+        <v>2166.1</v>
+      </c>
+      <c r="H2396" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2396" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2396" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2396" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2397" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2397" s="18"/>
+      <c r="B2397" s="18">
+        <v>45936</v>
+      </c>
       <c r="C2397" s="1"/>
       <c r="D2397" s="1"/>
       <c r="E2397" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2397" s="1"/>
-      <c r="G2397" s="10"/>
-      <c r="H2397" s="3"/>
-      <c r="I2397" s="12"/>
-      <c r="J2397" s="7"/>
+      <c r="F2397" s="1">
+        <v>235.03</v>
+      </c>
+      <c r="G2397" s="10">
+        <v>1478.33</v>
+      </c>
+      <c r="H2397" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2397" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2397" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="K2397" s="7"/>
     </row>
     <row r="2398" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2398" s="18"/>
+      <c r="B2398" s="18">
+        <v>45932</v>
+      </c>
       <c r="C2398" s="1"/>
       <c r="D2398" s="1"/>
       <c r="E2398" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2398" s="1"/>
-      <c r="G2398" s="10"/>
-      <c r="H2398" s="3"/>
-      <c r="I2398" s="12"/>
-      <c r="J2398" s="7"/>
-      <c r="K2398" s="7"/>
+      <c r="F2398" s="1">
+        <v>202</v>
+      </c>
+      <c r="G2398" s="10">
+        <v>1220.08</v>
+      </c>
+      <c r="H2398" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2398" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2398" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2398" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2399" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2399" s="18"/>
+      <c r="B2399" s="18">
+        <v>45933</v>
+      </c>
       <c r="C2399" s="1"/>
       <c r="D2399" s="1"/>
       <c r="E2399" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2399" s="1"/>
-      <c r="G2399" s="10"/>
-      <c r="H2399" s="3"/>
-      <c r="I2399" s="12"/>
-      <c r="J2399" s="7"/>
-      <c r="K2399" s="7"/>
+      <c r="F2399" s="1">
+        <v>79.489999999999995</v>
+      </c>
+      <c r="G2399" s="10">
+        <v>500</v>
+      </c>
+      <c r="H2399" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I2399" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2399" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2399" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2400" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2400" s="18"/>
+      <c r="B2400" s="18">
+        <v>45932</v>
+      </c>
       <c r="C2400" s="1"/>
       <c r="D2400" s="1"/>
       <c r="E2400" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2400" s="1"/>
-      <c r="G2400" s="10"/>
-      <c r="H2400" s="3"/>
-      <c r="I2400" s="12"/>
-      <c r="J2400" s="7"/>
-      <c r="K2400" s="7"/>
+      <c r="F2400" s="1">
+        <v>103.99</v>
+      </c>
+      <c r="G2400" s="10">
+        <v>664.5</v>
+      </c>
+      <c r="H2400" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2400" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2400" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K2400" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2401" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2401" s="18"/>
+      <c r="B2401" s="18">
+        <v>45931</v>
+      </c>
       <c r="C2401" s="1"/>
       <c r="D2401" s="1"/>
       <c r="E2401" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2401" s="1"/>
-      <c r="G2401" s="10"/>
-      <c r="H2401" s="3"/>
-      <c r="I2401" s="12"/>
-      <c r="J2401" s="7"/>
-      <c r="K2401" s="7"/>
+      <c r="F2401" s="1">
+        <v>200.33699999999999</v>
+      </c>
+      <c r="G2401" s="10">
+        <v>1200.02</v>
+      </c>
+      <c r="H2401" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2401" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2401" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="K2401" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2402" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2402" s="18">
@@ -78690,33 +78778,62 @@
       </c>
     </row>
     <row r="2403" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2403" s="18"/>
+      <c r="B2403" s="18">
+        <v>45933</v>
+      </c>
       <c r="C2403" s="1"/>
       <c r="D2403" s="1"/>
       <c r="E2403" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2403" s="1"/>
-      <c r="G2403" s="10"/>
-      <c r="H2403" s="3"/>
-      <c r="I2403" s="12"/>
-      <c r="J2403" s="7"/>
-      <c r="K2403" s="7"/>
+      <c r="F2403" s="1">
+        <v>54.186</v>
+      </c>
+      <c r="G2403" s="10">
+        <v>315.36</v>
+      </c>
+      <c r="H2403" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2403" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2403" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2403" s="7" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2404" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2404" s="18"/>
+      <c r="B2404" s="18">
+        <v>45933</v>
+      </c>
       <c r="C2404" s="1"/>
       <c r="D2404" s="1"/>
       <c r="E2404" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2404" s="1"/>
-      <c r="G2404" s="10"/>
-      <c r="H2404" s="3"/>
-      <c r="J2404" s="7"/>
-      <c r="K2404" s="7"/>
+      <c r="F2404" s="1">
+        <v>86.747</v>
+      </c>
+      <c r="G2404" s="10">
+        <v>504.86</v>
+      </c>
+      <c r="H2404" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2404" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2404" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2404" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2405" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2405" s="17">
@@ -79055,18 +79172,33 @@
       </c>
     </row>
     <row r="2415" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2415" s="18"/>
+      <c r="B2415" s="18">
+        <v>45932</v>
+      </c>
       <c r="C2415" s="1"/>
       <c r="D2415" s="1"/>
       <c r="E2415" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2415" s="1"/>
-      <c r="G2415" s="10"/>
-      <c r="H2415" s="3"/>
-      <c r="J2415" s="7"/>
-      <c r="K2415" s="7"/>
+      <c r="F2415" s="1">
+        <v>41.72</v>
+      </c>
+      <c r="G2415" s="10">
+        <v>249.53</v>
+      </c>
+      <c r="H2415" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2415" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2415" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2415" s="7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="2416" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2416" s="17">
@@ -79342,32 +79474,62 @@
       </c>
     </row>
     <row r="2425" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2425" s="18"/>
+      <c r="B2425" s="18">
+        <v>45933</v>
+      </c>
       <c r="C2425" s="1"/>
       <c r="D2425" s="1"/>
       <c r="E2425" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2425" s="1"/>
-      <c r="G2425" s="10"/>
-      <c r="H2425" s="3"/>
-      <c r="J2425" s="7"/>
-      <c r="K2425" s="7"/>
+      <c r="F2425" s="1">
+        <v>121.97499999999999</v>
+      </c>
+      <c r="G2425" s="10">
+        <v>709.89</v>
+      </c>
+      <c r="H2425" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2425" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2425" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2425" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2426" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2426" s="18"/>
+      <c r="B2426" s="18">
+        <v>45936</v>
+      </c>
       <c r="C2426" s="1"/>
       <c r="D2426" s="1"/>
       <c r="E2426" s="1">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="F2426" s="1"/>
-      <c r="G2426" s="10"/>
-      <c r="H2426" s="3"/>
-      <c r="J2426" s="7"/>
-      <c r="K2426" s="7"/>
+      <c r="F2426" s="1">
+        <v>200.28</v>
+      </c>
+      <c r="G2426" s="10">
+        <v>1259.76</v>
+      </c>
+      <c r="H2426" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2426" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2426" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2426" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="2427" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2427" s="17">
@@ -80455,32 +80617,62 @@
       </c>
     </row>
     <row r="2462" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2462" s="18"/>
+      <c r="B2462" s="18">
+        <v>45937</v>
+      </c>
       <c r="C2462" s="1"/>
       <c r="D2462" s="1"/>
       <c r="E2462" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2462" s="1"/>
-      <c r="G2462" s="10"/>
-      <c r="H2462" s="3"/>
-      <c r="J2462" s="7"/>
-      <c r="K2462" s="7"/>
+      <c r="F2462" s="1">
+        <v>169.12</v>
+      </c>
+      <c r="G2462" s="10">
+        <v>1063.8</v>
+      </c>
+      <c r="H2462" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2462" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2462" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2462" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2463" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2463" s="18"/>
+      <c r="B2463" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2463" s="1"/>
       <c r="D2463" s="1"/>
       <c r="E2463" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2463" s="1"/>
-      <c r="G2463" s="10"/>
-      <c r="H2463" s="3"/>
-      <c r="J2463" s="7"/>
-      <c r="K2463" s="7"/>
+      <c r="F2463" s="1">
+        <v>108.66</v>
+      </c>
+      <c r="G2463" s="10">
+        <v>632.4</v>
+      </c>
+      <c r="H2463" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2463" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2463" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2463" s="7" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="2464" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2464" s="18"/>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="764" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CECC443E-7596-4BE7-941F-214DFCA73E83}"/>
+  <xr:revisionPtr revIDLastSave="788" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFB4641F-19E1-4630-9815-B07BC92CBD98}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8104" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8113" uniqueCount="337">
   <si>
     <t>Data</t>
   </si>
@@ -80675,18 +80675,33 @@
       </c>
     </row>
     <row r="2464" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2464" s="18"/>
+      <c r="B2464" s="18">
+        <v>45944</v>
+      </c>
       <c r="C2464" s="1"/>
       <c r="D2464" s="1"/>
       <c r="E2464" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2464" s="1"/>
-      <c r="G2464" s="10"/>
-      <c r="H2464" s="3"/>
-      <c r="J2464" s="7"/>
-      <c r="K2464" s="7"/>
+      <c r="F2464" s="1">
+        <v>129.077</v>
+      </c>
+      <c r="G2464" s="10">
+        <v>751.23</v>
+      </c>
+      <c r="H2464" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2464" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2464" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2464" s="7" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2465" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2465" s="17">
@@ -80929,18 +80944,33 @@
       </c>
     </row>
     <row r="2472" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2472" s="18"/>
+      <c r="B2472" s="18">
+        <v>45944</v>
+      </c>
       <c r="C2472" s="1"/>
       <c r="D2472" s="1"/>
       <c r="E2472" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2472" s="1"/>
-      <c r="G2472" s="10"/>
-      <c r="H2472" s="3"/>
-      <c r="J2472" s="7"/>
-      <c r="K2472" s="7"/>
+      <c r="F2472" s="1">
+        <v>207.83199999999999</v>
+      </c>
+      <c r="G2472" s="10">
+        <v>1209.58</v>
+      </c>
+      <c r="H2472" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2472" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2472" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2472" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2473" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2473" s="17">
@@ -81150,18 +81180,33 @@
       <c r="K2481" s="7"/>
     </row>
     <row r="2482" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2482" s="18"/>
+      <c r="B2482" s="18">
+        <v>45940</v>
+      </c>
       <c r="C2482" s="1"/>
       <c r="D2482" s="1"/>
       <c r="E2482" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2482" s="1"/>
-      <c r="G2482" s="10"/>
-      <c r="H2482" s="3"/>
-      <c r="J2482" s="7"/>
-      <c r="K2482" s="7"/>
+      <c r="F2482" s="1">
+        <v>143.72999999999999</v>
+      </c>
+      <c r="G2482" s="10">
+        <v>932.81</v>
+      </c>
+      <c r="H2482" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2482" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2482" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2482" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2483" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2483" s="18"/>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="788" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFB4641F-19E1-4630-9815-B07BC92CBD98}"/>
+  <xr:revisionPtr revIDLastSave="863" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCAAA74-9836-4815-9EF5-12861ADC22C0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2848</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2851</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8113" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="338">
   <si>
     <t>Data</t>
   </si>
@@ -713,9 +713,6 @@
     <t>TEJ3A85</t>
   </si>
   <si>
-    <t>TEB9E27</t>
-  </si>
-  <si>
     <t>POSTO MIRANTE DO LAGO</t>
   </si>
   <si>
@@ -1050,6 +1047,12 @@
   </si>
   <si>
     <t>POSTO RABELO</t>
+  </si>
+  <si>
+    <t>AUTO POSTO JR</t>
+  </si>
+  <si>
+    <t>PAREBEM POSTO NITEROI</t>
   </si>
 </sst>
 </file>
@@ -1592,7 +1595,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2848"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="B1:L2851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -1652,7 +1656,7 @@
         <v>22</v>
       </c>
       <c r="L2" s="27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -2674,7 +2678,7 @@
         <v>58</v>
       </c>
       <c r="L33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
@@ -4933,7 +4937,7 @@
         <v>58</v>
       </c>
       <c r="L102" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103" spans="2:12" x14ac:dyDescent="0.25">
@@ -4965,7 +4969,7 @@
         <v>58</v>
       </c>
       <c r="L103" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.25">
@@ -7427,7 +7431,7 @@
         <v>58</v>
       </c>
       <c r="L178" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179" spans="2:12" x14ac:dyDescent="0.25">
@@ -7756,7 +7760,7 @@
         <v>58</v>
       </c>
       <c r="L188" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="189" spans="2:12" x14ac:dyDescent="0.25">
@@ -9170,7 +9174,7 @@
         <v>58</v>
       </c>
       <c r="L231" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="232" spans="2:12" x14ac:dyDescent="0.25">
@@ -11529,7 +11533,7 @@
         <v>58</v>
       </c>
       <c r="L303" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="304" spans="2:12" x14ac:dyDescent="0.25">
@@ -12081,7 +12085,7 @@
         <v>58</v>
       </c>
       <c r="L320" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="321" spans="2:11" x14ac:dyDescent="0.25">
@@ -14275,7 +14279,7 @@
         <v>58</v>
       </c>
       <c r="L387" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="388" spans="2:12" x14ac:dyDescent="0.25">
@@ -15124,7 +15128,7 @@
         <v>58</v>
       </c>
       <c r="L413" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="414" spans="2:12" x14ac:dyDescent="0.25">
@@ -15936,7 +15940,7 @@
         <v>58</v>
       </c>
       <c r="L438" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="439" spans="2:12" x14ac:dyDescent="0.25">
@@ -17541,7 +17545,7 @@
         <v>58</v>
       </c>
       <c r="L488" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="489" spans="2:12" x14ac:dyDescent="0.25">
@@ -18452,7 +18456,7 @@
         <v>58</v>
       </c>
       <c r="L516" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="517" spans="2:12" x14ac:dyDescent="0.25">
@@ -20126,7 +20130,7 @@
         <v>58</v>
       </c>
       <c r="L567" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="568" spans="2:12" x14ac:dyDescent="0.25">
@@ -22332,7 +22336,7 @@
         <v>58</v>
       </c>
       <c r="L634" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="635" spans="2:12" x14ac:dyDescent="0.25">
@@ -23870,7 +23874,7 @@
         <v>58</v>
       </c>
       <c r="L681" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="682" spans="2:12" x14ac:dyDescent="0.25">
@@ -26387,7 +26391,7 @@
         <v>58</v>
       </c>
       <c r="L759" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="760" spans="2:12" x14ac:dyDescent="0.25">
@@ -27473,7 +27477,7 @@
         <v>58</v>
       </c>
       <c r="L792" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="793" spans="2:12" x14ac:dyDescent="0.25">
@@ -28871,7 +28875,7 @@
         <v>58</v>
       </c>
       <c r="L835" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="836" spans="2:12" x14ac:dyDescent="0.25">
@@ -31073,7 +31077,7 @@
         <v>58</v>
       </c>
       <c r="L902" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="903" spans="2:12" x14ac:dyDescent="0.25">
@@ -31817,10 +31821,10 @@
         <v>23</v>
       </c>
       <c r="K925" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L925" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="926" spans="2:12" x14ac:dyDescent="0.25">
@@ -32666,7 +32670,7 @@
         <v>172</v>
       </c>
       <c r="L951" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="952" spans="2:12" x14ac:dyDescent="0.25">
@@ -33224,7 +33228,7 @@
         <v>58</v>
       </c>
       <c r="L968" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="969" spans="2:12" x14ac:dyDescent="0.25">
@@ -33944,10 +33948,10 @@
         <v>23</v>
       </c>
       <c r="K990" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L990" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.25">
@@ -35225,7 +35229,7 @@
         <v>172</v>
       </c>
       <c r="L1029" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1030" spans="2:12" x14ac:dyDescent="0.25">
@@ -35942,7 +35946,7 @@
         <v>58</v>
       </c>
       <c r="L1051" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1052" spans="2:12" x14ac:dyDescent="0.25">
@@ -36494,7 +36498,7 @@
         <v>172</v>
       </c>
       <c r="L1068" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1069" spans="2:12" x14ac:dyDescent="0.25">
@@ -37079,7 +37083,7 @@
         <v>58</v>
       </c>
       <c r="L1086" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1087" spans="2:12" x14ac:dyDescent="0.25">
@@ -37310,10 +37314,10 @@
         <v>23</v>
       </c>
       <c r="K1093" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1093" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1094" spans="2:12" x14ac:dyDescent="0.25">
@@ -37580,7 +37584,7 @@
         <v>172</v>
       </c>
       <c r="L1101" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1102" spans="2:12" x14ac:dyDescent="0.25">
@@ -38450,7 +38454,7 @@
         <v>58</v>
       </c>
       <c r="L1128" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1129" spans="2:12" x14ac:dyDescent="0.25">
@@ -39134,7 +39138,7 @@
         <v>172</v>
       </c>
       <c r="L1149" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1150" spans="2:12" x14ac:dyDescent="0.25">
@@ -39689,10 +39693,10 @@
         <v>187</v>
       </c>
       <c r="K1166" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1166" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1167" spans="2:12" x14ac:dyDescent="0.25">
@@ -39860,7 +39864,7 @@
         <v>58</v>
       </c>
       <c r="L1171" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1172" spans="2:12" x14ac:dyDescent="0.25">
@@ -40094,7 +40098,7 @@
         <v>58</v>
       </c>
       <c r="L1178" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1179" spans="2:12" x14ac:dyDescent="0.25">
@@ -41000,10 +41004,10 @@
         <v>187</v>
       </c>
       <c r="K1206" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1206" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1207" spans="2:12" x14ac:dyDescent="0.25">
@@ -41495,7 +41499,7 @@
         <v>172</v>
       </c>
       <c r="L1221" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1222" spans="2:12" x14ac:dyDescent="0.25">
@@ -42368,10 +42372,10 @@
         <v>187</v>
       </c>
       <c r="K1248" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1248" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1249" spans="2:12" x14ac:dyDescent="0.25">
@@ -42836,7 +42840,7 @@
         <v>172</v>
       </c>
       <c r="L1262" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1263" spans="2:12" x14ac:dyDescent="0.25">
@@ -43226,10 +43230,10 @@
         <v>187</v>
       </c>
       <c r="K1274" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1274" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1275" spans="2:12" x14ac:dyDescent="0.25">
@@ -43529,7 +43533,7 @@
         <v>58</v>
       </c>
       <c r="L1283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1284" spans="2:12" x14ac:dyDescent="0.25">
@@ -44126,7 +44130,7 @@
         <v>172</v>
       </c>
       <c r="L1301" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1302" spans="2:12" x14ac:dyDescent="0.25">
@@ -44813,10 +44817,10 @@
         <v>187</v>
       </c>
       <c r="K1322" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1322" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1323" spans="2:12" x14ac:dyDescent="0.25">
@@ -45575,7 +45579,7 @@
         <v>197</v>
       </c>
       <c r="L1345" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1346" spans="2:12" x14ac:dyDescent="0.25">
@@ -45953,10 +45957,10 @@
         <v>187</v>
       </c>
       <c r="K1357" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1357" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1358" spans="2:12" x14ac:dyDescent="0.25">
@@ -46454,7 +46458,7 @@
         <v>197</v>
       </c>
       <c r="L1372" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1373" spans="2:12" x14ac:dyDescent="0.25">
@@ -46742,7 +46746,7 @@
         <v>199</v>
       </c>
       <c r="L1381" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1382" spans="2:12" x14ac:dyDescent="0.25">
@@ -47075,7 +47079,7 @@
         <v>172</v>
       </c>
       <c r="L1391" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1392" spans="2:12" x14ac:dyDescent="0.25">
@@ -47477,7 +47481,7 @@
         <v>58</v>
       </c>
       <c r="L1404" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1405" spans="2:12" x14ac:dyDescent="0.25">
@@ -47513,7 +47517,7 @@
         <v>202</v>
       </c>
       <c r="L1405" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1406" spans="2:12" x14ac:dyDescent="0.25">
@@ -49500,7 +49504,7 @@
         <v>197</v>
       </c>
       <c r="L1472" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1473" spans="2:12" x14ac:dyDescent="0.25">
@@ -49565,7 +49569,7 @@
         <v>205</v>
       </c>
       <c r="L1474" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1475" spans="2:12" x14ac:dyDescent="0.25">
@@ -49597,7 +49601,7 @@
         <v>205</v>
       </c>
       <c r="L1475" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1476" spans="2:12" x14ac:dyDescent="0.25">
@@ -49629,7 +49633,7 @@
         <v>205</v>
       </c>
       <c r="L1476" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1477" spans="2:12" x14ac:dyDescent="0.25">
@@ -49750,7 +49754,7 @@
         <v>172</v>
       </c>
       <c r="L1480" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1481" spans="2:12" x14ac:dyDescent="0.25">
@@ -49811,7 +49815,7 @@
         <v>202</v>
       </c>
       <c r="L1482" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1483" spans="2:12" x14ac:dyDescent="0.25">
@@ -49843,7 +49847,7 @@
         <v>206</v>
       </c>
       <c r="L1483" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1484" spans="2:12" x14ac:dyDescent="0.25">
@@ -49875,7 +49879,7 @@
         <v>199</v>
       </c>
       <c r="L1484" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1485" spans="2:12" x14ac:dyDescent="0.25">
@@ -49907,7 +49911,7 @@
         <v>205</v>
       </c>
       <c r="L1485" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1486" spans="2:12" x14ac:dyDescent="0.25">
@@ -49972,7 +49976,7 @@
         <v>58</v>
       </c>
       <c r="L1487" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1488" spans="2:12" x14ac:dyDescent="0.25">
@@ -50008,7 +50012,7 @@
         <v>202</v>
       </c>
       <c r="L1488" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1489" spans="2:12" x14ac:dyDescent="0.25">
@@ -50038,7 +50042,7 @@
         <v>208</v>
       </c>
       <c r="L1489" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1490" spans="2:12" x14ac:dyDescent="0.25">
@@ -50133,7 +50137,7 @@
         <v>202</v>
       </c>
       <c r="L1492" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1493" spans="2:12" x14ac:dyDescent="0.25">
@@ -50484,7 +50488,7 @@
         <v>210</v>
       </c>
       <c r="L1504" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1505" spans="2:12" x14ac:dyDescent="0.25">
@@ -50710,7 +50714,7 @@
         <v>58</v>
       </c>
       <c r="L1511" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1512" spans="2:12" x14ac:dyDescent="0.25">
@@ -51156,10 +51160,10 @@
         <v>23</v>
       </c>
       <c r="K1525" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1525" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1526" spans="2:12" x14ac:dyDescent="0.25">
@@ -51228,7 +51232,7 @@
         <v>172</v>
       </c>
       <c r="L1527" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1528" spans="2:12" x14ac:dyDescent="0.25">
@@ -51297,7 +51301,7 @@
         <v>197</v>
       </c>
       <c r="L1529" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1530" spans="2:12" x14ac:dyDescent="0.25">
@@ -51461,7 +51465,7 @@
         <v>202</v>
       </c>
       <c r="L1534" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1535" spans="2:12" x14ac:dyDescent="0.25">
@@ -51728,7 +51732,7 @@
         <v>172</v>
       </c>
       <c r="L1542" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1543" spans="2:12" x14ac:dyDescent="0.25">
@@ -51893,10 +51897,10 @@
         <v>64</v>
       </c>
       <c r="K1547" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1547" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1548" spans="2:12" x14ac:dyDescent="0.25">
@@ -51965,7 +51969,7 @@
         <v>172</v>
       </c>
       <c r="L1549" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1550" spans="2:12" x14ac:dyDescent="0.25">
@@ -52166,7 +52170,7 @@
         <v>199</v>
       </c>
       <c r="L1555" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1556" spans="2:12" x14ac:dyDescent="0.25">
@@ -52429,7 +52433,7 @@
         <v>205</v>
       </c>
       <c r="L1563" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1564" spans="2:12" x14ac:dyDescent="0.25">
@@ -52498,7 +52502,7 @@
         <v>172</v>
       </c>
       <c r="L1565" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1566" spans="2:12" x14ac:dyDescent="0.25">
@@ -52996,7 +53000,7 @@
         <v>197</v>
       </c>
       <c r="L1580" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1581" spans="2:12" x14ac:dyDescent="0.25">
@@ -53161,10 +53165,10 @@
         <v>102</v>
       </c>
       <c r="K1585" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1585" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1586" spans="2:12" x14ac:dyDescent="0.25">
@@ -53299,7 +53303,7 @@
         <v>202</v>
       </c>
       <c r="L1589" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1590" spans="2:12" x14ac:dyDescent="0.25">
@@ -53628,7 +53632,7 @@
         <v>218</v>
       </c>
       <c r="L1599" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1600" spans="2:12" x14ac:dyDescent="0.25">
@@ -53664,7 +53668,7 @@
         <v>58</v>
       </c>
       <c r="L1600" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1601" spans="2:12" x14ac:dyDescent="0.25">
@@ -53826,7 +53830,7 @@
         <v>197</v>
       </c>
       <c r="L1605" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1606" spans="2:12" x14ac:dyDescent="0.25">
@@ -54089,7 +54093,7 @@
         <v>199</v>
       </c>
       <c r="L1613" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1614" spans="2:12" x14ac:dyDescent="0.25">
@@ -54317,7 +54321,7 @@
         <v>58</v>
       </c>
       <c r="L1620" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1621" spans="2:12" x14ac:dyDescent="0.25">
@@ -54353,7 +54357,7 @@
         <v>202</v>
       </c>
       <c r="L1621" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1622" spans="2:12" x14ac:dyDescent="0.25">
@@ -54386,10 +54390,10 @@
         <v>46</v>
       </c>
       <c r="K1622" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1622" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1623" spans="2:12" x14ac:dyDescent="0.25">
@@ -54425,7 +54429,7 @@
         <v>218</v>
       </c>
       <c r="L1623" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1624" spans="2:12" x14ac:dyDescent="0.25">
@@ -54725,7 +54729,7 @@
         <v>199</v>
       </c>
       <c r="L1632" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1633" spans="2:12" x14ac:dyDescent="0.25">
@@ -54914,7 +54918,7 @@
         <v>172</v>
       </c>
       <c r="L1638" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1639" spans="2:12" x14ac:dyDescent="0.25">
@@ -55066,7 +55070,7 @@
         <v>218</v>
       </c>
       <c r="L1643" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1644" spans="2:12" x14ac:dyDescent="0.25">
@@ -55192,10 +55196,10 @@
         <v>151</v>
       </c>
       <c r="K1647" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1647" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1648" spans="2:12" x14ac:dyDescent="0.25">
@@ -55440,7 +55444,7 @@
         <v>199</v>
       </c>
       <c r="L1655" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1656" spans="2:12" x14ac:dyDescent="0.25">
@@ -55821,7 +55825,7 @@
         <v>210</v>
       </c>
       <c r="L1668" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1669" spans="2:12" x14ac:dyDescent="0.25">
@@ -56051,7 +56055,7 @@
         <v>206</v>
       </c>
       <c r="L1676" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1677" spans="2:12" x14ac:dyDescent="0.25">
@@ -56431,7 +56435,7 @@
         <v>206</v>
       </c>
       <c r="L1689" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1690" spans="2:12" x14ac:dyDescent="0.25">
@@ -56460,7 +56464,10 @@
         <v>127</v>
       </c>
       <c r="K1690" s="7" t="s">
-        <v>224</v>
+        <v>202</v>
+      </c>
+      <c r="L1690" s="28" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="1691" spans="2:12" x14ac:dyDescent="0.25">
@@ -56521,7 +56528,7 @@
         <v>205</v>
       </c>
       <c r="L1692" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1693" spans="2:12" x14ac:dyDescent="0.25">
@@ -56553,7 +56560,7 @@
         <v>202</v>
       </c>
       <c r="L1693" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1694" spans="2:12" x14ac:dyDescent="0.25">
@@ -57739,7 +57746,7 @@
         <v>45870</v>
       </c>
       <c r="J1734" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K1734" s="7" t="s">
         <v>169</v>
@@ -57994,7 +58001,7 @@
         <v>45870</v>
       </c>
       <c r="J1743" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K1743" s="7" t="s">
         <v>77</v>
@@ -58145,7 +58152,7 @@
         <v>218</v>
       </c>
       <c r="L1748" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1749" spans="2:12" x14ac:dyDescent="0.25">
@@ -58293,7 +58300,7 @@
         <v>218</v>
       </c>
       <c r="L1753" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1754" spans="2:12" x14ac:dyDescent="0.25">
@@ -58497,7 +58504,7 @@
         <v>45839</v>
       </c>
       <c r="J1760" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K1760" s="2" t="s">
         <v>29</v>
@@ -58536,7 +58543,7 @@
         <v>205</v>
       </c>
       <c r="L1761" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1762" spans="2:12" x14ac:dyDescent="0.25">
@@ -58824,7 +58831,7 @@
         <v>197</v>
       </c>
       <c r="L1770" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1771" spans="2:12" x14ac:dyDescent="0.25">
@@ -59151,7 +59158,7 @@
         <v>218</v>
       </c>
       <c r="L1780" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1781" spans="2:12" x14ac:dyDescent="0.25">
@@ -59184,10 +59191,10 @@
         <v>92</v>
       </c>
       <c r="K1781" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1781" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1782" spans="2:12" x14ac:dyDescent="0.25">
@@ -59223,7 +59230,7 @@
         <v>172</v>
       </c>
       <c r="L1782" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1783" spans="2:12" x14ac:dyDescent="0.25">
@@ -59286,7 +59293,7 @@
         <v>45839</v>
       </c>
       <c r="J1784" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K1784" s="2" t="s">
         <v>81</v>
@@ -59379,7 +59386,7 @@
         <v>45839</v>
       </c>
       <c r="J1787" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K1787" s="2" t="s">
         <v>27</v>
@@ -59511,7 +59518,7 @@
         <v>45839</v>
       </c>
       <c r="J1791" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K1791" s="2" t="s">
         <v>38</v>
@@ -59604,7 +59611,7 @@
         <v>45839</v>
       </c>
       <c r="J1794" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K1794" s="2" t="s">
         <v>26</v>
@@ -59835,7 +59842,7 @@
         <v>172</v>
       </c>
       <c r="L1801" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1802" spans="2:12" x14ac:dyDescent="0.25">
@@ -60003,7 +60010,7 @@
         <v>202</v>
       </c>
       <c r="L1806" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1807" spans="2:12" x14ac:dyDescent="0.25">
@@ -60039,7 +60046,7 @@
         <v>218</v>
       </c>
       <c r="L1807" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1808" spans="2:12" x14ac:dyDescent="0.25">
@@ -60135,7 +60142,7 @@
         <v>45839</v>
       </c>
       <c r="J1810" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K1810" s="2" t="s">
         <v>36</v>
@@ -60204,7 +60211,7 @@
         <v>210</v>
       </c>
       <c r="L1812" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1813" spans="2:12" x14ac:dyDescent="0.25">
@@ -60234,7 +60241,7 @@
         <v>45839</v>
       </c>
       <c r="J1813" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K1813" s="2" t="s">
         <v>65</v>
@@ -60519,13 +60526,13 @@
         <v>45839</v>
       </c>
       <c r="J1822" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K1822" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1822" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1823" spans="2:12" x14ac:dyDescent="0.25">
@@ -60681,7 +60688,7 @@
         <v>45839</v>
       </c>
       <c r="J1827" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K1827" s="2" t="s">
         <v>29</v>
@@ -60720,7 +60727,7 @@
         <v>58</v>
       </c>
       <c r="L1828" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1829" spans="2:12" x14ac:dyDescent="0.25">
@@ -60882,7 +60889,7 @@
         <v>45839</v>
       </c>
       <c r="J1833" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K1833" s="2" t="s">
         <v>47</v>
@@ -60981,13 +60988,13 @@
         <v>45839</v>
       </c>
       <c r="J1836" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K1836" s="2" t="s">
         <v>172</v>
       </c>
       <c r="L1836" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1837" spans="2:12" x14ac:dyDescent="0.25">
@@ -61056,7 +61063,7 @@
         <v>218</v>
       </c>
       <c r="L1838" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="1839" spans="2:12" x14ac:dyDescent="0.25">
@@ -61086,13 +61093,13 @@
         <v>45839</v>
       </c>
       <c r="J1839" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K1839" s="2" t="s">
         <v>199</v>
       </c>
       <c r="L1839" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1840" spans="2:12" x14ac:dyDescent="0.25">
@@ -61155,7 +61162,7 @@
         <v>45839</v>
       </c>
       <c r="J1841" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K1841" s="2" t="s">
         <v>27</v>
@@ -61188,7 +61195,7 @@
         <v>45839</v>
       </c>
       <c r="J1842" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K1842" s="2" t="s">
         <v>63</v>
@@ -61254,7 +61261,7 @@
         <v>45839</v>
       </c>
       <c r="J1844" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K1844" s="2" t="s">
         <v>26</v>
@@ -61479,7 +61486,7 @@
         <v>45839</v>
       </c>
       <c r="J1851" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K1851" s="2" t="s">
         <v>37</v>
@@ -61644,7 +61651,7 @@
         <v>45839</v>
       </c>
       <c r="J1856" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K1856" s="2" t="s">
         <v>65</v>
@@ -61670,7 +61677,9 @@
       <c r="G1857" s="13">
         <v>270.07</v>
       </c>
-      <c r="H1857" s="3"/>
+      <c r="H1857" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1857" s="12">
         <v>45839</v>
       </c>
@@ -61681,7 +61690,7 @@
         <v>205</v>
       </c>
       <c r="L1857" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1858" spans="2:12" x14ac:dyDescent="0.25">
@@ -61704,7 +61713,9 @@
       <c r="G1858" s="13">
         <v>365.07</v>
       </c>
-      <c r="H1858" s="3"/>
+      <c r="H1858" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1858" s="12">
         <v>45839</v>
       </c>
@@ -61735,7 +61746,9 @@
       <c r="G1859" s="13">
         <v>199.55</v>
       </c>
-      <c r="H1859" s="3"/>
+      <c r="H1859" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1859" s="12">
         <v>45839</v>
       </c>
@@ -61746,7 +61759,7 @@
         <v>172</v>
       </c>
       <c r="L1859" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1860" spans="2:12" x14ac:dyDescent="0.25">
@@ -61769,7 +61782,9 @@
       <c r="G1860" s="13">
         <v>185.78</v>
       </c>
-      <c r="H1860" s="3"/>
+      <c r="H1860" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1860" s="12">
         <v>45839</v>
       </c>
@@ -61780,7 +61795,7 @@
         <v>202</v>
       </c>
       <c r="L1860" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1861" spans="2:12" x14ac:dyDescent="0.25">
@@ -61803,7 +61818,9 @@
       <c r="G1861" s="13">
         <v>894.92</v>
       </c>
-      <c r="H1861" s="3"/>
+      <c r="H1861" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1861" s="12">
         <v>45839</v>
       </c>
@@ -61834,7 +61851,9 @@
       <c r="G1862" s="13">
         <v>265</v>
       </c>
-      <c r="H1862" s="3"/>
+      <c r="H1862" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1862" s="12">
         <v>45839</v>
       </c>
@@ -61842,10 +61861,10 @@
         <v>183</v>
       </c>
       <c r="K1862" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1862" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1863" spans="2:12" x14ac:dyDescent="0.25">
@@ -61868,7 +61887,9 @@
       <c r="G1863" s="13">
         <v>885</v>
       </c>
-      <c r="H1863" s="3"/>
+      <c r="H1863" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1863" s="12">
         <v>45839</v>
       </c>
@@ -61899,7 +61920,9 @@
       <c r="G1864" s="13">
         <v>610.07000000000005</v>
       </c>
-      <c r="H1864" s="3"/>
+      <c r="H1864" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1864" s="12">
         <v>45839</v>
       </c>
@@ -61939,7 +61962,7 @@
         <v>202</v>
       </c>
       <c r="L1865" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1866" spans="2:12" x14ac:dyDescent="0.25">
@@ -61975,7 +61998,7 @@
         <v>58</v>
       </c>
       <c r="L1866" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1867" spans="2:12" x14ac:dyDescent="0.25">
@@ -62002,10 +62025,10 @@
         <v>46</v>
       </c>
       <c r="K1867" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1867" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1868" spans="2:12" x14ac:dyDescent="0.25">
@@ -62065,10 +62088,10 @@
         <v>23</v>
       </c>
       <c r="K1869" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L1869" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="1870" spans="2:12" x14ac:dyDescent="0.25">
@@ -62248,7 +62271,7 @@
         <v>44</v>
       </c>
       <c r="K1875" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1876" spans="2:12" x14ac:dyDescent="0.25">
@@ -62304,7 +62327,9 @@
       <c r="G1877" s="13">
         <v>576.99</v>
       </c>
-      <c r="H1877" s="3"/>
+      <c r="H1877" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1877" s="12">
         <v>45839</v>
       </c>
@@ -62329,7 +62354,9 @@
       <c r="G1878" s="13">
         <v>453.91</v>
       </c>
-      <c r="H1878" s="3"/>
+      <c r="H1878" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1878" s="12">
         <v>45839</v>
       </c>
@@ -62360,7 +62387,9 @@
       <c r="G1879" s="13">
         <v>166.46</v>
       </c>
-      <c r="H1879" s="3"/>
+      <c r="H1879" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1879" s="12">
         <v>45839</v>
       </c>
@@ -62371,7 +62400,7 @@
         <v>172</v>
       </c>
       <c r="L1879" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1880" spans="2:12" x14ac:dyDescent="0.25">
@@ -62394,7 +62423,9 @@
       <c r="G1880" s="13">
         <v>242.01</v>
       </c>
-      <c r="H1880" s="3"/>
+      <c r="H1880" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1880" s="12">
         <v>45839</v>
       </c>
@@ -62405,7 +62436,7 @@
         <v>202</v>
       </c>
       <c r="L1880" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1881" spans="2:12" x14ac:dyDescent="0.25">
@@ -62428,7 +62459,9 @@
       <c r="G1881" s="13">
         <v>921.23</v>
       </c>
-      <c r="H1881" s="3"/>
+      <c r="H1881" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1881" s="12">
         <v>45839</v>
       </c>
@@ -62459,7 +62492,9 @@
       <c r="G1882" s="13">
         <v>280.63</v>
       </c>
-      <c r="H1882" s="3"/>
+      <c r="H1882" s="3" t="s">
+        <v>7</v>
+      </c>
       <c r="I1882" s="12">
         <v>45839</v>
       </c>
@@ -62467,10 +62502,10 @@
         <v>162</v>
       </c>
       <c r="K1882" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1882" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1883" spans="2:12" x14ac:dyDescent="0.25">
@@ -62493,7 +62528,9 @@
       <c r="G1883" s="13">
         <v>405.51</v>
       </c>
-      <c r="H1883" s="3"/>
+      <c r="H1883" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1883" s="12">
         <v>45839</v>
       </c>
@@ -62524,12 +62561,14 @@
       <c r="G1884" s="13">
         <v>1000</v>
       </c>
-      <c r="H1884" s="3"/>
+      <c r="H1884" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I1884" s="12">
         <v>45839</v>
       </c>
       <c r="J1884" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K1884" s="2" t="s">
         <v>26</v>
@@ -62589,13 +62628,13 @@
         <v>45839</v>
       </c>
       <c r="J1886" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K1886" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L1886" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1887" spans="2:12" x14ac:dyDescent="0.25">
@@ -62691,13 +62730,13 @@
         <v>45839</v>
       </c>
       <c r="J1889" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K1889" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1889" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1890" spans="2:12" x14ac:dyDescent="0.25">
@@ -62727,7 +62766,7 @@
         <v>45839</v>
       </c>
       <c r="J1890" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K1890" s="2" t="s">
         <v>27</v>
@@ -62760,7 +62799,7 @@
         <v>45839</v>
       </c>
       <c r="J1891" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K1891" s="2" t="s">
         <v>26</v>
@@ -62793,13 +62832,13 @@
         <v>45839</v>
       </c>
       <c r="J1892" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K1892" s="2" t="s">
         <v>58</v>
       </c>
       <c r="L1892" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1893" spans="2:12" x14ac:dyDescent="0.25">
@@ -62862,13 +62901,13 @@
         <v>45839</v>
       </c>
       <c r="J1894" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K1894" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1894" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1895" spans="2:12" x14ac:dyDescent="0.25">
@@ -62931,7 +62970,7 @@
         <v>45839</v>
       </c>
       <c r="J1896" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K1896" s="2" t="s">
         <v>29</v>
@@ -62970,7 +63009,7 @@
         <v>199</v>
       </c>
       <c r="L1897" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1898" spans="2:12" x14ac:dyDescent="0.25">
@@ -63234,7 +63273,7 @@
         <v>44</v>
       </c>
       <c r="K1905" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1906" spans="2:12" x14ac:dyDescent="0.25">
@@ -63303,7 +63342,7 @@
         <v>172</v>
       </c>
       <c r="L1907" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1908" spans="2:12" x14ac:dyDescent="0.25">
@@ -63333,7 +63372,7 @@
         <v>45839</v>
       </c>
       <c r="J1908" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K1908" s="2" t="s">
         <v>36</v>
@@ -63363,10 +63402,10 @@
         <v>23</v>
       </c>
       <c r="K1909" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L1909" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1910" spans="2:12" x14ac:dyDescent="0.25">
@@ -63399,10 +63438,10 @@
         <v>23</v>
       </c>
       <c r="K1910" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L1910" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1911" spans="2:12" x14ac:dyDescent="0.25">
@@ -63438,7 +63477,7 @@
         <v>197</v>
       </c>
       <c r="L1911" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="1912" spans="2:12" x14ac:dyDescent="0.25">
@@ -63531,7 +63570,7 @@
         <v>96</v>
       </c>
       <c r="K1914" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1915" spans="2:12" x14ac:dyDescent="0.25">
@@ -63561,7 +63600,7 @@
         <v>45839</v>
       </c>
       <c r="J1915" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K1915" s="2" t="s">
         <v>26</v>
@@ -63624,7 +63663,7 @@
         <v>23</v>
       </c>
       <c r="K1917" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1918" spans="2:12" x14ac:dyDescent="0.25">
@@ -63660,7 +63699,7 @@
         <v>205</v>
       </c>
       <c r="L1918" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1919" spans="2:12" x14ac:dyDescent="0.25">
@@ -63696,7 +63735,7 @@
         <v>202</v>
       </c>
       <c r="L1919" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1920" spans="2:12" x14ac:dyDescent="0.25">
@@ -63759,13 +63798,13 @@
         <v>45839</v>
       </c>
       <c r="J1921" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K1921" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1921" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1922" spans="2:12" x14ac:dyDescent="0.25">
@@ -63798,7 +63837,7 @@
         <v>171</v>
       </c>
       <c r="K1922" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1923" spans="2:12" x14ac:dyDescent="0.25">
@@ -63963,10 +64002,10 @@
         <v>23</v>
       </c>
       <c r="K1927" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L1927" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="1928" spans="2:12" x14ac:dyDescent="0.25">
@@ -64035,7 +64074,7 @@
         <v>210</v>
       </c>
       <c r="L1929" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1930" spans="2:12" x14ac:dyDescent="0.25">
@@ -64068,10 +64107,10 @@
         <v>112</v>
       </c>
       <c r="K1930" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1930" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1931" spans="2:12" x14ac:dyDescent="0.25">
@@ -64260,7 +64299,7 @@
         <v>205</v>
       </c>
       <c r="L1936" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="1937" spans="2:12" x14ac:dyDescent="0.25">
@@ -64362,7 +64401,7 @@
         <v>199</v>
       </c>
       <c r="L1939" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="1940" spans="2:12" x14ac:dyDescent="0.25">
@@ -64494,10 +64533,10 @@
         <v>112</v>
       </c>
       <c r="K1943" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1943" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1944" spans="2:12" x14ac:dyDescent="0.25">
@@ -64560,7 +64599,7 @@
         <v>45839</v>
       </c>
       <c r="J1945" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K1945" s="2" t="s">
         <v>104</v>
@@ -64593,13 +64632,13 @@
         <v>45839</v>
       </c>
       <c r="J1946" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K1946" s="2" t="s">
         <v>172</v>
       </c>
       <c r="L1946" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1947" spans="2:12" x14ac:dyDescent="0.25">
@@ -64629,7 +64668,7 @@
         <v>45839</v>
       </c>
       <c r="J1947" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K1947" s="2" t="s">
         <v>27</v>
@@ -64665,7 +64704,7 @@
         <v>44</v>
       </c>
       <c r="K1948" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1949" spans="2:12" x14ac:dyDescent="0.25">
@@ -64932,7 +64971,7 @@
         <v>172</v>
       </c>
       <c r="L1956" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1957" spans="2:12" x14ac:dyDescent="0.25">
@@ -64968,7 +65007,7 @@
         <v>208</v>
       </c>
       <c r="L1957" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1958" spans="2:12" x14ac:dyDescent="0.25">
@@ -65025,7 +65064,7 @@
         <v>45839</v>
       </c>
       <c r="J1959" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="K1959" s="2" t="s">
         <v>36</v>
@@ -65091,7 +65130,7 @@
         <v>45839</v>
       </c>
       <c r="J1961" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K1961" s="2" t="s">
         <v>104</v>
@@ -65154,10 +65193,10 @@
         <v>64</v>
       </c>
       <c r="K1963" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L1963" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="1964" spans="2:12" x14ac:dyDescent="0.25">
@@ -65223,7 +65262,7 @@
         <v>23</v>
       </c>
       <c r="K1965" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="1966" spans="2:12" x14ac:dyDescent="0.25">
@@ -65256,7 +65295,7 @@
         <v>206</v>
       </c>
       <c r="L1966" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="1967" spans="2:12" x14ac:dyDescent="0.25">
@@ -65289,10 +65328,10 @@
         <v>166</v>
       </c>
       <c r="K1967" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1967" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1968" spans="2:12" x14ac:dyDescent="0.25">
@@ -65394,7 +65433,7 @@
         <v>58</v>
       </c>
       <c r="L1970" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="1971" spans="2:12" x14ac:dyDescent="0.25">
@@ -65451,7 +65490,7 @@
         <v>45839</v>
       </c>
       <c r="J1972" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K1972" s="2" t="s">
         <v>35</v>
@@ -65484,7 +65523,7 @@
         <v>45839</v>
       </c>
       <c r="J1973" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K1973" s="2" t="s">
         <v>35</v>
@@ -65607,7 +65646,7 @@
         <v>44</v>
       </c>
       <c r="K1977" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1978" spans="2:12" x14ac:dyDescent="0.25">
@@ -65673,10 +65712,10 @@
         <v>31</v>
       </c>
       <c r="K1979" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L1979" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1980" spans="2:12" x14ac:dyDescent="0.25">
@@ -65766,7 +65805,7 @@
         <v>202</v>
       </c>
       <c r="L1982" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="1983" spans="2:12" x14ac:dyDescent="0.25">
@@ -65835,7 +65874,7 @@
         <v>208</v>
       </c>
       <c r="L1984" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="1985" spans="2:12" x14ac:dyDescent="0.25">
@@ -65871,7 +65910,7 @@
         <v>172</v>
       </c>
       <c r="L1985" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="1986" spans="2:12" x14ac:dyDescent="0.25">
@@ -65901,7 +65940,7 @@
         <v>45839</v>
       </c>
       <c r="J1986" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K1986" s="2" t="s">
         <v>27</v>
@@ -65967,7 +66006,7 @@
         <v>45839</v>
       </c>
       <c r="J1988" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K1988" s="2" t="s">
         <v>38</v>
@@ -66000,13 +66039,13 @@
         <v>45839</v>
       </c>
       <c r="J1989" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K1989" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L1989" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="1990" spans="2:12" x14ac:dyDescent="0.25">
@@ -66061,7 +66100,7 @@
         <v>45870</v>
       </c>
       <c r="J1991" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K1991" s="7" t="s">
         <v>111</v>
@@ -66152,10 +66191,10 @@
         <v>46</v>
       </c>
       <c r="K1994" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L1994" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="1995" spans="2:12" x14ac:dyDescent="0.25">
@@ -66204,7 +66243,7 @@
         <v>45901</v>
       </c>
       <c r="J1996" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K1996" s="7" t="s">
         <v>38</v>
@@ -66272,7 +66311,7 @@
         <v>210</v>
       </c>
       <c r="L1998" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="1999" spans="2:12" x14ac:dyDescent="0.25">
@@ -66437,7 +66476,7 @@
         <v>45870</v>
       </c>
       <c r="J2004" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K2004" s="7" t="s">
         <v>169</v>
@@ -66495,7 +66534,7 @@
         <v>45931</v>
       </c>
       <c r="J2006" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K2006" s="7" t="s">
         <v>27</v>
@@ -67742,7 +67781,7 @@
         <v>201</v>
       </c>
       <c r="K2049" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2050" spans="2:11" x14ac:dyDescent="0.25">
@@ -69088,7 +69127,7 @@
         <v>45931</v>
       </c>
       <c r="J2096" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K2096" s="7" t="s">
         <v>169</v>
@@ -69204,7 +69243,7 @@
         <v>45931</v>
       </c>
       <c r="J2100" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K2100" s="7" t="s">
         <v>25</v>
@@ -69294,7 +69333,7 @@
         <v>201</v>
       </c>
       <c r="K2103" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2104" spans="2:11" x14ac:dyDescent="0.25">
@@ -69375,7 +69414,7 @@
         <v>45931</v>
       </c>
       <c r="J2106" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K2106" s="7" t="s">
         <v>25</v>
@@ -69894,7 +69933,7 @@
         <v>201</v>
       </c>
       <c r="K2124" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2125" spans="2:11" x14ac:dyDescent="0.25">
@@ -70123,7 +70162,7 @@
         <v>201</v>
       </c>
       <c r="K2132" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2133" spans="2:11" x14ac:dyDescent="0.25">
@@ -70468,7 +70507,7 @@
         <v>45931</v>
       </c>
       <c r="J2144" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K2144" s="7" t="s">
         <v>77</v>
@@ -70961,7 +71000,7 @@
         <v>45901</v>
       </c>
       <c r="J2161" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K2161" s="7" t="s">
         <v>71</v>
@@ -71371,10 +71410,10 @@
         <v>64</v>
       </c>
       <c r="K2175" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2175" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2176" spans="2:12" x14ac:dyDescent="0.25">
@@ -71437,7 +71476,7 @@
         <v>45870</v>
       </c>
       <c r="J2177" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K2177" s="2" t="s">
         <v>104</v>
@@ -71503,7 +71542,7 @@
         <v>45870</v>
       </c>
       <c r="J2179" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K2179" s="2" t="s">
         <v>60</v>
@@ -71596,7 +71635,7 @@
         <v>218</v>
       </c>
       <c r="L2182" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2183" spans="2:12" x14ac:dyDescent="0.25">
@@ -71629,10 +71668,10 @@
         <v>46</v>
       </c>
       <c r="K2183" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2183" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2184" spans="2:12" x14ac:dyDescent="0.25">
@@ -71665,7 +71704,7 @@
         <v>44</v>
       </c>
       <c r="K2184" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2185" spans="2:12" x14ac:dyDescent="0.25">
@@ -71736,7 +71775,7 @@
     </row>
     <row r="2187" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2187" s="17">
-        <v>45929.265277777777</v>
+        <v>45929</v>
       </c>
       <c r="C2187" s="1"/>
       <c r="D2187" s="1"/>
@@ -72074,7 +72113,7 @@
         <v>23</v>
       </c>
       <c r="K2197" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2198" spans="2:12" x14ac:dyDescent="0.25">
@@ -72110,7 +72149,7 @@
         <v>197</v>
       </c>
       <c r="L2198" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2199" spans="2:12" x14ac:dyDescent="0.25">
@@ -72143,7 +72182,7 @@
         <v>161</v>
       </c>
       <c r="K2199" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2200" spans="2:12" x14ac:dyDescent="0.25">
@@ -72242,10 +72281,10 @@
         <v>46</v>
       </c>
       <c r="K2202" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2202" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2203" spans="2:12" x14ac:dyDescent="0.25">
@@ -72281,7 +72320,7 @@
         <v>210</v>
       </c>
       <c r="L2203" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2204" spans="2:12" x14ac:dyDescent="0.25">
@@ -72479,7 +72518,7 @@
         <v>44</v>
       </c>
       <c r="K2209" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2210" spans="2:12" x14ac:dyDescent="0.25">
@@ -72611,10 +72650,10 @@
         <v>23</v>
       </c>
       <c r="K2213" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2213" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2214" spans="2:12" x14ac:dyDescent="0.25">
@@ -72716,7 +72755,7 @@
         <v>208</v>
       </c>
       <c r="L2216" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2217" spans="2:12" x14ac:dyDescent="0.25">
@@ -72746,7 +72785,7 @@
         <v>45870</v>
       </c>
       <c r="J2217" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K2217" s="2" t="s">
         <v>27</v>
@@ -72839,7 +72878,7 @@
         <v>45870</v>
       </c>
       <c r="J2220" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K2220" s="2" t="s">
         <v>38</v>
@@ -72872,7 +72911,7 @@
         <v>45870</v>
       </c>
       <c r="J2221" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K2221" s="2" t="s">
         <v>29</v>
@@ -73073,7 +73112,7 @@
         <v>44</v>
       </c>
       <c r="K2227" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2228" spans="2:12" x14ac:dyDescent="0.25">
@@ -73109,7 +73148,7 @@
         <v>202</v>
       </c>
       <c r="L2228" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2229" spans="2:12" x14ac:dyDescent="0.25">
@@ -73178,7 +73217,7 @@
         <v>218</v>
       </c>
       <c r="L2230" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2231" spans="2:12" x14ac:dyDescent="0.25">
@@ -73337,7 +73376,7 @@
         <v>23</v>
       </c>
       <c r="K2235" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2236" spans="2:12" x14ac:dyDescent="0.25">
@@ -73370,10 +73409,10 @@
         <v>112</v>
       </c>
       <c r="K2236" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2236" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2237" spans="2:12" x14ac:dyDescent="0.25">
@@ -73442,7 +73481,7 @@
         <v>205</v>
       </c>
       <c r="L2238" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2239" spans="2:12" x14ac:dyDescent="0.25">
@@ -73667,7 +73706,7 @@
         <v>44</v>
       </c>
       <c r="K2245" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2246" spans="2:12" x14ac:dyDescent="0.25">
@@ -73703,7 +73742,7 @@
         <v>210</v>
       </c>
       <c r="L2246" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2247" spans="2:12" x14ac:dyDescent="0.25">
@@ -73739,7 +73778,7 @@
         <v>218</v>
       </c>
       <c r="L2247" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2248" spans="2:12" x14ac:dyDescent="0.25">
@@ -73796,13 +73835,13 @@
         <v>45870</v>
       </c>
       <c r="J2249" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K2249" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2249" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2250" spans="2:12" x14ac:dyDescent="0.25">
@@ -73832,7 +73871,7 @@
         <v>45870</v>
       </c>
       <c r="J2250" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K2250" s="2" t="s">
         <v>29</v>
@@ -73871,7 +73910,7 @@
         <v>58</v>
       </c>
       <c r="L2251" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2252" spans="2:12" x14ac:dyDescent="0.25">
@@ -73901,13 +73940,13 @@
         <v>45870</v>
       </c>
       <c r="J2252" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K2252" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2252" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2253" spans="2:12" x14ac:dyDescent="0.25">
@@ -73973,10 +74012,10 @@
         <v>102</v>
       </c>
       <c r="K2254" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2254" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2255" spans="2:12" x14ac:dyDescent="0.25">
@@ -74006,7 +74045,7 @@
         <v>45870</v>
       </c>
       <c r="J2255" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K2255" s="2" t="s">
         <v>65</v>
@@ -74072,7 +74111,7 @@
         <v>45870</v>
       </c>
       <c r="J2257" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K2257" s="2" t="s">
         <v>56</v>
@@ -74111,7 +74150,7 @@
         <v>199</v>
       </c>
       <c r="L2258" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2259" spans="2:12" x14ac:dyDescent="0.25">
@@ -74174,7 +74213,7 @@
         <v>45870</v>
       </c>
       <c r="J2260" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K2260" s="2" t="s">
         <v>104</v>
@@ -74207,7 +74246,7 @@
         <v>45870</v>
       </c>
       <c r="J2261" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K2261" s="2" t="s">
         <v>29</v>
@@ -74240,7 +74279,7 @@
         <v>45870</v>
       </c>
       <c r="J2262" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K2262" s="2" t="s">
         <v>71</v>
@@ -74312,7 +74351,7 @@
         <v>197</v>
       </c>
       <c r="L2264" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2265" spans="2:12" x14ac:dyDescent="0.25">
@@ -74342,7 +74381,7 @@
         <v>45870</v>
       </c>
       <c r="J2265" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K2265" s="2" t="s">
         <v>52</v>
@@ -74369,7 +74408,7 @@
         <v>45870</v>
       </c>
       <c r="J2266" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K2266" s="2" t="s">
         <v>114</v>
@@ -74402,7 +74441,7 @@
         <v>45870</v>
       </c>
       <c r="J2267" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K2267" s="2" t="s">
         <v>27</v>
@@ -74537,10 +74576,10 @@
         <v>23</v>
       </c>
       <c r="K2271" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2271" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2272" spans="2:12" x14ac:dyDescent="0.25">
@@ -74705,7 +74744,7 @@
         <v>44</v>
       </c>
       <c r="K2276" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2277" spans="2:12" x14ac:dyDescent="0.25">
@@ -74741,7 +74780,7 @@
         <v>210</v>
       </c>
       <c r="L2277" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2278" spans="2:12" x14ac:dyDescent="0.25">
@@ -74810,7 +74849,7 @@
         <v>218</v>
       </c>
       <c r="L2279" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2280" spans="2:12" x14ac:dyDescent="0.25">
@@ -74846,7 +74885,7 @@
         <v>202</v>
       </c>
       <c r="L2280" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2281" spans="2:12" x14ac:dyDescent="0.25">
@@ -74903,7 +74942,7 @@
         <v>45870</v>
       </c>
       <c r="J2282" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K2282" s="2" t="s">
         <v>52</v>
@@ -74936,10 +74975,10 @@
         <v>45870</v>
       </c>
       <c r="J2283" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K2283" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2284" spans="2:12" x14ac:dyDescent="0.25">
@@ -75062,13 +75101,13 @@
         <v>45870</v>
       </c>
       <c r="J2287" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K2287" s="2" t="s">
         <v>210</v>
       </c>
       <c r="L2287" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2288" spans="2:12" x14ac:dyDescent="0.25">
@@ -75098,13 +75137,13 @@
         <v>45870</v>
       </c>
       <c r="J2288" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K2288" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2288" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2289" spans="2:12" x14ac:dyDescent="0.25">
@@ -75239,7 +75278,7 @@
         <v>208</v>
       </c>
       <c r="L2292" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2293" spans="2:12" x14ac:dyDescent="0.25">
@@ -75272,7 +75311,7 @@
         <v>171</v>
       </c>
       <c r="K2293" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2294" spans="2:12" x14ac:dyDescent="0.25">
@@ -75428,7 +75467,7 @@
         <v>45870</v>
       </c>
       <c r="J2298" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K2298" s="2" t="s">
         <v>39</v>
@@ -75626,7 +75665,7 @@
         <v>45870</v>
       </c>
       <c r="J2304" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K2304" s="2" t="s">
         <v>104</v>
@@ -75665,7 +75704,7 @@
         <v>202</v>
       </c>
       <c r="L2305" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2306" spans="2:12" x14ac:dyDescent="0.25">
@@ -75695,13 +75734,13 @@
         <v>45870</v>
       </c>
       <c r="J2306" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K2306" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2306" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2307" spans="2:12" x14ac:dyDescent="0.25">
@@ -75731,13 +75770,13 @@
         <v>45870</v>
       </c>
       <c r="J2307" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K2307" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2307" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2308" spans="2:12" x14ac:dyDescent="0.25">
@@ -75767,13 +75806,13 @@
         <v>45870</v>
       </c>
       <c r="J2308" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K2308" s="2" t="s">
         <v>210</v>
       </c>
       <c r="L2308" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2309" spans="2:12" x14ac:dyDescent="0.25">
@@ -75806,10 +75845,10 @@
         <v>23</v>
       </c>
       <c r="K2309" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2309" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2310" spans="2:12" x14ac:dyDescent="0.25">
@@ -75839,13 +75878,13 @@
         <v>45870</v>
       </c>
       <c r="J2310" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K2310" s="2" t="s">
         <v>218</v>
       </c>
       <c r="L2310" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2311" spans="2:12" x14ac:dyDescent="0.25">
@@ -75971,7 +76010,7 @@
         <v>23</v>
       </c>
       <c r="K2314" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2315" spans="2:12" x14ac:dyDescent="0.25">
@@ -76001,7 +76040,7 @@
         <v>45870</v>
       </c>
       <c r="J2315" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2315" s="2" t="s">
         <v>27</v>
@@ -76100,7 +76139,7 @@
         <v>45870</v>
       </c>
       <c r="J2318" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K2318" s="2" t="s">
         <v>26</v>
@@ -76193,7 +76232,7 @@
         <v>45870</v>
       </c>
       <c r="J2321" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2321" s="2" t="s">
         <v>39</v>
@@ -76220,13 +76259,13 @@
         <v>45870</v>
       </c>
       <c r="J2322" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K2322" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L2322" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2323" spans="2:12" x14ac:dyDescent="0.25">
@@ -76325,7 +76364,7 @@
         <v>44</v>
       </c>
       <c r="K2325" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2326" spans="2:12" x14ac:dyDescent="0.25">
@@ -76394,7 +76433,7 @@
         <v>202</v>
       </c>
       <c r="L2327" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2328" spans="2:12" x14ac:dyDescent="0.25">
@@ -76430,7 +76469,7 @@
         <v>208</v>
       </c>
       <c r="L2328" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2329" spans="2:12" x14ac:dyDescent="0.25">
@@ -76466,7 +76505,7 @@
         <v>172</v>
       </c>
       <c r="L2329" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2330" spans="2:12" x14ac:dyDescent="0.25">
@@ -76496,13 +76535,13 @@
         <v>45870</v>
       </c>
       <c r="J2330" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K2330" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2330" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2331" spans="2:12" x14ac:dyDescent="0.25">
@@ -76757,7 +76796,7 @@
         <v>210</v>
       </c>
       <c r="L2338" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2339" spans="2:12" x14ac:dyDescent="0.25">
@@ -76787,13 +76826,13 @@
         <v>45870</v>
       </c>
       <c r="J2339" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K2339" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2339" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2340" spans="2:12" x14ac:dyDescent="0.25">
@@ -76826,10 +76865,10 @@
         <v>102</v>
       </c>
       <c r="K2340" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2340" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2341" spans="2:12" x14ac:dyDescent="0.25">
@@ -76886,7 +76925,7 @@
         <v>45870</v>
       </c>
       <c r="J2342" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K2342" s="2" t="s">
         <v>39</v>
@@ -76955,10 +76994,10 @@
         <v>181</v>
       </c>
       <c r="K2344" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2344" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2345" spans="2:12" x14ac:dyDescent="0.25">
@@ -77021,7 +77060,7 @@
         <v>45870</v>
       </c>
       <c r="J2346" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K2346" s="2" t="s">
         <v>65</v>
@@ -77060,7 +77099,7 @@
         <v>205</v>
       </c>
       <c r="L2347" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2348" spans="2:12" x14ac:dyDescent="0.25">
@@ -77090,13 +77129,13 @@
         <v>45870</v>
       </c>
       <c r="J2348" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K2348" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2348" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2349" spans="2:12" x14ac:dyDescent="0.25">
@@ -77222,7 +77261,7 @@
         <v>23</v>
       </c>
       <c r="K2352" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2353" spans="2:12" x14ac:dyDescent="0.25">
@@ -77384,7 +77423,7 @@
         <v>45870</v>
       </c>
       <c r="J2357" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K2357" s="2" t="s">
         <v>38</v>
@@ -77486,10 +77525,10 @@
         <v>145</v>
       </c>
       <c r="K2360" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2360" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2361" spans="2:12" x14ac:dyDescent="0.25">
@@ -77684,7 +77723,7 @@
         <v>45870</v>
       </c>
       <c r="J2366" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K2366" s="2" t="s">
         <v>38</v>
@@ -77717,7 +77756,7 @@
         <v>45870</v>
       </c>
       <c r="J2367" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K2367" s="2" t="s">
         <v>29</v>
@@ -77783,7 +77822,7 @@
         <v>45870</v>
       </c>
       <c r="J2369" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2369" s="2" t="s">
         <v>39</v>
@@ -77816,13 +77855,13 @@
         <v>45870</v>
       </c>
       <c r="J2370" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K2370" s="2" t="s">
         <v>172</v>
       </c>
       <c r="L2370" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2371" spans="2:12" x14ac:dyDescent="0.25">
@@ -77888,10 +77927,10 @@
         <v>23</v>
       </c>
       <c r="K2372" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2372" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2373" spans="2:12" x14ac:dyDescent="0.25">
@@ -77993,7 +78032,7 @@
         <v>202</v>
       </c>
       <c r="L2375" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2376" spans="2:12" x14ac:dyDescent="0.25">
@@ -78077,7 +78116,7 @@
         <v>45931</v>
       </c>
       <c r="J2378" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K2378" s="7" t="s">
         <v>169</v>
@@ -78135,7 +78174,7 @@
         <v>45931</v>
       </c>
       <c r="J2380" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K2380" s="7" t="s">
         <v>169</v>
@@ -78678,7 +78717,7 @@
         <v>500</v>
       </c>
       <c r="H2399" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I2399" s="12">
         <v>45931</v>
@@ -78713,7 +78752,7 @@
         <v>45931</v>
       </c>
       <c r="J2400" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K2400" s="7" t="s">
         <v>169</v>
@@ -78742,7 +78781,7 @@
         <v>45931</v>
       </c>
       <c r="J2401" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K2401" s="7" t="s">
         <v>29</v>
@@ -78898,7 +78937,7 @@
         <v>46</v>
       </c>
       <c r="K2406" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2407" spans="2:12" x14ac:dyDescent="0.25">
@@ -78934,7 +78973,7 @@
         <v>218</v>
       </c>
       <c r="L2407" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2408" spans="2:12" x14ac:dyDescent="0.25">
@@ -78970,7 +79009,7 @@
         <v>208</v>
       </c>
       <c r="L2408" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2409" spans="2:12" x14ac:dyDescent="0.25">
@@ -79003,10 +79042,10 @@
         <v>46</v>
       </c>
       <c r="K2409" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2409" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2410" spans="2:12" x14ac:dyDescent="0.25">
@@ -79096,13 +79135,13 @@
         <v>45901</v>
       </c>
       <c r="J2412" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K2412" s="2" t="s">
         <v>199</v>
       </c>
       <c r="L2412" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2413" spans="2:12" x14ac:dyDescent="0.25">
@@ -79135,7 +79174,7 @@
         <v>23</v>
       </c>
       <c r="K2413" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2414" spans="2:12" x14ac:dyDescent="0.25">
@@ -79165,7 +79204,7 @@
         <v>45901</v>
       </c>
       <c r="J2414" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K2414" s="2" t="s">
         <v>65</v>
@@ -79220,7 +79259,9 @@
       <c r="G2416" s="2">
         <v>187.79</v>
       </c>
-      <c r="H2416" s="3"/>
+      <c r="H2416" t="s">
+        <v>7</v>
+      </c>
       <c r="I2416" s="12">
         <v>45901</v>
       </c>
@@ -79231,7 +79272,7 @@
         <v>210</v>
       </c>
       <c r="L2416" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2417" spans="2:12" x14ac:dyDescent="0.25">
@@ -79254,7 +79295,9 @@
       <c r="G2417" s="2">
         <v>915</v>
       </c>
-      <c r="H2417" s="3"/>
+      <c r="H2417" t="s">
+        <v>8</v>
+      </c>
       <c r="I2417" s="12">
         <v>45901</v>
       </c>
@@ -79285,7 +79328,9 @@
       <c r="G2418" s="16">
         <v>1074.03</v>
       </c>
-      <c r="H2418" s="3"/>
+      <c r="H2418" t="s">
+        <v>8</v>
+      </c>
       <c r="I2418" s="12">
         <v>45901</v>
       </c>
@@ -79310,7 +79355,9 @@
       <c r="G2419" s="2">
         <v>484</v>
       </c>
-      <c r="H2419" s="3"/>
+      <c r="H2419" t="s">
+        <v>8</v>
+      </c>
       <c r="I2419" s="12">
         <v>45901</v>
       </c>
@@ -79335,7 +79382,9 @@
       <c r="G2420" s="2">
         <v>100</v>
       </c>
-      <c r="H2420" s="3"/>
+      <c r="H2420" t="s">
+        <v>7</v>
+      </c>
       <c r="I2420" s="12">
         <v>45901</v>
       </c>
@@ -79343,10 +79392,10 @@
         <v>160</v>
       </c>
       <c r="K2420" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L2420" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2421" spans="2:12" x14ac:dyDescent="0.25">
@@ -79369,7 +79418,9 @@
       <c r="G2421" s="16">
         <v>1169.9100000000001</v>
       </c>
-      <c r="H2421" s="3"/>
+      <c r="H2421" t="s">
+        <v>8</v>
+      </c>
       <c r="I2421" s="12">
         <v>45901</v>
       </c>
@@ -79400,7 +79451,9 @@
       <c r="G2422" s="2">
         <v>123.34</v>
       </c>
-      <c r="H2422" s="3"/>
+      <c r="H2422" t="s">
+        <v>7</v>
+      </c>
       <c r="I2422" s="12">
         <v>45901</v>
       </c>
@@ -79408,7 +79461,7 @@
         <v>161</v>
       </c>
       <c r="K2422" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2423" spans="2:12" x14ac:dyDescent="0.25">
@@ -79431,7 +79484,9 @@
       <c r="G2423" s="2">
         <v>61.76</v>
       </c>
-      <c r="H2423" s="3"/>
+      <c r="H2423" t="s">
+        <v>10</v>
+      </c>
       <c r="I2423" s="12">
         <v>45901</v>
       </c>
@@ -79462,7 +79517,9 @@
       <c r="G2424" s="2">
         <v>500</v>
       </c>
-      <c r="H2424" s="3"/>
+      <c r="H2424" t="s">
+        <v>8</v>
+      </c>
       <c r="I2424" s="12">
         <v>45901</v>
       </c>
@@ -79551,18 +79608,20 @@
       <c r="G2427" s="2">
         <v>100</v>
       </c>
-      <c r="H2427" s="3"/>
+      <c r="H2427" t="s">
+        <v>7</v>
+      </c>
       <c r="I2427" s="12">
         <v>45901</v>
       </c>
       <c r="J2427" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K2427" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2427" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2428" spans="2:12" x14ac:dyDescent="0.25">
@@ -79585,18 +79644,20 @@
       <c r="G2428" s="2">
         <v>150</v>
       </c>
-      <c r="H2428" s="3"/>
+      <c r="H2428" t="s">
+        <v>7</v>
+      </c>
       <c r="I2428" s="12">
         <v>45901</v>
       </c>
       <c r="J2428" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="K2428" s="2" t="s">
         <v>202</v>
       </c>
       <c r="L2428" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2429" spans="2:12" x14ac:dyDescent="0.25">
@@ -79619,7 +79680,9 @@
       <c r="G2429" s="2">
         <v>217.89</v>
       </c>
-      <c r="H2429" s="3"/>
+      <c r="H2429" t="s">
+        <v>7</v>
+      </c>
       <c r="I2429" s="12">
         <v>45901</v>
       </c>
@@ -79630,7 +79693,7 @@
         <v>172</v>
       </c>
       <c r="L2429" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2430" spans="2:12" x14ac:dyDescent="0.25">
@@ -79647,7 +79710,9 @@
       <c r="G2430" s="2">
         <v>406.67</v>
       </c>
-      <c r="H2430" s="3"/>
+      <c r="H2430" t="s">
+        <v>8</v>
+      </c>
       <c r="I2430" s="12">
         <v>45901</v>
       </c>
@@ -79678,18 +79743,20 @@
       <c r="G2431" s="2">
         <v>159.22999999999999</v>
       </c>
-      <c r="H2431" s="3"/>
+      <c r="H2431" t="s">
+        <v>7</v>
+      </c>
       <c r="I2431" s="12">
         <v>45901</v>
       </c>
       <c r="J2431" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K2431" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2431" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2432" spans="2:12" x14ac:dyDescent="0.25">
@@ -79712,7 +79779,9 @@
       <c r="G2432" s="2">
         <v>843.66</v>
       </c>
-      <c r="H2432" s="3"/>
+      <c r="H2432" t="s">
+        <v>8</v>
+      </c>
       <c r="I2432" s="12">
         <v>45901</v>
       </c>
@@ -79743,12 +79812,14 @@
       <c r="G2433" s="2">
         <v>184.67</v>
       </c>
-      <c r="H2433" s="3"/>
+      <c r="H2433" t="s">
+        <v>7</v>
+      </c>
       <c r="I2433" s="12">
         <v>45901</v>
       </c>
       <c r="J2433" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K2433" s="2" t="s">
         <v>39</v>
@@ -79774,7 +79845,9 @@
       <c r="G2434" s="2">
         <v>900</v>
       </c>
-      <c r="H2434" s="3"/>
+      <c r="H2434" t="s">
+        <v>8</v>
+      </c>
       <c r="I2434" s="12">
         <v>45901</v>
       </c>
@@ -79805,7 +79878,9 @@
       <c r="G2435" s="16">
         <v>2179.96</v>
       </c>
-      <c r="H2435" s="3"/>
+      <c r="H2435" t="s">
+        <v>8</v>
+      </c>
       <c r="I2435" s="12">
         <v>45901</v>
       </c>
@@ -79836,18 +79911,20 @@
       <c r="G2436" s="2">
         <v>198.42</v>
       </c>
-      <c r="H2436" s="3"/>
+      <c r="H2436" t="s">
+        <v>7</v>
+      </c>
       <c r="I2436" s="12">
         <v>45901</v>
       </c>
       <c r="J2436" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K2436" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2436" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2437" spans="2:12" x14ac:dyDescent="0.25">
@@ -79864,7 +79941,9 @@
       <c r="G2437" s="16">
         <v>1170.7</v>
       </c>
-      <c r="H2437" s="3"/>
+      <c r="H2437" t="s">
+        <v>8</v>
+      </c>
       <c r="I2437" s="12">
         <v>45901</v>
       </c>
@@ -79895,12 +79974,14 @@
       <c r="G2438" s="16">
         <v>1350</v>
       </c>
-      <c r="H2438" s="3"/>
+      <c r="H2438" t="s">
+        <v>8</v>
+      </c>
       <c r="I2438" s="12">
         <v>45901</v>
       </c>
       <c r="J2438" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K2438" s="2" t="s">
         <v>29</v>
@@ -79926,7 +80007,9 @@
       <c r="G2439" s="2">
         <v>887.37</v>
       </c>
-      <c r="H2439" s="3"/>
+      <c r="H2439" t="s">
+        <v>8</v>
+      </c>
       <c r="I2439" s="12">
         <v>45901</v>
       </c>
@@ -79957,7 +80040,9 @@
       <c r="G2440" s="16">
         <v>1150.1199999999999</v>
       </c>
-      <c r="H2440" s="3"/>
+      <c r="H2440" t="s">
+        <v>8</v>
+      </c>
       <c r="I2440" s="12">
         <v>45901</v>
       </c>
@@ -79988,7 +80073,9 @@
       <c r="G2441" s="2">
         <v>626.72</v>
       </c>
-      <c r="H2441" s="3"/>
+      <c r="H2441" t="s">
+        <v>8</v>
+      </c>
       <c r="I2441" s="12">
         <v>45901</v>
       </c>
@@ -80019,7 +80106,9 @@
       <c r="G2442" s="2">
         <v>619.61</v>
       </c>
-      <c r="H2442" s="3"/>
+      <c r="H2442" t="s">
+        <v>8</v>
+      </c>
       <c r="I2442" s="12">
         <v>45901</v>
       </c>
@@ -80050,7 +80139,9 @@
       <c r="G2443" s="2">
         <v>107.26</v>
       </c>
-      <c r="H2443" s="3"/>
+      <c r="H2443" t="s">
+        <v>7</v>
+      </c>
       <c r="I2443" s="12">
         <v>45901</v>
       </c>
@@ -80061,7 +80152,7 @@
         <v>208</v>
       </c>
       <c r="L2443" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2444" spans="2:12" x14ac:dyDescent="0.25">
@@ -80084,7 +80175,9 @@
       <c r="G2444" s="2">
         <v>525.67999999999995</v>
       </c>
-      <c r="H2444" s="3"/>
+      <c r="H2444" t="s">
+        <v>8</v>
+      </c>
       <c r="I2444" s="12">
         <v>45901</v>
       </c>
@@ -80109,7 +80202,9 @@
       <c r="G2445" s="16">
         <v>1239.5899999999999</v>
       </c>
-      <c r="H2445" s="3"/>
+      <c r="H2445" t="s">
+        <v>8</v>
+      </c>
       <c r="I2445" s="12">
         <v>45901</v>
       </c>
@@ -80140,12 +80235,14 @@
       <c r="G2446" s="2">
         <v>200</v>
       </c>
-      <c r="H2446" s="3"/>
+      <c r="H2446" t="s">
+        <v>8</v>
+      </c>
       <c r="I2446" s="12">
         <v>45901</v>
       </c>
       <c r="J2446" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K2446" s="2" t="s">
         <v>71</v>
@@ -80171,7 +80268,9 @@
       <c r="G2447" s="2">
         <v>238.04</v>
       </c>
-      <c r="H2447" s="3"/>
+      <c r="H2447" t="s">
+        <v>7</v>
+      </c>
       <c r="I2447" s="12">
         <v>45901</v>
       </c>
@@ -80182,7 +80281,7 @@
         <v>197</v>
       </c>
       <c r="L2447" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2448" spans="2:12" x14ac:dyDescent="0.25">
@@ -80205,7 +80304,9 @@
       <c r="G2448" s="2">
         <v>232.11</v>
       </c>
-      <c r="H2448" s="3"/>
+      <c r="H2448" t="s">
+        <v>7</v>
+      </c>
       <c r="I2448" s="12">
         <v>45901</v>
       </c>
@@ -80213,10 +80314,10 @@
         <v>23</v>
       </c>
       <c r="K2448" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2448" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2449" spans="2:12" x14ac:dyDescent="0.25">
@@ -80239,12 +80340,14 @@
       <c r="G2449" s="16">
         <v>1264.9100000000001</v>
       </c>
-      <c r="H2449" s="3"/>
+      <c r="H2449" t="s">
+        <v>8</v>
+      </c>
       <c r="I2449" s="12">
         <v>45901</v>
       </c>
       <c r="J2449" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K2449" s="2" t="s">
         <v>52</v>
@@ -80270,12 +80373,14 @@
       <c r="G2450" s="2">
         <v>187.55</v>
       </c>
-      <c r="H2450" s="3"/>
+      <c r="H2450" t="s">
+        <v>7</v>
+      </c>
       <c r="I2450" s="12">
         <v>45901</v>
       </c>
       <c r="J2450" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2450" s="2" t="s">
         <v>39</v>
@@ -80295,12 +80400,14 @@
       <c r="G2451" s="2">
         <v>700</v>
       </c>
-      <c r="H2451" s="3"/>
+      <c r="H2451" t="s">
+        <v>8</v>
+      </c>
       <c r="I2451" s="12">
         <v>45901</v>
       </c>
       <c r="J2451" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K2451" s="2" t="s">
         <v>71</v>
@@ -80326,7 +80433,9 @@
       <c r="G2452" s="16">
         <v>1029.99</v>
       </c>
-      <c r="H2452" s="3"/>
+      <c r="H2452" t="s">
+        <v>8</v>
+      </c>
       <c r="I2452" s="12">
         <v>45901</v>
       </c>
@@ -80357,18 +80466,20 @@
       <c r="G2453" s="2">
         <v>150.82</v>
       </c>
-      <c r="H2453" s="3"/>
+      <c r="H2453" t="s">
+        <v>7</v>
+      </c>
       <c r="I2453" s="12">
         <v>45901</v>
       </c>
       <c r="J2453" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K2453" s="2" t="s">
         <v>199</v>
       </c>
       <c r="L2453" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2454" spans="2:12" x14ac:dyDescent="0.25">
@@ -80391,12 +80502,14 @@
       <c r="G2454" s="16">
         <v>1238.19</v>
       </c>
-      <c r="H2454" s="3"/>
+      <c r="H2454" t="s">
+        <v>8</v>
+      </c>
       <c r="I2454" s="12">
         <v>45901</v>
       </c>
       <c r="J2454" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K2454" s="2" t="s">
         <v>63</v>
@@ -80422,18 +80535,20 @@
       <c r="G2455" s="2">
         <v>255.18</v>
       </c>
-      <c r="H2455" s="3"/>
+      <c r="H2455" t="s">
+        <v>7</v>
+      </c>
       <c r="I2455" s="12">
         <v>45901</v>
       </c>
       <c r="J2455" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K2455" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2455" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2456" spans="2:12" x14ac:dyDescent="0.25">
@@ -80456,7 +80571,9 @@
       <c r="G2456" s="2">
         <v>146.35</v>
       </c>
-      <c r="H2456" s="3"/>
+      <c r="H2456" t="s">
+        <v>8</v>
+      </c>
       <c r="I2456" s="12">
         <v>45901</v>
       </c>
@@ -80481,7 +80598,9 @@
       <c r="G2457" s="2">
         <v>994.82</v>
       </c>
-      <c r="H2457" s="3"/>
+      <c r="H2457" t="s">
+        <v>8</v>
+      </c>
       <c r="I2457" s="12">
         <v>45901</v>
       </c>
@@ -80512,7 +80631,9 @@
       <c r="G2458" s="2">
         <v>200</v>
       </c>
-      <c r="H2458" s="3"/>
+      <c r="H2458" t="s">
+        <v>8</v>
+      </c>
       <c r="I2458" s="12">
         <v>45901</v>
       </c>
@@ -80543,7 +80664,9 @@
       <c r="G2459" s="16">
         <v>1130.02</v>
       </c>
-      <c r="H2459" s="3"/>
+      <c r="H2459" t="s">
+        <v>8</v>
+      </c>
       <c r="I2459" s="12">
         <v>45901</v>
       </c>
@@ -80574,7 +80697,9 @@
       <c r="G2460" s="2">
         <v>755</v>
       </c>
-      <c r="H2460" s="3"/>
+      <c r="H2460" t="s">
+        <v>8</v>
+      </c>
       <c r="I2460" s="12">
         <v>45901</v>
       </c>
@@ -80605,7 +80730,9 @@
       <c r="G2461" s="16">
         <v>1268.0999999999999</v>
       </c>
-      <c r="H2461" s="3"/>
+      <c r="H2461" t="s">
+        <v>8</v>
+      </c>
       <c r="I2461" s="12">
         <v>45901</v>
       </c>
@@ -80671,7 +80798,7 @@
         <v>201</v>
       </c>
       <c r="K2463" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2464" spans="2:12" x14ac:dyDescent="0.25">
@@ -80736,7 +80863,7 @@
         <v>202</v>
       </c>
       <c r="L2465" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2466" spans="2:12" x14ac:dyDescent="0.25">
@@ -80772,7 +80899,7 @@
         <v>218</v>
       </c>
       <c r="L2466" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2467" spans="2:12" x14ac:dyDescent="0.25">
@@ -80805,7 +80932,7 @@
         <v>46</v>
       </c>
       <c r="K2467" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2468" spans="2:12" x14ac:dyDescent="0.25">
@@ -80835,7 +80962,7 @@
         <v>45901</v>
       </c>
       <c r="J2468" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K2468" s="2" t="s">
         <v>104</v>
@@ -80871,10 +80998,10 @@
         <v>23</v>
       </c>
       <c r="K2469" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2469" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2470" spans="2:12" x14ac:dyDescent="0.25">
@@ -80907,7 +81034,7 @@
         <v>23</v>
       </c>
       <c r="K2470" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2471" spans="2:12" x14ac:dyDescent="0.25">
@@ -80976,11 +81103,15 @@
       <c r="B2473" s="17">
         <v>45909.326504629629</v>
       </c>
-      <c r="C2473" s="1"/>
-      <c r="D2473" s="1"/>
+      <c r="C2473">
+        <v>5372</v>
+      </c>
+      <c r="D2473">
+        <v>5633</v>
+      </c>
       <c r="E2473" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="F2473" s="2">
         <v>1.5</v>
@@ -80988,22 +81119,35 @@
       <c r="G2473" s="2">
         <v>10</v>
       </c>
-      <c r="H2473" s="3"/>
+      <c r="H2473" t="s">
+        <v>7</v>
+      </c>
       <c r="I2473" s="12">
         <v>45901</v>
       </c>
-      <c r="J2473" s="7"/>
-      <c r="K2473" s="7"/>
+      <c r="J2473" t="s">
+        <v>336</v>
+      </c>
+      <c r="K2473" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2473" s="28" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="2474" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2474" s="17">
         <v>45909.32712962963</v>
       </c>
-      <c r="C2474" s="1"/>
-      <c r="D2474" s="1"/>
+      <c r="C2474">
+        <v>450018</v>
+      </c>
+      <c r="D2474">
+        <v>450727</v>
+      </c>
       <c r="E2474" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F2474" s="2">
         <v>222.43</v>
@@ -81011,22 +81155,32 @@
       <c r="G2474" s="16">
         <v>1287.8599999999999</v>
       </c>
-      <c r="H2474" s="3"/>
+      <c r="H2474" t="s">
+        <v>8</v>
+      </c>
       <c r="I2474" s="12">
         <v>45901</v>
       </c>
-      <c r="J2474" s="7"/>
-      <c r="K2474" s="7"/>
+      <c r="J2474" t="s">
+        <v>90</v>
+      </c>
+      <c r="K2474" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2475" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2475" s="17">
         <v>45909.328773148147</v>
       </c>
-      <c r="C2475" s="1"/>
-      <c r="D2475" s="1"/>
+      <c r="C2475">
+        <v>5633</v>
+      </c>
+      <c r="D2475">
+        <v>5700</v>
+      </c>
       <c r="E2475" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F2475" s="2">
         <v>24.5</v>
@@ -81034,22 +81188,35 @@
       <c r="G2475" s="2">
         <v>140.69999999999999</v>
       </c>
-      <c r="H2475" s="3"/>
+      <c r="H2475" t="s">
+        <v>7</v>
+      </c>
       <c r="I2475" s="12">
         <v>45901</v>
       </c>
-      <c r="J2475" s="7"/>
-      <c r="K2475" s="7"/>
+      <c r="J2475" t="s">
+        <v>336</v>
+      </c>
+      <c r="K2475" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2475" s="28" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="2476" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2476" s="17">
         <v>45909.342488425929</v>
       </c>
-      <c r="C2476" s="1"/>
-      <c r="D2476" s="1"/>
+      <c r="C2476">
+        <v>350835</v>
+      </c>
+      <c r="D2476">
+        <v>351791</v>
+      </c>
       <c r="E2476" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="F2476" s="2">
         <v>102.1</v>
@@ -81057,22 +81224,32 @@
       <c r="G2476" s="2">
         <v>632.04999999999995</v>
       </c>
-      <c r="H2476" s="3"/>
+      <c r="H2476" t="s">
+        <v>8</v>
+      </c>
       <c r="I2476" s="12">
         <v>45901</v>
       </c>
-      <c r="J2476" s="7"/>
-      <c r="K2476" s="7"/>
+      <c r="J2476" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2476" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2477" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2477" s="17">
         <v>45909.350023148145</v>
       </c>
-      <c r="C2477" s="1"/>
-      <c r="D2477" s="1"/>
+      <c r="C2477">
+        <v>458044</v>
+      </c>
+      <c r="D2477">
+        <v>458806</v>
+      </c>
       <c r="E2477" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>762</v>
       </c>
       <c r="F2477" s="2">
         <v>211.43</v>
@@ -81080,19 +81257,25 @@
       <c r="G2477" s="16">
         <v>1308.8</v>
       </c>
-      <c r="H2477" s="3"/>
+      <c r="H2477" t="s">
+        <v>8</v>
+      </c>
       <c r="I2477" s="12">
         <v>45901</v>
       </c>
-      <c r="J2477" s="7"/>
-      <c r="K2477" s="7"/>
+      <c r="J2477" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2477" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2478" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2478" s="17">
         <v>45909.356863425928</v>
       </c>
-      <c r="C2478" s="1"/>
-      <c r="D2478" s="1"/>
+      <c r="C2478"/>
+      <c r="D2478"/>
       <c r="E2478" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
@@ -81103,19 +81286,28 @@
       <c r="G2478" s="2">
         <v>128.22999999999999</v>
       </c>
-      <c r="H2478" s="3"/>
+      <c r="H2478" t="s">
+        <v>7</v>
+      </c>
       <c r="I2478" s="12">
         <v>45901</v>
       </c>
-      <c r="J2478" s="7"/>
-      <c r="K2478" s="7"/>
+      <c r="J2478" t="s">
+        <v>282</v>
+      </c>
+      <c r="K2478" t="s">
+        <v>206</v>
+      </c>
+      <c r="L2478" s="28" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="2479" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2479" s="17">
         <v>45909.636273148149</v>
       </c>
-      <c r="C2479" s="1"/>
-      <c r="D2479" s="1"/>
+      <c r="C2479"/>
+      <c r="D2479"/>
       <c r="E2479" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
@@ -81126,22 +81318,32 @@
       <c r="G2479" s="2">
         <v>650.22</v>
       </c>
-      <c r="H2479" s="3"/>
+      <c r="H2479" t="s">
+        <v>8</v>
+      </c>
       <c r="I2479" s="12">
         <v>45901</v>
       </c>
-      <c r="J2479" s="7"/>
-      <c r="K2479" s="7"/>
+      <c r="J2479" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2479" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="2480" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2480" s="17">
         <v>45909.738553240742</v>
       </c>
-      <c r="C2480" s="1"/>
-      <c r="D2480" s="1"/>
+      <c r="C2480">
+        <v>6210</v>
+      </c>
+      <c r="D2480">
+        <v>6449</v>
+      </c>
       <c r="E2480" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="F2480" s="2">
         <v>29.33</v>
@@ -81149,22 +81351,35 @@
       <c r="G2480" s="2">
         <v>169.54</v>
       </c>
-      <c r="H2480" s="3"/>
+      <c r="H2480" t="s">
+        <v>7</v>
+      </c>
       <c r="I2480" s="12">
         <v>45901</v>
       </c>
-      <c r="J2480" s="7"/>
-      <c r="K2480" s="7"/>
+      <c r="J2480" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2480" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2480" s="28" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="2481" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2481" s="17">
         <v>45909.771215277775</v>
       </c>
-      <c r="C2481" s="1"/>
-      <c r="D2481" s="1"/>
+      <c r="C2481">
+        <v>10815</v>
+      </c>
+      <c r="D2481">
+        <v>11268</v>
+      </c>
       <c r="E2481" s="1">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>453</v>
       </c>
       <c r="F2481" s="2">
         <v>35.08</v>
@@ -81172,12 +81387,18 @@
       <c r="G2481" s="2">
         <v>220.7</v>
       </c>
-      <c r="H2481" s="3"/>
+      <c r="H2481" t="s">
+        <v>7</v>
+      </c>
       <c r="I2481" s="12">
         <v>45901</v>
       </c>
-      <c r="J2481" s="7"/>
-      <c r="K2481" s="7"/>
+      <c r="J2481" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2481" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="2482" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2482" s="18">
@@ -81208,7 +81429,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2483" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2483" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2483" s="18"/>
       <c r="C2483" s="1"/>
       <c r="D2483" s="1"/>
@@ -81375,13 +81596,13 @@
         <v>45901</v>
       </c>
       <c r="J2488" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K2488" s="2" t="s">
         <v>199</v>
       </c>
       <c r="L2488" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2489" spans="2:12" x14ac:dyDescent="0.25">
@@ -81395,6 +81616,9 @@
       <c r="G2489" s="2">
         <v>300</v>
       </c>
+      <c r="H2489" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I2489" s="12">
         <v>45901</v>
       </c>
@@ -81429,10 +81653,10 @@
         <v>31</v>
       </c>
       <c r="K2490" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L2490" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2491" spans="2:12" x14ac:dyDescent="0.25">
@@ -81468,7 +81692,7 @@
         <v>218</v>
       </c>
       <c r="L2491" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2492" spans="2:12" x14ac:dyDescent="0.25">
@@ -81663,7 +81887,7 @@
         <v>45901</v>
       </c>
       <c r="J2497" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2497" s="2" t="s">
         <v>27</v>
@@ -81702,7 +81926,7 @@
         <v>197</v>
       </c>
       <c r="L2498" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2499" spans="2:12" x14ac:dyDescent="0.25">
@@ -81738,7 +81962,7 @@
         <v>208</v>
       </c>
       <c r="L2499" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2500" spans="2:12" x14ac:dyDescent="0.25">
@@ -81834,7 +82058,7 @@
         <v>45901</v>
       </c>
       <c r="J2502" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K2502" s="2" t="s">
         <v>29</v>
@@ -81960,13 +82184,13 @@
         <v>45901</v>
       </c>
       <c r="J2506" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K2506" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2507" spans="2:12" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2507" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2507" s="18"/>
       <c r="C2507" s="1"/>
       <c r="D2507" s="1"/>
@@ -81980,7 +82204,7 @@
       <c r="J2507" s="7"/>
       <c r="K2507" s="7"/>
     </row>
-    <row r="2508" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2508" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2508" s="18"/>
       <c r="C2508" s="1"/>
       <c r="D2508" s="1"/>
@@ -81994,7 +82218,7 @@
       <c r="J2508" s="7"/>
       <c r="K2508" s="7"/>
     </row>
-    <row r="2509" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2509" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2509" s="18"/>
       <c r="C2509" s="1"/>
       <c r="D2509" s="1"/>
@@ -82008,7 +82232,7 @@
       <c r="J2509" s="7"/>
       <c r="K2509" s="7"/>
     </row>
-    <row r="2510" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2510" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2510" s="18"/>
       <c r="C2510" s="1"/>
       <c r="D2510" s="1"/>
@@ -82148,7 +82372,7 @@
         <v>202</v>
       </c>
       <c r="L2514" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2515" spans="2:12" x14ac:dyDescent="0.25">
@@ -82178,7 +82402,7 @@
         <v>206</v>
       </c>
       <c r="L2515" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2516" spans="2:12" x14ac:dyDescent="0.25">
@@ -82247,7 +82471,7 @@
         <v>205</v>
       </c>
       <c r="L2517" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2518" spans="2:12" x14ac:dyDescent="0.25">
@@ -82277,13 +82501,13 @@
         <v>45901</v>
       </c>
       <c r="J2518" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K2518" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2518" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2519" spans="2:12" x14ac:dyDescent="0.25">
@@ -82307,7 +82531,7 @@
         <v>45901</v>
       </c>
       <c r="J2519" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2519" s="2" t="s">
         <v>39</v>
@@ -82346,7 +82570,7 @@
         <v>210</v>
       </c>
       <c r="L2520" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2521" spans="2:12" x14ac:dyDescent="0.25">
@@ -82409,13 +82633,13 @@
         <v>45901</v>
       </c>
       <c r="J2522" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K2522" s="2" t="s">
         <v>199</v>
       </c>
       <c r="L2522" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2523" spans="2:12" x14ac:dyDescent="0.25">
@@ -82448,7 +82672,7 @@
         <v>46</v>
       </c>
       <c r="K2523" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2524" spans="2:12" x14ac:dyDescent="0.25">
@@ -82481,10 +82705,10 @@
         <v>23</v>
       </c>
       <c r="K2524" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2524" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2525" spans="2:12" x14ac:dyDescent="0.25">
@@ -82514,7 +82738,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2526" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2526" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2526" s="18"/>
       <c r="C2526" s="1"/>
       <c r="D2526" s="1"/>
@@ -82528,7 +82752,7 @@
       <c r="J2526" s="7"/>
       <c r="K2526" s="7"/>
     </row>
-    <row r="2527" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2527" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2527" s="18"/>
       <c r="C2527" s="1"/>
       <c r="D2527" s="1"/>
@@ -82542,7 +82766,7 @@
       <c r="J2527" s="7"/>
       <c r="K2527" s="7"/>
     </row>
-    <row r="2528" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2528" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2528" s="18"/>
       <c r="C2528" s="1"/>
       <c r="D2528" s="1"/>
@@ -82556,7 +82780,7 @@
       <c r="J2528" s="7"/>
       <c r="K2528" s="7"/>
     </row>
-    <row r="2529" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2529" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2529" s="18"/>
       <c r="C2529" s="1"/>
       <c r="D2529" s="1"/>
@@ -82570,7 +82794,7 @@
       <c r="J2529" s="7"/>
       <c r="K2529" s="7"/>
     </row>
-    <row r="2530" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2530" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2530" s="18"/>
       <c r="C2530" s="1"/>
       <c r="D2530" s="1"/>
@@ -82584,7 +82808,7 @@
       <c r="J2530" s="7"/>
       <c r="K2530" s="7"/>
     </row>
-    <row r="2531" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2531" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2531" s="18"/>
       <c r="C2531" s="1"/>
       <c r="D2531" s="1"/>
@@ -82691,13 +82915,13 @@
         <v>45901</v>
       </c>
       <c r="J2534" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K2534" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2534" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2535" spans="2:12" x14ac:dyDescent="0.25">
@@ -82766,7 +82990,7 @@
         <v>210</v>
       </c>
       <c r="L2536" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2537" spans="2:12" x14ac:dyDescent="0.25">
@@ -82796,7 +83020,7 @@
         <v>199</v>
       </c>
       <c r="L2537" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2538" spans="2:12" x14ac:dyDescent="0.25">
@@ -82832,7 +83056,7 @@
         <v>218</v>
       </c>
       <c r="L2538" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2539" spans="2:12" x14ac:dyDescent="0.25">
@@ -82862,7 +83086,7 @@
         <v>45901</v>
       </c>
       <c r="J2539" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K2539" s="2" t="s">
         <v>65</v>
@@ -82964,10 +83188,10 @@
         <v>96</v>
       </c>
       <c r="K2542" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2543" spans="2:12" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2543" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2543" s="18"/>
       <c r="C2543" s="1"/>
       <c r="D2543" s="1"/>
@@ -82981,7 +83205,7 @@
       <c r="J2543" s="7"/>
       <c r="K2543" s="7"/>
     </row>
-    <row r="2544" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2544" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2544" s="18"/>
       <c r="C2544" s="1"/>
       <c r="D2544" s="1"/>
@@ -82995,7 +83219,7 @@
       <c r="J2544" s="7"/>
       <c r="K2544" s="7"/>
     </row>
-    <row r="2545" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2545" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2545" s="18"/>
       <c r="C2545" s="1"/>
       <c r="D2545" s="1"/>
@@ -83009,7 +83233,7 @@
       <c r="J2545" s="7"/>
       <c r="K2545" s="7"/>
     </row>
-    <row r="2546" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2546" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2546" s="18"/>
       <c r="C2546" s="1"/>
       <c r="D2546" s="1"/>
@@ -83023,7 +83247,7 @@
       <c r="J2546" s="7"/>
       <c r="K2546" s="7"/>
     </row>
-    <row r="2547" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2547" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2547" s="18"/>
       <c r="C2547" s="1"/>
       <c r="D2547" s="1"/>
@@ -83037,7 +83261,7 @@
       <c r="J2547" s="7"/>
       <c r="K2547" s="7"/>
     </row>
-    <row r="2548" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2548" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2548" s="18"/>
       <c r="C2548" s="1"/>
       <c r="D2548" s="1"/>
@@ -83078,16 +83302,16 @@
         <v>45901</v>
       </c>
       <c r="J2549" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K2549" s="2" t="s">
         <v>206</v>
       </c>
       <c r="L2549" s="28" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="2550" spans="2:12" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2550" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2550" s="17"/>
       <c r="E2550" s="1">
         <f t="shared" si="44"/>
@@ -83182,7 +83406,7 @@
         <v>45901</v>
       </c>
       <c r="J2553" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K2553" s="2" t="s">
         <v>56</v>
@@ -83245,7 +83469,7 @@
         <v>171</v>
       </c>
       <c r="K2555" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2556" spans="2:12" x14ac:dyDescent="0.25">
@@ -83275,13 +83499,13 @@
         <v>45901</v>
       </c>
       <c r="J2556" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K2556" s="2" t="s">
         <v>172</v>
       </c>
       <c r="L2556" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2557" spans="2:12" x14ac:dyDescent="0.25">
@@ -83317,7 +83541,7 @@
         <v>202</v>
       </c>
       <c r="L2557" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2558" spans="2:12" x14ac:dyDescent="0.25">
@@ -83350,13 +83574,13 @@
         <v>23</v>
       </c>
       <c r="K2558" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2558" s="29" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2559" spans="2:12" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="2559" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2559" s="18"/>
       <c r="C2559" s="1"/>
       <c r="D2559" s="1"/>
@@ -83370,7 +83594,7 @@
       <c r="J2559" s="7"/>
       <c r="K2559" s="7"/>
     </row>
-    <row r="2560" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2560" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2560" s="18"/>
       <c r="C2560" s="1"/>
       <c r="D2560" s="1"/>
@@ -83438,7 +83662,7 @@
         <v>45901</v>
       </c>
       <c r="J2562" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K2562" s="3" t="s">
         <v>69</v>
@@ -83573,7 +83797,7 @@
         <v>46</v>
       </c>
       <c r="K2566" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2567" spans="2:12" x14ac:dyDescent="0.25">
@@ -83669,7 +83893,7 @@
         <v>202</v>
       </c>
       <c r="L2569" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2570" spans="2:12" x14ac:dyDescent="0.25">
@@ -83702,10 +83926,10 @@
         <v>112</v>
       </c>
       <c r="K2570" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2570" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2571" spans="2:12" x14ac:dyDescent="0.25">
@@ -83741,7 +83965,7 @@
         <v>218</v>
       </c>
       <c r="L2571" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2572" spans="2:12" x14ac:dyDescent="0.25">
@@ -83771,7 +83995,7 @@
         <v>45901</v>
       </c>
       <c r="J2572" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K2572" s="2" t="s">
         <v>39</v>
@@ -83804,7 +84028,7 @@
         <v>45901</v>
       </c>
       <c r="J2573" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K2573" s="2" t="s">
         <v>25</v>
@@ -83903,7 +84127,7 @@
         <v>172</v>
       </c>
       <c r="L2576" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2577" spans="2:12" x14ac:dyDescent="0.25">
@@ -84035,10 +84259,10 @@
         <v>46</v>
       </c>
       <c r="K2580" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2580" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2581" spans="2:12" x14ac:dyDescent="0.25">
@@ -84068,7 +84292,7 @@
         <v>45901</v>
       </c>
       <c r="J2581" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K2581" s="2" t="s">
         <v>26</v>
@@ -84203,7 +84427,7 @@
         <v>23</v>
       </c>
       <c r="K2585" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2586" spans="2:12" x14ac:dyDescent="0.25">
@@ -84233,13 +84457,13 @@
         <v>45901</v>
       </c>
       <c r="J2586" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K2586" s="2" t="s">
         <v>218</v>
       </c>
       <c r="L2586" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2587" spans="2:12" x14ac:dyDescent="0.25">
@@ -84407,7 +84631,7 @@
         <v>208</v>
       </c>
       <c r="L2591" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2592" spans="2:12" x14ac:dyDescent="0.25">
@@ -84476,7 +84700,7 @@
         <v>210</v>
       </c>
       <c r="L2593" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2594" spans="2:12" x14ac:dyDescent="0.25">
@@ -84509,7 +84733,7 @@
         <v>23</v>
       </c>
       <c r="K2594" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2595" spans="2:12" x14ac:dyDescent="0.25">
@@ -84572,13 +84796,13 @@
         <v>45901</v>
       </c>
       <c r="J2596" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K2596" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2596" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2597" spans="2:12" x14ac:dyDescent="0.25">
@@ -84614,7 +84838,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2598" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2598" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2598" s="18"/>
       <c r="C2598" s="1"/>
       <c r="D2598" s="1"/>
@@ -84628,7 +84852,7 @@
       <c r="J2598" s="7"/>
       <c r="K2598" s="7"/>
     </row>
-    <row r="2599" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2599" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2599" s="18"/>
       <c r="C2599" s="1"/>
       <c r="D2599" s="1"/>
@@ -84642,7 +84866,7 @@
       <c r="J2599" s="7"/>
       <c r="K2599" s="7"/>
     </row>
-    <row r="2600" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2600" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2600" s="18"/>
       <c r="C2600" s="1"/>
       <c r="D2600" s="1"/>
@@ -84749,10 +84973,10 @@
         <v>45901</v>
       </c>
       <c r="K2603" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L2603" s="29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2604" spans="2:12" x14ac:dyDescent="0.25">
@@ -84782,13 +85006,13 @@
         <v>45901</v>
       </c>
       <c r="J2604" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K2604" s="2" t="s">
         <v>206</v>
       </c>
       <c r="L2604" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2605" spans="2:12" x14ac:dyDescent="0.25">
@@ -84947,10 +85171,10 @@
         <v>82</v>
       </c>
       <c r="K2609" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2610" spans="2:12" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2610" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2610" s="18"/>
       <c r="C2610" s="1"/>
       <c r="D2610" s="1"/>
@@ -84964,7 +85188,7 @@
       <c r="J2610" s="7"/>
       <c r="K2610" s="7"/>
     </row>
-    <row r="2611" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2611" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2611" s="18"/>
       <c r="C2611" s="1"/>
       <c r="D2611" s="1"/>
@@ -84978,7 +85202,7 @@
       <c r="J2611" s="7"/>
       <c r="K2611" s="7"/>
     </row>
-    <row r="2612" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2612" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2612" s="18"/>
       <c r="C2612" s="1"/>
       <c r="D2612" s="1"/>
@@ -84992,7 +85216,7 @@
       <c r="J2612" s="7"/>
       <c r="K2612" s="7"/>
     </row>
-    <row r="2613" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2613" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2613" s="18"/>
       <c r="C2613" s="1"/>
       <c r="D2613" s="1"/>
@@ -85033,13 +85257,13 @@
         <v>45901</v>
       </c>
       <c r="J2614" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K2614" s="2" t="s">
         <v>210</v>
       </c>
       <c r="L2614" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2615" spans="2:12" x14ac:dyDescent="0.25">
@@ -85069,7 +85293,7 @@
         <v>45901</v>
       </c>
       <c r="J2615" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K2615" s="2" t="s">
         <v>84</v>
@@ -85102,13 +85326,13 @@
         <v>45901</v>
       </c>
       <c r="J2616" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K2616" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2616" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2617" spans="2:12" x14ac:dyDescent="0.25">
@@ -85144,7 +85368,7 @@
         <v>206</v>
       </c>
       <c r="L2617" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2618" spans="2:12" x14ac:dyDescent="0.25">
@@ -85207,7 +85431,7 @@
         <v>199</v>
       </c>
       <c r="L2619" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2620" spans="2:12" x14ac:dyDescent="0.25">
@@ -85273,10 +85497,10 @@
         <v>102</v>
       </c>
       <c r="K2621" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2621" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2622" spans="2:12" x14ac:dyDescent="0.25">
@@ -85345,7 +85569,7 @@
         <v>172</v>
       </c>
       <c r="L2623" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2624" spans="2:12" x14ac:dyDescent="0.25">
@@ -85375,7 +85599,7 @@
         <v>45901</v>
       </c>
       <c r="J2624" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2624" s="2" t="s">
         <v>39</v>
@@ -85441,7 +85665,7 @@
         <v>45901</v>
       </c>
       <c r="J2626" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K2626" s="2" t="s">
         <v>29</v>
@@ -85477,13 +85701,13 @@
         <v>31</v>
       </c>
       <c r="K2627" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L2627" s="28" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="2628" spans="2:12" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="2628" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2628" s="18"/>
       <c r="C2628" s="1"/>
       <c r="D2628" s="1"/>
@@ -85497,7 +85721,7 @@
       <c r="J2628" s="7"/>
       <c r="K2628" s="7"/>
     </row>
-    <row r="2629" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2629" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2629" s="18"/>
       <c r="C2629" s="1"/>
       <c r="D2629" s="1"/>
@@ -85511,7 +85735,7 @@
       <c r="J2629" s="7"/>
       <c r="K2629" s="7"/>
     </row>
-    <row r="2630" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2630" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2630" s="18"/>
       <c r="C2630" s="1"/>
       <c r="D2630" s="1"/>
@@ -85525,7 +85749,7 @@
       <c r="J2630" s="7"/>
       <c r="K2630" s="7"/>
     </row>
-    <row r="2631" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2631" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2631" s="18"/>
       <c r="C2631" s="1"/>
       <c r="D2631" s="1"/>
@@ -85539,7 +85763,7 @@
       <c r="J2631" s="7"/>
       <c r="K2631" s="7"/>
     </row>
-    <row r="2632" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2632" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2632" s="18"/>
       <c r="C2632" s="1"/>
       <c r="D2632" s="1"/>
@@ -85553,7 +85777,7 @@
       <c r="J2632" s="7"/>
       <c r="K2632" s="7"/>
     </row>
-    <row r="2633" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2633" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2633" s="18"/>
       <c r="C2633" s="1"/>
       <c r="D2633" s="1"/>
@@ -85663,10 +85887,10 @@
         <v>162</v>
       </c>
       <c r="K2636" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2636" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2637" spans="2:12" x14ac:dyDescent="0.25">
@@ -85696,13 +85920,13 @@
         <v>45901</v>
       </c>
       <c r="J2637" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K2637" s="2" t="s">
         <v>208</v>
       </c>
       <c r="L2637" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2638" spans="2:12" x14ac:dyDescent="0.25">
@@ -85738,7 +85962,7 @@
         <v>199</v>
       </c>
       <c r="L2638" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2639" spans="2:12" x14ac:dyDescent="0.25">
@@ -85768,13 +85992,13 @@
         <v>45901</v>
       </c>
       <c r="J2639" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K2639" s="2" t="s">
         <v>210</v>
       </c>
       <c r="L2639" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2640" spans="2:12" x14ac:dyDescent="0.25">
@@ -85837,7 +86061,7 @@
         <v>45901</v>
       </c>
       <c r="J2641" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K2641" s="2" t="s">
         <v>27</v>
@@ -85903,7 +86127,7 @@
         <v>45901</v>
       </c>
       <c r="J2643" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K2643" s="2" t="s">
         <v>71</v>
@@ -85936,7 +86160,7 @@
         <v>45901</v>
       </c>
       <c r="J2644" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K2644" s="2" t="s">
         <v>29</v>
@@ -85975,7 +86199,7 @@
         <v>206</v>
       </c>
       <c r="L2645" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2646" spans="2:12" x14ac:dyDescent="0.25">
@@ -86074,10 +86298,10 @@
         <v>23</v>
       </c>
       <c r="K2648" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L2648" s="29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2649" spans="2:12" x14ac:dyDescent="0.25">
@@ -86107,13 +86331,13 @@
         <v>45901</v>
       </c>
       <c r="J2649" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K2649" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2650" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2650" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2650" s="18"/>
       <c r="C2650" s="1"/>
       <c r="D2650" s="1"/>
@@ -86127,7 +86351,7 @@
       <c r="J2650" s="7"/>
       <c r="K2650" s="7"/>
     </row>
-    <row r="2651" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2651" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2651" s="18"/>
       <c r="C2651" s="1"/>
       <c r="D2651" s="1"/>
@@ -86141,7 +86365,7 @@
       <c r="J2651" s="7"/>
       <c r="K2651" s="7"/>
     </row>
-    <row r="2652" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2652" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2652" s="18"/>
       <c r="C2652" s="1"/>
       <c r="D2652" s="1"/>
@@ -86155,7 +86379,7 @@
       <c r="J2652" s="7"/>
       <c r="K2652" s="7"/>
     </row>
-    <row r="2653" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2653" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2653" s="18"/>
       <c r="C2653" s="1"/>
       <c r="D2653" s="1"/>
@@ -86169,7 +86393,7 @@
       <c r="J2653" s="7"/>
       <c r="K2653" s="7"/>
     </row>
-    <row r="2654" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2654" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2654" s="18"/>
       <c r="C2654" s="1"/>
       <c r="D2654" s="1"/>
@@ -86203,7 +86427,9 @@
       <c r="G2655" s="2">
         <v>254.76</v>
       </c>
-      <c r="H2655" s="3"/>
+      <c r="H2655" t="s">
+        <v>7</v>
+      </c>
       <c r="I2655" s="12">
         <v>45901</v>
       </c>
@@ -86234,7 +86460,9 @@
       <c r="G2656" s="2">
         <v>239.48</v>
       </c>
-      <c r="H2656" s="3"/>
+      <c r="H2656" t="s">
+        <v>7</v>
+      </c>
       <c r="I2656" s="12">
         <v>45901</v>
       </c>
@@ -86242,7 +86470,7 @@
         <v>46</v>
       </c>
       <c r="K2656" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2657" spans="2:12" x14ac:dyDescent="0.25">
@@ -86265,7 +86493,9 @@
       <c r="G2657" s="2">
         <v>399.55</v>
       </c>
-      <c r="H2657" s="3"/>
+      <c r="H2657" t="s">
+        <v>8</v>
+      </c>
       <c r="I2657" s="12">
         <v>45901</v>
       </c>
@@ -86296,7 +86526,9 @@
       <c r="G2658" s="16">
         <v>1050</v>
       </c>
-      <c r="H2658" s="3"/>
+      <c r="H2658" t="s">
+        <v>8</v>
+      </c>
       <c r="I2658" s="12">
         <v>45901</v>
       </c>
@@ -86327,12 +86559,14 @@
       <c r="G2659" s="2">
         <v>148.83000000000001</v>
       </c>
-      <c r="H2659" s="3"/>
+      <c r="H2659" t="s">
+        <v>7</v>
+      </c>
       <c r="I2659" s="12">
         <v>45901</v>
       </c>
       <c r="J2659" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="K2659" s="2" t="s">
         <v>39</v>
@@ -86358,12 +86592,14 @@
       <c r="G2660" s="16">
         <v>1145</v>
       </c>
-      <c r="H2660" s="3"/>
+      <c r="H2660" t="s">
+        <v>8</v>
+      </c>
       <c r="I2660" s="12">
         <v>45901</v>
       </c>
       <c r="J2660" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K2660" s="2" t="s">
         <v>34</v>
@@ -86389,7 +86625,9 @@
       <c r="G2661" s="16">
         <v>1126.99</v>
       </c>
-      <c r="H2661" s="3"/>
+      <c r="H2661" t="s">
+        <v>8</v>
+      </c>
       <c r="I2661" s="12">
         <v>45901</v>
       </c>
@@ -86420,7 +86658,9 @@
       <c r="G2662" s="2">
         <v>800.07</v>
       </c>
-      <c r="H2662" s="3"/>
+      <c r="H2662" t="s">
+        <v>8</v>
+      </c>
       <c r="I2662" s="12">
         <v>45901</v>
       </c>
@@ -86451,7 +86691,9 @@
       <c r="G2663" s="2">
         <v>974.21</v>
       </c>
-      <c r="H2663" s="3"/>
+      <c r="H2663" t="s">
+        <v>8</v>
+      </c>
       <c r="I2663" s="12">
         <v>45901</v>
       </c>
@@ -86482,7 +86724,9 @@
       <c r="G2664" s="2">
         <v>995.05</v>
       </c>
-      <c r="H2664" s="3"/>
+      <c r="H2664" t="s">
+        <v>8</v>
+      </c>
       <c r="I2664" s="12">
         <v>45901</v>
       </c>
@@ -86513,7 +86757,9 @@
       <c r="G2665" s="2">
         <v>280</v>
       </c>
-      <c r="H2665" s="3"/>
+      <c r="H2665" t="s">
+        <v>7</v>
+      </c>
       <c r="I2665" s="12">
         <v>45901</v>
       </c>
@@ -86524,10 +86770,10 @@
         <v>202</v>
       </c>
       <c r="L2665" s="28" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2666" spans="2:12" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2666" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2666" s="18"/>
       <c r="C2666" s="1"/>
       <c r="D2666" s="1"/>
@@ -86541,7 +86787,7 @@
       <c r="J2666" s="7"/>
       <c r="K2666" s="7"/>
     </row>
-    <row r="2667" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2667" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2667" s="18"/>
       <c r="C2667" s="1"/>
       <c r="D2667" s="1"/>
@@ -86555,7 +86801,7 @@
       <c r="J2667" s="7"/>
       <c r="K2667" s="7"/>
     </row>
-    <row r="2668" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2668" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2668" s="18"/>
       <c r="C2668" s="1"/>
       <c r="D2668" s="1"/>
@@ -86569,7 +86815,7 @@
       <c r="J2668" s="7"/>
       <c r="K2668" s="7"/>
     </row>
-    <row r="2669" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2669" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2669" s="18"/>
       <c r="C2669" s="1"/>
       <c r="D2669" s="1"/>
@@ -86583,7 +86829,7 @@
       <c r="J2669" s="7"/>
       <c r="K2669" s="7"/>
     </row>
-    <row r="2670" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2670" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2670" s="18"/>
       <c r="C2670" s="1"/>
       <c r="D2670" s="1"/>
@@ -86795,7 +87041,7 @@
         <v>210</v>
       </c>
       <c r="L2676" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2677" spans="2:12" x14ac:dyDescent="0.25">
@@ -86825,7 +87071,7 @@
         <v>45901</v>
       </c>
       <c r="J2677" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K2677" s="2" t="s">
         <v>25</v>
@@ -86894,10 +87140,10 @@
         <v>23</v>
       </c>
       <c r="K2679" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L2679" s="28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2680" spans="2:12" x14ac:dyDescent="0.25">
@@ -86933,7 +87179,7 @@
         <v>197</v>
       </c>
       <c r="L2680" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2681" spans="2:12" x14ac:dyDescent="0.25">
@@ -86963,13 +87209,13 @@
         <v>45901</v>
       </c>
       <c r="J2681" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K2681" s="2" t="s">
         <v>205</v>
       </c>
       <c r="L2681" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2682" spans="2:12" x14ac:dyDescent="0.25">
@@ -87005,7 +87251,7 @@
         <v>172</v>
       </c>
       <c r="L2682" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2683" spans="2:12" x14ac:dyDescent="0.25">
@@ -87041,7 +87287,7 @@
         <v>218</v>
       </c>
       <c r="L2683" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2684" spans="2:12" x14ac:dyDescent="0.25">
@@ -87065,7 +87311,7 @@
         <v>45901</v>
       </c>
       <c r="J2684" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K2684" s="2" t="s">
         <v>80</v>
@@ -87230,7 +87476,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2690" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2690" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2690" s="18"/>
       <c r="C2690" s="1"/>
       <c r="D2690" s="1"/>
@@ -87242,7 +87488,7 @@
       <c r="G2690" s="10"/>
       <c r="K2690" s="7"/>
     </row>
-    <row r="2691" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2691" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2691" s="18"/>
       <c r="C2691" s="1"/>
       <c r="D2691" s="1"/>
@@ -87254,7 +87500,7 @@
       <c r="G2691" s="10"/>
       <c r="K2691" s="7"/>
     </row>
-    <row r="2692" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2692" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2692" s="18"/>
       <c r="C2692" s="1"/>
       <c r="D2692" s="1"/>
@@ -87266,7 +87512,7 @@
       <c r="G2692" s="10"/>
       <c r="K2692" s="7"/>
     </row>
-    <row r="2693" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2693" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2693" s="18"/>
       <c r="C2693" s="1"/>
       <c r="D2693" s="1"/>
@@ -87278,7 +87524,7 @@
       <c r="G2693" s="10"/>
       <c r="K2693" s="7"/>
     </row>
-    <row r="2694" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2694" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2694" s="18"/>
       <c r="C2694" s="1"/>
       <c r="D2694" s="1"/>
@@ -87290,7 +87536,7 @@
       <c r="G2694" s="10"/>
       <c r="K2694" s="7"/>
     </row>
-    <row r="2695" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2695" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2695" s="18"/>
       <c r="C2695" s="1"/>
       <c r="D2695" s="1"/>
@@ -87302,7 +87548,7 @@
       <c r="G2695" s="10"/>
       <c r="K2695" s="7"/>
     </row>
-    <row r="2696" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2696" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2696" s="18"/>
       <c r="C2696" s="1"/>
       <c r="D2696" s="1"/>
@@ -87314,7 +87560,7 @@
       <c r="G2696" s="10"/>
       <c r="K2696" s="7"/>
     </row>
-    <row r="2697" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2697" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2697" s="18"/>
       <c r="C2697" s="1"/>
       <c r="D2697" s="1"/>
@@ -87326,7 +87572,7 @@
       <c r="G2697" s="10"/>
       <c r="K2697" s="7"/>
     </row>
-    <row r="2698" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2698" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2698" s="18"/>
       <c r="C2698" s="1"/>
       <c r="D2698" s="1"/>
@@ -87338,7 +87584,7 @@
       <c r="G2698" s="10"/>
       <c r="K2698" s="7"/>
     </row>
-    <row r="2699" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2699" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2699" s="18"/>
       <c r="C2699" s="1"/>
       <c r="D2699" s="1"/>
@@ -87350,7 +87596,7 @@
       <c r="G2699" s="10"/>
       <c r="K2699" s="7"/>
     </row>
-    <row r="2700" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2700" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2700" s="18"/>
       <c r="C2700" s="1"/>
       <c r="D2700" s="1"/>
@@ -87362,7 +87608,7 @@
       <c r="G2700" s="10"/>
       <c r="K2700" s="7"/>
     </row>
-    <row r="2701" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2701" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2701" s="18"/>
       <c r="C2701" s="1"/>
       <c r="D2701" s="1"/>
@@ -87374,7 +87620,7 @@
       <c r="G2701" s="10"/>
       <c r="K2701" s="7"/>
     </row>
-    <row r="2702" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2702" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2702" s="18"/>
       <c r="C2702" s="1"/>
       <c r="D2702" s="1"/>
@@ -87386,7 +87632,7 @@
       <c r="G2702" s="10"/>
       <c r="K2702" s="7"/>
     </row>
-    <row r="2703" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2703" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2703" s="18"/>
       <c r="C2703" s="1"/>
       <c r="D2703" s="1"/>
@@ -87398,7 +87644,7 @@
       <c r="G2703" s="10"/>
       <c r="K2703" s="7"/>
     </row>
-    <row r="2704" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2704" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2704" s="18"/>
       <c r="C2704" s="1"/>
       <c r="D2704" s="1"/>
@@ -87410,7 +87656,7 @@
       <c r="G2704" s="10"/>
       <c r="K2704" s="7"/>
     </row>
-    <row r="2705" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2705" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2705" s="18"/>
       <c r="C2705" s="1"/>
       <c r="D2705" s="1"/>
@@ -87422,7 +87668,7 @@
       <c r="G2705" s="10"/>
       <c r="K2705" s="7"/>
     </row>
-    <row r="2706" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2706" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2706" s="18"/>
       <c r="C2706" s="1"/>
       <c r="D2706" s="1"/>
@@ -87434,7 +87680,7 @@
       <c r="G2706" s="10"/>
       <c r="K2706" s="7"/>
     </row>
-    <row r="2707" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2707" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2707" s="18"/>
       <c r="C2707" s="1"/>
       <c r="D2707" s="1"/>
@@ -87446,7 +87692,7 @@
       <c r="G2707" s="10"/>
       <c r="K2707" s="7"/>
     </row>
-    <row r="2708" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2708" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2708" s="18"/>
       <c r="C2708" s="1"/>
       <c r="D2708" s="1"/>
@@ -87458,7 +87704,7 @@
       <c r="G2708" s="10"/>
       <c r="K2708" s="7"/>
     </row>
-    <row r="2709" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2709" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2709" s="18"/>
       <c r="C2709" s="1"/>
       <c r="D2709" s="1"/>
@@ -87470,7 +87716,7 @@
       <c r="G2709" s="10"/>
       <c r="K2709" s="7"/>
     </row>
-    <row r="2710" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2710" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2710" s="18"/>
       <c r="C2710" s="1"/>
       <c r="D2710" s="1"/>
@@ -87482,7 +87728,7 @@
       <c r="G2710" s="10"/>
       <c r="K2710" s="7"/>
     </row>
-    <row r="2711" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2711" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2711" s="18"/>
       <c r="C2711" s="1"/>
       <c r="D2711" s="1"/>
@@ -87494,7 +87740,7 @@
       <c r="G2711" s="10"/>
       <c r="K2711" s="7"/>
     </row>
-    <row r="2712" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2712" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2712" s="18"/>
       <c r="C2712" s="1"/>
       <c r="D2712" s="1"/>
@@ -87506,7 +87752,7 @@
       <c r="G2712" s="10"/>
       <c r="K2712" s="7"/>
     </row>
-    <row r="2713" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2713" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2713" s="18"/>
       <c r="C2713" s="1"/>
       <c r="D2713" s="1"/>
@@ -87518,7 +87764,7 @@
       <c r="G2713" s="10"/>
       <c r="K2713" s="7"/>
     </row>
-    <row r="2714" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2714" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2714" s="18"/>
       <c r="C2714" s="1"/>
       <c r="D2714" s="1"/>
@@ -87530,7 +87776,7 @@
       <c r="G2714" s="10"/>
       <c r="K2714" s="7"/>
     </row>
-    <row r="2715" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2715" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2715" s="18"/>
       <c r="C2715" s="1"/>
       <c r="D2715" s="1"/>
@@ -87542,7 +87788,7 @@
       <c r="G2715" s="10"/>
       <c r="K2715" s="7"/>
     </row>
-    <row r="2716" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2716" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2716" s="18"/>
       <c r="C2716" s="1"/>
       <c r="D2716" s="1"/>
@@ -87554,7 +87800,7 @@
       <c r="G2716" s="10"/>
       <c r="K2716" s="7"/>
     </row>
-    <row r="2717" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2717" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2717" s="18"/>
       <c r="C2717" s="1"/>
       <c r="D2717" s="1"/>
@@ -87566,7 +87812,7 @@
       <c r="G2717" s="10"/>
       <c r="K2717" s="7"/>
     </row>
-    <row r="2718" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2718" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2718" s="18"/>
       <c r="C2718" s="1"/>
       <c r="D2718" s="1"/>
@@ -87578,7 +87824,7 @@
       <c r="G2718" s="10"/>
       <c r="K2718" s="7"/>
     </row>
-    <row r="2719" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2719" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2719" s="18"/>
       <c r="C2719" s="1"/>
       <c r="D2719" s="1"/>
@@ -87590,7 +87836,7 @@
       <c r="G2719" s="10"/>
       <c r="K2719" s="7"/>
     </row>
-    <row r="2720" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2720" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2720" s="18"/>
       <c r="C2720" s="1"/>
       <c r="D2720" s="1"/>
@@ -87602,7 +87848,7 @@
       <c r="G2720" s="10"/>
       <c r="K2720" s="7"/>
     </row>
-    <row r="2721" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2721" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2721" s="18"/>
       <c r="C2721" s="1"/>
       <c r="D2721" s="1"/>
@@ -87614,7 +87860,7 @@
       <c r="G2721" s="10"/>
       <c r="K2721" s="7"/>
     </row>
-    <row r="2722" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2722" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2722" s="18"/>
       <c r="C2722" s="1"/>
       <c r="D2722" s="1"/>
@@ -87626,7 +87872,7 @@
       <c r="G2722" s="10"/>
       <c r="K2722" s="7"/>
     </row>
-    <row r="2723" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2723" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2723" s="18"/>
       <c r="C2723" s="1"/>
       <c r="D2723" s="1"/>
@@ -87638,7 +87884,7 @@
       <c r="G2723" s="10"/>
       <c r="K2723" s="7"/>
     </row>
-    <row r="2724" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2724" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2724" s="18"/>
       <c r="C2724" s="1"/>
       <c r="D2724" s="1"/>
@@ -87650,7 +87896,7 @@
       <c r="G2724" s="10"/>
       <c r="K2724" s="7"/>
     </row>
-    <row r="2725" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2725" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2725" s="18"/>
       <c r="C2725" s="1"/>
       <c r="D2725" s="1"/>
@@ -87662,7 +87908,7 @@
       <c r="G2725" s="10"/>
       <c r="K2725" s="7"/>
     </row>
-    <row r="2726" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2726" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2726" s="18"/>
       <c r="C2726" s="1"/>
       <c r="D2726" s="1"/>
@@ -87674,7 +87920,7 @@
       <c r="G2726" s="10"/>
       <c r="K2726" s="7"/>
     </row>
-    <row r="2727" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2727" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2727" s="18"/>
       <c r="C2727" s="1"/>
       <c r="D2727" s="1"/>
@@ -87686,7 +87932,7 @@
       <c r="G2727" s="10"/>
       <c r="K2727" s="7"/>
     </row>
-    <row r="2728" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2728" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2728" s="18"/>
       <c r="C2728" s="1"/>
       <c r="D2728" s="1"/>
@@ -87698,7 +87944,7 @@
       <c r="G2728" s="10"/>
       <c r="K2728" s="7"/>
     </row>
-    <row r="2729" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2729" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2729" s="18"/>
       <c r="C2729" s="1"/>
       <c r="D2729" s="1"/>
@@ -87710,7 +87956,7 @@
       <c r="G2729" s="10"/>
       <c r="K2729" s="7"/>
     </row>
-    <row r="2730" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2730" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2730" s="18"/>
       <c r="C2730" s="1"/>
       <c r="D2730" s="1"/>
@@ -87722,7 +87968,7 @@
       <c r="G2730" s="10"/>
       <c r="K2730" s="7"/>
     </row>
-    <row r="2731" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2731" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2731" s="18"/>
       <c r="C2731" s="1"/>
       <c r="D2731" s="1"/>
@@ -87734,7 +87980,7 @@
       <c r="G2731" s="10"/>
       <c r="K2731" s="7"/>
     </row>
-    <row r="2732" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2732" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2732" s="18"/>
       <c r="C2732" s="1"/>
       <c r="D2732" s="1"/>
@@ -87746,7 +87992,7 @@
       <c r="G2732" s="10"/>
       <c r="K2732" s="7"/>
     </row>
-    <row r="2733" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2733" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2733" s="18"/>
       <c r="C2733" s="1"/>
       <c r="D2733" s="1"/>
@@ -87758,7 +88004,7 @@
       <c r="G2733" s="10"/>
       <c r="K2733" s="7"/>
     </row>
-    <row r="2734" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2734" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2734" s="18"/>
       <c r="C2734" s="1"/>
       <c r="D2734" s="1"/>
@@ -87770,7 +88016,7 @@
       <c r="G2734" s="10"/>
       <c r="K2734" s="7"/>
     </row>
-    <row r="2735" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2735" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2735" s="18"/>
       <c r="C2735" s="1"/>
       <c r="D2735" s="1"/>
@@ -87782,7 +88028,7 @@
       <c r="G2735" s="10"/>
       <c r="K2735" s="7"/>
     </row>
-    <row r="2736" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2736" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2736" s="18"/>
       <c r="C2736" s="1"/>
       <c r="D2736" s="1"/>
@@ -87794,7 +88040,7 @@
       <c r="G2736" s="10"/>
       <c r="K2736" s="7"/>
     </row>
-    <row r="2737" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2737" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2737" s="18"/>
       <c r="C2737" s="1"/>
       <c r="D2737" s="1"/>
@@ -87806,7 +88052,7 @@
       <c r="G2737" s="10"/>
       <c r="K2737" s="7"/>
     </row>
-    <row r="2738" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2738" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2738" s="18"/>
       <c r="C2738" s="1"/>
       <c r="D2738" s="1"/>
@@ -87818,7 +88064,7 @@
       <c r="G2738" s="10"/>
       <c r="K2738" s="7"/>
     </row>
-    <row r="2739" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2739" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2739" s="18"/>
       <c r="C2739" s="1"/>
       <c r="D2739" s="1"/>
@@ -87830,7 +88076,7 @@
       <c r="G2739" s="10"/>
       <c r="K2739" s="7"/>
     </row>
-    <row r="2740" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2740" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2740" s="18"/>
       <c r="C2740" s="1"/>
       <c r="D2740" s="1"/>
@@ -87842,7 +88088,7 @@
       <c r="G2740" s="10"/>
       <c r="K2740" s="7"/>
     </row>
-    <row r="2741" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2741" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2741" s="18"/>
       <c r="C2741" s="1"/>
       <c r="D2741" s="1"/>
@@ -87854,7 +88100,7 @@
       <c r="G2741" s="10"/>
       <c r="K2741" s="7"/>
     </row>
-    <row r="2742" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2742" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2742" s="18"/>
       <c r="C2742" s="1"/>
       <c r="D2742" s="1"/>
@@ -87866,7 +88112,7 @@
       <c r="G2742" s="10"/>
       <c r="K2742" s="7"/>
     </row>
-    <row r="2743" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2743" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2743" s="18"/>
       <c r="C2743" s="1"/>
       <c r="D2743" s="1"/>
@@ -87878,7 +88124,7 @@
       <c r="G2743" s="10"/>
       <c r="K2743" s="7"/>
     </row>
-    <row r="2744" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2744" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2744" s="18"/>
       <c r="C2744" s="1"/>
       <c r="D2744" s="1"/>
@@ -87890,7 +88136,7 @@
       <c r="G2744" s="10"/>
       <c r="K2744" s="7"/>
     </row>
-    <row r="2745" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2745" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2745" s="18"/>
       <c r="C2745" s="1"/>
       <c r="D2745" s="1"/>
@@ -87902,7 +88148,7 @@
       <c r="G2745" s="10"/>
       <c r="K2745" s="7"/>
     </row>
-    <row r="2746" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2746" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2746" s="18"/>
       <c r="C2746" s="1"/>
       <c r="D2746" s="1"/>
@@ -87914,7 +88160,7 @@
       <c r="G2746" s="10"/>
       <c r="K2746" s="7"/>
     </row>
-    <row r="2747" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2747" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2747" s="18"/>
       <c r="C2747" s="1"/>
       <c r="D2747" s="1"/>
@@ -87926,7 +88172,7 @@
       <c r="G2747" s="10"/>
       <c r="K2747" s="7"/>
     </row>
-    <row r="2748" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2748" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2748" s="18"/>
       <c r="C2748" s="1"/>
       <c r="D2748" s="1"/>
@@ -87938,7 +88184,7 @@
       <c r="G2748" s="10"/>
       <c r="K2748" s="7"/>
     </row>
-    <row r="2749" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2749" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2749" s="18"/>
       <c r="C2749" s="1"/>
       <c r="D2749" s="1"/>
@@ -87950,7 +88196,7 @@
       <c r="G2749" s="10"/>
       <c r="K2749" s="7"/>
     </row>
-    <row r="2750" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2750" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2750" s="18"/>
       <c r="C2750" s="1"/>
       <c r="D2750" s="1"/>
@@ -87962,7 +88208,7 @@
       <c r="G2750" s="10"/>
       <c r="K2750" s="7"/>
     </row>
-    <row r="2751" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2751" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2751" s="18"/>
       <c r="C2751" s="1"/>
       <c r="D2751" s="1"/>
@@ -87974,7 +88220,7 @@
       <c r="G2751" s="10"/>
       <c r="K2751" s="7"/>
     </row>
-    <row r="2752" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2752" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2752" s="18"/>
       <c r="C2752" s="1"/>
       <c r="D2752" s="1"/>
@@ -87986,7 +88232,7 @@
       <c r="G2752" s="10"/>
       <c r="K2752" s="7"/>
     </row>
-    <row r="2753" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2753" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2753" s="18"/>
       <c r="C2753" s="1"/>
       <c r="D2753" s="1"/>
@@ -87998,7 +88244,7 @@
       <c r="G2753" s="10"/>
       <c r="K2753" s="7"/>
     </row>
-    <row r="2754" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2754" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2754" s="18"/>
       <c r="C2754" s="1"/>
       <c r="D2754" s="1"/>
@@ -88010,7 +88256,7 @@
       <c r="G2754" s="10"/>
       <c r="K2754" s="7"/>
     </row>
-    <row r="2755" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2755" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2755" s="18"/>
       <c r="C2755" s="1"/>
       <c r="D2755" s="1"/>
@@ -88022,7 +88268,7 @@
       <c r="G2755" s="10"/>
       <c r="K2755" s="7"/>
     </row>
-    <row r="2756" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2756" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2756" s="18"/>
       <c r="C2756" s="1"/>
       <c r="D2756" s="1"/>
@@ -88034,7 +88280,7 @@
       <c r="G2756" s="10"/>
       <c r="K2756" s="7"/>
     </row>
-    <row r="2757" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2757" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2757" s="18"/>
       <c r="C2757" s="1"/>
       <c r="D2757" s="1"/>
@@ -88046,7 +88292,7 @@
       <c r="G2757" s="10"/>
       <c r="K2757" s="7"/>
     </row>
-    <row r="2758" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2758" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2758" s="18"/>
       <c r="C2758" s="1"/>
       <c r="D2758" s="1"/>
@@ -88058,7 +88304,7 @@
       <c r="G2758" s="10"/>
       <c r="K2758" s="7"/>
     </row>
-    <row r="2759" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2759" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2759" s="18"/>
       <c r="C2759" s="1"/>
       <c r="D2759" s="1"/>
@@ -88070,7 +88316,7 @@
       <c r="G2759" s="10"/>
       <c r="K2759" s="7"/>
     </row>
-    <row r="2760" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2760" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2760" s="18"/>
       <c r="C2760" s="1"/>
       <c r="D2760" s="1"/>
@@ -88082,7 +88328,7 @@
       <c r="G2760" s="10"/>
       <c r="K2760" s="7"/>
     </row>
-    <row r="2761" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2761" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2761" s="18"/>
       <c r="C2761" s="1"/>
       <c r="D2761" s="1"/>
@@ -88094,7 +88340,7 @@
       <c r="G2761" s="10"/>
       <c r="K2761" s="7"/>
     </row>
-    <row r="2762" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2762" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2762" s="18"/>
       <c r="C2762" s="1"/>
       <c r="D2762" s="1"/>
@@ -88106,7 +88352,7 @@
       <c r="G2762" s="10"/>
       <c r="K2762" s="7"/>
     </row>
-    <row r="2763" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2763" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2763" s="18"/>
       <c r="C2763" s="1"/>
       <c r="D2763" s="1"/>
@@ -88118,7 +88364,7 @@
       <c r="G2763" s="10"/>
       <c r="K2763" s="7"/>
     </row>
-    <row r="2764" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2764" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2764" s="18"/>
       <c r="C2764" s="1"/>
       <c r="D2764" s="1"/>
@@ -88130,7 +88376,7 @@
       <c r="G2764" s="10"/>
       <c r="K2764" s="7"/>
     </row>
-    <row r="2765" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2765" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2765" s="18"/>
       <c r="C2765" s="1"/>
       <c r="D2765" s="1"/>
@@ -88142,7 +88388,7 @@
       <c r="G2765" s="10"/>
       <c r="K2765" s="7"/>
     </row>
-    <row r="2766" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2766" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2766" s="18"/>
       <c r="C2766" s="1"/>
       <c r="D2766" s="1"/>
@@ -88154,7 +88400,7 @@
       <c r="G2766" s="10"/>
       <c r="K2766" s="7"/>
     </row>
-    <row r="2767" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2767" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2767" s="18"/>
       <c r="C2767" s="1"/>
       <c r="D2767" s="1"/>
@@ -88166,7 +88412,7 @@
       <c r="G2767" s="10"/>
       <c r="K2767" s="7"/>
     </row>
-    <row r="2768" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2768" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2768" s="18"/>
       <c r="C2768" s="1"/>
       <c r="D2768" s="1"/>
@@ -88178,7 +88424,7 @@
       <c r="G2768" s="10"/>
       <c r="K2768" s="7"/>
     </row>
-    <row r="2769" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2769" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2769" s="18"/>
       <c r="C2769" s="1"/>
       <c r="D2769" s="1"/>
@@ -88190,7 +88436,7 @@
       <c r="G2769" s="10"/>
       <c r="K2769" s="7"/>
     </row>
-    <row r="2770" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2770" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2770" s="18"/>
       <c r="C2770" s="1"/>
       <c r="D2770" s="1"/>
@@ -88202,7 +88448,7 @@
       <c r="G2770" s="10"/>
       <c r="K2770" s="7"/>
     </row>
-    <row r="2771" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2771" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2771" s="18"/>
       <c r="C2771" s="1"/>
       <c r="D2771" s="1"/>
@@ -88214,7 +88460,7 @@
       <c r="G2771" s="10"/>
       <c r="K2771" s="7"/>
     </row>
-    <row r="2772" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2772" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2772" s="18"/>
       <c r="C2772" s="1"/>
       <c r="D2772" s="1"/>
@@ -88226,7 +88472,7 @@
       <c r="G2772" s="10"/>
       <c r="K2772" s="7"/>
     </row>
-    <row r="2773" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2773" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2773" s="18"/>
       <c r="C2773" s="1"/>
       <c r="D2773" s="1"/>
@@ -88238,7 +88484,7 @@
       <c r="G2773" s="10"/>
       <c r="K2773" s="7"/>
     </row>
-    <row r="2774" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2774" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2774" s="18"/>
       <c r="C2774" s="1"/>
       <c r="D2774" s="1"/>
@@ -88250,7 +88496,7 @@
       <c r="G2774" s="10"/>
       <c r="K2774" s="7"/>
     </row>
-    <row r="2775" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2775" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2775" s="18"/>
       <c r="C2775" s="1"/>
       <c r="D2775" s="1"/>
@@ -88262,7 +88508,7 @@
       <c r="G2775" s="10"/>
       <c r="K2775" s="7"/>
     </row>
-    <row r="2776" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2776" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2776" s="18"/>
       <c r="C2776" s="1"/>
       <c r="D2776" s="1"/>
@@ -88274,7 +88520,7 @@
       <c r="G2776" s="10"/>
       <c r="K2776" s="7"/>
     </row>
-    <row r="2777" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2777" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2777" s="18"/>
       <c r="C2777" s="1"/>
       <c r="D2777" s="1"/>
@@ -88286,7 +88532,7 @@
       <c r="G2777" s="10"/>
       <c r="K2777" s="7"/>
     </row>
-    <row r="2778" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2778" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2778" s="18"/>
       <c r="C2778" s="1"/>
       <c r="D2778" s="1"/>
@@ -88298,7 +88544,7 @@
       <c r="G2778" s="10"/>
       <c r="K2778" s="7"/>
     </row>
-    <row r="2779" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2779" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2779" s="18"/>
       <c r="C2779" s="1"/>
       <c r="D2779" s="1"/>
@@ -88310,7 +88556,7 @@
       <c r="G2779" s="10"/>
       <c r="K2779" s="7"/>
     </row>
-    <row r="2780" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2780" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2780" s="18"/>
       <c r="C2780" s="1"/>
       <c r="D2780" s="1"/>
@@ -88322,7 +88568,7 @@
       <c r="G2780" s="10"/>
       <c r="K2780" s="7"/>
     </row>
-    <row r="2781" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2781" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2781" s="18"/>
       <c r="C2781" s="1"/>
       <c r="D2781" s="1"/>
@@ -88334,7 +88580,7 @@
       <c r="G2781" s="10"/>
       <c r="K2781" s="7"/>
     </row>
-    <row r="2782" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2782" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2782" s="18"/>
       <c r="C2782" s="1"/>
       <c r="D2782" s="1"/>
@@ -88346,7 +88592,7 @@
       <c r="G2782" s="10"/>
       <c r="K2782" s="7"/>
     </row>
-    <row r="2783" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2783" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2783" s="18"/>
       <c r="C2783" s="1"/>
       <c r="D2783" s="1"/>
@@ -88358,7 +88604,7 @@
       <c r="G2783" s="10"/>
       <c r="K2783" s="7"/>
     </row>
-    <row r="2784" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2784" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2784" s="18"/>
       <c r="C2784" s="1"/>
       <c r="D2784" s="1"/>
@@ -88370,7 +88616,7 @@
       <c r="G2784" s="10"/>
       <c r="K2784" s="7"/>
     </row>
-    <row r="2785" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2785" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2785" s="18"/>
       <c r="C2785" s="1"/>
       <c r="D2785" s="1"/>
@@ -88382,7 +88628,7 @@
       <c r="G2785" s="10"/>
       <c r="K2785" s="7"/>
     </row>
-    <row r="2786" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2786" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2786" s="18"/>
       <c r="C2786" s="1"/>
       <c r="D2786" s="1"/>
@@ -88394,7 +88640,7 @@
       <c r="G2786" s="10"/>
       <c r="K2786" s="7"/>
     </row>
-    <row r="2787" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2787" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2787" s="18"/>
       <c r="C2787" s="1"/>
       <c r="D2787" s="1"/>
@@ -88406,7 +88652,7 @@
       <c r="G2787" s="10"/>
       <c r="K2787" s="7"/>
     </row>
-    <row r="2788" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2788" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2788" s="18"/>
       <c r="C2788" s="1"/>
       <c r="D2788" s="1"/>
@@ -88418,7 +88664,7 @@
       <c r="G2788" s="10"/>
       <c r="K2788" s="7"/>
     </row>
-    <row r="2789" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2789" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2789" s="18"/>
       <c r="C2789" s="1"/>
       <c r="D2789" s="1"/>
@@ -88430,7 +88676,7 @@
       <c r="G2789" s="10"/>
       <c r="K2789" s="7"/>
     </row>
-    <row r="2790" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2790" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2790" s="18"/>
       <c r="C2790" s="1"/>
       <c r="D2790" s="1"/>
@@ -88442,7 +88688,7 @@
       <c r="G2790" s="10"/>
       <c r="K2790" s="7"/>
     </row>
-    <row r="2791" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2791" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2791" s="18"/>
       <c r="C2791" s="1"/>
       <c r="D2791" s="1"/>
@@ -88454,7 +88700,7 @@
       <c r="G2791" s="10"/>
       <c r="K2791" s="7"/>
     </row>
-    <row r="2792" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2792" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2792" s="18"/>
       <c r="C2792" s="1"/>
       <c r="D2792" s="1"/>
@@ -88466,7 +88712,7 @@
       <c r="G2792" s="10"/>
       <c r="K2792" s="7"/>
     </row>
-    <row r="2793" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2793" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2793" s="18"/>
       <c r="C2793" s="1"/>
       <c r="D2793" s="1"/>
@@ -88478,7 +88724,7 @@
       <c r="G2793" s="10"/>
       <c r="K2793" s="7"/>
     </row>
-    <row r="2794" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2794" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2794" s="18"/>
       <c r="C2794" s="1"/>
       <c r="D2794" s="1"/>
@@ -88490,7 +88736,7 @@
       <c r="G2794" s="10"/>
       <c r="K2794" s="7"/>
     </row>
-    <row r="2795" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2795" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2795" s="18"/>
       <c r="C2795" s="1"/>
       <c r="D2795" s="1"/>
@@ -88502,7 +88748,7 @@
       <c r="G2795" s="10"/>
       <c r="K2795" s="7"/>
     </row>
-    <row r="2796" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2796" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2796" s="18"/>
       <c r="C2796" s="1"/>
       <c r="D2796" s="1"/>
@@ -88514,7 +88760,7 @@
       <c r="G2796" s="10"/>
       <c r="K2796" s="7"/>
     </row>
-    <row r="2797" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2797" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2797" s="18"/>
       <c r="C2797" s="1"/>
       <c r="D2797" s="1"/>
@@ -88526,7 +88772,7 @@
       <c r="G2797" s="10"/>
       <c r="K2797" s="7"/>
     </row>
-    <row r="2798" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2798" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2798" s="18"/>
       <c r="C2798" s="1"/>
       <c r="D2798" s="1"/>
@@ -88538,7 +88784,7 @@
       <c r="G2798" s="10"/>
       <c r="K2798" s="7"/>
     </row>
-    <row r="2799" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2799" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2799" s="18"/>
       <c r="C2799" s="1"/>
       <c r="D2799" s="1"/>
@@ -88550,7 +88796,7 @@
       <c r="G2799" s="10"/>
       <c r="K2799" s="7"/>
     </row>
-    <row r="2800" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2800" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2800" s="18"/>
       <c r="C2800" s="1"/>
       <c r="D2800" s="1"/>
@@ -88562,7 +88808,7 @@
       <c r="G2800" s="10"/>
       <c r="K2800" s="7"/>
     </row>
-    <row r="2801" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2801" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2801" s="18"/>
       <c r="C2801" s="1"/>
       <c r="D2801" s="1"/>
@@ -88574,7 +88820,7 @@
       <c r="G2801" s="10"/>
       <c r="K2801" s="7"/>
     </row>
-    <row r="2802" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2802" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2802" s="18"/>
       <c r="C2802" s="1"/>
       <c r="D2802" s="1"/>
@@ -88586,7 +88832,7 @@
       <c r="G2802" s="10"/>
       <c r="K2802" s="7"/>
     </row>
-    <row r="2803" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2803" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2803" s="18"/>
       <c r="C2803" s="1"/>
       <c r="D2803" s="1"/>
@@ -88598,7 +88844,7 @@
       <c r="G2803" s="10"/>
       <c r="K2803" s="7"/>
     </row>
-    <row r="2804" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2804" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2804" s="18"/>
       <c r="C2804" s="1"/>
       <c r="D2804" s="1"/>
@@ -88610,7 +88856,7 @@
       <c r="G2804" s="10"/>
       <c r="K2804" s="7"/>
     </row>
-    <row r="2805" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2805" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2805" s="18"/>
       <c r="C2805" s="1"/>
       <c r="D2805" s="1"/>
@@ -88622,7 +88868,7 @@
       <c r="G2805" s="10"/>
       <c r="K2805" s="7"/>
     </row>
-    <row r="2806" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2806" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2806" s="18"/>
       <c r="C2806" s="1"/>
       <c r="D2806" s="1"/>
@@ -88634,7 +88880,7 @@
       <c r="G2806" s="10"/>
       <c r="K2806" s="7"/>
     </row>
-    <row r="2807" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2807" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2807" s="18"/>
       <c r="C2807" s="1"/>
       <c r="D2807" s="1"/>
@@ -88646,7 +88892,7 @@
       <c r="G2807" s="10"/>
       <c r="K2807" s="7"/>
     </row>
-    <row r="2808" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2808" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2808" s="18"/>
       <c r="C2808" s="1"/>
       <c r="D2808" s="1"/>
@@ -88658,7 +88904,7 @@
       <c r="G2808" s="10"/>
       <c r="K2808" s="7"/>
     </row>
-    <row r="2809" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2809" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2809" s="18"/>
       <c r="C2809" s="1"/>
       <c r="D2809" s="1"/>
@@ -88670,7 +88916,7 @@
       <c r="G2809" s="10"/>
       <c r="K2809" s="7"/>
     </row>
-    <row r="2810" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2810" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2810" s="18"/>
       <c r="C2810" s="1"/>
       <c r="D2810" s="1"/>
@@ -88682,7 +88928,7 @@
       <c r="G2810" s="10"/>
       <c r="K2810" s="7"/>
     </row>
-    <row r="2811" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2811" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2811" s="18"/>
       <c r="C2811" s="1"/>
       <c r="D2811" s="1"/>
@@ -88694,7 +88940,7 @@
       <c r="G2811" s="10"/>
       <c r="K2811" s="7"/>
     </row>
-    <row r="2812" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2812" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2812" s="18"/>
       <c r="C2812" s="1"/>
       <c r="D2812" s="1"/>
@@ -88706,7 +88952,7 @@
       <c r="G2812" s="10"/>
       <c r="K2812" s="7"/>
     </row>
-    <row r="2813" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2813" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2813" s="18"/>
       <c r="C2813" s="1"/>
       <c r="D2813" s="1"/>
@@ -88718,7 +88964,7 @@
       <c r="G2813" s="10"/>
       <c r="K2813" s="7"/>
     </row>
-    <row r="2814" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2814" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2814" s="18"/>
       <c r="C2814" s="1"/>
       <c r="D2814" s="1"/>
@@ -88730,7 +88976,7 @@
       <c r="G2814" s="10"/>
       <c r="K2814" s="7"/>
     </row>
-    <row r="2815" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2815" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2815" s="18"/>
       <c r="C2815" s="1"/>
       <c r="D2815" s="1"/>
@@ -88742,7 +88988,7 @@
       <c r="G2815" s="10"/>
       <c r="K2815" s="7"/>
     </row>
-    <row r="2816" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2816" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2816" s="18"/>
       <c r="C2816" s="1"/>
       <c r="D2816" s="1"/>
@@ -88754,7 +89000,7 @@
       <c r="G2816" s="10"/>
       <c r="K2816" s="7"/>
     </row>
-    <row r="2817" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2817" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2817" s="18"/>
       <c r="C2817" s="1"/>
       <c r="D2817" s="1"/>
@@ -88766,7 +89012,7 @@
       <c r="G2817" s="10"/>
       <c r="K2817" s="7"/>
     </row>
-    <row r="2818" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2818" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2818" s="18"/>
       <c r="C2818" s="1"/>
       <c r="D2818" s="1"/>
@@ -88778,7 +89024,7 @@
       <c r="G2818" s="10"/>
       <c r="K2818" s="7"/>
     </row>
-    <row r="2819" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2819" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2819" s="18"/>
       <c r="C2819" s="1"/>
       <c r="D2819" s="1"/>
@@ -88790,7 +89036,7 @@
       <c r="G2819" s="10"/>
       <c r="K2819" s="7"/>
     </row>
-    <row r="2820" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2820" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2820" s="18"/>
       <c r="C2820" s="1"/>
       <c r="D2820" s="1"/>
@@ -88802,7 +89048,7 @@
       <c r="G2820" s="10"/>
       <c r="K2820" s="7"/>
     </row>
-    <row r="2821" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2821" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2821" s="18"/>
       <c r="C2821" s="1"/>
       <c r="D2821" s="1"/>
@@ -88814,7 +89060,7 @@
       <c r="G2821" s="10"/>
       <c r="K2821" s="7"/>
     </row>
-    <row r="2822" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2822" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2822" s="18"/>
       <c r="C2822" s="1"/>
       <c r="D2822" s="1"/>
@@ -88826,7 +89072,7 @@
       <c r="G2822" s="10"/>
       <c r="K2822" s="7"/>
     </row>
-    <row r="2823" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2823" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2823" s="18"/>
       <c r="C2823" s="1"/>
       <c r="D2823" s="1"/>
@@ -88838,7 +89084,7 @@
       <c r="G2823" s="10"/>
       <c r="K2823" s="7"/>
     </row>
-    <row r="2824" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2824" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2824" s="18"/>
       <c r="C2824" s="1"/>
       <c r="D2824" s="1"/>
@@ -88850,7 +89096,7 @@
       <c r="G2824" s="10"/>
       <c r="K2824" s="7"/>
     </row>
-    <row r="2825" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2825" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2825" s="18"/>
       <c r="C2825" s="1"/>
       <c r="D2825" s="1"/>
@@ -88862,7 +89108,7 @@
       <c r="G2825" s="10"/>
       <c r="K2825" s="7"/>
     </row>
-    <row r="2826" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2826" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2826" s="18"/>
       <c r="C2826" s="1"/>
       <c r="D2826" s="1"/>
@@ -88874,7 +89120,7 @@
       <c r="G2826" s="10"/>
       <c r="K2826" s="7"/>
     </row>
-    <row r="2827" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2827" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2827" s="18"/>
       <c r="C2827" s="1"/>
       <c r="D2827" s="1"/>
@@ -88886,7 +89132,7 @@
       <c r="G2827" s="10"/>
       <c r="K2827" s="7"/>
     </row>
-    <row r="2828" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2828" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2828" s="18"/>
       <c r="C2828" s="1"/>
       <c r="D2828" s="1"/>
@@ -88898,7 +89144,7 @@
       <c r="G2828" s="10"/>
       <c r="K2828" s="7"/>
     </row>
-    <row r="2829" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2829" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2829" s="18"/>
       <c r="C2829" s="1"/>
       <c r="D2829" s="1"/>
@@ -88910,7 +89156,7 @@
       <c r="G2829" s="10"/>
       <c r="K2829" s="7"/>
     </row>
-    <row r="2830" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2830" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2830" s="18"/>
       <c r="C2830" s="1"/>
       <c r="D2830" s="1"/>
@@ -88922,7 +89168,7 @@
       <c r="G2830" s="10"/>
       <c r="K2830" s="7"/>
     </row>
-    <row r="2831" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2831" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2831" s="18"/>
       <c r="C2831" s="1"/>
       <c r="D2831" s="1"/>
@@ -88934,7 +89180,7 @@
       <c r="G2831" s="10"/>
       <c r="K2831" s="7"/>
     </row>
-    <row r="2832" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2832" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2832" s="18"/>
       <c r="C2832" s="1"/>
       <c r="D2832" s="1"/>
@@ -88946,7 +89192,7 @@
       <c r="G2832" s="10"/>
       <c r="K2832" s="7"/>
     </row>
-    <row r="2833" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2833" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2833" s="18"/>
       <c r="C2833" s="1"/>
       <c r="D2833" s="1"/>
@@ -88958,7 +89204,7 @@
       <c r="G2833" s="10"/>
       <c r="K2833" s="7"/>
     </row>
-    <row r="2834" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2834" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2834" s="18"/>
       <c r="C2834" s="1"/>
       <c r="D2834" s="1"/>
@@ -88970,7 +89216,7 @@
       <c r="G2834" s="10"/>
       <c r="K2834" s="7"/>
     </row>
-    <row r="2835" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2835" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2835" s="18"/>
       <c r="C2835" s="1"/>
       <c r="D2835" s="1"/>
@@ -88982,7 +89228,7 @@
       <c r="G2835" s="10"/>
       <c r="K2835" s="7"/>
     </row>
-    <row r="2836" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2836" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2836" s="18"/>
       <c r="C2836" s="1"/>
       <c r="D2836" s="1"/>
@@ -88994,7 +89240,7 @@
       <c r="G2836" s="10"/>
       <c r="K2836" s="7"/>
     </row>
-    <row r="2837" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2837" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2837" s="18"/>
       <c r="C2837" s="1"/>
       <c r="D2837" s="1"/>
@@ -89006,7 +89252,7 @@
       <c r="G2837" s="10"/>
       <c r="K2837" s="7"/>
     </row>
-    <row r="2838" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2838" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2838" s="18"/>
       <c r="C2838" s="1"/>
       <c r="D2838" s="1"/>
@@ -89018,7 +89264,7 @@
       <c r="G2838" s="10"/>
       <c r="K2838" s="7"/>
     </row>
-    <row r="2839" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2839" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2839" s="18"/>
       <c r="C2839" s="1"/>
       <c r="D2839" s="1"/>
@@ -89030,7 +89276,7 @@
       <c r="G2839" s="10"/>
       <c r="K2839" s="7"/>
     </row>
-    <row r="2840" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2840" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2840" s="18"/>
       <c r="C2840" s="1"/>
       <c r="D2840" s="1"/>
@@ -89042,7 +89288,7 @@
       <c r="G2840" s="10"/>
       <c r="K2840" s="7"/>
     </row>
-    <row r="2841" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2841" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2841" s="18"/>
       <c r="C2841" s="1"/>
       <c r="D2841" s="1"/>
@@ -89054,7 +89300,7 @@
       <c r="G2841" s="10"/>
       <c r="K2841" s="7"/>
     </row>
-    <row r="2842" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2842" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2842" s="18"/>
       <c r="C2842" s="1"/>
       <c r="D2842" s="1"/>
@@ -89066,7 +89312,7 @@
       <c r="G2842" s="10"/>
       <c r="K2842" s="7"/>
     </row>
-    <row r="2843" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2843" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2843" s="18"/>
       <c r="C2843" s="1"/>
       <c r="D2843" s="1"/>
@@ -89078,7 +89324,7 @@
       <c r="G2843" s="10"/>
       <c r="K2843" s="7"/>
     </row>
-    <row r="2844" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2844" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2844" s="18"/>
       <c r="C2844" s="1"/>
       <c r="D2844" s="1"/>
@@ -89090,7 +89336,7 @@
       <c r="G2844" s="10"/>
       <c r="K2844" s="7"/>
     </row>
-    <row r="2845" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2845" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2845" s="18"/>
       <c r="C2845" s="1"/>
       <c r="D2845" s="1"/>
@@ -89102,7 +89348,7 @@
       <c r="G2845" s="10"/>
       <c r="K2845" s="7"/>
     </row>
-    <row r="2846" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2846" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2846" s="18"/>
       <c r="C2846" s="1"/>
       <c r="D2846" s="1"/>
@@ -89114,7 +89360,7 @@
       <c r="G2846" s="10"/>
       <c r="K2846" s="7"/>
     </row>
-    <row r="2847" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2847" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2847" s="18"/>
       <c r="C2847" s="1"/>
       <c r="D2847" s="1"/>
@@ -89126,7 +89372,7 @@
       <c r="G2847" s="10"/>
       <c r="K2847" s="7"/>
     </row>
-    <row r="2848" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2848" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B2848" s="18"/>
       <c r="C2848" s="1"/>
       <c r="D2848" s="1"/>
@@ -89138,8 +89384,83 @@
       <c r="G2848" s="10"/>
       <c r="K2848" s="7"/>
     </row>
+    <row r="2849" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2849" s="23">
+        <v>45944</v>
+      </c>
+      <c r="F2849" s="2">
+        <v>180.19</v>
+      </c>
+      <c r="G2849" s="2">
+        <v>1133.44</v>
+      </c>
+      <c r="H2849" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2849" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2849" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2849" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2850" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2850" s="23">
+        <v>45941</v>
+      </c>
+      <c r="F2850" s="2">
+        <v>38.04</v>
+      </c>
+      <c r="G2850" s="2">
+        <v>227.86</v>
+      </c>
+      <c r="H2850" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2850" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2850" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K2850" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2851" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2851" s="23">
+        <v>45941</v>
+      </c>
+      <c r="F2851" s="2">
+        <v>200</v>
+      </c>
+      <c r="G2851" s="2">
+        <v>1128</v>
+      </c>
+      <c r="H2851" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2851" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2851" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="K2851" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:L2848" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:L2851" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="863" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FCAAA74-9836-4815-9EF5-12861ADC22C0}"/>
+  <xr:revisionPtr revIDLastSave="864" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3E31DDF-85EC-4B78-A3A1-A93CD8E71BE4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -1595,7 +1595,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <sheetPr filterMode="1"/>
   <dimension ref="B1:L2851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -81429,7 +81428,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2483" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2483" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2483" s="18"/>
       <c r="C2483" s="1"/>
       <c r="D2483" s="1"/>
@@ -82190,7 +82189,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2507" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2507" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2507" s="18"/>
       <c r="C2507" s="1"/>
       <c r="D2507" s="1"/>
@@ -82204,7 +82203,7 @@
       <c r="J2507" s="7"/>
       <c r="K2507" s="7"/>
     </row>
-    <row r="2508" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2508" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2508" s="18"/>
       <c r="C2508" s="1"/>
       <c r="D2508" s="1"/>
@@ -82218,7 +82217,7 @@
       <c r="J2508" s="7"/>
       <c r="K2508" s="7"/>
     </row>
-    <row r="2509" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2509" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2509" s="18"/>
       <c r="C2509" s="1"/>
       <c r="D2509" s="1"/>
@@ -82232,7 +82231,7 @@
       <c r="J2509" s="7"/>
       <c r="K2509" s="7"/>
     </row>
-    <row r="2510" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2510" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2510" s="18"/>
       <c r="C2510" s="1"/>
       <c r="D2510" s="1"/>
@@ -82738,7 +82737,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2526" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2526" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2526" s="18"/>
       <c r="C2526" s="1"/>
       <c r="D2526" s="1"/>
@@ -82752,7 +82751,7 @@
       <c r="J2526" s="7"/>
       <c r="K2526" s="7"/>
     </row>
-    <row r="2527" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2527" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2527" s="18"/>
       <c r="C2527" s="1"/>
       <c r="D2527" s="1"/>
@@ -82766,7 +82765,7 @@
       <c r="J2527" s="7"/>
       <c r="K2527" s="7"/>
     </row>
-    <row r="2528" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2528" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2528" s="18"/>
       <c r="C2528" s="1"/>
       <c r="D2528" s="1"/>
@@ -82780,7 +82779,7 @@
       <c r="J2528" s="7"/>
       <c r="K2528" s="7"/>
     </row>
-    <row r="2529" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2529" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2529" s="18"/>
       <c r="C2529" s="1"/>
       <c r="D2529" s="1"/>
@@ -82794,7 +82793,7 @@
       <c r="J2529" s="7"/>
       <c r="K2529" s="7"/>
     </row>
-    <row r="2530" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2530" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2530" s="18"/>
       <c r="C2530" s="1"/>
       <c r="D2530" s="1"/>
@@ -82808,7 +82807,7 @@
       <c r="J2530" s="7"/>
       <c r="K2530" s="7"/>
     </row>
-    <row r="2531" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2531" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2531" s="18"/>
       <c r="C2531" s="1"/>
       <c r="D2531" s="1"/>
@@ -83191,7 +83190,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2543" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2543" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2543" s="18"/>
       <c r="C2543" s="1"/>
       <c r="D2543" s="1"/>
@@ -83205,7 +83204,7 @@
       <c r="J2543" s="7"/>
       <c r="K2543" s="7"/>
     </row>
-    <row r="2544" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2544" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2544" s="18"/>
       <c r="C2544" s="1"/>
       <c r="D2544" s="1"/>
@@ -83219,7 +83218,7 @@
       <c r="J2544" s="7"/>
       <c r="K2544" s="7"/>
     </row>
-    <row r="2545" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2545" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2545" s="18"/>
       <c r="C2545" s="1"/>
       <c r="D2545" s="1"/>
@@ -83233,7 +83232,7 @@
       <c r="J2545" s="7"/>
       <c r="K2545" s="7"/>
     </row>
-    <row r="2546" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2546" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2546" s="18"/>
       <c r="C2546" s="1"/>
       <c r="D2546" s="1"/>
@@ -83247,7 +83246,7 @@
       <c r="J2546" s="7"/>
       <c r="K2546" s="7"/>
     </row>
-    <row r="2547" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2547" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2547" s="18"/>
       <c r="C2547" s="1"/>
       <c r="D2547" s="1"/>
@@ -83261,7 +83260,7 @@
       <c r="J2547" s="7"/>
       <c r="K2547" s="7"/>
     </row>
-    <row r="2548" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2548" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2548" s="18"/>
       <c r="C2548" s="1"/>
       <c r="D2548" s="1"/>
@@ -83311,7 +83310,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="2550" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2550" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2550" s="17"/>
       <c r="E2550" s="1">
         <f t="shared" si="44"/>
@@ -83580,7 +83579,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="2559" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2559" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2559" s="18"/>
       <c r="C2559" s="1"/>
       <c r="D2559" s="1"/>
@@ -83594,7 +83593,7 @@
       <c r="J2559" s="7"/>
       <c r="K2559" s="7"/>
     </row>
-    <row r="2560" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2560" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2560" s="18"/>
       <c r="C2560" s="1"/>
       <c r="D2560" s="1"/>
@@ -84838,7 +84837,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2598" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2598" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2598" s="18"/>
       <c r="C2598" s="1"/>
       <c r="D2598" s="1"/>
@@ -84852,7 +84851,7 @@
       <c r="J2598" s="7"/>
       <c r="K2598" s="7"/>
     </row>
-    <row r="2599" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2599" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2599" s="18"/>
       <c r="C2599" s="1"/>
       <c r="D2599" s="1"/>
@@ -84866,7 +84865,7 @@
       <c r="J2599" s="7"/>
       <c r="K2599" s="7"/>
     </row>
-    <row r="2600" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2600" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2600" s="18"/>
       <c r="C2600" s="1"/>
       <c r="D2600" s="1"/>
@@ -85174,7 +85173,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="2610" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2610" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2610" s="18"/>
       <c r="C2610" s="1"/>
       <c r="D2610" s="1"/>
@@ -85188,7 +85187,7 @@
       <c r="J2610" s="7"/>
       <c r="K2610" s="7"/>
     </row>
-    <row r="2611" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2611" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2611" s="18"/>
       <c r="C2611" s="1"/>
       <c r="D2611" s="1"/>
@@ -85202,7 +85201,7 @@
       <c r="J2611" s="7"/>
       <c r="K2611" s="7"/>
     </row>
-    <row r="2612" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2612" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2612" s="18"/>
       <c r="C2612" s="1"/>
       <c r="D2612" s="1"/>
@@ -85216,7 +85215,7 @@
       <c r="J2612" s="7"/>
       <c r="K2612" s="7"/>
     </row>
-    <row r="2613" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2613" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2613" s="18"/>
       <c r="C2613" s="1"/>
       <c r="D2613" s="1"/>
@@ -85707,7 +85706,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="2628" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2628" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2628" s="18"/>
       <c r="C2628" s="1"/>
       <c r="D2628" s="1"/>
@@ -85721,7 +85720,7 @@
       <c r="J2628" s="7"/>
       <c r="K2628" s="7"/>
     </row>
-    <row r="2629" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2629" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2629" s="18"/>
       <c r="C2629" s="1"/>
       <c r="D2629" s="1"/>
@@ -85735,7 +85734,7 @@
       <c r="J2629" s="7"/>
       <c r="K2629" s="7"/>
     </row>
-    <row r="2630" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2630" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2630" s="18"/>
       <c r="C2630" s="1"/>
       <c r="D2630" s="1"/>
@@ -85749,7 +85748,7 @@
       <c r="J2630" s="7"/>
       <c r="K2630" s="7"/>
     </row>
-    <row r="2631" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2631" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2631" s="18"/>
       <c r="C2631" s="1"/>
       <c r="D2631" s="1"/>
@@ -85763,7 +85762,7 @@
       <c r="J2631" s="7"/>
       <c r="K2631" s="7"/>
     </row>
-    <row r="2632" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2632" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2632" s="18"/>
       <c r="C2632" s="1"/>
       <c r="D2632" s="1"/>
@@ -85777,7 +85776,7 @@
       <c r="J2632" s="7"/>
       <c r="K2632" s="7"/>
     </row>
-    <row r="2633" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2633" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2633" s="18"/>
       <c r="C2633" s="1"/>
       <c r="D2633" s="1"/>
@@ -86337,7 +86336,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2650" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2650" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2650" s="18"/>
       <c r="C2650" s="1"/>
       <c r="D2650" s="1"/>
@@ -86351,7 +86350,7 @@
       <c r="J2650" s="7"/>
       <c r="K2650" s="7"/>
     </row>
-    <row r="2651" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2651" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2651" s="18"/>
       <c r="C2651" s="1"/>
       <c r="D2651" s="1"/>
@@ -86365,7 +86364,7 @@
       <c r="J2651" s="7"/>
       <c r="K2651" s="7"/>
     </row>
-    <row r="2652" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2652" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2652" s="18"/>
       <c r="C2652" s="1"/>
       <c r="D2652" s="1"/>
@@ -86379,7 +86378,7 @@
       <c r="J2652" s="7"/>
       <c r="K2652" s="7"/>
     </row>
-    <row r="2653" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2653" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2653" s="18"/>
       <c r="C2653" s="1"/>
       <c r="D2653" s="1"/>
@@ -86393,7 +86392,7 @@
       <c r="J2653" s="7"/>
       <c r="K2653" s="7"/>
     </row>
-    <row r="2654" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2654" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2654" s="18"/>
       <c r="C2654" s="1"/>
       <c r="D2654" s="1"/>
@@ -86773,7 +86772,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="2666" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2666" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2666" s="18"/>
       <c r="C2666" s="1"/>
       <c r="D2666" s="1"/>
@@ -86787,7 +86786,7 @@
       <c r="J2666" s="7"/>
       <c r="K2666" s="7"/>
     </row>
-    <row r="2667" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2667" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2667" s="18"/>
       <c r="C2667" s="1"/>
       <c r="D2667" s="1"/>
@@ -86801,7 +86800,7 @@
       <c r="J2667" s="7"/>
       <c r="K2667" s="7"/>
     </row>
-    <row r="2668" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2668" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2668" s="18"/>
       <c r="C2668" s="1"/>
       <c r="D2668" s="1"/>
@@ -86815,7 +86814,7 @@
       <c r="J2668" s="7"/>
       <c r="K2668" s="7"/>
     </row>
-    <row r="2669" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2669" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2669" s="18"/>
       <c r="C2669" s="1"/>
       <c r="D2669" s="1"/>
@@ -86829,7 +86828,7 @@
       <c r="J2669" s="7"/>
       <c r="K2669" s="7"/>
     </row>
-    <row r="2670" spans="2:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2670" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2670" s="18"/>
       <c r="C2670" s="1"/>
       <c r="D2670" s="1"/>
@@ -87476,7 +87475,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="2690" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2690" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2690" s="18"/>
       <c r="C2690" s="1"/>
       <c r="D2690" s="1"/>
@@ -87488,7 +87487,7 @@
       <c r="G2690" s="10"/>
       <c r="K2690" s="7"/>
     </row>
-    <row r="2691" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2691" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2691" s="18"/>
       <c r="C2691" s="1"/>
       <c r="D2691" s="1"/>
@@ -87500,7 +87499,7 @@
       <c r="G2691" s="10"/>
       <c r="K2691" s="7"/>
     </row>
-    <row r="2692" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2692" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2692" s="18"/>
       <c r="C2692" s="1"/>
       <c r="D2692" s="1"/>
@@ -87512,7 +87511,7 @@
       <c r="G2692" s="10"/>
       <c r="K2692" s="7"/>
     </row>
-    <row r="2693" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2693" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2693" s="18"/>
       <c r="C2693" s="1"/>
       <c r="D2693" s="1"/>
@@ -87524,7 +87523,7 @@
       <c r="G2693" s="10"/>
       <c r="K2693" s="7"/>
     </row>
-    <row r="2694" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2694" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2694" s="18"/>
       <c r="C2694" s="1"/>
       <c r="D2694" s="1"/>
@@ -87536,7 +87535,7 @@
       <c r="G2694" s="10"/>
       <c r="K2694" s="7"/>
     </row>
-    <row r="2695" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2695" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2695" s="18"/>
       <c r="C2695" s="1"/>
       <c r="D2695" s="1"/>
@@ -87548,7 +87547,7 @@
       <c r="G2695" s="10"/>
       <c r="K2695" s="7"/>
     </row>
-    <row r="2696" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2696" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2696" s="18"/>
       <c r="C2696" s="1"/>
       <c r="D2696" s="1"/>
@@ -87560,7 +87559,7 @@
       <c r="G2696" s="10"/>
       <c r="K2696" s="7"/>
     </row>
-    <row r="2697" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2697" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2697" s="18"/>
       <c r="C2697" s="1"/>
       <c r="D2697" s="1"/>
@@ -87572,7 +87571,7 @@
       <c r="G2697" s="10"/>
       <c r="K2697" s="7"/>
     </row>
-    <row r="2698" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2698" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2698" s="18"/>
       <c r="C2698" s="1"/>
       <c r="D2698" s="1"/>
@@ -87584,7 +87583,7 @@
       <c r="G2698" s="10"/>
       <c r="K2698" s="7"/>
     </row>
-    <row r="2699" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2699" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2699" s="18"/>
       <c r="C2699" s="1"/>
       <c r="D2699" s="1"/>
@@ -87596,7 +87595,7 @@
       <c r="G2699" s="10"/>
       <c r="K2699" s="7"/>
     </row>
-    <row r="2700" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2700" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2700" s="18"/>
       <c r="C2700" s="1"/>
       <c r="D2700" s="1"/>
@@ -87608,7 +87607,7 @@
       <c r="G2700" s="10"/>
       <c r="K2700" s="7"/>
     </row>
-    <row r="2701" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2701" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2701" s="18"/>
       <c r="C2701" s="1"/>
       <c r="D2701" s="1"/>
@@ -87620,7 +87619,7 @@
       <c r="G2701" s="10"/>
       <c r="K2701" s="7"/>
     </row>
-    <row r="2702" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2702" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2702" s="18"/>
       <c r="C2702" s="1"/>
       <c r="D2702" s="1"/>
@@ -87632,7 +87631,7 @@
       <c r="G2702" s="10"/>
       <c r="K2702" s="7"/>
     </row>
-    <row r="2703" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2703" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2703" s="18"/>
       <c r="C2703" s="1"/>
       <c r="D2703" s="1"/>
@@ -87644,7 +87643,7 @@
       <c r="G2703" s="10"/>
       <c r="K2703" s="7"/>
     </row>
-    <row r="2704" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2704" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2704" s="18"/>
       <c r="C2704" s="1"/>
       <c r="D2704" s="1"/>
@@ -87656,7 +87655,7 @@
       <c r="G2704" s="10"/>
       <c r="K2704" s="7"/>
     </row>
-    <row r="2705" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2705" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2705" s="18"/>
       <c r="C2705" s="1"/>
       <c r="D2705" s="1"/>
@@ -87668,7 +87667,7 @@
       <c r="G2705" s="10"/>
       <c r="K2705" s="7"/>
     </row>
-    <row r="2706" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2706" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2706" s="18"/>
       <c r="C2706" s="1"/>
       <c r="D2706" s="1"/>
@@ -87680,7 +87679,7 @@
       <c r="G2706" s="10"/>
       <c r="K2706" s="7"/>
     </row>
-    <row r="2707" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2707" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2707" s="18"/>
       <c r="C2707" s="1"/>
       <c r="D2707" s="1"/>
@@ -87692,7 +87691,7 @@
       <c r="G2707" s="10"/>
       <c r="K2707" s="7"/>
     </row>
-    <row r="2708" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2708" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2708" s="18"/>
       <c r="C2708" s="1"/>
       <c r="D2708" s="1"/>
@@ -87704,7 +87703,7 @@
       <c r="G2708" s="10"/>
       <c r="K2708" s="7"/>
     </row>
-    <row r="2709" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2709" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2709" s="18"/>
       <c r="C2709" s="1"/>
       <c r="D2709" s="1"/>
@@ -87716,7 +87715,7 @@
       <c r="G2709" s="10"/>
       <c r="K2709" s="7"/>
     </row>
-    <row r="2710" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2710" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2710" s="18"/>
       <c r="C2710" s="1"/>
       <c r="D2710" s="1"/>
@@ -87728,7 +87727,7 @@
       <c r="G2710" s="10"/>
       <c r="K2710" s="7"/>
     </row>
-    <row r="2711" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2711" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2711" s="18"/>
       <c r="C2711" s="1"/>
       <c r="D2711" s="1"/>
@@ -87740,7 +87739,7 @@
       <c r="G2711" s="10"/>
       <c r="K2711" s="7"/>
     </row>
-    <row r="2712" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2712" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2712" s="18"/>
       <c r="C2712" s="1"/>
       <c r="D2712" s="1"/>
@@ -87752,7 +87751,7 @@
       <c r="G2712" s="10"/>
       <c r="K2712" s="7"/>
     </row>
-    <row r="2713" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2713" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2713" s="18"/>
       <c r="C2713" s="1"/>
       <c r="D2713" s="1"/>
@@ -87764,7 +87763,7 @@
       <c r="G2713" s="10"/>
       <c r="K2713" s="7"/>
     </row>
-    <row r="2714" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2714" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2714" s="18"/>
       <c r="C2714" s="1"/>
       <c r="D2714" s="1"/>
@@ -87776,7 +87775,7 @@
       <c r="G2714" s="10"/>
       <c r="K2714" s="7"/>
     </row>
-    <row r="2715" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2715" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2715" s="18"/>
       <c r="C2715" s="1"/>
       <c r="D2715" s="1"/>
@@ -87788,7 +87787,7 @@
       <c r="G2715" s="10"/>
       <c r="K2715" s="7"/>
     </row>
-    <row r="2716" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2716" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2716" s="18"/>
       <c r="C2716" s="1"/>
       <c r="D2716" s="1"/>
@@ -87800,7 +87799,7 @@
       <c r="G2716" s="10"/>
       <c r="K2716" s="7"/>
     </row>
-    <row r="2717" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2717" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2717" s="18"/>
       <c r="C2717" s="1"/>
       <c r="D2717" s="1"/>
@@ -87812,7 +87811,7 @@
       <c r="G2717" s="10"/>
       <c r="K2717" s="7"/>
     </row>
-    <row r="2718" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2718" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2718" s="18"/>
       <c r="C2718" s="1"/>
       <c r="D2718" s="1"/>
@@ -87824,7 +87823,7 @@
       <c r="G2718" s="10"/>
       <c r="K2718" s="7"/>
     </row>
-    <row r="2719" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2719" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2719" s="18"/>
       <c r="C2719" s="1"/>
       <c r="D2719" s="1"/>
@@ -87836,7 +87835,7 @@
       <c r="G2719" s="10"/>
       <c r="K2719" s="7"/>
     </row>
-    <row r="2720" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2720" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2720" s="18"/>
       <c r="C2720" s="1"/>
       <c r="D2720" s="1"/>
@@ -87848,7 +87847,7 @@
       <c r="G2720" s="10"/>
       <c r="K2720" s="7"/>
     </row>
-    <row r="2721" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2721" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2721" s="18"/>
       <c r="C2721" s="1"/>
       <c r="D2721" s="1"/>
@@ -87860,7 +87859,7 @@
       <c r="G2721" s="10"/>
       <c r="K2721" s="7"/>
     </row>
-    <row r="2722" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2722" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2722" s="18"/>
       <c r="C2722" s="1"/>
       <c r="D2722" s="1"/>
@@ -87872,7 +87871,7 @@
       <c r="G2722" s="10"/>
       <c r="K2722" s="7"/>
     </row>
-    <row r="2723" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2723" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2723" s="18"/>
       <c r="C2723" s="1"/>
       <c r="D2723" s="1"/>
@@ -87884,7 +87883,7 @@
       <c r="G2723" s="10"/>
       <c r="K2723" s="7"/>
     </row>
-    <row r="2724" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2724" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2724" s="18"/>
       <c r="C2724" s="1"/>
       <c r="D2724" s="1"/>
@@ -87896,7 +87895,7 @@
       <c r="G2724" s="10"/>
       <c r="K2724" s="7"/>
     </row>
-    <row r="2725" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2725" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2725" s="18"/>
       <c r="C2725" s="1"/>
       <c r="D2725" s="1"/>
@@ -87908,7 +87907,7 @@
       <c r="G2725" s="10"/>
       <c r="K2725" s="7"/>
     </row>
-    <row r="2726" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2726" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2726" s="18"/>
       <c r="C2726" s="1"/>
       <c r="D2726" s="1"/>
@@ -87920,7 +87919,7 @@
       <c r="G2726" s="10"/>
       <c r="K2726" s="7"/>
     </row>
-    <row r="2727" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2727" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2727" s="18"/>
       <c r="C2727" s="1"/>
       <c r="D2727" s="1"/>
@@ -87932,7 +87931,7 @@
       <c r="G2727" s="10"/>
       <c r="K2727" s="7"/>
     </row>
-    <row r="2728" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2728" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2728" s="18"/>
       <c r="C2728" s="1"/>
       <c r="D2728" s="1"/>
@@ -87944,7 +87943,7 @@
       <c r="G2728" s="10"/>
       <c r="K2728" s="7"/>
     </row>
-    <row r="2729" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2729" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2729" s="18"/>
       <c r="C2729" s="1"/>
       <c r="D2729" s="1"/>
@@ -87956,7 +87955,7 @@
       <c r="G2729" s="10"/>
       <c r="K2729" s="7"/>
     </row>
-    <row r="2730" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2730" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2730" s="18"/>
       <c r="C2730" s="1"/>
       <c r="D2730" s="1"/>
@@ -87968,7 +87967,7 @@
       <c r="G2730" s="10"/>
       <c r="K2730" s="7"/>
     </row>
-    <row r="2731" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2731" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2731" s="18"/>
       <c r="C2731" s="1"/>
       <c r="D2731" s="1"/>
@@ -87980,7 +87979,7 @@
       <c r="G2731" s="10"/>
       <c r="K2731" s="7"/>
     </row>
-    <row r="2732" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2732" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2732" s="18"/>
       <c r="C2732" s="1"/>
       <c r="D2732" s="1"/>
@@ -87992,7 +87991,7 @@
       <c r="G2732" s="10"/>
       <c r="K2732" s="7"/>
     </row>
-    <row r="2733" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2733" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2733" s="18"/>
       <c r="C2733" s="1"/>
       <c r="D2733" s="1"/>
@@ -88004,7 +88003,7 @@
       <c r="G2733" s="10"/>
       <c r="K2733" s="7"/>
     </row>
-    <row r="2734" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2734" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2734" s="18"/>
       <c r="C2734" s="1"/>
       <c r="D2734" s="1"/>
@@ -88016,7 +88015,7 @@
       <c r="G2734" s="10"/>
       <c r="K2734" s="7"/>
     </row>
-    <row r="2735" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2735" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2735" s="18"/>
       <c r="C2735" s="1"/>
       <c r="D2735" s="1"/>
@@ -88028,7 +88027,7 @@
       <c r="G2735" s="10"/>
       <c r="K2735" s="7"/>
     </row>
-    <row r="2736" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2736" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2736" s="18"/>
       <c r="C2736" s="1"/>
       <c r="D2736" s="1"/>
@@ -88040,7 +88039,7 @@
       <c r="G2736" s="10"/>
       <c r="K2736" s="7"/>
     </row>
-    <row r="2737" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2737" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2737" s="18"/>
       <c r="C2737" s="1"/>
       <c r="D2737" s="1"/>
@@ -88052,7 +88051,7 @@
       <c r="G2737" s="10"/>
       <c r="K2737" s="7"/>
     </row>
-    <row r="2738" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2738" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2738" s="18"/>
       <c r="C2738" s="1"/>
       <c r="D2738" s="1"/>
@@ -88064,7 +88063,7 @@
       <c r="G2738" s="10"/>
       <c r="K2738" s="7"/>
     </row>
-    <row r="2739" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2739" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2739" s="18"/>
       <c r="C2739" s="1"/>
       <c r="D2739" s="1"/>
@@ -88076,7 +88075,7 @@
       <c r="G2739" s="10"/>
       <c r="K2739" s="7"/>
     </row>
-    <row r="2740" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2740" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2740" s="18"/>
       <c r="C2740" s="1"/>
       <c r="D2740" s="1"/>
@@ -88088,7 +88087,7 @@
       <c r="G2740" s="10"/>
       <c r="K2740" s="7"/>
     </row>
-    <row r="2741" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2741" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2741" s="18"/>
       <c r="C2741" s="1"/>
       <c r="D2741" s="1"/>
@@ -88100,7 +88099,7 @@
       <c r="G2741" s="10"/>
       <c r="K2741" s="7"/>
     </row>
-    <row r="2742" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2742" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2742" s="18"/>
       <c r="C2742" s="1"/>
       <c r="D2742" s="1"/>
@@ -88112,7 +88111,7 @@
       <c r="G2742" s="10"/>
       <c r="K2742" s="7"/>
     </row>
-    <row r="2743" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2743" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2743" s="18"/>
       <c r="C2743" s="1"/>
       <c r="D2743" s="1"/>
@@ -88124,7 +88123,7 @@
       <c r="G2743" s="10"/>
       <c r="K2743" s="7"/>
     </row>
-    <row r="2744" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2744" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2744" s="18"/>
       <c r="C2744" s="1"/>
       <c r="D2744" s="1"/>
@@ -88136,7 +88135,7 @@
       <c r="G2744" s="10"/>
       <c r="K2744" s="7"/>
     </row>
-    <row r="2745" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2745" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2745" s="18"/>
       <c r="C2745" s="1"/>
       <c r="D2745" s="1"/>
@@ -88148,7 +88147,7 @@
       <c r="G2745" s="10"/>
       <c r="K2745" s="7"/>
     </row>
-    <row r="2746" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2746" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2746" s="18"/>
       <c r="C2746" s="1"/>
       <c r="D2746" s="1"/>
@@ -88160,7 +88159,7 @@
       <c r="G2746" s="10"/>
       <c r="K2746" s="7"/>
     </row>
-    <row r="2747" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2747" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2747" s="18"/>
       <c r="C2747" s="1"/>
       <c r="D2747" s="1"/>
@@ -88172,7 +88171,7 @@
       <c r="G2747" s="10"/>
       <c r="K2747" s="7"/>
     </row>
-    <row r="2748" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2748" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2748" s="18"/>
       <c r="C2748" s="1"/>
       <c r="D2748" s="1"/>
@@ -88184,7 +88183,7 @@
       <c r="G2748" s="10"/>
       <c r="K2748" s="7"/>
     </row>
-    <row r="2749" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2749" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2749" s="18"/>
       <c r="C2749" s="1"/>
       <c r="D2749" s="1"/>
@@ -88196,7 +88195,7 @@
       <c r="G2749" s="10"/>
       <c r="K2749" s="7"/>
     </row>
-    <row r="2750" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2750" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2750" s="18"/>
       <c r="C2750" s="1"/>
       <c r="D2750" s="1"/>
@@ -88208,7 +88207,7 @@
       <c r="G2750" s="10"/>
       <c r="K2750" s="7"/>
     </row>
-    <row r="2751" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2751" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2751" s="18"/>
       <c r="C2751" s="1"/>
       <c r="D2751" s="1"/>
@@ -88220,7 +88219,7 @@
       <c r="G2751" s="10"/>
       <c r="K2751" s="7"/>
     </row>
-    <row r="2752" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2752" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2752" s="18"/>
       <c r="C2752" s="1"/>
       <c r="D2752" s="1"/>
@@ -88232,7 +88231,7 @@
       <c r="G2752" s="10"/>
       <c r="K2752" s="7"/>
     </row>
-    <row r="2753" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2753" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2753" s="18"/>
       <c r="C2753" s="1"/>
       <c r="D2753" s="1"/>
@@ -88244,7 +88243,7 @@
       <c r="G2753" s="10"/>
       <c r="K2753" s="7"/>
     </row>
-    <row r="2754" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2754" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2754" s="18"/>
       <c r="C2754" s="1"/>
       <c r="D2754" s="1"/>
@@ -88256,7 +88255,7 @@
       <c r="G2754" s="10"/>
       <c r="K2754" s="7"/>
     </row>
-    <row r="2755" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2755" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2755" s="18"/>
       <c r="C2755" s="1"/>
       <c r="D2755" s="1"/>
@@ -88268,7 +88267,7 @@
       <c r="G2755" s="10"/>
       <c r="K2755" s="7"/>
     </row>
-    <row r="2756" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2756" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2756" s="18"/>
       <c r="C2756" s="1"/>
       <c r="D2756" s="1"/>
@@ -88280,7 +88279,7 @@
       <c r="G2756" s="10"/>
       <c r="K2756" s="7"/>
     </row>
-    <row r="2757" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2757" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2757" s="18"/>
       <c r="C2757" s="1"/>
       <c r="D2757" s="1"/>
@@ -88292,7 +88291,7 @@
       <c r="G2757" s="10"/>
       <c r="K2757" s="7"/>
     </row>
-    <row r="2758" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2758" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2758" s="18"/>
       <c r="C2758" s="1"/>
       <c r="D2758" s="1"/>
@@ -88304,7 +88303,7 @@
       <c r="G2758" s="10"/>
       <c r="K2758" s="7"/>
     </row>
-    <row r="2759" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2759" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2759" s="18"/>
       <c r="C2759" s="1"/>
       <c r="D2759" s="1"/>
@@ -88316,7 +88315,7 @@
       <c r="G2759" s="10"/>
       <c r="K2759" s="7"/>
     </row>
-    <row r="2760" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2760" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2760" s="18"/>
       <c r="C2760" s="1"/>
       <c r="D2760" s="1"/>
@@ -88328,7 +88327,7 @@
       <c r="G2760" s="10"/>
       <c r="K2760" s="7"/>
     </row>
-    <row r="2761" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2761" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2761" s="18"/>
       <c r="C2761" s="1"/>
       <c r="D2761" s="1"/>
@@ -88340,7 +88339,7 @@
       <c r="G2761" s="10"/>
       <c r="K2761" s="7"/>
     </row>
-    <row r="2762" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2762" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2762" s="18"/>
       <c r="C2762" s="1"/>
       <c r="D2762" s="1"/>
@@ -88352,7 +88351,7 @@
       <c r="G2762" s="10"/>
       <c r="K2762" s="7"/>
     </row>
-    <row r="2763" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2763" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2763" s="18"/>
       <c r="C2763" s="1"/>
       <c r="D2763" s="1"/>
@@ -88364,7 +88363,7 @@
       <c r="G2763" s="10"/>
       <c r="K2763" s="7"/>
     </row>
-    <row r="2764" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2764" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2764" s="18"/>
       <c r="C2764" s="1"/>
       <c r="D2764" s="1"/>
@@ -88376,7 +88375,7 @@
       <c r="G2764" s="10"/>
       <c r="K2764" s="7"/>
     </row>
-    <row r="2765" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2765" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2765" s="18"/>
       <c r="C2765" s="1"/>
       <c r="D2765" s="1"/>
@@ -88388,7 +88387,7 @@
       <c r="G2765" s="10"/>
       <c r="K2765" s="7"/>
     </row>
-    <row r="2766" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2766" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2766" s="18"/>
       <c r="C2766" s="1"/>
       <c r="D2766" s="1"/>
@@ -88400,7 +88399,7 @@
       <c r="G2766" s="10"/>
       <c r="K2766" s="7"/>
     </row>
-    <row r="2767" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2767" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2767" s="18"/>
       <c r="C2767" s="1"/>
       <c r="D2767" s="1"/>
@@ -88412,7 +88411,7 @@
       <c r="G2767" s="10"/>
       <c r="K2767" s="7"/>
     </row>
-    <row r="2768" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2768" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2768" s="18"/>
       <c r="C2768" s="1"/>
       <c r="D2768" s="1"/>
@@ -88424,7 +88423,7 @@
       <c r="G2768" s="10"/>
       <c r="K2768" s="7"/>
     </row>
-    <row r="2769" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2769" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2769" s="18"/>
       <c r="C2769" s="1"/>
       <c r="D2769" s="1"/>
@@ -88436,7 +88435,7 @@
       <c r="G2769" s="10"/>
       <c r="K2769" s="7"/>
     </row>
-    <row r="2770" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2770" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2770" s="18"/>
       <c r="C2770" s="1"/>
       <c r="D2770" s="1"/>
@@ -88448,7 +88447,7 @@
       <c r="G2770" s="10"/>
       <c r="K2770" s="7"/>
     </row>
-    <row r="2771" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2771" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2771" s="18"/>
       <c r="C2771" s="1"/>
       <c r="D2771" s="1"/>
@@ -88460,7 +88459,7 @@
       <c r="G2771" s="10"/>
       <c r="K2771" s="7"/>
     </row>
-    <row r="2772" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2772" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2772" s="18"/>
       <c r="C2772" s="1"/>
       <c r="D2772" s="1"/>
@@ -88472,7 +88471,7 @@
       <c r="G2772" s="10"/>
       <c r="K2772" s="7"/>
     </row>
-    <row r="2773" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2773" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2773" s="18"/>
       <c r="C2773" s="1"/>
       <c r="D2773" s="1"/>
@@ -88484,7 +88483,7 @@
       <c r="G2773" s="10"/>
       <c r="K2773" s="7"/>
     </row>
-    <row r="2774" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2774" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2774" s="18"/>
       <c r="C2774" s="1"/>
       <c r="D2774" s="1"/>
@@ -88496,7 +88495,7 @@
       <c r="G2774" s="10"/>
       <c r="K2774" s="7"/>
     </row>
-    <row r="2775" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2775" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2775" s="18"/>
       <c r="C2775" s="1"/>
       <c r="D2775" s="1"/>
@@ -88508,7 +88507,7 @@
       <c r="G2775" s="10"/>
       <c r="K2775" s="7"/>
     </row>
-    <row r="2776" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2776" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2776" s="18"/>
       <c r="C2776" s="1"/>
       <c r="D2776" s="1"/>
@@ -88520,7 +88519,7 @@
       <c r="G2776" s="10"/>
       <c r="K2776" s="7"/>
     </row>
-    <row r="2777" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2777" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2777" s="18"/>
       <c r="C2777" s="1"/>
       <c r="D2777" s="1"/>
@@ -88532,7 +88531,7 @@
       <c r="G2777" s="10"/>
       <c r="K2777" s="7"/>
     </row>
-    <row r="2778" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2778" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2778" s="18"/>
       <c r="C2778" s="1"/>
       <c r="D2778" s="1"/>
@@ -88544,7 +88543,7 @@
       <c r="G2778" s="10"/>
       <c r="K2778" s="7"/>
     </row>
-    <row r="2779" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2779" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2779" s="18"/>
       <c r="C2779" s="1"/>
       <c r="D2779" s="1"/>
@@ -88556,7 +88555,7 @@
       <c r="G2779" s="10"/>
       <c r="K2779" s="7"/>
     </row>
-    <row r="2780" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2780" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2780" s="18"/>
       <c r="C2780" s="1"/>
       <c r="D2780" s="1"/>
@@ -88568,7 +88567,7 @@
       <c r="G2780" s="10"/>
       <c r="K2780" s="7"/>
     </row>
-    <row r="2781" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2781" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2781" s="18"/>
       <c r="C2781" s="1"/>
       <c r="D2781" s="1"/>
@@ -88580,7 +88579,7 @@
       <c r="G2781" s="10"/>
       <c r="K2781" s="7"/>
     </row>
-    <row r="2782" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2782" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2782" s="18"/>
       <c r="C2782" s="1"/>
       <c r="D2782" s="1"/>
@@ -88592,7 +88591,7 @@
       <c r="G2782" s="10"/>
       <c r="K2782" s="7"/>
     </row>
-    <row r="2783" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2783" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2783" s="18"/>
       <c r="C2783" s="1"/>
       <c r="D2783" s="1"/>
@@ -88604,7 +88603,7 @@
       <c r="G2783" s="10"/>
       <c r="K2783" s="7"/>
     </row>
-    <row r="2784" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2784" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2784" s="18"/>
       <c r="C2784" s="1"/>
       <c r="D2784" s="1"/>
@@ -88616,7 +88615,7 @@
       <c r="G2784" s="10"/>
       <c r="K2784" s="7"/>
     </row>
-    <row r="2785" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2785" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2785" s="18"/>
       <c r="C2785" s="1"/>
       <c r="D2785" s="1"/>
@@ -88628,7 +88627,7 @@
       <c r="G2785" s="10"/>
       <c r="K2785" s="7"/>
     </row>
-    <row r="2786" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2786" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2786" s="18"/>
       <c r="C2786" s="1"/>
       <c r="D2786" s="1"/>
@@ -88640,7 +88639,7 @@
       <c r="G2786" s="10"/>
       <c r="K2786" s="7"/>
     </row>
-    <row r="2787" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2787" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2787" s="18"/>
       <c r="C2787" s="1"/>
       <c r="D2787" s="1"/>
@@ -88652,7 +88651,7 @@
       <c r="G2787" s="10"/>
       <c r="K2787" s="7"/>
     </row>
-    <row r="2788" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2788" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2788" s="18"/>
       <c r="C2788" s="1"/>
       <c r="D2788" s="1"/>
@@ -88664,7 +88663,7 @@
       <c r="G2788" s="10"/>
       <c r="K2788" s="7"/>
     </row>
-    <row r="2789" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2789" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2789" s="18"/>
       <c r="C2789" s="1"/>
       <c r="D2789" s="1"/>
@@ -88676,7 +88675,7 @@
       <c r="G2789" s="10"/>
       <c r="K2789" s="7"/>
     </row>
-    <row r="2790" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2790" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2790" s="18"/>
       <c r="C2790" s="1"/>
       <c r="D2790" s="1"/>
@@ -88688,7 +88687,7 @@
       <c r="G2790" s="10"/>
       <c r="K2790" s="7"/>
     </row>
-    <row r="2791" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2791" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2791" s="18"/>
       <c r="C2791" s="1"/>
       <c r="D2791" s="1"/>
@@ -88700,7 +88699,7 @@
       <c r="G2791" s="10"/>
       <c r="K2791" s="7"/>
     </row>
-    <row r="2792" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2792" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2792" s="18"/>
       <c r="C2792" s="1"/>
       <c r="D2792" s="1"/>
@@ -88712,7 +88711,7 @@
       <c r="G2792" s="10"/>
       <c r="K2792" s="7"/>
     </row>
-    <row r="2793" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2793" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2793" s="18"/>
       <c r="C2793" s="1"/>
       <c r="D2793" s="1"/>
@@ -88724,7 +88723,7 @@
       <c r="G2793" s="10"/>
       <c r="K2793" s="7"/>
     </row>
-    <row r="2794" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2794" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2794" s="18"/>
       <c r="C2794" s="1"/>
       <c r="D2794" s="1"/>
@@ -88736,7 +88735,7 @@
       <c r="G2794" s="10"/>
       <c r="K2794" s="7"/>
     </row>
-    <row r="2795" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2795" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2795" s="18"/>
       <c r="C2795" s="1"/>
       <c r="D2795" s="1"/>
@@ -88748,7 +88747,7 @@
       <c r="G2795" s="10"/>
       <c r="K2795" s="7"/>
     </row>
-    <row r="2796" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2796" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2796" s="18"/>
       <c r="C2796" s="1"/>
       <c r="D2796" s="1"/>
@@ -88760,7 +88759,7 @@
       <c r="G2796" s="10"/>
       <c r="K2796" s="7"/>
     </row>
-    <row r="2797" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2797" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2797" s="18"/>
       <c r="C2797" s="1"/>
       <c r="D2797" s="1"/>
@@ -88772,7 +88771,7 @@
       <c r="G2797" s="10"/>
       <c r="K2797" s="7"/>
     </row>
-    <row r="2798" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2798" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2798" s="18"/>
       <c r="C2798" s="1"/>
       <c r="D2798" s="1"/>
@@ -88784,7 +88783,7 @@
       <c r="G2798" s="10"/>
       <c r="K2798" s="7"/>
     </row>
-    <row r="2799" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2799" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2799" s="18"/>
       <c r="C2799" s="1"/>
       <c r="D2799" s="1"/>
@@ -88796,7 +88795,7 @@
       <c r="G2799" s="10"/>
       <c r="K2799" s="7"/>
     </row>
-    <row r="2800" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2800" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2800" s="18"/>
       <c r="C2800" s="1"/>
       <c r="D2800" s="1"/>
@@ -88808,7 +88807,7 @@
       <c r="G2800" s="10"/>
       <c r="K2800" s="7"/>
     </row>
-    <row r="2801" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2801" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2801" s="18"/>
       <c r="C2801" s="1"/>
       <c r="D2801" s="1"/>
@@ -88820,7 +88819,7 @@
       <c r="G2801" s="10"/>
       <c r="K2801" s="7"/>
     </row>
-    <row r="2802" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2802" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2802" s="18"/>
       <c r="C2802" s="1"/>
       <c r="D2802" s="1"/>
@@ -88832,7 +88831,7 @@
       <c r="G2802" s="10"/>
       <c r="K2802" s="7"/>
     </row>
-    <row r="2803" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2803" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2803" s="18"/>
       <c r="C2803" s="1"/>
       <c r="D2803" s="1"/>
@@ -88844,7 +88843,7 @@
       <c r="G2803" s="10"/>
       <c r="K2803" s="7"/>
     </row>
-    <row r="2804" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2804" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2804" s="18"/>
       <c r="C2804" s="1"/>
       <c r="D2804" s="1"/>
@@ -88856,7 +88855,7 @@
       <c r="G2804" s="10"/>
       <c r="K2804" s="7"/>
     </row>
-    <row r="2805" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2805" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2805" s="18"/>
       <c r="C2805" s="1"/>
       <c r="D2805" s="1"/>
@@ -88868,7 +88867,7 @@
       <c r="G2805" s="10"/>
       <c r="K2805" s="7"/>
     </row>
-    <row r="2806" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2806" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2806" s="18"/>
       <c r="C2806" s="1"/>
       <c r="D2806" s="1"/>
@@ -88880,7 +88879,7 @@
       <c r="G2806" s="10"/>
       <c r="K2806" s="7"/>
     </row>
-    <row r="2807" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2807" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2807" s="18"/>
       <c r="C2807" s="1"/>
       <c r="D2807" s="1"/>
@@ -88892,7 +88891,7 @@
       <c r="G2807" s="10"/>
       <c r="K2807" s="7"/>
     </row>
-    <row r="2808" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2808" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2808" s="18"/>
       <c r="C2808" s="1"/>
       <c r="D2808" s="1"/>
@@ -88904,7 +88903,7 @@
       <c r="G2808" s="10"/>
       <c r="K2808" s="7"/>
     </row>
-    <row r="2809" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2809" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2809" s="18"/>
       <c r="C2809" s="1"/>
       <c r="D2809" s="1"/>
@@ -88916,7 +88915,7 @@
       <c r="G2809" s="10"/>
       <c r="K2809" s="7"/>
     </row>
-    <row r="2810" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2810" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2810" s="18"/>
       <c r="C2810" s="1"/>
       <c r="D2810" s="1"/>
@@ -88928,7 +88927,7 @@
       <c r="G2810" s="10"/>
       <c r="K2810" s="7"/>
     </row>
-    <row r="2811" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2811" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2811" s="18"/>
       <c r="C2811" s="1"/>
       <c r="D2811" s="1"/>
@@ -88940,7 +88939,7 @@
       <c r="G2811" s="10"/>
       <c r="K2811" s="7"/>
     </row>
-    <row r="2812" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2812" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2812" s="18"/>
       <c r="C2812" s="1"/>
       <c r="D2812" s="1"/>
@@ -88952,7 +88951,7 @@
       <c r="G2812" s="10"/>
       <c r="K2812" s="7"/>
     </row>
-    <row r="2813" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2813" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2813" s="18"/>
       <c r="C2813" s="1"/>
       <c r="D2813" s="1"/>
@@ -88964,7 +88963,7 @@
       <c r="G2813" s="10"/>
       <c r="K2813" s="7"/>
     </row>
-    <row r="2814" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2814" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2814" s="18"/>
       <c r="C2814" s="1"/>
       <c r="D2814" s="1"/>
@@ -88976,7 +88975,7 @@
       <c r="G2814" s="10"/>
       <c r="K2814" s="7"/>
     </row>
-    <row r="2815" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2815" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2815" s="18"/>
       <c r="C2815" s="1"/>
       <c r="D2815" s="1"/>
@@ -88988,7 +88987,7 @@
       <c r="G2815" s="10"/>
       <c r="K2815" s="7"/>
     </row>
-    <row r="2816" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2816" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2816" s="18"/>
       <c r="C2816" s="1"/>
       <c r="D2816" s="1"/>
@@ -89000,7 +88999,7 @@
       <c r="G2816" s="10"/>
       <c r="K2816" s="7"/>
     </row>
-    <row r="2817" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2817" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2817" s="18"/>
       <c r="C2817" s="1"/>
       <c r="D2817" s="1"/>
@@ -89012,7 +89011,7 @@
       <c r="G2817" s="10"/>
       <c r="K2817" s="7"/>
     </row>
-    <row r="2818" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2818" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2818" s="18"/>
       <c r="C2818" s="1"/>
       <c r="D2818" s="1"/>
@@ -89024,7 +89023,7 @@
       <c r="G2818" s="10"/>
       <c r="K2818" s="7"/>
     </row>
-    <row r="2819" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2819" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2819" s="18"/>
       <c r="C2819" s="1"/>
       <c r="D2819" s="1"/>
@@ -89036,7 +89035,7 @@
       <c r="G2819" s="10"/>
       <c r="K2819" s="7"/>
     </row>
-    <row r="2820" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2820" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2820" s="18"/>
       <c r="C2820" s="1"/>
       <c r="D2820" s="1"/>
@@ -89048,7 +89047,7 @@
       <c r="G2820" s="10"/>
       <c r="K2820" s="7"/>
     </row>
-    <row r="2821" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2821" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2821" s="18"/>
       <c r="C2821" s="1"/>
       <c r="D2821" s="1"/>
@@ -89060,7 +89059,7 @@
       <c r="G2821" s="10"/>
       <c r="K2821" s="7"/>
     </row>
-    <row r="2822" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2822" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2822" s="18"/>
       <c r="C2822" s="1"/>
       <c r="D2822" s="1"/>
@@ -89072,7 +89071,7 @@
       <c r="G2822" s="10"/>
       <c r="K2822" s="7"/>
     </row>
-    <row r="2823" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2823" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2823" s="18"/>
       <c r="C2823" s="1"/>
       <c r="D2823" s="1"/>
@@ -89084,7 +89083,7 @@
       <c r="G2823" s="10"/>
       <c r="K2823" s="7"/>
     </row>
-    <row r="2824" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2824" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2824" s="18"/>
       <c r="C2824" s="1"/>
       <c r="D2824" s="1"/>
@@ -89096,7 +89095,7 @@
       <c r="G2824" s="10"/>
       <c r="K2824" s="7"/>
     </row>
-    <row r="2825" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2825" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2825" s="18"/>
       <c r="C2825" s="1"/>
       <c r="D2825" s="1"/>
@@ -89108,7 +89107,7 @@
       <c r="G2825" s="10"/>
       <c r="K2825" s="7"/>
     </row>
-    <row r="2826" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2826" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2826" s="18"/>
       <c r="C2826" s="1"/>
       <c r="D2826" s="1"/>
@@ -89120,7 +89119,7 @@
       <c r="G2826" s="10"/>
       <c r="K2826" s="7"/>
     </row>
-    <row r="2827" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2827" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2827" s="18"/>
       <c r="C2827" s="1"/>
       <c r="D2827" s="1"/>
@@ -89132,7 +89131,7 @@
       <c r="G2827" s="10"/>
       <c r="K2827" s="7"/>
     </row>
-    <row r="2828" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2828" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2828" s="18"/>
       <c r="C2828" s="1"/>
       <c r="D2828" s="1"/>
@@ -89144,7 +89143,7 @@
       <c r="G2828" s="10"/>
       <c r="K2828" s="7"/>
     </row>
-    <row r="2829" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2829" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2829" s="18"/>
       <c r="C2829" s="1"/>
       <c r="D2829" s="1"/>
@@ -89156,7 +89155,7 @@
       <c r="G2829" s="10"/>
       <c r="K2829" s="7"/>
     </row>
-    <row r="2830" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2830" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2830" s="18"/>
       <c r="C2830" s="1"/>
       <c r="D2830" s="1"/>
@@ -89168,7 +89167,7 @@
       <c r="G2830" s="10"/>
       <c r="K2830" s="7"/>
     </row>
-    <row r="2831" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2831" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2831" s="18"/>
       <c r="C2831" s="1"/>
       <c r="D2831" s="1"/>
@@ -89180,7 +89179,7 @@
       <c r="G2831" s="10"/>
       <c r="K2831" s="7"/>
     </row>
-    <row r="2832" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2832" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2832" s="18"/>
       <c r="C2832" s="1"/>
       <c r="D2832" s="1"/>
@@ -89192,7 +89191,7 @@
       <c r="G2832" s="10"/>
       <c r="K2832" s="7"/>
     </row>
-    <row r="2833" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2833" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2833" s="18"/>
       <c r="C2833" s="1"/>
       <c r="D2833" s="1"/>
@@ -89204,7 +89203,7 @@
       <c r="G2833" s="10"/>
       <c r="K2833" s="7"/>
     </row>
-    <row r="2834" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2834" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2834" s="18"/>
       <c r="C2834" s="1"/>
       <c r="D2834" s="1"/>
@@ -89216,7 +89215,7 @@
       <c r="G2834" s="10"/>
       <c r="K2834" s="7"/>
     </row>
-    <row r="2835" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2835" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2835" s="18"/>
       <c r="C2835" s="1"/>
       <c r="D2835" s="1"/>
@@ -89228,7 +89227,7 @@
       <c r="G2835" s="10"/>
       <c r="K2835" s="7"/>
     </row>
-    <row r="2836" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2836" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2836" s="18"/>
       <c r="C2836" s="1"/>
       <c r="D2836" s="1"/>
@@ -89240,7 +89239,7 @@
       <c r="G2836" s="10"/>
       <c r="K2836" s="7"/>
     </row>
-    <row r="2837" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2837" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2837" s="18"/>
       <c r="C2837" s="1"/>
       <c r="D2837" s="1"/>
@@ -89252,7 +89251,7 @@
       <c r="G2837" s="10"/>
       <c r="K2837" s="7"/>
     </row>
-    <row r="2838" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2838" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2838" s="18"/>
       <c r="C2838" s="1"/>
       <c r="D2838" s="1"/>
@@ -89264,7 +89263,7 @@
       <c r="G2838" s="10"/>
       <c r="K2838" s="7"/>
     </row>
-    <row r="2839" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2839" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2839" s="18"/>
       <c r="C2839" s="1"/>
       <c r="D2839" s="1"/>
@@ -89276,7 +89275,7 @@
       <c r="G2839" s="10"/>
       <c r="K2839" s="7"/>
     </row>
-    <row r="2840" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2840" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2840" s="18"/>
       <c r="C2840" s="1"/>
       <c r="D2840" s="1"/>
@@ -89288,7 +89287,7 @@
       <c r="G2840" s="10"/>
       <c r="K2840" s="7"/>
     </row>
-    <row r="2841" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2841" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2841" s="18"/>
       <c r="C2841" s="1"/>
       <c r="D2841" s="1"/>
@@ -89300,7 +89299,7 @@
       <c r="G2841" s="10"/>
       <c r="K2841" s="7"/>
     </row>
-    <row r="2842" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2842" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2842" s="18"/>
       <c r="C2842" s="1"/>
       <c r="D2842" s="1"/>
@@ -89312,7 +89311,7 @@
       <c r="G2842" s="10"/>
       <c r="K2842" s="7"/>
     </row>
-    <row r="2843" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2843" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2843" s="18"/>
       <c r="C2843" s="1"/>
       <c r="D2843" s="1"/>
@@ -89324,7 +89323,7 @@
       <c r="G2843" s="10"/>
       <c r="K2843" s="7"/>
     </row>
-    <row r="2844" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2844" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2844" s="18"/>
       <c r="C2844" s="1"/>
       <c r="D2844" s="1"/>
@@ -89336,7 +89335,7 @@
       <c r="G2844" s="10"/>
       <c r="K2844" s="7"/>
     </row>
-    <row r="2845" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2845" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2845" s="18"/>
       <c r="C2845" s="1"/>
       <c r="D2845" s="1"/>
@@ -89348,7 +89347,7 @@
       <c r="G2845" s="10"/>
       <c r="K2845" s="7"/>
     </row>
-    <row r="2846" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2846" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2846" s="18"/>
       <c r="C2846" s="1"/>
       <c r="D2846" s="1"/>
@@ -89360,7 +89359,7 @@
       <c r="G2846" s="10"/>
       <c r="K2846" s="7"/>
     </row>
-    <row r="2847" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2847" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2847" s="18"/>
       <c r="C2847" s="1"/>
       <c r="D2847" s="1"/>
@@ -89372,7 +89371,7 @@
       <c r="G2847" s="10"/>
       <c r="K2847" s="7"/>
     </row>
-    <row r="2848" spans="2:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2848" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2848" s="18"/>
       <c r="C2848" s="1"/>
       <c r="D2848" s="1"/>
@@ -89454,13 +89453,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:L2851" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:L2851" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="864" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3E31DDF-85EC-4B78-A3A1-A93CD8E71BE4}"/>
+  <xr:revisionPtr revIDLastSave="988" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E36DC13-89CF-4EB3-AC1C-22199B2A65C6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2851</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2845</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8230" uniqueCount="338">
   <si>
     <t>Data</t>
   </si>
@@ -1595,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2851"/>
+  <dimension ref="B1:L2676"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -81429,18 +81429,33 @@
       </c>
     </row>
     <row r="2483" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2483" s="18"/>
+      <c r="B2483" s="18">
+        <v>45945</v>
+      </c>
       <c r="C2483" s="1"/>
       <c r="D2483" s="1"/>
       <c r="E2483" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2483" s="1"/>
-      <c r="G2483" s="10"/>
-      <c r="H2483" s="3"/>
-      <c r="J2483" s="7"/>
-      <c r="K2483" s="7"/>
+      <c r="F2483" s="1">
+        <v>106.02</v>
+      </c>
+      <c r="G2483" s="10">
+        <v>688.07</v>
+      </c>
+      <c r="H2483" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2483" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2483" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2483" s="7" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="2484" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2484" s="17">
@@ -82190,80 +82205,142 @@
       </c>
     </row>
     <row r="2507" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2507" s="18"/>
+      <c r="B2507" s="18">
+        <v>45945</v>
+      </c>
       <c r="C2507" s="1"/>
       <c r="D2507" s="1"/>
       <c r="E2507" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2507" s="1"/>
-      <c r="G2507" s="10"/>
-      <c r="H2507" s="3"/>
-      <c r="J2507" s="7"/>
-      <c r="K2507" s="7"/>
+      <c r="F2507" s="1">
+        <v>326.17</v>
+      </c>
+      <c r="G2507" s="10">
+        <v>2051.66</v>
+      </c>
+      <c r="H2507" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2507" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2507" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2507" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2508" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2508" s="18"/>
+      <c r="B2508" s="18">
+        <v>45945</v>
+      </c>
       <c r="C2508" s="1"/>
       <c r="D2508" s="1"/>
       <c r="E2508" s="1">
         <f t="shared" si="43"/>
         <v>0</v>
       </c>
-      <c r="F2508" s="1"/>
-      <c r="G2508" s="10"/>
-      <c r="H2508" s="3"/>
-      <c r="J2508" s="7"/>
-      <c r="K2508" s="7"/>
+      <c r="F2508" s="1">
+        <v>230.24</v>
+      </c>
+      <c r="G2508" s="10">
+        <v>1461.9</v>
+      </c>
+      <c r="H2508" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2508" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2508" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2508" s="7" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="2509" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2509" s="18"/>
-      <c r="C2509" s="1"/>
-      <c r="D2509" s="1"/>
+      <c r="B2509" s="17">
+        <v>45911.288321759261</v>
+      </c>
+      <c r="C2509" s="2">
+        <v>734637</v>
+      </c>
+      <c r="D2509" s="2">
+        <v>735668</v>
+      </c>
       <c r="E2509" s="1">
-        <f t="shared" ref="E2509:E2572" si="44">D2509-C2509</f>
-        <v>0</v>
-      </c>
-      <c r="F2509" s="1"/>
-      <c r="G2509" s="10"/>
-      <c r="H2509" s="3"/>
-      <c r="J2509" s="7"/>
-      <c r="K2509" s="7"/>
+        <f t="shared" ref="E2509:E2555" si="44">D2509-C2509</f>
+        <v>1031</v>
+      </c>
+      <c r="F2509" s="2">
+        <v>181</v>
+      </c>
+      <c r="G2509" s="16">
+        <v>1093.25</v>
+      </c>
+      <c r="H2509" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2509" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2509" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2509" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2510" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2510" s="18"/>
-      <c r="C2510" s="1"/>
-      <c r="D2510" s="1"/>
+      <c r="B2510" s="17">
+        <v>45911.296377314815</v>
+      </c>
       <c r="E2510" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="F2510" s="1"/>
-      <c r="G2510" s="10"/>
-      <c r="H2510" s="3"/>
-      <c r="J2510" s="7"/>
-      <c r="K2510" s="7"/>
+      <c r="F2510" s="2">
+        <v>115.89</v>
+      </c>
+      <c r="G2510" s="2">
+        <v>700</v>
+      </c>
+      <c r="H2510" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2510" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2510" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2510" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2511" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2511" s="17">
-        <v>45911.288321759261</v>
+        <v>45911.346331018518</v>
       </c>
       <c r="C2511" s="2">
-        <v>734637</v>
+        <v>506623</v>
       </c>
       <c r="D2511" s="2">
-        <v>735668</v>
+        <v>507097</v>
       </c>
       <c r="E2511" s="1">
         <f t="shared" si="44"/>
-        <v>1031</v>
+        <v>474</v>
       </c>
       <c r="F2511" s="2">
-        <v>181</v>
-      </c>
-      <c r="G2511" s="16">
-        <v>1093.25</v>
+        <v>63.66</v>
+      </c>
+      <c r="G2511" s="2">
+        <v>394.07</v>
       </c>
       <c r="H2511" s="2" t="s">
         <v>8</v>
@@ -82272,121 +82349,131 @@
         <v>45901</v>
       </c>
       <c r="J2511" s="2" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="K2511" s="2" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2512" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2512" s="17">
-        <v>45911.296377314815</v>
+        <v>45911.349166666667</v>
+      </c>
+      <c r="C2512" s="2">
+        <v>9136</v>
+      </c>
+      <c r="D2512" s="2">
+        <v>9569</v>
       </c>
       <c r="E2512" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="F2512" s="2">
-        <v>115.89</v>
+        <v>39.46</v>
       </c>
       <c r="G2512" s="2">
-        <v>700</v>
+        <v>248.2</v>
       </c>
       <c r="H2512" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2512" s="12">
         <v>45901</v>
       </c>
       <c r="J2512" s="2" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="K2512" s="2" t="s">
-        <v>65</v>
+        <v>202</v>
+      </c>
+      <c r="L2512" s="28" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="2513" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2513" s="17">
-        <v>45911.346331018518</v>
-      </c>
-      <c r="C2513" s="2">
-        <v>506623</v>
-      </c>
-      <c r="D2513" s="2">
-        <v>507097</v>
+        <v>45911.371365740742</v>
       </c>
       <c r="E2513" s="1">
         <f t="shared" si="44"/>
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="F2513" s="2">
-        <v>63.66</v>
+        <v>20.88</v>
       </c>
       <c r="G2513" s="2">
-        <v>394.07</v>
+        <v>121.94</v>
       </c>
       <c r="H2513" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2513" s="12">
         <v>45901</v>
       </c>
       <c r="J2513" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="K2513" s="2" t="s">
-        <v>78</v>
+        <v>206</v>
+      </c>
+      <c r="L2513" s="28" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="2514" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2514" s="17">
-        <v>45911.349166666667</v>
+        <v>45911.466261574074</v>
       </c>
       <c r="C2514" s="2">
-        <v>9136</v>
+        <v>585915</v>
       </c>
       <c r="D2514" s="2">
-        <v>9569</v>
+        <v>586945</v>
       </c>
       <c r="E2514" s="1">
         <f t="shared" si="44"/>
-        <v>433</v>
+        <v>1030</v>
       </c>
       <c r="F2514" s="2">
-        <v>39.46</v>
+        <v>121.58</v>
       </c>
       <c r="G2514" s="2">
-        <v>248.2</v>
+        <v>746.5</v>
       </c>
       <c r="H2514" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2514" s="12">
         <v>45901</v>
       </c>
       <c r="J2514" s="2" t="s">
-        <v>64</v>
+        <v>184</v>
       </c>
       <c r="K2514" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L2514" s="28" t="s">
-        <v>330</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="L2514" s="28"/>
     </row>
     <row r="2515" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2515" s="17">
-        <v>45911.371365740742</v>
+        <v>45911.521331018521</v>
+      </c>
+      <c r="C2515" s="2">
+        <v>9272</v>
+      </c>
+      <c r="D2515" s="2">
+        <v>9651</v>
       </c>
       <c r="E2515" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>379</v>
       </c>
       <c r="F2515" s="2">
-        <v>20.88</v>
+        <v>14.97</v>
       </c>
       <c r="G2515" s="2">
-        <v>121.94</v>
+        <v>100</v>
       </c>
       <c r="H2515" s="2" t="s">
         <v>7</v>
@@ -82395,103 +82482,98 @@
         <v>45901</v>
       </c>
       <c r="J2515" s="2" t="s">
-        <v>133</v>
+        <v>70</v>
       </c>
       <c r="K2515" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L2515" s="28" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2516" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2516" s="17">
-        <v>45911.466261574074</v>
+        <v>45911.552372685182</v>
       </c>
       <c r="C2516" s="2">
-        <v>585915</v>
+        <v>8762</v>
       </c>
       <c r="D2516" s="2">
-        <v>586945</v>
+        <v>9099</v>
       </c>
       <c r="E2516" s="1">
         <f t="shared" si="44"/>
-        <v>1030</v>
+        <v>337</v>
       </c>
       <c r="F2516" s="2">
-        <v>121.58</v>
+        <v>36.74</v>
       </c>
       <c r="G2516" s="2">
-        <v>746.5</v>
+        <v>216.4</v>
       </c>
       <c r="H2516" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2516" s="12">
         <v>45901</v>
       </c>
       <c r="J2516" s="2" t="s">
-        <v>184</v>
+        <v>300</v>
       </c>
       <c r="K2516" s="2" t="s">
-        <v>81</v>
+        <v>240</v>
+      </c>
+      <c r="L2516" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2517" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2517" s="17">
-        <v>45911.521331018521</v>
-      </c>
-      <c r="C2517" s="2">
-        <v>9272</v>
-      </c>
-      <c r="D2517" s="2">
-        <v>9651</v>
+        <v>45911.571562500001</v>
       </c>
       <c r="E2517" s="1">
         <f t="shared" si="44"/>
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="F2517" s="2">
-        <v>14.97</v>
+        <v>41.47</v>
       </c>
       <c r="G2517" s="2">
-        <v>100</v>
+        <v>240.11</v>
       </c>
       <c r="H2517" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I2517" s="12">
         <v>45901</v>
       </c>
       <c r="J2517" s="2" t="s">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="K2517" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2517" s="28" t="s">
-        <v>324</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="L2517" s="28"/>
     </row>
     <row r="2518" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2518" s="17">
-        <v>45911.552372685182</v>
+        <v>45911.594664351855</v>
       </c>
       <c r="C2518" s="2">
-        <v>8762</v>
+        <v>5700</v>
       </c>
       <c r="D2518" s="2">
-        <v>9099</v>
+        <v>5926</v>
       </c>
       <c r="E2518" s="1">
         <f t="shared" si="44"/>
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="F2518" s="2">
-        <v>36.74</v>
+        <v>27.44</v>
       </c>
       <c r="G2518" s="2">
-        <v>216.4</v>
+        <v>164.37</v>
       </c>
       <c r="H2518" s="2" t="s">
         <v>7</v>
@@ -82500,10 +82582,10 @@
         <v>45901</v>
       </c>
       <c r="J2518" s="2" t="s">
-        <v>300</v>
+        <v>98</v>
       </c>
       <c r="K2518" s="2" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="L2518" s="29" t="s">
         <v>323</v>
@@ -82511,50 +82593,56 @@
     </row>
     <row r="2519" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2519" s="17">
-        <v>45911.571562500001</v>
+        <v>45911.626828703702</v>
+      </c>
+      <c r="C2519" s="2">
+        <v>302815</v>
+      </c>
+      <c r="D2519" s="2">
+        <v>303929</v>
       </c>
       <c r="E2519" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>1114</v>
       </c>
       <c r="F2519" s="2">
-        <v>41.47</v>
-      </c>
-      <c r="G2519" s="2">
-        <v>240.11</v>
+        <v>164.91</v>
+      </c>
+      <c r="G2519" s="16">
+        <v>1020.81</v>
       </c>
       <c r="H2519" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I2519" s="12">
         <v>45901</v>
       </c>
       <c r="J2519" s="2" t="s">
-        <v>280</v>
+        <v>23</v>
       </c>
       <c r="K2519" s="2" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2520" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2520" s="17">
-        <v>45911.594664351855</v>
+        <v>45911.673402777778</v>
       </c>
       <c r="C2520" s="2">
-        <v>5700</v>
+        <v>9554</v>
       </c>
       <c r="D2520" s="2">
-        <v>5926</v>
+        <v>9821</v>
       </c>
       <c r="E2520" s="1">
         <f t="shared" si="44"/>
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="F2520" s="2">
-        <v>27.44</v>
+        <v>23.04</v>
       </c>
       <c r="G2520" s="2">
-        <v>164.37</v>
+        <v>150</v>
       </c>
       <c r="H2520" s="2" t="s">
         <v>7</v>
@@ -82563,67 +82651,67 @@
         <v>45901</v>
       </c>
       <c r="J2520" s="2" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="K2520" s="2" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="L2520" s="28" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2521" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2521" s="17">
-        <v>45911.626828703702</v>
+        <v>45911.722442129627</v>
       </c>
       <c r="C2521" s="2">
-        <v>302815</v>
+        <v>11268</v>
       </c>
       <c r="D2521" s="2">
-        <v>303929</v>
+        <v>11770</v>
       </c>
       <c r="E2521" s="1">
         <f t="shared" si="44"/>
-        <v>1114</v>
+        <v>502</v>
       </c>
       <c r="F2521" s="2">
-        <v>164.91</v>
-      </c>
-      <c r="G2521" s="16">
-        <v>1020.81</v>
+        <v>23.84</v>
+      </c>
+      <c r="G2521" s="2">
+        <v>150</v>
       </c>
       <c r="H2521" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2521" s="12">
         <v>45901</v>
       </c>
       <c r="J2521" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="K2521" s="2" t="s">
-        <v>80</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2522" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2522" s="17">
-        <v>45911.673402777778</v>
+        <v>45911.752858796295</v>
       </c>
       <c r="C2522" s="2">
-        <v>9554</v>
+        <v>12832</v>
       </c>
       <c r="D2522" s="2">
-        <v>9821</v>
+        <v>13286</v>
       </c>
       <c r="E2522" s="1">
         <f t="shared" si="44"/>
-        <v>267</v>
+        <v>454</v>
       </c>
       <c r="F2522" s="2">
-        <v>23.04</v>
+        <v>40.08</v>
       </c>
       <c r="G2522" s="2">
-        <v>150</v>
+        <v>232.08</v>
       </c>
       <c r="H2522" s="2" t="s">
         <v>7</v>
@@ -82632,70 +82720,64 @@
         <v>45901</v>
       </c>
       <c r="J2522" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="K2522" s="2" t="s">
-        <v>199</v>
+        <v>23</v>
+      </c>
+      <c r="K2522" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="L2522" s="28" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2523" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2523" s="17">
-        <v>45911.722442129627</v>
-      </c>
-      <c r="C2523" s="2">
-        <v>11268</v>
-      </c>
-      <c r="D2523" s="2">
-        <v>11770</v>
+        <v>45911.774282407408</v>
       </c>
       <c r="E2523" s="1">
         <f t="shared" si="44"/>
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="F2523" s="2">
-        <v>23.84</v>
-      </c>
-      <c r="G2523" s="2">
-        <v>150</v>
+        <v>176.48</v>
+      </c>
+      <c r="G2523" s="16">
+        <v>1134.79</v>
       </c>
       <c r="H2523" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2523" s="12">
         <v>45901</v>
       </c>
       <c r="J2523" s="2" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="K2523" s="2" t="s">
-        <v>242</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2524" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2524" s="17">
-        <v>45911.752858796295</v>
+        <v>45915.257349537038</v>
       </c>
       <c r="C2524" s="2">
-        <v>12832</v>
+        <v>800523</v>
       </c>
       <c r="D2524" s="2">
-        <v>13286</v>
+        <v>802164</v>
       </c>
       <c r="E2524" s="1">
         <f t="shared" si="44"/>
-        <v>454</v>
+        <v>1641</v>
       </c>
       <c r="F2524" s="2">
-        <v>40.08</v>
-      </c>
-      <c r="G2524" s="2">
-        <v>232.08</v>
+        <v>165.68</v>
+      </c>
+      <c r="G2524" s="16">
+        <v>1025.5999999999999</v>
       </c>
       <c r="H2524" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2524" s="12">
         <v>45901</v>
@@ -82703,26 +82785,29 @@
       <c r="J2524" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="K2524" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L2524" s="28" t="s">
-        <v>327</v>
+      <c r="K2524" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2525" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2525" s="17">
-        <v>45911.774282407408</v>
+        <v>45915.263078703705</v>
+      </c>
+      <c r="C2525" s="2">
+        <v>589308</v>
+      </c>
+      <c r="D2525" s="2">
+        <v>589898</v>
       </c>
       <c r="E2525" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="F2525" s="2">
-        <v>176.48</v>
+        <v>216.24</v>
       </c>
       <c r="G2525" s="16">
-        <v>1134.79</v>
+        <v>1338.53</v>
       </c>
       <c r="H2525" s="2" t="s">
         <v>8</v>
@@ -82731,115 +82816,234 @@
         <v>45901</v>
       </c>
       <c r="J2525" s="2" t="s">
-        <v>101</v>
+        <v>185</v>
       </c>
       <c r="K2525" s="2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2526" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2526" s="18"/>
-      <c r="C2526" s="1"/>
-      <c r="D2526" s="1"/>
+      <c r="B2526" s="17">
+        <v>45915.285509259258</v>
+      </c>
+      <c r="C2526" s="2">
+        <v>9651</v>
+      </c>
+      <c r="D2526" s="2">
+        <v>9895</v>
+      </c>
       <c r="E2526" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2526" s="1"/>
-      <c r="G2526" s="10"/>
-      <c r="H2526" s="3"/>
-      <c r="J2526" s="7"/>
-      <c r="K2526" s="7"/>
+        <v>244</v>
+      </c>
+      <c r="F2526" s="2">
+        <v>36.14</v>
+      </c>
+      <c r="G2526" s="2">
+        <v>212.91</v>
+      </c>
+      <c r="H2526" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2526" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2526" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K2526" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L2526" s="28" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="2527" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2527" s="18"/>
-      <c r="C2527" s="1"/>
-      <c r="D2527" s="1"/>
+      <c r="B2527" s="17">
+        <v>45915.334606481483</v>
+      </c>
+      <c r="C2527" s="2">
+        <v>458806</v>
+      </c>
+      <c r="D2527" s="2">
+        <v>459748</v>
+      </c>
       <c r="E2527" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2527" s="1"/>
-      <c r="G2527" s="10"/>
-      <c r="H2527" s="3"/>
-      <c r="J2527" s="7"/>
-      <c r="K2527" s="7"/>
+        <v>942</v>
+      </c>
+      <c r="F2527" s="2">
+        <v>167.85</v>
+      </c>
+      <c r="G2527" s="16">
+        <v>1000.38</v>
+      </c>
+      <c r="H2527" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2527" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2527" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2527" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2528" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2528" s="18"/>
-      <c r="C2528" s="1"/>
-      <c r="D2528" s="1"/>
+      <c r="B2528" s="17">
+        <v>45915.363738425927</v>
+      </c>
+      <c r="C2528" s="2">
+        <v>5926</v>
+      </c>
+      <c r="D2528" s="2">
+        <v>6157</v>
+      </c>
       <c r="E2528" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2528" s="1"/>
-      <c r="G2528" s="10"/>
-      <c r="H2528" s="3"/>
-      <c r="J2528" s="7"/>
-      <c r="K2528" s="7"/>
+        <v>231</v>
+      </c>
+      <c r="F2528" s="2">
+        <v>24.09</v>
+      </c>
+      <c r="G2528" s="2">
+        <v>151.53</v>
+      </c>
+      <c r="H2528" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2528" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2528" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2528" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="L2528" s="28"/>
     </row>
     <row r="2529" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2529" s="18"/>
-      <c r="C2529" s="1"/>
-      <c r="D2529" s="1"/>
+      <c r="B2529" s="17">
+        <v>45915.408020833333</v>
+      </c>
       <c r="E2529" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="F2529" s="1"/>
-      <c r="G2529" s="10"/>
-      <c r="H2529" s="3"/>
-      <c r="J2529" s="7"/>
-      <c r="K2529" s="7"/>
+      <c r="F2529" s="2">
+        <v>26.01</v>
+      </c>
+      <c r="G2529" s="2">
+        <v>148.91</v>
+      </c>
+      <c r="H2529" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2529" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2529" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2529" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L2529" s="28" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="2530" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2530" s="18"/>
-      <c r="C2530" s="1"/>
-      <c r="D2530" s="1"/>
+      <c r="B2530" s="17">
+        <v>45915.495752314811</v>
+      </c>
+      <c r="C2530" s="2">
+        <v>10659</v>
+      </c>
+      <c r="D2530" s="2">
+        <v>10941</v>
+      </c>
       <c r="E2530" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2530" s="1"/>
-      <c r="G2530" s="10"/>
-      <c r="H2530" s="3"/>
-      <c r="J2530" s="7"/>
-      <c r="K2530" s="7"/>
+        <v>282</v>
+      </c>
+      <c r="F2530" s="2">
+        <v>23.53</v>
+      </c>
+      <c r="G2530" s="2">
+        <v>148</v>
+      </c>
+      <c r="H2530" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2530" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2530" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2530" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2530" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="2531" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2531" s="18"/>
-      <c r="C2531" s="1"/>
-      <c r="D2531" s="1"/>
+      <c r="B2531" s="17">
+        <v>45915.543564814812</v>
+      </c>
+      <c r="C2531" s="2">
+        <v>435266</v>
+      </c>
+      <c r="D2531" s="2">
+        <v>435429</v>
+      </c>
       <c r="E2531" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2531" s="1"/>
-      <c r="G2531" s="10"/>
-      <c r="H2531" s="3"/>
-      <c r="J2531" s="7"/>
-      <c r="K2531" s="7"/>
+        <v>163</v>
+      </c>
+      <c r="F2531" s="2">
+        <v>160.65</v>
+      </c>
+      <c r="G2531" s="2">
+        <v>946.22</v>
+      </c>
+      <c r="H2531" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2531" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2531" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="K2531" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2531" s="28"/>
     </row>
     <row r="2532" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2532" s="17">
-        <v>45915.257349537038</v>
+        <v>45915.596319444441</v>
       </c>
       <c r="C2532" s="2">
-        <v>800523</v>
+        <v>408759</v>
       </c>
       <c r="D2532" s="2">
-        <v>802164</v>
+        <v>409974</v>
       </c>
       <c r="E2532" s="1">
         <f t="shared" si="44"/>
-        <v>1641</v>
+        <v>1215</v>
       </c>
       <c r="F2532" s="2">
-        <v>165.68</v>
+        <v>190.33</v>
       </c>
       <c r="G2532" s="16">
-        <v>1025.5999999999999</v>
+        <v>1178.17</v>
       </c>
       <c r="H2532" s="2" t="s">
         <v>8</v>
@@ -82851,28 +83055,28 @@
         <v>23</v>
       </c>
       <c r="K2532" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2533" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2533" s="17">
-        <v>45915.263078703705</v>
+        <v>45915.685925925929</v>
       </c>
       <c r="C2533" s="2">
-        <v>589308</v>
+        <v>802164</v>
       </c>
       <c r="D2533" s="2">
-        <v>589898</v>
+        <v>802442</v>
       </c>
       <c r="E2533" s="1">
         <f t="shared" si="44"/>
-        <v>590</v>
+        <v>278</v>
       </c>
       <c r="F2533" s="2">
-        <v>216.24</v>
-      </c>
-      <c r="G2533" s="16">
-        <v>1338.53</v>
+        <v>80.180000000000007</v>
+      </c>
+      <c r="G2533" s="2">
+        <v>496.32</v>
       </c>
       <c r="H2533" s="2" t="s">
         <v>8</v>
@@ -82881,31 +83085,31 @@
         <v>45901</v>
       </c>
       <c r="J2533" s="2" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="K2533" s="2" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2534" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2534" s="17">
-        <v>45915.285509259258</v>
+        <v>45915.726574074077</v>
       </c>
       <c r="C2534" s="2">
-        <v>9651</v>
+        <v>11911</v>
       </c>
       <c r="D2534" s="2">
-        <v>9895</v>
+        <v>12261</v>
       </c>
       <c r="E2534" s="1">
         <f t="shared" si="44"/>
-        <v>244</v>
+        <v>350</v>
       </c>
       <c r="F2534" s="2">
-        <v>36.14</v>
+        <v>22.76</v>
       </c>
       <c r="G2534" s="2">
-        <v>212.91</v>
+        <v>149.31</v>
       </c>
       <c r="H2534" s="2" t="s">
         <v>7</v>
@@ -82914,97 +83118,100 @@
         <v>45901</v>
       </c>
       <c r="J2534" s="2" t="s">
-        <v>291</v>
+        <v>96</v>
       </c>
       <c r="K2534" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2534" s="28" t="s">
-        <v>324</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2535" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2535" s="17">
-        <v>45915.334606481483</v>
+        <v>45916.335821759261</v>
       </c>
       <c r="C2535" s="2">
-        <v>458806</v>
+        <v>4753</v>
       </c>
       <c r="D2535" s="2">
-        <v>459748</v>
+        <v>5097</v>
       </c>
       <c r="E2535" s="1">
         <f t="shared" si="44"/>
-        <v>942</v>
+        <v>344</v>
       </c>
       <c r="F2535" s="2">
-        <v>167.85</v>
-      </c>
-      <c r="G2535" s="16">
-        <v>1000.38</v>
+        <v>23.84</v>
+      </c>
+      <c r="G2535" s="2">
+        <v>150</v>
       </c>
       <c r="H2535" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2535" s="12">
         <v>45901</v>
       </c>
       <c r="J2535" s="2" t="s">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="K2535" s="2" t="s">
-        <v>52</v>
+        <v>206</v>
+      </c>
+      <c r="L2535" s="28" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="2536" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2536" s="17">
-        <v>45915.363738425927</v>
+        <v>45916.514039351852</v>
       </c>
       <c r="C2536" s="2">
-        <v>5926</v>
+        <v>735668</v>
       </c>
       <c r="D2536" s="2">
-        <v>6157</v>
+        <v>736290</v>
       </c>
       <c r="E2536" s="1">
         <f t="shared" si="44"/>
-        <v>231</v>
+        <v>622</v>
       </c>
       <c r="F2536" s="2">
-        <v>24.09</v>
-      </c>
-      <c r="G2536" s="2">
-        <v>151.53</v>
+        <v>196.51</v>
+      </c>
+      <c r="G2536" s="16">
+        <v>1216.44</v>
       </c>
       <c r="H2536" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2536" s="12">
         <v>45901</v>
       </c>
       <c r="J2536" s="2" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="K2536" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L2536" s="28" t="s">
-        <v>317</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2537" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2537" s="17">
-        <v>45915.408020833333</v>
+        <v>45916.61614583333</v>
+      </c>
+      <c r="C2537" s="2">
+        <v>490905</v>
+      </c>
+      <c r="D2537" s="2">
+        <v>491500</v>
       </c>
       <c r="E2537" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>595</v>
       </c>
       <c r="F2537" s="2">
-        <v>26.01</v>
+        <v>32.96</v>
       </c>
       <c r="G2537" s="2">
-        <v>148.91</v>
+        <v>197.43</v>
       </c>
       <c r="H2537" s="2" t="s">
         <v>7</v>
@@ -83013,70 +83220,52 @@
         <v>45901</v>
       </c>
       <c r="J2537" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="K2537" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L2537" s="28" t="s">
-        <v>321</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2538" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2538" s="17">
-        <v>45915.495752314811</v>
-      </c>
-      <c r="C2538" s="2">
-        <v>10659</v>
-      </c>
-      <c r="D2538" s="2">
-        <v>10941</v>
+        <v>45916.616238425922</v>
       </c>
       <c r="E2538" s="1">
         <f t="shared" si="44"/>
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="F2538" s="2">
-        <v>23.53</v>
+        <v>28.77</v>
       </c>
       <c r="G2538" s="2">
-        <v>148</v>
+        <v>172.36</v>
       </c>
       <c r="H2538" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I2538" s="12">
         <v>45901</v>
       </c>
       <c r="J2538" s="2" t="s">
-        <v>46</v>
+        <v>265</v>
       </c>
       <c r="K2538" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2538" t="s">
-        <v>325</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2539" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2539" s="17">
-        <v>45915.543564814812</v>
-      </c>
-      <c r="C2539" s="2">
-        <v>435266</v>
-      </c>
-      <c r="D2539" s="2">
-        <v>435429</v>
+        <v>45916.629062499997</v>
       </c>
       <c r="E2539" s="1">
         <f t="shared" si="44"/>
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="F2539" s="2">
-        <v>160.65</v>
+        <v>141.97</v>
       </c>
       <c r="G2539" s="2">
-        <v>946.22</v>
+        <v>864.6</v>
       </c>
       <c r="H2539" s="2" t="s">
         <v>8</v>
@@ -83085,97 +83274,100 @@
         <v>45901</v>
       </c>
       <c r="J2539" s="2" t="s">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="K2539" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2540" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2540" s="17">
-        <v>45915.596319444441</v>
+        <v>45916.737037037034</v>
       </c>
       <c r="C2540" s="2">
-        <v>408759</v>
+        <v>12261</v>
       </c>
       <c r="D2540" s="2">
-        <v>409974</v>
+        <v>12493</v>
       </c>
       <c r="E2540" s="1">
         <f t="shared" si="44"/>
-        <v>1215</v>
+        <v>232</v>
       </c>
       <c r="F2540" s="2">
-        <v>190.33</v>
-      </c>
-      <c r="G2540" s="16">
-        <v>1178.17</v>
+        <v>13.94</v>
+      </c>
+      <c r="G2540" s="2">
+        <v>81.83</v>
       </c>
       <c r="H2540" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2540" s="12">
         <v>45901</v>
       </c>
       <c r="J2540" s="2" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="K2540" s="2" t="s">
-        <v>63</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2541" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2541" s="17">
-        <v>45915.685925925929</v>
+        <v>45916.739837962959</v>
       </c>
       <c r="C2541" s="2">
-        <v>802164</v>
+        <v>11499</v>
       </c>
       <c r="D2541" s="2">
-        <v>802442</v>
+        <v>11873</v>
       </c>
       <c r="E2541" s="1">
         <f t="shared" si="44"/>
-        <v>278</v>
+        <v>374</v>
       </c>
       <c r="F2541" s="2">
-        <v>80.180000000000007</v>
+        <v>36.049999999999997</v>
       </c>
       <c r="G2541" s="2">
-        <v>496.32</v>
+        <v>234.01</v>
       </c>
       <c r="H2541" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2541" s="12">
         <v>45901</v>
       </c>
       <c r="J2541" s="2" t="s">
-        <v>23</v>
+        <v>255</v>
       </c>
       <c r="K2541" s="2" t="s">
-        <v>77</v>
+        <v>172</v>
+      </c>
+      <c r="L2541" s="28" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="2542" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2542" s="17">
-        <v>45915.726574074077</v>
+        <v>45916.814791666664</v>
       </c>
       <c r="C2542" s="2">
-        <v>11911</v>
+        <v>9569</v>
       </c>
       <c r="D2542" s="2">
-        <v>12261</v>
+        <v>9945</v>
       </c>
       <c r="E2542" s="1">
         <f t="shared" si="44"/>
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="F2542" s="2">
-        <v>22.76</v>
+        <v>41.28</v>
       </c>
       <c r="G2542" s="2">
-        <v>149.31</v>
+        <v>259.64999999999998</v>
       </c>
       <c r="H2542" s="2" t="s">
         <v>7</v>
@@ -83184,115 +83376,229 @@
         <v>45901</v>
       </c>
       <c r="J2542" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="K2542" s="2" t="s">
-        <v>242</v>
+        <v>202</v>
+      </c>
+      <c r="L2542" s="28" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="2543" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2543" s="18"/>
-      <c r="C2543" s="1"/>
-      <c r="D2543" s="1"/>
+      <c r="B2543" s="17">
+        <v>45916.855208333334</v>
+      </c>
+      <c r="C2543" s="2">
+        <v>4168</v>
+      </c>
+      <c r="D2543" s="2">
+        <v>4576</v>
+      </c>
       <c r="E2543" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2543" s="1"/>
-      <c r="G2543" s="10"/>
-      <c r="H2543" s="3"/>
-      <c r="J2543" s="7"/>
-      <c r="K2543" s="7"/>
+        <v>408</v>
+      </c>
+      <c r="F2543" s="2">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="G2543" s="2">
+        <v>216.76</v>
+      </c>
+      <c r="H2543" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2543" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2543" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2543" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2543" s="29" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="2544" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2544" s="18"/>
-      <c r="C2544" s="1"/>
-      <c r="D2544" s="1"/>
+      <c r="B2544" s="17">
+        <v>45919.353472222225</v>
+      </c>
       <c r="E2544" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="F2544" s="1"/>
-      <c r="G2544" s="10"/>
-      <c r="H2544" s="3"/>
-      <c r="J2544" s="7"/>
-      <c r="K2544" s="7"/>
+      <c r="F2544" s="2">
+        <v>317.74</v>
+      </c>
+      <c r="G2544" s="16">
+        <v>1966.83</v>
+      </c>
+      <c r="H2544" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2544" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2544" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2544" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2545" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2545" s="18"/>
-      <c r="C2545" s="1"/>
-      <c r="D2545" s="1"/>
+      <c r="B2545" s="17">
+        <v>45919.366666666669</v>
+      </c>
+      <c r="C2545" s="2">
+        <v>73083</v>
+      </c>
+      <c r="D2545" s="2">
+        <v>76414</v>
+      </c>
       <c r="E2545" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2545" s="1"/>
-      <c r="G2545" s="10"/>
-      <c r="H2545" s="3"/>
-      <c r="J2545" s="7"/>
-      <c r="K2545" s="7"/>
+        <v>3331</v>
+      </c>
+      <c r="F2545" s="2">
+        <v>128.68</v>
+      </c>
+      <c r="G2545" s="2">
+        <v>824.04</v>
+      </c>
+      <c r="H2545" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2545" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2545" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="K2545" s="3" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2546" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2546" s="18"/>
-      <c r="C2546" s="1"/>
-      <c r="D2546" s="1"/>
+      <c r="B2546" s="17">
+        <v>45919.393750000003</v>
+      </c>
+      <c r="C2546" s="2">
+        <v>747894</v>
+      </c>
+      <c r="D2546" s="2">
+        <v>748507</v>
+      </c>
       <c r="E2546" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2546" s="1"/>
-      <c r="G2546" s="10"/>
-      <c r="H2546" s="3"/>
-      <c r="J2546" s="7"/>
-      <c r="K2546" s="7"/>
+        <v>613</v>
+      </c>
+      <c r="F2546" s="2">
+        <v>78.239999999999995</v>
+      </c>
+      <c r="G2546" s="2">
+        <v>500</v>
+      </c>
+      <c r="H2546" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2546" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2546" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K2546" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="2547" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2547" s="18"/>
-      <c r="C2547" s="1"/>
-      <c r="D2547" s="1"/>
+      <c r="B2547" s="17">
+        <v>45919.527083333334</v>
+      </c>
+      <c r="C2547" s="2">
+        <v>725387</v>
+      </c>
+      <c r="D2547" s="2">
+        <v>726555</v>
+      </c>
       <c r="E2547" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2547" s="1"/>
-      <c r="G2547" s="10"/>
-      <c r="H2547" s="3"/>
-      <c r="J2547" s="7"/>
-      <c r="K2547" s="7"/>
+        <v>1168</v>
+      </c>
+      <c r="F2547" s="2">
+        <v>184</v>
+      </c>
+      <c r="G2547" s="16">
+        <v>1146.32</v>
+      </c>
+      <c r="H2547" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2547" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2547" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K2547" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2548" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2548" s="18"/>
-      <c r="C2548" s="1"/>
-      <c r="D2548" s="1"/>
+      <c r="B2548" s="17">
+        <v>45919.544444444444</v>
+      </c>
+      <c r="C2548" s="2">
+        <v>460536</v>
+      </c>
+      <c r="D2548" s="2">
+        <v>461093</v>
+      </c>
       <c r="E2548" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2548" s="1"/>
-      <c r="G2548" s="10"/>
-      <c r="H2548" s="3"/>
-      <c r="J2548" s="7"/>
-      <c r="K2548" s="7"/>
+        <v>557</v>
+      </c>
+      <c r="F2548" s="2">
+        <v>148.19</v>
+      </c>
+      <c r="G2548" s="2">
+        <v>917.32</v>
+      </c>
+      <c r="H2548" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2548" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2548" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2548" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="2549" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2549" s="17">
-        <v>45916.335821759261</v>
+        <v>45919.554861111108</v>
       </c>
       <c r="C2549" s="2">
-        <v>4753</v>
+        <v>12493</v>
       </c>
       <c r="D2549" s="2">
-        <v>5097</v>
+        <v>13026</v>
       </c>
       <c r="E2549" s="1">
         <f t="shared" si="44"/>
-        <v>344</v>
+        <v>533</v>
       </c>
       <c r="F2549" s="2">
-        <v>23.84</v>
+        <v>31.9</v>
       </c>
       <c r="G2549" s="2">
-        <v>150</v>
+        <v>200.65</v>
       </c>
       <c r="H2549" s="2" t="s">
         <v>7</v>
@@ -83301,42 +83607,59 @@
         <v>45901</v>
       </c>
       <c r="J2549" s="2" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="K2549" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L2549" s="28" t="s">
-        <v>320</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2550" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2550" s="17"/>
+      <c r="B2550" s="17">
+        <v>45919.611111111109</v>
+      </c>
       <c r="E2550" s="1">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="I2550" s="12"/>
+      <c r="F2550" s="2">
+        <v>138.72999999999999</v>
+      </c>
+      <c r="G2550" s="2">
+        <v>851.82</v>
+      </c>
+      <c r="H2550" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2550" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2550" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K2550" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L2550" s="28"/>
     </row>
     <row r="2551" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2551" s="17">
-        <v>45916.514039351852</v>
+        <v>45919.752083333333</v>
       </c>
       <c r="C2551" s="2">
-        <v>735668</v>
+        <v>748507</v>
       </c>
       <c r="D2551" s="2">
-        <v>736290</v>
+        <v>748835</v>
       </c>
       <c r="E2551" s="1">
         <f t="shared" si="44"/>
-        <v>622</v>
+        <v>328</v>
       </c>
       <c r="F2551" s="2">
-        <v>196.51</v>
+        <v>209.2</v>
       </c>
       <c r="G2551" s="16">
-        <v>1216.44</v>
+        <v>1294.99</v>
       </c>
       <c r="H2551" s="2" t="s">
         <v>8</v>
@@ -83348,28 +83671,29 @@
         <v>23</v>
       </c>
       <c r="K2551" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="L2551" s="28"/>
     </row>
     <row r="2552" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2552" s="17">
-        <v>45916.61614583333</v>
+        <v>45923.34097222222</v>
       </c>
       <c r="C2552" s="2">
-        <v>490905</v>
+        <v>9945</v>
       </c>
       <c r="D2552" s="2">
-        <v>491500</v>
+        <v>10247</v>
       </c>
       <c r="E2552" s="1">
         <f t="shared" si="44"/>
-        <v>595</v>
+        <v>302</v>
       </c>
       <c r="F2552" s="2">
-        <v>32.96</v>
+        <v>27.71</v>
       </c>
       <c r="G2552" s="2">
-        <v>197.43</v>
+        <v>166.02</v>
       </c>
       <c r="H2552" s="2" t="s">
         <v>7</v>
@@ -83378,85 +83702,106 @@
         <v>45901</v>
       </c>
       <c r="J2552" s="2" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="K2552" s="2" t="s">
-        <v>39</v>
+        <v>202</v>
+      </c>
+      <c r="L2552" s="28" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="2553" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2553" s="17">
-        <v>45916.616238425922</v>
+        <v>45923.344444444447</v>
+      </c>
+      <c r="C2553" s="2">
+        <v>9439</v>
+      </c>
+      <c r="D2553" s="2">
+        <v>9943</v>
       </c>
       <c r="E2553" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="F2553" s="2">
-        <v>28.77</v>
+        <v>38.4</v>
       </c>
       <c r="G2553" s="2">
-        <v>172.36</v>
+        <v>239.23</v>
       </c>
       <c r="H2553" s="2" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I2553" s="12">
         <v>45901</v>
       </c>
       <c r="J2553" s="2" t="s">
-        <v>265</v>
+        <v>112</v>
       </c>
       <c r="K2553" s="2" t="s">
-        <v>56</v>
+        <v>240</v>
+      </c>
+      <c r="L2553" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2554" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2554" s="17">
-        <v>45916.629062499997</v>
+        <v>45923.352777777778</v>
+      </c>
+      <c r="C2554" s="2">
+        <v>11331</v>
+      </c>
+      <c r="D2554" s="2">
+        <v>11795</v>
       </c>
       <c r="E2554" s="1">
         <f t="shared" si="44"/>
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="F2554" s="2">
-        <v>141.97</v>
+        <v>35.18</v>
       </c>
       <c r="G2554" s="2">
-        <v>864.6</v>
+        <v>210.74</v>
       </c>
       <c r="H2554" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2554" s="12">
         <v>45901</v>
       </c>
       <c r="J2554" s="2" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="K2554" s="2" t="s">
-        <v>34</v>
+        <v>218</v>
+      </c>
+      <c r="L2554" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="2555" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2555" s="17">
-        <v>45916.737037037034</v>
+        <v>45923.364583333336</v>
       </c>
       <c r="C2555" s="2">
-        <v>12261</v>
+        <v>491850</v>
       </c>
       <c r="D2555" s="2">
-        <v>12493</v>
+        <v>492183</v>
       </c>
       <c r="E2555" s="1">
         <f t="shared" si="44"/>
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="F2555" s="2">
-        <v>13.94</v>
+        <v>30.29</v>
       </c>
       <c r="G2555" s="2">
-        <v>81.83</v>
+        <v>178.43</v>
       </c>
       <c r="H2555" s="2" t="s">
         <v>7</v>
@@ -83465,106 +83810,94 @@
         <v>45901</v>
       </c>
       <c r="J2555" s="2" t="s">
-        <v>171</v>
+        <v>302</v>
       </c>
       <c r="K2555" s="2" t="s">
-        <v>242</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2556" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2556" s="17">
-        <v>45916.739837962959</v>
+        <v>45923.427777777775</v>
       </c>
       <c r="C2556" s="2">
-        <v>11499</v>
+        <v>149739</v>
       </c>
       <c r="D2556" s="2">
-        <v>11873</v>
+        <v>149996</v>
       </c>
       <c r="E2556" s="1">
-        <f t="shared" si="44"/>
-        <v>374</v>
+        <f t="shared" ref="E2556:E2606" si="45">D2556-C2556</f>
+        <v>257</v>
       </c>
       <c r="F2556" s="2">
-        <v>36.049999999999997</v>
+        <v>114.36</v>
       </c>
       <c r="G2556" s="2">
-        <v>234.01</v>
+        <v>723.94</v>
       </c>
       <c r="H2556" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2556" s="12">
         <v>45901</v>
       </c>
       <c r="J2556" s="2" t="s">
-        <v>255</v>
+        <v>303</v>
       </c>
       <c r="K2556" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2556" s="28" t="s">
-        <v>329</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2557" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2557" s="17">
-        <v>45916.814791666664</v>
+        <v>45923.624305555553</v>
       </c>
       <c r="C2557" s="2">
-        <v>9569</v>
+        <v>726555</v>
       </c>
       <c r="D2557" s="2">
-        <v>9945</v>
+        <v>727160</v>
       </c>
       <c r="E2557" s="1">
-        <f t="shared" si="44"/>
-        <v>376</v>
+        <f t="shared" si="45"/>
+        <v>605</v>
       </c>
       <c r="F2557" s="2">
-        <v>41.28</v>
-      </c>
-      <c r="G2557" s="2">
-        <v>259.64999999999998</v>
+        <v>182.71</v>
+      </c>
+      <c r="G2557" s="16">
+        <v>1112.72</v>
       </c>
       <c r="H2557" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2557" s="12">
         <v>45901</v>
       </c>
       <c r="J2557" s="2" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="K2557" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L2557" s="28" t="s">
-        <v>330</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2558" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2558" s="17">
-        <v>45916.855208333334</v>
-      </c>
-      <c r="C2558" s="2">
-        <v>4168</v>
-      </c>
-      <c r="D2558" s="2">
-        <v>4576</v>
+        <v>45923.732638888891</v>
       </c>
       <c r="E2558" s="1">
-        <f t="shared" si="44"/>
-        <v>408</v>
+        <f t="shared" si="45"/>
+        <v>0</v>
       </c>
       <c r="F2558" s="2">
-        <v>36.799999999999997</v>
+        <v>118.58</v>
       </c>
       <c r="G2558" s="2">
-        <v>216.76</v>
+        <v>722.16</v>
       </c>
       <c r="H2558" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2558" s="12">
         <v>45901</v>
@@ -83573,53 +83906,97 @@
         <v>23</v>
       </c>
       <c r="K2558" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="L2558" s="29" t="s">
-        <v>322</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2559" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2559" s="18"/>
-      <c r="C2559" s="1"/>
-      <c r="D2559" s="1"/>
+      <c r="B2559" s="17">
+        <v>45923.743750000001</v>
+      </c>
+      <c r="C2559" s="2">
+        <v>12280</v>
+      </c>
+      <c r="D2559" s="2">
+        <v>12533</v>
+      </c>
       <c r="E2559" s="1">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2559" s="1"/>
-      <c r="G2559" s="10"/>
-      <c r="H2559" s="3"/>
-      <c r="J2559" s="7"/>
-      <c r="K2559" s="7"/>
+        <f t="shared" si="45"/>
+        <v>253</v>
+      </c>
+      <c r="F2559" s="2">
+        <v>25.11</v>
+      </c>
+      <c r="G2559" s="2">
+        <v>145.41999999999999</v>
+      </c>
+      <c r="H2559" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2559" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2559" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2559" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2559" s="28" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="2560" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2560" s="18"/>
-      <c r="C2560" s="1"/>
-      <c r="D2560" s="1"/>
+      <c r="B2560" s="17">
+        <v>45923.788888888892</v>
+      </c>
+      <c r="C2560" s="2">
+        <v>453011</v>
+      </c>
+      <c r="D2560" s="2">
+        <v>453830</v>
+      </c>
       <c r="E2560" s="1">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="F2560" s="1"/>
-      <c r="G2560" s="10"/>
-      <c r="H2560" s="3"/>
-      <c r="J2560" s="7"/>
-      <c r="K2560" s="7"/>
+        <f t="shared" si="45"/>
+        <v>819</v>
+      </c>
+      <c r="F2560" s="2">
+        <v>206.36</v>
+      </c>
+      <c r="G2560" s="16">
+        <v>1411.56</v>
+      </c>
+      <c r="H2560" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2560" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2560" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K2560" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2561" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2561" s="17">
-        <v>45919.353472222225</v>
+        <v>45923.844444444447</v>
+      </c>
+      <c r="C2561" s="2">
+        <v>803755</v>
+      </c>
+      <c r="D2561" s="2">
+        <v>804142</v>
       </c>
       <c r="E2561" s="1">
-        <f t="shared" si="44"/>
-        <v>0</v>
+        <f t="shared" si="45"/>
+        <v>387</v>
       </c>
       <c r="F2561" s="2">
-        <v>317.74</v>
-      </c>
-      <c r="G2561" s="16">
-        <v>1966.83</v>
+        <v>50.08</v>
+      </c>
+      <c r="G2561" s="2">
+        <v>300</v>
       </c>
       <c r="H2561" s="2" t="s">
         <v>8</v>
@@ -83628,97 +84005,100 @@
         <v>45901</v>
       </c>
       <c r="J2561" s="2" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="K2561" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2562" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2562" s="17">
-        <v>45919.366666666669</v>
+        <v>45917.300219907411</v>
       </c>
       <c r="C2562" s="2">
-        <v>73083</v>
+        <v>220948</v>
       </c>
       <c r="D2562" s="2">
-        <v>76414</v>
+        <v>222131</v>
       </c>
       <c r="E2562" s="1">
-        <f t="shared" si="44"/>
-        <v>3331</v>
+        <f t="shared" si="45"/>
+        <v>1183</v>
       </c>
       <c r="F2562" s="2">
-        <v>128.68</v>
+        <v>55.41</v>
       </c>
       <c r="G2562" s="2">
-        <v>824.04</v>
+        <v>326.39999999999998</v>
       </c>
       <c r="H2562" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2562" s="12">
         <v>45901</v>
       </c>
       <c r="J2562" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K2562" s="3" t="s">
-        <v>69</v>
+        <v>23</v>
+      </c>
+      <c r="K2562" s="2" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="2563" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2563" s="17">
-        <v>45919.393750000003</v>
+        <v>45917.350046296298</v>
       </c>
       <c r="C2563" s="2">
-        <v>747894</v>
+        <v>9099</v>
       </c>
       <c r="D2563" s="2">
-        <v>748507</v>
+        <v>9439</v>
       </c>
       <c r="E2563" s="1">
-        <f t="shared" si="44"/>
-        <v>613</v>
+        <f t="shared" si="45"/>
+        <v>340</v>
       </c>
       <c r="F2563" s="2">
-        <v>78.239999999999995</v>
+        <v>31.65</v>
       </c>
       <c r="G2563" s="2">
-        <v>500</v>
+        <v>190.81</v>
       </c>
       <c r="H2563" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2563" s="12">
         <v>45901</v>
       </c>
       <c r="J2563" s="2" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="K2563" s="2" t="s">
-        <v>27</v>
+        <v>240</v>
+      </c>
+      <c r="L2563" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2564" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2564" s="17">
-        <v>45919.527083333334</v>
+        <v>45917.387835648151</v>
       </c>
       <c r="C2564" s="2">
-        <v>725387</v>
+        <v>736290</v>
       </c>
       <c r="D2564" s="2">
-        <v>726555</v>
+        <v>736457</v>
       </c>
       <c r="E2564" s="1">
-        <f t="shared" si="44"/>
-        <v>1168</v>
+        <f t="shared" si="45"/>
+        <v>167</v>
       </c>
       <c r="F2564" s="2">
-        <v>184</v>
-      </c>
-      <c r="G2564" s="16">
-        <v>1146.32</v>
+        <v>99.26</v>
+      </c>
+      <c r="G2564" s="2">
+        <v>580.66999999999996</v>
       </c>
       <c r="H2564" s="2" t="s">
         <v>8</v>
@@ -83727,31 +84107,32 @@
         <v>45901</v>
       </c>
       <c r="J2564" s="2" t="s">
-        <v>183</v>
+        <v>239</v>
       </c>
       <c r="K2564" s="2" t="s">
-        <v>104</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="L2564" s="29"/>
     </row>
     <row r="2565" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2565" s="17">
-        <v>45919.544444444444</v>
+        <v>45917.406782407408</v>
       </c>
       <c r="C2565" s="2">
-        <v>460536</v>
+        <v>589898</v>
       </c>
       <c r="D2565" s="2">
-        <v>461093</v>
+        <v>590532</v>
       </c>
       <c r="E2565" s="1">
-        <f t="shared" si="44"/>
-        <v>557</v>
+        <f t="shared" si="45"/>
+        <v>634</v>
       </c>
       <c r="F2565" s="2">
-        <v>148.19</v>
-      </c>
-      <c r="G2565" s="2">
-        <v>917.32</v>
+        <v>202.98</v>
+      </c>
+      <c r="G2565" s="16">
+        <v>1307.19</v>
       </c>
       <c r="H2565" s="2" t="s">
         <v>8</v>
@@ -83760,58 +84141,64 @@
         <v>45901</v>
       </c>
       <c r="J2565" s="2" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="K2565" s="2" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2566" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2566" s="17">
-        <v>45919.554861111108</v>
+        <v>45917.455208333333</v>
       </c>
       <c r="C2566" s="2">
-        <v>12493</v>
+        <v>802442</v>
       </c>
       <c r="D2566" s="2">
-        <v>13026</v>
+        <v>803009</v>
       </c>
       <c r="E2566" s="1">
-        <f t="shared" si="44"/>
-        <v>533</v>
+        <f t="shared" si="45"/>
+        <v>567</v>
       </c>
       <c r="F2566" s="2">
-        <v>31.9</v>
+        <v>31.29</v>
       </c>
       <c r="G2566" s="2">
-        <v>200.65</v>
+        <v>200</v>
       </c>
       <c r="H2566" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2566" s="12">
         <v>45901</v>
       </c>
       <c r="J2566" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="K2566" s="2" t="s">
-        <v>242</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2567" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2567" s="17">
-        <v>45919.611111111109</v>
+        <v>45917.565115740741</v>
+      </c>
+      <c r="C2567" s="2">
+        <v>459748</v>
+      </c>
+      <c r="D2567" s="2">
+        <v>460536</v>
       </c>
       <c r="E2567" s="1">
-        <f t="shared" si="44"/>
-        <v>0</v>
+        <f t="shared" si="45"/>
+        <v>788</v>
       </c>
       <c r="F2567" s="2">
-        <v>138.72999999999999</v>
-      </c>
-      <c r="G2567" s="2">
-        <v>851.82</v>
+        <v>222.16</v>
+      </c>
+      <c r="G2567" s="16">
+        <v>1375.2</v>
       </c>
       <c r="H2567" s="2" t="s">
         <v>8</v>
@@ -83820,31 +84207,31 @@
         <v>45901</v>
       </c>
       <c r="J2567" s="2" t="s">
-        <v>184</v>
+        <v>23</v>
       </c>
       <c r="K2567" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2568" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2568" s="17">
-        <v>45919.752083333333</v>
+        <v>45917.578715277778</v>
       </c>
       <c r="C2568" s="2">
-        <v>748507</v>
+        <v>160007</v>
       </c>
       <c r="D2568" s="2">
-        <v>748835</v>
+        <v>160449</v>
       </c>
       <c r="E2568" s="1">
-        <f t="shared" si="44"/>
-        <v>328</v>
+        <f t="shared" si="45"/>
+        <v>442</v>
       </c>
       <c r="F2568" s="2">
-        <v>209.2</v>
-      </c>
-      <c r="G2568" s="16">
-        <v>1294.99</v>
+        <v>24.23</v>
+      </c>
+      <c r="G2568" s="2">
+        <v>100</v>
       </c>
       <c r="H2568" s="2" t="s">
         <v>8</v>
@@ -83856,28 +84243,28 @@
         <v>23</v>
       </c>
       <c r="K2568" s="2" t="s">
-        <v>27</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2569" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2569" s="17">
-        <v>45923.34097222222</v>
+        <v>45917.586608796293</v>
       </c>
       <c r="C2569" s="2">
-        <v>9945</v>
+        <v>10941</v>
       </c>
       <c r="D2569" s="2">
-        <v>10247</v>
+        <v>11331</v>
       </c>
       <c r="E2569" s="1">
-        <f t="shared" si="44"/>
-        <v>302</v>
+        <f t="shared" si="45"/>
+        <v>390</v>
       </c>
       <c r="F2569" s="2">
-        <v>27.71</v>
+        <v>29.03</v>
       </c>
       <c r="G2569" s="2">
-        <v>166.02</v>
+        <v>185.5</v>
       </c>
       <c r="H2569" s="2" t="s">
         <v>7</v>
@@ -83886,73 +84273,71 @@
         <v>45901</v>
       </c>
       <c r="J2569" s="2" t="s">
-        <v>23</v>
+        <v>304</v>
       </c>
       <c r="K2569" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L2569" s="28" t="s">
-        <v>330</v>
+        <v>218</v>
+      </c>
+      <c r="L2569" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="2570" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2570" s="17">
-        <v>45923.344444444447</v>
+        <v>45917.64707175926</v>
       </c>
       <c r="C2570" s="2">
-        <v>9439</v>
+        <v>451682</v>
       </c>
       <c r="D2570" s="2">
-        <v>9943</v>
+        <v>452549</v>
       </c>
       <c r="E2570" s="1">
-        <f t="shared" si="44"/>
-        <v>504</v>
+        <f t="shared" si="45"/>
+        <v>867</v>
       </c>
       <c r="F2570" s="2">
-        <v>38.4</v>
-      </c>
-      <c r="G2570" s="2">
-        <v>239.23</v>
+        <v>217.1</v>
+      </c>
+      <c r="G2570" s="16">
+        <v>1485.01</v>
       </c>
       <c r="H2570" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2570" s="12">
         <v>45901</v>
       </c>
       <c r="J2570" s="2" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="K2570" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2570" s="29" t="s">
-        <v>323</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="L2570" s="28"/>
     </row>
     <row r="2571" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2571" s="17">
-        <v>45923.352777777778</v>
+        <v>45917.673391203702</v>
       </c>
       <c r="C2571" s="2">
-        <v>11331</v>
+        <v>803009</v>
       </c>
       <c r="D2571" s="2">
-        <v>11795</v>
+        <v>803201</v>
       </c>
       <c r="E2571" s="1">
-        <f t="shared" si="44"/>
-        <v>464</v>
+        <f t="shared" si="45"/>
+        <v>192</v>
       </c>
       <c r="F2571" s="2">
-        <v>35.18</v>
-      </c>
-      <c r="G2571" s="2">
-        <v>210.74</v>
+        <v>181.94</v>
+      </c>
+      <c r="G2571" s="16">
+        <v>1126.22</v>
       </c>
       <c r="H2571" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2571" s="12">
         <v>45901</v>
@@ -83961,64 +84346,61 @@
         <v>23</v>
       </c>
       <c r="K2571" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2571" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2572" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2572" s="17">
-        <v>45923.364583333336</v>
+        <v>45917.699097222219</v>
       </c>
       <c r="C2572" s="2">
-        <v>491850</v>
+        <v>155399</v>
       </c>
       <c r="D2572" s="2">
-        <v>492183</v>
+        <v>156490</v>
       </c>
       <c r="E2572" s="1">
-        <f t="shared" si="44"/>
-        <v>333</v>
+        <f t="shared" si="45"/>
+        <v>1091</v>
       </c>
       <c r="F2572" s="2">
-        <v>30.29</v>
-      </c>
-      <c r="G2572" s="2">
-        <v>178.43</v>
+        <v>340.86</v>
+      </c>
+      <c r="G2572" s="16">
+        <v>2109.9499999999998</v>
       </c>
       <c r="H2572" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2572" s="12">
         <v>45901</v>
       </c>
       <c r="J2572" s="2" t="s">
-        <v>302</v>
+        <v>23</v>
       </c>
       <c r="K2572" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2573" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2573" s="17">
-        <v>45923.427777777775</v>
+        <v>45922.273611111108</v>
       </c>
       <c r="C2573" s="2">
-        <v>149739</v>
+        <v>432019</v>
       </c>
       <c r="D2573" s="2">
-        <v>149996</v>
+        <v>432929</v>
       </c>
       <c r="E2573" s="1">
-        <f t="shared" ref="E2573:E2636" si="45">D2573-C2573</f>
-        <v>257</v>
+        <f t="shared" si="45"/>
+        <v>910</v>
       </c>
       <c r="F2573" s="2">
-        <v>114.36</v>
+        <v>114.96</v>
       </c>
       <c r="G2573" s="2">
-        <v>723.94</v>
+        <v>700.11</v>
       </c>
       <c r="H2573" s="2" t="s">
         <v>8</v>
@@ -84027,34 +84409,34 @@
         <v>45901</v>
       </c>
       <c r="J2573" s="2" t="s">
-        <v>303</v>
+        <v>165</v>
       </c>
       <c r="K2573" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2574" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2574" s="17">
-        <v>45923.624305555553</v>
+        <v>45922.362500000003</v>
       </c>
       <c r="C2574" s="2">
-        <v>726555</v>
+        <v>6907</v>
       </c>
       <c r="D2574" s="2">
-        <v>727160</v>
+        <v>7301</v>
       </c>
       <c r="E2574" s="1">
         <f t="shared" si="45"/>
-        <v>605</v>
+        <v>394</v>
       </c>
       <c r="F2574" s="2">
-        <v>182.71</v>
-      </c>
-      <c r="G2574" s="16">
-        <v>1112.72</v>
+        <v>30.91</v>
+      </c>
+      <c r="G2574" s="2">
+        <v>182.05</v>
       </c>
       <c r="H2574" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2574" s="12">
         <v>45901</v>
@@ -84063,22 +84445,31 @@
         <v>23</v>
       </c>
       <c r="K2574" s="2" t="s">
-        <v>104</v>
+        <v>208</v>
+      </c>
+      <c r="L2574" s="28" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="2575" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2575" s="17">
-        <v>45923.732638888891</v>
+        <v>45922.390277777777</v>
+      </c>
+      <c r="C2575" s="2">
+        <v>590532</v>
+      </c>
+      <c r="D2575" s="2">
+        <v>591136</v>
       </c>
       <c r="E2575" s="1">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>604</v>
       </c>
       <c r="F2575" s="2">
-        <v>118.58</v>
-      </c>
-      <c r="G2575" s="2">
-        <v>722.16</v>
+        <v>204.02</v>
+      </c>
+      <c r="G2575" s="16">
+        <v>1313.92</v>
       </c>
       <c r="H2575" s="2" t="s">
         <v>8</v>
@@ -84087,31 +84478,31 @@
         <v>45901</v>
       </c>
       <c r="J2575" s="2" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="K2575" s="2" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2576" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2576" s="17">
-        <v>45923.743750000001</v>
+        <v>45922.450694444444</v>
       </c>
       <c r="C2576" s="2">
-        <v>12280</v>
+        <v>6621</v>
       </c>
       <c r="D2576" s="2">
-        <v>12533</v>
+        <v>6856</v>
       </c>
       <c r="E2576" s="1">
         <f t="shared" si="45"/>
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="F2576" s="2">
-        <v>25.11</v>
+        <v>197.11</v>
       </c>
       <c r="G2576" s="2">
-        <v>145.41999999999999</v>
+        <v>116.09</v>
       </c>
       <c r="H2576" s="2" t="s">
         <v>7</v>
@@ -84123,31 +84514,28 @@
         <v>23</v>
       </c>
       <c r="K2576" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2576" s="28" t="s">
-        <v>329</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2577" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2577" s="17">
-        <v>45923.788888888892</v>
+        <v>45922.561805555553</v>
       </c>
       <c r="C2577" s="2">
-        <v>453011</v>
+        <v>160449</v>
       </c>
       <c r="D2577" s="2">
-        <v>453830</v>
+        <v>160804</v>
       </c>
       <c r="E2577" s="1">
         <f t="shared" si="45"/>
-        <v>819</v>
+        <v>355</v>
       </c>
       <c r="F2577" s="2">
-        <v>206.36</v>
-      </c>
-      <c r="G2577" s="16">
-        <v>1411.56</v>
+        <v>24.64</v>
+      </c>
+      <c r="G2577" s="2">
+        <v>150</v>
       </c>
       <c r="H2577" s="2" t="s">
         <v>8</v>
@@ -84156,31 +84544,31 @@
         <v>45901</v>
       </c>
       <c r="J2577" s="2" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="K2577" s="2" t="s">
-        <v>29</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2578" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2578" s="17">
-        <v>45923.844444444447</v>
+        <v>45922.56527777778</v>
       </c>
       <c r="C2578" s="2">
-        <v>803755</v>
+        <v>436502</v>
       </c>
       <c r="D2578" s="2">
-        <v>804142</v>
+        <v>437078</v>
       </c>
       <c r="E2578" s="1">
         <f t="shared" si="45"/>
-        <v>387</v>
+        <v>576</v>
       </c>
       <c r="F2578" s="2">
-        <v>50.08</v>
-      </c>
-      <c r="G2578" s="2">
-        <v>300</v>
+        <v>199.2</v>
+      </c>
+      <c r="G2578" s="16">
+        <v>1223.1400000000001</v>
       </c>
       <c r="H2578" s="2" t="s">
         <v>8</v>
@@ -84189,31 +84577,31 @@
         <v>45901</v>
       </c>
       <c r="J2578" s="2" t="s">
-        <v>105</v>
+        <v>184</v>
       </c>
       <c r="K2578" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2579" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2579" s="17">
-        <v>45917.300219907411</v>
+        <v>45922.574305555558</v>
       </c>
       <c r="C2579" s="2">
-        <v>220948</v>
+        <v>13797</v>
       </c>
       <c r="D2579" s="2">
-        <v>222131</v>
+        <v>14329</v>
       </c>
       <c r="E2579" s="1">
         <f t="shared" si="45"/>
-        <v>1183</v>
+        <v>532</v>
       </c>
       <c r="F2579" s="2">
-        <v>55.41</v>
+        <v>39.729999999999997</v>
       </c>
       <c r="G2579" s="2">
-        <v>326.39999999999998</v>
+        <v>237.98</v>
       </c>
       <c r="H2579" s="2" t="s">
         <v>7</v>
@@ -84222,67 +84610,67 @@
         <v>45901</v>
       </c>
       <c r="J2579" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2579" s="2" t="s">
-        <v>87</v>
+        <v>248</v>
+      </c>
+      <c r="K2579" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L2579" s="28" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2580" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2580" s="17">
-        <v>45917.350046296298</v>
+        <v>45922.664583333331</v>
       </c>
       <c r="C2580" s="2">
-        <v>9099</v>
+        <v>803201</v>
       </c>
       <c r="D2580" s="2">
-        <v>9439</v>
+        <v>803755</v>
       </c>
       <c r="E2580" s="1">
         <f t="shared" si="45"/>
-        <v>340</v>
+        <v>554</v>
       </c>
       <c r="F2580" s="2">
-        <v>31.65</v>
-      </c>
-      <c r="G2580" s="2">
-        <v>190.81</v>
+        <v>183.34</v>
+      </c>
+      <c r="G2580" s="16">
+        <v>1116.54</v>
       </c>
       <c r="H2580" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2580" s="12">
         <v>45901</v>
       </c>
       <c r="J2580" s="2" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="K2580" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2580" s="29" t="s">
-        <v>323</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2581" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2581" s="17">
-        <v>45917.387835648151</v>
+        <v>45924.324999999997</v>
       </c>
       <c r="C2581" s="2">
-        <v>736290</v>
+        <v>770704</v>
       </c>
       <c r="D2581" s="2">
-        <v>736457</v>
+        <v>771221</v>
       </c>
       <c r="E2581" s="1">
         <f t="shared" si="45"/>
-        <v>167</v>
+        <v>517</v>
       </c>
       <c r="F2581" s="2">
-        <v>99.26</v>
-      </c>
-      <c r="G2581" s="2">
-        <v>580.66999999999996</v>
+        <v>187.65</v>
+      </c>
+      <c r="G2581" s="16">
+        <v>1246.04</v>
       </c>
       <c r="H2581" s="2" t="s">
         <v>8</v>
@@ -84291,31 +84679,31 @@
         <v>45901</v>
       </c>
       <c r="J2581" s="2" t="s">
-        <v>239</v>
+        <v>76</v>
       </c>
       <c r="K2581" s="2" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2582" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2582" s="17">
-        <v>45917.406782407408</v>
+        <v>45924.361111111109</v>
       </c>
       <c r="C2582" s="2">
-        <v>589898</v>
+        <v>736816</v>
       </c>
       <c r="D2582" s="2">
-        <v>590532</v>
+        <v>737691</v>
       </c>
       <c r="E2582" s="1">
         <f t="shared" si="45"/>
-        <v>634</v>
+        <v>875</v>
       </c>
       <c r="F2582" s="2">
-        <v>202.98</v>
-      </c>
-      <c r="G2582" s="16">
-        <v>1307.19</v>
+        <v>135</v>
+      </c>
+      <c r="G2582" s="2">
+        <v>789.76</v>
       </c>
       <c r="H2582" s="2" t="s">
         <v>8</v>
@@ -84324,97 +84712,100 @@
         <v>45901</v>
       </c>
       <c r="J2582" s="2" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="K2582" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2583" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2583" s="17">
-        <v>45917.455208333333</v>
+        <v>45924.365972222222</v>
       </c>
       <c r="C2583" s="2">
-        <v>802442</v>
+        <v>4576</v>
       </c>
       <c r="D2583" s="2">
-        <v>803009</v>
+        <v>5044</v>
       </c>
       <c r="E2583" s="1">
         <f t="shared" si="45"/>
-        <v>567</v>
+        <v>468</v>
       </c>
       <c r="F2583" s="2">
-        <v>31.29</v>
+        <v>37.5</v>
       </c>
       <c r="G2583" s="2">
-        <v>200</v>
+        <v>224.66</v>
       </c>
       <c r="H2583" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2583" s="12">
         <v>45901</v>
       </c>
-      <c r="J2583" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="K2583" s="2" t="s">
-        <v>77</v>
+        <v>241</v>
+      </c>
+      <c r="L2583" s="29" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="2584" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2584" s="17">
-        <v>45917.565115740741</v>
+        <v>45924.383333333331</v>
       </c>
       <c r="C2584" s="2">
-        <v>459748</v>
+        <v>5400</v>
       </c>
       <c r="D2584" s="2">
-        <v>460536</v>
+        <v>6050</v>
       </c>
       <c r="E2584" s="1">
         <f t="shared" si="45"/>
-        <v>788</v>
+        <v>650</v>
       </c>
       <c r="F2584" s="2">
-        <v>222.16</v>
-      </c>
-      <c r="G2584" s="16">
-        <v>1375.2</v>
+        <v>24.82</v>
+      </c>
+      <c r="G2584" s="2">
+        <v>154.65</v>
       </c>
       <c r="H2584" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2584" s="12">
         <v>45901</v>
       </c>
       <c r="J2584" s="2" t="s">
-        <v>23</v>
+        <v>305</v>
       </c>
       <c r="K2584" s="2" t="s">
-        <v>52</v>
+        <v>206</v>
+      </c>
+      <c r="L2584" s="28" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="2585" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2585" s="17">
-        <v>45917.578715277778</v>
+        <v>45924.405555555553</v>
       </c>
       <c r="C2585" s="2">
-        <v>160007</v>
+        <v>437078</v>
       </c>
       <c r="D2585" s="2">
-        <v>160449</v>
+        <v>437531</v>
       </c>
       <c r="E2585" s="1">
         <f t="shared" si="45"/>
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F2585" s="2">
-        <v>24.23</v>
-      </c>
-      <c r="G2585" s="2">
-        <v>100</v>
+        <v>172.04</v>
+      </c>
+      <c r="G2585" s="16">
+        <v>1116.54</v>
       </c>
       <c r="H2585" s="2" t="s">
         <v>8</v>
@@ -84423,100 +84814,96 @@
         <v>45901</v>
       </c>
       <c r="J2585" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="K2585" s="2" t="s">
-        <v>252</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="L2585" s="28"/>
     </row>
     <row r="2586" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2586" s="17">
-        <v>45917.586608796293</v>
+        <v>45924.607638888891</v>
       </c>
       <c r="C2586" s="2">
-        <v>10941</v>
+        <v>804142</v>
       </c>
       <c r="D2586" s="2">
-        <v>11331</v>
+        <v>804443</v>
       </c>
       <c r="E2586" s="1">
         <f t="shared" si="45"/>
-        <v>390</v>
+        <v>301</v>
       </c>
       <c r="F2586" s="2">
-        <v>29.03</v>
+        <v>157.46</v>
       </c>
       <c r="G2586" s="2">
-        <v>185.5</v>
+        <v>958.95</v>
       </c>
       <c r="H2586" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2586" s="12">
         <v>45901</v>
       </c>
-      <c r="J2586" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="K2586" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2586" t="s">
-        <v>325</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2587" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2587" s="17">
-        <v>45917.64707175926</v>
+        <v>45924.70208333333</v>
       </c>
       <c r="C2587" s="2">
-        <v>451682</v>
+        <v>492183</v>
       </c>
       <c r="D2587" s="2">
-        <v>452549</v>
+        <v>492582</v>
       </c>
       <c r="E2587" s="1">
         <f t="shared" si="45"/>
-        <v>867</v>
+        <v>399</v>
       </c>
       <c r="F2587" s="2">
-        <v>217.1</v>
-      </c>
-      <c r="G2587" s="16">
-        <v>1485.01</v>
+        <v>38.17</v>
+      </c>
+      <c r="G2587" s="2">
+        <v>224.82</v>
       </c>
       <c r="H2587" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2587" s="12">
         <v>45901</v>
       </c>
       <c r="J2587" s="2" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="K2587" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="L2587" s="28"/>
     </row>
     <row r="2588" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2588" s="17">
-        <v>45917.673391203702</v>
+        <v>45924.727777777778</v>
       </c>
       <c r="C2588" s="2">
-        <v>803009</v>
+        <v>461093</v>
       </c>
       <c r="D2588" s="2">
-        <v>803201</v>
+        <v>461871</v>
       </c>
       <c r="E2588" s="1">
         <f t="shared" si="45"/>
-        <v>192</v>
+        <v>778</v>
       </c>
       <c r="F2588" s="2">
-        <v>181.94</v>
+        <v>22.91</v>
       </c>
       <c r="G2588" s="16">
-        <v>1126.22</v>
+        <v>1395.59</v>
       </c>
       <c r="H2588" s="2" t="s">
         <v>8</v>
@@ -84524,167 +84911,165 @@
       <c r="I2588" s="12">
         <v>45901</v>
       </c>
-      <c r="J2588" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="K2588" s="2" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2589" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2589" s="17">
-        <v>45917.699097222219</v>
+        <v>45924.728472222225</v>
       </c>
       <c r="C2589" s="2">
-        <v>155399</v>
+        <v>13026</v>
       </c>
       <c r="D2589" s="2">
-        <v>156490</v>
+        <v>13402</v>
       </c>
       <c r="E2589" s="1">
         <f t="shared" si="45"/>
-        <v>1091</v>
+        <v>376</v>
       </c>
       <c r="F2589" s="2">
-        <v>340.86</v>
-      </c>
-      <c r="G2589" s="16">
-        <v>2109.9499999999998</v>
+        <v>27.11</v>
+      </c>
+      <c r="G2589" s="2">
+        <v>170.52</v>
       </c>
       <c r="H2589" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2589" s="12">
         <v>45901</v>
       </c>
       <c r="J2589" s="2" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="K2589" s="2" t="s">
-        <v>35</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2590" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2590" s="17">
-        <v>45922.273611111108</v>
+        <v>45918.321527777778</v>
       </c>
       <c r="C2590" s="2">
-        <v>432019</v>
+        <v>6157</v>
       </c>
       <c r="D2590" s="2">
-        <v>432929</v>
+        <v>6621</v>
       </c>
       <c r="E2590" s="1">
         <f t="shared" si="45"/>
-        <v>910</v>
+        <v>464</v>
       </c>
       <c r="F2590" s="2">
-        <v>114.96</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="G2590" s="2">
-        <v>700.11</v>
+        <v>259.37</v>
       </c>
       <c r="H2590" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2590" s="12">
         <v>45901</v>
       </c>
       <c r="J2590" s="2" t="s">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="K2590" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="L2590" s="28"/>
     </row>
     <row r="2591" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2591" s="17">
-        <v>45922.362500000003</v>
+        <v>45918.347222222219</v>
       </c>
       <c r="C2591" s="2">
-        <v>6907</v>
+        <v>309541</v>
       </c>
       <c r="D2591" s="2">
-        <v>7301</v>
+        <v>310183</v>
       </c>
       <c r="E2591" s="1">
         <f t="shared" si="45"/>
-        <v>394</v>
+        <v>642</v>
       </c>
       <c r="F2591" s="2">
-        <v>30.91</v>
-      </c>
-      <c r="G2591" s="2">
-        <v>182.05</v>
+        <v>186.29</v>
+      </c>
+      <c r="G2591" s="16">
+        <v>1076.75</v>
       </c>
       <c r="H2591" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2591" s="12">
         <v>45901</v>
       </c>
       <c r="J2591" s="2" t="s">
-        <v>23</v>
+        <v>277</v>
       </c>
       <c r="K2591" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L2591" s="28" t="s">
-        <v>326</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2592" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2592" s="17">
-        <v>45922.390277777777</v>
+        <v>45918.367361111108</v>
       </c>
       <c r="C2592" s="2">
-        <v>590532</v>
+        <v>6475</v>
       </c>
       <c r="D2592" s="2">
-        <v>591136</v>
+        <v>6907</v>
       </c>
       <c r="E2592" s="1">
         <f t="shared" si="45"/>
-        <v>604</v>
+        <v>432</v>
       </c>
       <c r="F2592" s="2">
-        <v>204.02</v>
-      </c>
-      <c r="G2592" s="16">
-        <v>1313.92</v>
+        <v>34.96</v>
+      </c>
+      <c r="G2592" s="2">
+        <v>204.17</v>
       </c>
       <c r="H2592" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2592" s="12">
         <v>45901</v>
       </c>
       <c r="J2592" s="2" t="s">
-        <v>137</v>
+        <v>244</v>
       </c>
       <c r="K2592" s="2" t="s">
-        <v>38</v>
+        <v>208</v>
+      </c>
+      <c r="L2592" s="28" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="2593" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2593" s="17">
-        <v>45922.450694444444</v>
+        <v>45918.400000000001</v>
       </c>
       <c r="C2593" s="2">
-        <v>6621</v>
+        <v>5097</v>
       </c>
       <c r="D2593" s="2">
-        <v>6856</v>
+        <v>5400</v>
       </c>
       <c r="E2593" s="1">
         <f t="shared" si="45"/>
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="F2593" s="2">
-        <v>197.11</v>
+        <v>31.36</v>
       </c>
       <c r="G2593" s="2">
-        <v>116.09</v>
+        <v>176.87</v>
       </c>
       <c r="H2593" s="2" t="s">
         <v>7</v>
@@ -84693,34 +85078,34 @@
         <v>45901</v>
       </c>
       <c r="J2593" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="K2593" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L2593" s="28" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2594" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2594" s="17">
-        <v>45922.561805555553</v>
+        <v>45918.40902777778</v>
       </c>
       <c r="C2594" s="2">
-        <v>160449</v>
+        <v>435429</v>
       </c>
       <c r="D2594" s="2">
-        <v>160804</v>
+        <v>436351</v>
       </c>
       <c r="E2594" s="1">
         <f t="shared" si="45"/>
-        <v>355</v>
+        <v>922</v>
       </c>
       <c r="F2594" s="2">
-        <v>24.64</v>
+        <v>114.38</v>
       </c>
       <c r="G2594" s="2">
-        <v>150</v>
+        <v>722.88</v>
       </c>
       <c r="H2594" s="2" t="s">
         <v>8</v>
@@ -84729,175 +85114,233 @@
         <v>45901</v>
       </c>
       <c r="J2594" s="2" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="K2594" s="2" t="s">
-        <v>252</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2595" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2595" s="17">
-        <v>45922.56527777778</v>
-      </c>
-      <c r="C2595" s="2">
-        <v>436502</v>
-      </c>
-      <c r="D2595" s="2">
-        <v>437078</v>
+        <v>45918.415277777778</v>
       </c>
       <c r="E2595" s="1">
         <f t="shared" si="45"/>
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="F2595" s="2">
-        <v>199.2</v>
-      </c>
-      <c r="G2595" s="16">
-        <v>1223.1400000000001</v>
+        <v>25.34</v>
+      </c>
+      <c r="G2595" s="2">
+        <v>163.44</v>
       </c>
       <c r="H2595" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2595" s="12">
         <v>45901</v>
       </c>
       <c r="J2595" s="2" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K2595" s="2" t="s">
-        <v>65</v>
+        <v>199</v>
+      </c>
+      <c r="L2595" s="28" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="2596" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2596" s="17">
-        <v>45922.574305555558</v>
+        <v>45918.488194444442</v>
       </c>
       <c r="C2596" s="2">
-        <v>13797</v>
+        <v>736457</v>
       </c>
       <c r="D2596" s="2">
-        <v>14329</v>
+        <v>736816</v>
       </c>
       <c r="E2596" s="1">
         <f t="shared" si="45"/>
-        <v>532</v>
+        <v>359</v>
       </c>
       <c r="F2596" s="2">
-        <v>39.729999999999997</v>
+        <v>141.34</v>
       </c>
       <c r="G2596" s="2">
-        <v>237.98</v>
+        <v>853.72</v>
       </c>
       <c r="H2596" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2596" s="12">
         <v>45901</v>
       </c>
       <c r="J2596" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K2596" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L2596" s="28" t="s">
-        <v>327</v>
+        <v>140</v>
+      </c>
+      <c r="K2596" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2597" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2597" s="17">
-        <v>45922.664583333331</v>
+        <v>45918.495833333334</v>
       </c>
       <c r="C2597" s="2">
-        <v>803201</v>
+        <v>13286</v>
       </c>
       <c r="D2597" s="2">
-        <v>803755</v>
+        <v>13797</v>
       </c>
       <c r="E2597" s="1">
         <f t="shared" si="45"/>
-        <v>554</v>
+        <v>511</v>
       </c>
       <c r="F2597" s="2">
-        <v>183.34</v>
-      </c>
-      <c r="G2597" s="16">
-        <v>1116.54</v>
+        <v>40.51</v>
+      </c>
+      <c r="G2597" s="2">
+        <v>242.67</v>
       </c>
       <c r="H2597" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2597" s="12">
         <v>45901</v>
       </c>
       <c r="J2597" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2597" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
+      </c>
+      <c r="K2597" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L2597" s="28" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2598" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2598" s="18"/>
-      <c r="C2598" s="1"/>
-      <c r="D2598" s="1"/>
+      <c r="B2598" s="17">
+        <v>45918.536805555559</v>
+      </c>
+      <c r="C2598" s="2">
+        <v>8183</v>
+      </c>
+      <c r="D2598" s="2">
+        <v>9083</v>
+      </c>
       <c r="E2598" s="1">
         <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2598" s="1"/>
-      <c r="G2598" s="10"/>
-      <c r="H2598" s="3"/>
-      <c r="J2598" s="7"/>
-      <c r="K2598" s="7"/>
+        <v>900</v>
+      </c>
+      <c r="F2598" s="2">
+        <v>12.03</v>
+      </c>
+      <c r="G2598" s="2">
+        <v>72.09</v>
+      </c>
+      <c r="H2598" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2598" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2598" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2598" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L2598" s="28"/>
     </row>
     <row r="2599" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2599" s="18"/>
-      <c r="C2599" s="1"/>
-      <c r="D2599" s="1"/>
+      <c r="B2599" s="17">
+        <v>45918.634027777778</v>
+      </c>
+      <c r="C2599" s="2">
+        <v>11873</v>
+      </c>
+      <c r="D2599" s="2">
+        <v>12280</v>
+      </c>
       <c r="E2599" s="1">
         <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2599" s="1"/>
-      <c r="G2599" s="10"/>
-      <c r="H2599" s="3"/>
-      <c r="J2599" s="7"/>
-      <c r="K2599" s="7"/>
+        <v>407</v>
+      </c>
+      <c r="F2599" s="2">
+        <v>34.119999999999997</v>
+      </c>
+      <c r="G2599" s="2">
+        <v>201</v>
+      </c>
+      <c r="H2599" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2599" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2599" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2599" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2599" s="28" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="2600" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2600" s="18"/>
-      <c r="C2600" s="1"/>
-      <c r="D2600" s="1"/>
+      <c r="B2600" s="17">
+        <v>45918.720833333333</v>
+      </c>
+      <c r="C2600" s="2">
+        <v>491500</v>
+      </c>
+      <c r="D2600" s="2">
+        <v>491850</v>
+      </c>
       <c r="E2600" s="1">
         <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2600" s="1"/>
-      <c r="G2600" s="10"/>
-      <c r="H2600" s="3"/>
-      <c r="J2600" s="7"/>
-      <c r="K2600" s="7"/>
+        <v>350</v>
+      </c>
+      <c r="F2600" s="2">
+        <v>35.75</v>
+      </c>
+      <c r="G2600" s="2">
+        <v>203.42</v>
+      </c>
+      <c r="H2600" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2600" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2600" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="K2600" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2601" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2601" s="17">
-        <v>45924.324999999997</v>
+        <v>45918.787499999999</v>
       </c>
       <c r="C2601" s="2">
-        <v>770704</v>
+        <v>436351</v>
       </c>
       <c r="D2601" s="2">
-        <v>771221</v>
+        <v>436502</v>
       </c>
       <c r="E2601" s="1">
         <f t="shared" si="45"/>
-        <v>517</v>
+        <v>151</v>
       </c>
       <c r="F2601" s="2">
-        <v>187.65</v>
+        <v>168.62</v>
       </c>
       <c r="G2601" s="16">
-        <v>1246.04</v>
+        <v>1084.25</v>
       </c>
       <c r="H2601" s="2" t="s">
         <v>8</v>
@@ -84906,31 +85349,31 @@
         <v>45901</v>
       </c>
       <c r="J2601" s="2" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="K2601" s="2" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2602" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2602" s="17">
-        <v>45924.361111111109</v>
+        <v>45918.847222222219</v>
       </c>
       <c r="C2602" s="2">
-        <v>736816</v>
+        <v>452549</v>
       </c>
       <c r="D2602" s="2">
-        <v>737691</v>
+        <v>453011</v>
       </c>
       <c r="E2602" s="1">
         <f t="shared" si="45"/>
-        <v>875</v>
+        <v>462</v>
       </c>
       <c r="F2602" s="2">
-        <v>135</v>
-      </c>
-      <c r="G2602" s="2">
-        <v>789.76</v>
+        <v>165.48</v>
+      </c>
+      <c r="G2602" s="16">
+        <v>1057.42</v>
       </c>
       <c r="H2602" s="2" t="s">
         <v>8</v>
@@ -84939,31 +85382,31 @@
         <v>45901</v>
       </c>
       <c r="J2602" s="2" t="s">
-        <v>74</v>
+        <v>307</v>
       </c>
       <c r="K2602" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2603" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2603" s="17">
-        <v>45924.365972222222</v>
+        <v>45918.87777777778</v>
       </c>
       <c r="C2603" s="2">
-        <v>4576</v>
+        <v>8580</v>
       </c>
       <c r="D2603" s="2">
-        <v>5044</v>
+        <v>9476</v>
       </c>
       <c r="E2603" s="1">
         <f t="shared" si="45"/>
-        <v>468</v>
+        <v>896</v>
       </c>
       <c r="F2603" s="2">
-        <v>37.5</v>
+        <v>34.159999999999997</v>
       </c>
       <c r="G2603" s="2">
-        <v>224.66</v>
+        <v>200</v>
       </c>
       <c r="H2603" s="2" t="s">
         <v>7</v>
@@ -84971,592 +85414,685 @@
       <c r="I2603" s="12">
         <v>45901</v>
       </c>
+      <c r="J2603" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="K2603" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="L2603" s="29" t="s">
-        <v>322</v>
+        <v>251</v>
+      </c>
+      <c r="L2603" s="28" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="2604" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2604" s="17">
-        <v>45924.383333333331</v>
+        <v>45925.277083333334</v>
       </c>
       <c r="C2604" s="2">
-        <v>5400</v>
+        <v>737691</v>
       </c>
       <c r="D2604" s="2">
-        <v>6050</v>
+        <v>737947</v>
       </c>
       <c r="E2604" s="1">
         <f t="shared" si="45"/>
-        <v>650</v>
+        <v>256</v>
       </c>
       <c r="F2604" s="2">
-        <v>24.82</v>
+        <v>102.81</v>
       </c>
       <c r="G2604" s="2">
-        <v>154.65</v>
+        <v>621</v>
       </c>
       <c r="H2604" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2604" s="12">
+        <v>8</v>
+      </c>
+      <c r="I2604" s="26">
         <v>45901</v>
       </c>
       <c r="J2604" s="2" t="s">
-        <v>305</v>
+        <v>140</v>
       </c>
       <c r="K2604" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L2604" s="28" t="s">
-        <v>320</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2605" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2605" s="17">
-        <v>45924.405555555553</v>
+        <v>45925.40902777778</v>
       </c>
       <c r="C2605" s="2">
-        <v>437078</v>
+        <v>591136</v>
       </c>
       <c r="D2605" s="2">
-        <v>437531</v>
+        <v>592022</v>
       </c>
       <c r="E2605" s="1">
         <f t="shared" si="45"/>
-        <v>453</v>
+        <v>886</v>
       </c>
       <c r="F2605" s="2">
-        <v>172.04</v>
-      </c>
-      <c r="G2605" s="16">
-        <v>1116.54</v>
+        <v>111.01</v>
+      </c>
+      <c r="G2605" s="2">
+        <v>653.85</v>
       </c>
       <c r="H2605" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2605" s="12">
+      <c r="I2605" s="26">
         <v>45901</v>
       </c>
       <c r="J2605" s="2" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="K2605" s="2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2606" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2606" s="17">
-        <v>45924.607638888891</v>
+        <v>45925.429861111108</v>
       </c>
       <c r="C2606" s="2">
-        <v>804142</v>
+        <v>9943</v>
       </c>
       <c r="D2606" s="2">
-        <v>804443</v>
+        <v>10351</v>
       </c>
       <c r="E2606" s="1">
         <f t="shared" si="45"/>
-        <v>301</v>
+        <v>408</v>
       </c>
       <c r="F2606" s="2">
-        <v>157.46</v>
+        <v>42</v>
       </c>
       <c r="G2606" s="2">
-        <v>958.95</v>
+        <v>309.12</v>
       </c>
       <c r="H2606" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2606" s="12">
+        <v>7</v>
+      </c>
+      <c r="I2606" s="26">
         <v>45901</v>
       </c>
+      <c r="J2606" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="K2606" s="2" t="s">
-        <v>77</v>
+        <v>240</v>
+      </c>
+      <c r="L2606" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2607" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2607" s="17">
-        <v>45924.70208333333</v>
+        <v>45925.438194444447</v>
       </c>
       <c r="C2607" s="2">
-        <v>492183</v>
+        <v>7301</v>
       </c>
       <c r="D2607" s="2">
-        <v>492582</v>
+        <v>7641</v>
       </c>
       <c r="E2607" s="1">
-        <f t="shared" si="45"/>
-        <v>399</v>
+        <f t="shared" ref="E2607:E2649" si="46">D2607-C2607</f>
+        <v>340</v>
       </c>
       <c r="F2607" s="2">
-        <v>38.17</v>
+        <v>30.37</v>
       </c>
       <c r="G2607" s="2">
-        <v>224.82</v>
+        <v>203.18</v>
       </c>
       <c r="H2607" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2607" s="12">
+      <c r="I2607" s="26">
         <v>45901</v>
       </c>
       <c r="J2607" s="2" t="s">
-        <v>74</v>
+        <v>308</v>
       </c>
       <c r="K2607" s="2" t="s">
-        <v>39</v>
+        <v>208</v>
+      </c>
+      <c r="L2607" s="28" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="2608" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2608" s="17">
-        <v>45924.727777777778</v>
+        <v>45925.449305555558</v>
       </c>
       <c r="C2608" s="2">
-        <v>461093</v>
+        <v>10382</v>
       </c>
       <c r="D2608" s="2">
-        <v>461871</v>
+        <v>10909</v>
       </c>
       <c r="E2608" s="1">
-        <f t="shared" si="45"/>
-        <v>778</v>
+        <f t="shared" si="46"/>
+        <v>527</v>
       </c>
       <c r="F2608" s="2">
-        <v>22.91</v>
-      </c>
-      <c r="G2608" s="16">
-        <v>1395.59</v>
+        <v>38.39</v>
+      </c>
+      <c r="G2608" s="2">
+        <v>229.96</v>
       </c>
       <c r="H2608" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2608" s="12">
+        <v>7</v>
+      </c>
+      <c r="I2608" s="26">
         <v>45901</v>
       </c>
+      <c r="J2608" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="K2608" s="2" t="s">
-        <v>52</v>
+        <v>199</v>
+      </c>
+      <c r="L2608" s="28" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="2609" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2609" s="17">
-        <v>45924.728472222225</v>
+        <v>45925.564583333333</v>
       </c>
       <c r="C2609" s="2">
-        <v>13026</v>
+        <v>6856</v>
       </c>
       <c r="D2609" s="2">
-        <v>13402</v>
+        <v>7202</v>
       </c>
       <c r="E2609" s="1">
-        <f t="shared" si="45"/>
-        <v>376</v>
+        <f t="shared" si="46"/>
+        <v>346</v>
       </c>
       <c r="F2609" s="2">
-        <v>27.11</v>
+        <v>32.89</v>
       </c>
       <c r="G2609" s="2">
-        <v>170.52</v>
+        <v>216.75</v>
       </c>
       <c r="H2609" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2609" s="12">
+      <c r="I2609" s="26">
         <v>45901</v>
       </c>
       <c r="J2609" s="2" t="s">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="K2609" s="2" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2610" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2610" s="18"/>
-      <c r="C2610" s="1"/>
-      <c r="D2610" s="1"/>
+      <c r="B2610" s="17">
+        <v>45925.573611111111</v>
+      </c>
+      <c r="C2610" s="2">
+        <v>310183</v>
+      </c>
+      <c r="D2610" s="2">
+        <v>311439</v>
+      </c>
       <c r="E2610" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2610" s="1"/>
-      <c r="G2610" s="10"/>
-      <c r="H2610" s="3"/>
-      <c r="J2610" s="7"/>
-      <c r="K2610" s="7"/>
+        <f t="shared" si="46"/>
+        <v>1256</v>
+      </c>
+      <c r="F2610" s="2">
+        <v>233.93</v>
+      </c>
+      <c r="G2610" s="16">
+        <v>1448.07</v>
+      </c>
+      <c r="H2610" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2610" s="26">
+        <v>45901</v>
+      </c>
+      <c r="J2610" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2610" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2610" s="28"/>
     </row>
     <row r="2611" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2611" s="18"/>
-      <c r="C2611" s="1"/>
-      <c r="D2611" s="1"/>
+      <c r="B2611" s="17">
+        <v>45925.588194444441</v>
+      </c>
+      <c r="C2611" s="2">
+        <v>748835</v>
+      </c>
+      <c r="D2611" s="2">
+        <v>750026</v>
+      </c>
       <c r="E2611" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2611" s="1"/>
-      <c r="G2611" s="10"/>
-      <c r="H2611" s="3"/>
-      <c r="J2611" s="7"/>
-      <c r="K2611" s="7"/>
+        <f t="shared" si="46"/>
+        <v>1191</v>
+      </c>
+      <c r="F2611" s="2">
+        <v>68.489999999999995</v>
+      </c>
+      <c r="G2611" s="2">
+        <v>400</v>
+      </c>
+      <c r="H2611" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2611" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2611" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K2611" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2611" s="28"/>
     </row>
     <row r="2612" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2612" s="18"/>
-      <c r="C2612" s="1"/>
-      <c r="D2612" s="1"/>
+      <c r="B2612" s="17">
+        <v>45925.589583333334</v>
+      </c>
+      <c r="C2612" s="2">
+        <v>9083</v>
+      </c>
+      <c r="D2612" s="2">
+        <v>9536</v>
+      </c>
       <c r="E2612" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2612" s="1"/>
-      <c r="G2612" s="10"/>
-      <c r="H2612" s="3"/>
-      <c r="J2612" s="7"/>
-      <c r="K2612" s="7"/>
+        <f t="shared" si="46"/>
+        <v>453</v>
+      </c>
+      <c r="F2612" s="2">
+        <v>13</v>
+      </c>
+      <c r="G2612" s="2">
+        <v>75.14</v>
+      </c>
+      <c r="H2612" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2612" s="26">
+        <v>45901</v>
+      </c>
+      <c r="J2612" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2612" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="2613" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2613" s="18"/>
-      <c r="C2613" s="1"/>
-      <c r="D2613" s="1"/>
+      <c r="B2613" s="17">
+        <v>45925.637499999997</v>
+      </c>
+      <c r="C2613" s="2">
+        <v>459137</v>
+      </c>
+      <c r="D2613" s="2">
+        <v>461828</v>
+      </c>
       <c r="E2613" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2613" s="1"/>
-      <c r="G2613" s="10"/>
-      <c r="H2613" s="3"/>
-      <c r="J2613" s="7"/>
-      <c r="K2613" s="7"/>
+        <f t="shared" si="46"/>
+        <v>2691</v>
+      </c>
+      <c r="F2613" s="2">
+        <v>159.61000000000001</v>
+      </c>
+      <c r="G2613" s="16">
+        <v>1021.56</v>
+      </c>
+      <c r="H2613" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2613" s="26">
+        <v>45901</v>
+      </c>
+      <c r="J2613" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="K2613" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2613" s="28"/>
     </row>
     <row r="2614" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2614" s="17">
-        <v>45918.321527777778</v>
+        <v>45925.645138888889</v>
       </c>
       <c r="C2614" s="2">
-        <v>6157</v>
+        <v>453830</v>
       </c>
       <c r="D2614" s="2">
-        <v>6621</v>
+        <v>454253</v>
       </c>
       <c r="E2614" s="1">
-        <f t="shared" si="45"/>
-        <v>464</v>
+        <f t="shared" si="46"/>
+        <v>423</v>
       </c>
       <c r="F2614" s="2">
-        <v>38.200000000000003</v>
+        <v>135.65</v>
       </c>
       <c r="G2614" s="2">
-        <v>259.37</v>
+        <v>866.8</v>
       </c>
       <c r="H2614" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2614" s="12">
+        <v>8</v>
+      </c>
+      <c r="I2614" s="26">
         <v>45901</v>
       </c>
       <c r="J2614" s="2" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="K2614" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L2614" s="28" t="s">
-        <v>317</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2615" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2615" s="17">
-        <v>45918.347222222219</v>
+        <v>45925.691666666666</v>
       </c>
       <c r="C2615" s="2">
-        <v>309541</v>
+        <v>6050</v>
       </c>
       <c r="D2615" s="2">
-        <v>310183</v>
+        <v>6450</v>
       </c>
       <c r="E2615" s="1">
-        <f t="shared" si="45"/>
-        <v>642</v>
+        <f t="shared" si="46"/>
+        <v>400</v>
       </c>
       <c r="F2615" s="2">
-        <v>186.29</v>
-      </c>
-      <c r="G2615" s="16">
-        <v>1076.75</v>
+        <v>30.44</v>
+      </c>
+      <c r="G2615" s="2">
+        <v>177.77</v>
       </c>
       <c r="H2615" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2615" s="12">
+        <v>7</v>
+      </c>
+      <c r="I2615" s="26">
         <v>45901</v>
       </c>
       <c r="J2615" s="2" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="K2615" s="2" t="s">
-        <v>84</v>
+        <v>206</v>
+      </c>
+      <c r="L2615" s="28" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="2616" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2616" s="17">
-        <v>45918.367361111108</v>
+        <v>45925.753472222219</v>
       </c>
       <c r="C2616" s="2">
-        <v>6475</v>
+        <v>156490</v>
       </c>
       <c r="D2616" s="2">
-        <v>6907</v>
+        <v>157598</v>
       </c>
       <c r="E2616" s="1">
-        <f t="shared" si="45"/>
-        <v>432</v>
+        <f t="shared" si="46"/>
+        <v>1108</v>
       </c>
       <c r="F2616" s="2">
-        <v>34.96</v>
-      </c>
-      <c r="G2616" s="2">
-        <v>204.17</v>
+        <v>377.87</v>
+      </c>
+      <c r="G2616" s="16">
+        <v>2301.23</v>
       </c>
       <c r="H2616" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2616" s="12">
+        <v>8</v>
+      </c>
+      <c r="I2616" s="26">
         <v>45901</v>
       </c>
       <c r="J2616" s="2" t="s">
-        <v>244</v>
+        <v>23</v>
       </c>
       <c r="K2616" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L2616" s="28" t="s">
-        <v>326</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2617" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2617" s="17">
-        <v>45918.400000000001</v>
+        <v>45925.818749999999</v>
       </c>
       <c r="C2617" s="2">
-        <v>5097</v>
+        <v>437531</v>
       </c>
       <c r="D2617" s="2">
-        <v>5400</v>
+        <v>437872</v>
       </c>
       <c r="E2617" s="1">
-        <f t="shared" si="45"/>
-        <v>303</v>
+        <f t="shared" si="46"/>
+        <v>341</v>
       </c>
       <c r="F2617" s="2">
-        <v>31.36</v>
-      </c>
-      <c r="G2617" s="2">
-        <v>176.87</v>
+        <v>170.01</v>
+      </c>
+      <c r="G2617" s="16">
+        <v>1093.17</v>
       </c>
       <c r="H2617" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2617" s="12">
+        <v>8</v>
+      </c>
+      <c r="I2617" s="26">
         <v>45901</v>
       </c>
       <c r="J2617" s="2" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="K2617" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L2617" s="28" t="s">
-        <v>320</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="L2617" s="28"/>
     </row>
     <row r="2618" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2618" s="17">
-        <v>45918.40902777778</v>
+        <v>45925.869444444441</v>
       </c>
       <c r="C2618" s="2">
-        <v>435429</v>
+        <v>10351</v>
       </c>
       <c r="D2618" s="2">
-        <v>436351</v>
+        <v>10801</v>
       </c>
       <c r="E2618" s="1">
-        <f t="shared" si="45"/>
-        <v>922</v>
+        <f t="shared" si="46"/>
+        <v>450</v>
       </c>
       <c r="F2618" s="2">
-        <v>114.38</v>
+        <v>41.09</v>
       </c>
       <c r="G2618" s="2">
-        <v>722.88</v>
+        <v>246.17</v>
       </c>
       <c r="H2618" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2618" s="12">
+        <v>7</v>
+      </c>
+      <c r="I2618" s="26">
         <v>45901</v>
       </c>
       <c r="J2618" s="2" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="K2618" s="2" t="s">
-        <v>65</v>
+        <v>240</v>
+      </c>
+      <c r="L2618" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="2619" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2619" s="17">
-        <v>45918.415277777778</v>
+        <v>45925.904166666667</v>
+      </c>
+      <c r="C2619" s="2">
+        <v>592022</v>
+      </c>
+      <c r="D2619" s="2">
+        <v>592426</v>
       </c>
       <c r="E2619" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
+        <f t="shared" si="46"/>
+        <v>404</v>
       </c>
       <c r="F2619" s="2">
-        <v>25.34</v>
+        <v>118.42</v>
       </c>
       <c r="G2619" s="2">
-        <v>163.44</v>
+        <v>692.76</v>
       </c>
       <c r="H2619" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2619" s="12">
+        <v>8</v>
+      </c>
+      <c r="I2619" s="26">
         <v>45901</v>
       </c>
       <c r="J2619" s="2" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="K2619" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L2619" s="28" t="s">
-        <v>321</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2620" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2620" s="17">
-        <v>45918.488194444442</v>
+        <v>45926.366666666669</v>
       </c>
       <c r="C2620" s="2">
-        <v>736457</v>
+        <v>222131</v>
       </c>
       <c r="D2620" s="2">
-        <v>736816</v>
+        <v>222637</v>
       </c>
       <c r="E2620" s="1">
-        <f t="shared" si="45"/>
-        <v>359</v>
+        <f t="shared" si="46"/>
+        <v>506</v>
       </c>
       <c r="F2620" s="2">
-        <v>141.34</v>
+        <v>447.75</v>
       </c>
       <c r="G2620" s="2">
-        <v>853.72</v>
-      </c>
-      <c r="H2620" s="2" t="s">
-        <v>8</v>
+        <v>254.76</v>
+      </c>
+      <c r="H2620" t="s">
+        <v>7</v>
       </c>
       <c r="I2620" s="12">
         <v>45901</v>
       </c>
       <c r="J2620" s="2" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="K2620" s="2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2621" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2621" s="17">
-        <v>45918.495833333334</v>
+        <v>45926.409722222219</v>
       </c>
       <c r="C2621" s="2">
-        <v>13286</v>
+        <v>13402</v>
       </c>
       <c r="D2621" s="2">
-        <v>13797</v>
+        <v>14043</v>
       </c>
       <c r="E2621" s="1">
-        <f t="shared" si="45"/>
-        <v>511</v>
+        <f t="shared" si="46"/>
+        <v>641</v>
       </c>
       <c r="F2621" s="2">
-        <v>40.51</v>
+        <v>38.07</v>
       </c>
       <c r="G2621" s="2">
-        <v>242.67</v>
-      </c>
-      <c r="H2621" s="2" t="s">
+        <v>239.48</v>
+      </c>
+      <c r="H2621" t="s">
         <v>7</v>
       </c>
       <c r="I2621" s="12">
         <v>45901</v>
       </c>
       <c r="J2621" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2621" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L2621" s="28" t="s">
-        <v>327</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="K2621" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L2621" s="28"/>
     </row>
     <row r="2622" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2622" s="17">
-        <v>45918.536805555559</v>
+        <v>45926.415277777778</v>
       </c>
       <c r="C2622" s="2">
-        <v>8183</v>
+        <v>149996</v>
       </c>
       <c r="D2622" s="2">
-        <v>9083</v>
+        <v>150654</v>
       </c>
       <c r="E2622" s="1">
-        <f t="shared" si="45"/>
-        <v>900</v>
+        <f t="shared" si="46"/>
+        <v>658</v>
       </c>
       <c r="F2622" s="2">
-        <v>12.03</v>
+        <v>65.069999999999993</v>
       </c>
       <c r="G2622" s="2">
-        <v>72.09</v>
-      </c>
-      <c r="H2622" s="2" t="s">
-        <v>10</v>
+        <v>399.55</v>
+      </c>
+      <c r="H2622" t="s">
+        <v>8</v>
       </c>
       <c r="I2622" s="12">
         <v>45901</v>
       </c>
       <c r="J2622" s="2" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="K2622" s="2" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2623" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2623" s="17">
-        <v>45918.634027777778</v>
+        <v>45926.425000000003</v>
       </c>
       <c r="C2623" s="2">
-        <v>11873</v>
+        <v>750026</v>
       </c>
       <c r="D2623" s="2">
-        <v>12280</v>
+        <v>750329</v>
       </c>
       <c r="E2623" s="1">
-        <f t="shared" si="45"/>
-        <v>407</v>
+        <f t="shared" si="46"/>
+        <v>303</v>
       </c>
       <c r="F2623" s="2">
-        <v>34.119999999999997</v>
-      </c>
-      <c r="G2623" s="2">
-        <v>201</v>
-      </c>
-      <c r="H2623" s="2" t="s">
-        <v>7</v>
+        <v>172.41</v>
+      </c>
+      <c r="G2623" s="16">
+        <v>1050</v>
+      </c>
+      <c r="H2623" t="s">
+        <v>8</v>
       </c>
       <c r="I2623" s="12">
         <v>45901</v>
@@ -85565,33 +86101,30 @@
         <v>23</v>
       </c>
       <c r="K2623" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2623" s="28" t="s">
-        <v>329</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2624" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2624" s="17">
-        <v>45918.720833333333</v>
+        <v>45926.439583333333</v>
       </c>
       <c r="C2624" s="2">
-        <v>491500</v>
+        <v>492582</v>
       </c>
       <c r="D2624" s="2">
-        <v>491850</v>
+        <v>492843</v>
       </c>
       <c r="E2624" s="1">
-        <f t="shared" si="45"/>
-        <v>350</v>
+        <f t="shared" si="46"/>
+        <v>261</v>
       </c>
       <c r="F2624" s="2">
-        <v>35.75</v>
+        <v>26.62</v>
       </c>
       <c r="G2624" s="2">
-        <v>203.42</v>
-      </c>
-      <c r="H2624" s="2" t="s">
+        <v>148.83000000000001</v>
+      </c>
+      <c r="H2624" t="s">
         <v>7</v>
       </c>
       <c r="I2624" s="12">
@@ -85606,3854 +86139,926 @@
     </row>
     <row r="2625" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2625" s="17">
-        <v>45918.787499999999</v>
+        <v>45926.507638888892</v>
       </c>
       <c r="C2625" s="2">
-        <v>436351</v>
+        <v>432929</v>
       </c>
       <c r="D2625" s="2">
-        <v>436502</v>
+        <v>434038</v>
       </c>
       <c r="E2625" s="1">
-        <f t="shared" si="45"/>
-        <v>151</v>
+        <f t="shared" si="46"/>
+        <v>1109</v>
       </c>
       <c r="F2625" s="2">
-        <v>168.62</v>
+        <v>168.63</v>
       </c>
       <c r="G2625" s="16">
-        <v>1084.25</v>
-      </c>
-      <c r="H2625" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H2625" t="s">
         <v>8</v>
       </c>
       <c r="I2625" s="12">
         <v>45901</v>
       </c>
       <c r="J2625" s="2" t="s">
-        <v>101</v>
+        <v>311</v>
       </c>
       <c r="K2625" s="2" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2626" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2626" s="17">
-        <v>45918.847222222219</v>
+        <v>45926.510416666664</v>
       </c>
       <c r="C2626" s="2">
-        <v>452549</v>
+        <v>352434</v>
       </c>
       <c r="D2626" s="2">
-        <v>453011</v>
+        <v>354029</v>
       </c>
       <c r="E2626" s="1">
-        <f t="shared" si="45"/>
-        <v>462</v>
+        <f t="shared" si="46"/>
+        <v>1595</v>
       </c>
       <c r="F2626" s="2">
-        <v>165.48</v>
+        <v>185.05</v>
       </c>
       <c r="G2626" s="16">
-        <v>1057.42</v>
-      </c>
-      <c r="H2626" s="2" t="s">
+        <v>1126.99</v>
+      </c>
+      <c r="H2626" t="s">
         <v>8</v>
       </c>
       <c r="I2626" s="12">
         <v>45901</v>
       </c>
       <c r="J2626" s="2" t="s">
-        <v>307</v>
+        <v>23</v>
       </c>
       <c r="K2626" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2627" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2627" s="17">
-        <v>45918.87777777778</v>
+        <v>45926.513888888891</v>
       </c>
       <c r="C2627" s="2">
-        <v>8580</v>
+        <v>461871</v>
       </c>
       <c r="D2627" s="2">
-        <v>9476</v>
+        <v>462388</v>
       </c>
       <c r="E2627" s="1">
-        <f t="shared" si="45"/>
-        <v>896</v>
+        <f t="shared" si="46"/>
+        <v>517</v>
       </c>
       <c r="F2627" s="2">
-        <v>34.159999999999997</v>
+        <v>131.37</v>
       </c>
       <c r="G2627" s="2">
-        <v>200</v>
-      </c>
-      <c r="H2627" s="2" t="s">
-        <v>7</v>
+        <v>800.07</v>
+      </c>
+      <c r="H2627" t="s">
+        <v>8</v>
       </c>
       <c r="I2627" s="12">
         <v>45901</v>
       </c>
       <c r="J2627" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K2627" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="L2627" s="28" t="s">
-        <v>319</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2628" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2628" s="18"/>
-      <c r="C2628" s="1"/>
-      <c r="D2628" s="1"/>
+      <c r="B2628" s="17">
+        <v>45926.536111111112</v>
+      </c>
+      <c r="C2628" s="2">
+        <v>771221</v>
+      </c>
+      <c r="D2628" s="2">
+        <v>771930</v>
+      </c>
       <c r="E2628" s="1">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
+        <v>709</v>
+      </c>
+      <c r="F2628" s="2">
+        <v>150.11000000000001</v>
+      </c>
+      <c r="G2628" s="2">
+        <v>974.21</v>
+      </c>
+      <c r="H2628" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2628" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2628" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2628" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2629" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2629" s="17">
+        <v>45926.607638888891</v>
+      </c>
+      <c r="C2629" s="2">
+        <v>804443</v>
+      </c>
+      <c r="D2629" s="2">
+        <v>804995</v>
+      </c>
+      <c r="E2629" s="1">
+        <f t="shared" si="46"/>
+        <v>552</v>
+      </c>
+      <c r="F2629" s="2">
+        <v>163.38999999999999</v>
+      </c>
+      <c r="G2629" s="2">
+        <v>995.05</v>
+      </c>
+      <c r="H2629" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2629" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2629" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2629" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2630" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2630" s="17">
+        <v>45926.793749999997</v>
+      </c>
+      <c r="C2630" s="2">
+        <v>10247</v>
+      </c>
+      <c r="D2630" s="2">
+        <v>10701</v>
+      </c>
+      <c r="E2630" s="1">
+        <f t="shared" si="46"/>
+        <v>454</v>
+      </c>
+      <c r="F2630" s="2">
+        <v>49.2</v>
+      </c>
+      <c r="G2630" s="2">
+        <v>280</v>
+      </c>
+      <c r="H2630" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2630" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2630" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2630" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L2630" s="28" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2631" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2631" s="17">
+        <v>45929.240972222222</v>
+      </c>
+      <c r="C2631" s="2">
+        <v>76414</v>
+      </c>
+      <c r="D2631" s="2">
+        <v>77930</v>
+      </c>
+      <c r="E2631" s="1">
+        <f t="shared" si="46"/>
+        <v>1516</v>
+      </c>
+      <c r="F2631" s="2">
+        <v>1.61</v>
+      </c>
+      <c r="G2631" s="2">
+        <v>10</v>
+      </c>
+      <c r="H2631" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2631" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2631" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2631" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2631" s="28"/>
+    </row>
+    <row r="2632" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2632" s="17">
+        <v>45929.245833333334</v>
+      </c>
+      <c r="C2632" s="2">
+        <v>77930</v>
+      </c>
+      <c r="D2632" s="2">
+        <v>77930</v>
+      </c>
+      <c r="E2632" s="1">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="F2628" s="1"/>
-      <c r="G2628" s="10"/>
-      <c r="H2628" s="3"/>
-      <c r="J2628" s="7"/>
-      <c r="K2628" s="7"/>
-    </row>
-    <row r="2629" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2629" s="18"/>
-      <c r="C2629" s="1"/>
-      <c r="D2629" s="1"/>
-      <c r="E2629" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2629" s="1"/>
-      <c r="G2629" s="10"/>
-      <c r="H2629" s="3"/>
-      <c r="J2629" s="7"/>
-      <c r="K2629" s="7"/>
-    </row>
-    <row r="2630" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2630" s="18"/>
-      <c r="C2630" s="1"/>
-      <c r="D2630" s="1"/>
-      <c r="E2630" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2630" s="1"/>
-      <c r="G2630" s="10"/>
-      <c r="H2630" s="3"/>
-      <c r="J2630" s="7"/>
-      <c r="K2630" s="7"/>
-    </row>
-    <row r="2631" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2631" s="18"/>
-      <c r="C2631" s="1"/>
-      <c r="D2631" s="1"/>
-      <c r="E2631" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2631" s="1"/>
-      <c r="G2631" s="10"/>
-      <c r="H2631" s="3"/>
-      <c r="J2631" s="7"/>
-      <c r="K2631" s="7"/>
-    </row>
-    <row r="2632" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2632" s="18"/>
-      <c r="C2632" s="1"/>
-      <c r="D2632" s="1"/>
-      <c r="E2632" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2632" s="1"/>
-      <c r="G2632" s="10"/>
-      <c r="H2632" s="3"/>
-      <c r="J2632" s="7"/>
-      <c r="K2632" s="7"/>
+      <c r="F2632" s="2">
+        <v>69.25</v>
+      </c>
+      <c r="G2632" s="2">
+        <v>395.58</v>
+      </c>
+      <c r="H2632" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2632" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2632" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="K2632" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L2632" s="28"/>
     </row>
     <row r="2633" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2633" s="18"/>
-      <c r="C2633" s="1"/>
-      <c r="D2633" s="1"/>
+      <c r="B2633" s="17">
+        <v>45929.270138888889</v>
+      </c>
+      <c r="C2633" s="2">
+        <v>116141</v>
+      </c>
+      <c r="D2633" s="2">
+        <v>117290</v>
+      </c>
       <c r="E2633" s="1">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="F2633" s="1"/>
-      <c r="G2633" s="10"/>
-      <c r="H2633" s="3"/>
-      <c r="J2633" s="7"/>
-      <c r="K2633" s="7"/>
+        <f t="shared" si="46"/>
+        <v>1149</v>
+      </c>
+      <c r="F2633" s="2">
+        <v>556.04</v>
+      </c>
+      <c r="G2633" s="16">
+        <v>3497.5</v>
+      </c>
+      <c r="H2633" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2633" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2633" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2633" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2633" s="28"/>
     </row>
     <row r="2634" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2634" s="17">
-        <v>45925.277083333334</v>
+        <v>45929.275000000001</v>
       </c>
       <c r="C2634" s="2">
-        <v>737691</v>
+        <v>434038</v>
       </c>
       <c r="D2634" s="2">
-        <v>737947</v>
+        <v>434245</v>
       </c>
       <c r="E2634" s="1">
-        <f t="shared" si="45"/>
-        <v>256</v>
+        <f t="shared" si="46"/>
+        <v>207</v>
       </c>
       <c r="F2634" s="2">
-        <v>102.81</v>
+        <v>53.39</v>
       </c>
       <c r="G2634" s="2">
-        <v>621</v>
+        <v>325.14999999999998</v>
       </c>
       <c r="H2634" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2634" s="26">
+      <c r="I2634" s="12">
         <v>45901</v>
       </c>
       <c r="J2634" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="K2634" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2635" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2635" s="17">
-        <v>45925.40902777778</v>
+        <v>45929.283333333333</v>
       </c>
       <c r="C2635" s="2">
-        <v>591136</v>
+        <v>461828</v>
       </c>
       <c r="D2635" s="2">
-        <v>592022</v>
+        <v>462056</v>
       </c>
       <c r="E2635" s="1">
-        <f t="shared" si="45"/>
-        <v>886</v>
+        <f t="shared" si="46"/>
+        <v>228</v>
       </c>
       <c r="F2635" s="2">
-        <v>111.01</v>
+        <v>65.95</v>
       </c>
       <c r="G2635" s="2">
-        <v>653.85</v>
+        <v>414.83</v>
       </c>
       <c r="H2635" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2635" s="26">
+      <c r="I2635" s="12">
         <v>45901</v>
       </c>
       <c r="J2635" s="2" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K2635" s="2" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2636" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2636" s="17">
-        <v>45925.429861111108</v>
+        <v>45929.317361111112</v>
       </c>
       <c r="C2636" s="2">
-        <v>9943</v>
+        <v>7202</v>
       </c>
       <c r="D2636" s="2">
-        <v>10351</v>
+        <v>7367</v>
       </c>
       <c r="E2636" s="1">
-        <f t="shared" si="45"/>
-        <v>408</v>
+        <f t="shared" si="46"/>
+        <v>165</v>
       </c>
       <c r="F2636" s="2">
-        <v>42</v>
+        <v>12.09</v>
       </c>
       <c r="G2636" s="2">
-        <v>309.12</v>
+        <v>77.19</v>
       </c>
       <c r="H2636" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2636" s="26">
+      <c r="I2636" s="12">
         <v>45901</v>
       </c>
       <c r="J2636" s="2" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="K2636" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2636" s="29" t="s">
-        <v>323</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2637" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2637" s="17">
-        <v>45925.438194444447</v>
+        <v>45929.367361111108</v>
       </c>
       <c r="C2637" s="2">
-        <v>7301</v>
+        <v>150654</v>
       </c>
       <c r="D2637" s="2">
-        <v>7641</v>
+        <v>151023</v>
       </c>
       <c r="E2637" s="1">
-        <f t="shared" ref="E2637:E2700" si="46">D2637-C2637</f>
-        <v>340</v>
+        <f t="shared" si="46"/>
+        <v>369</v>
       </c>
       <c r="F2637" s="2">
-        <v>30.37</v>
+        <v>20</v>
       </c>
       <c r="G2637" s="2">
-        <v>203.18</v>
+        <v>105</v>
       </c>
       <c r="H2637" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2637" s="26">
+        <v>9</v>
+      </c>
+      <c r="I2637" s="12">
         <v>45901</v>
       </c>
       <c r="J2637" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K2637" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L2637" s="28" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2638" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2638" s="17">
-        <v>45925.449305555558</v>
+        <v>45929.375694444447</v>
       </c>
       <c r="C2638" s="2">
-        <v>10382</v>
+        <v>592426</v>
       </c>
       <c r="D2638" s="2">
-        <v>10909</v>
+        <v>593033</v>
       </c>
       <c r="E2638" s="1">
         <f t="shared" si="46"/>
-        <v>527</v>
+        <v>607</v>
       </c>
       <c r="F2638" s="2">
-        <v>38.39</v>
+        <v>74.7</v>
       </c>
       <c r="G2638" s="2">
-        <v>229.96</v>
+        <v>481.11</v>
       </c>
       <c r="H2638" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2638" s="26">
+        <v>8</v>
+      </c>
+      <c r="I2638" s="12">
         <v>45901</v>
       </c>
       <c r="J2638" s="2" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="K2638" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L2638" s="28" t="s">
-        <v>321</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2639" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2639" s="17">
-        <v>45925.564583333333</v>
+        <v>45929.382638888892</v>
       </c>
       <c r="C2639" s="2">
-        <v>6856</v>
+        <v>14329</v>
       </c>
       <c r="D2639" s="2">
-        <v>7202</v>
+        <v>14813</v>
       </c>
       <c r="E2639" s="1">
         <f t="shared" si="46"/>
-        <v>346</v>
+        <v>484</v>
       </c>
       <c r="F2639" s="2">
-        <v>32.89</v>
+        <v>44.7</v>
       </c>
       <c r="G2639" s="2">
-        <v>216.75</v>
+        <v>258.85000000000002</v>
       </c>
       <c r="H2639" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2639" s="26">
+      <c r="I2639" s="12">
         <v>45901</v>
       </c>
       <c r="J2639" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="K2639" s="2" t="s">
-        <v>210</v>
+        <v>23</v>
+      </c>
+      <c r="K2639" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="L2639" s="28" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2640" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2640" s="17">
-        <v>45925.573611111111</v>
+        <v>45929.595138888886</v>
       </c>
       <c r="C2640" s="2">
-        <v>310183</v>
+        <v>6647</v>
       </c>
       <c r="D2640" s="2">
-        <v>311439</v>
+        <v>7065</v>
       </c>
       <c r="E2640" s="1">
         <f t="shared" si="46"/>
-        <v>1256</v>
+        <v>418</v>
       </c>
       <c r="F2640" s="2">
-        <v>233.93</v>
-      </c>
-      <c r="G2640" s="16">
-        <v>1448.07</v>
+        <v>40.479999999999997</v>
+      </c>
+      <c r="G2640" s="2">
+        <v>242.49</v>
       </c>
       <c r="H2640" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2640" s="26">
+        <v>7</v>
+      </c>
+      <c r="I2640" s="12">
         <v>45901</v>
       </c>
       <c r="J2640" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K2640" s="2" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2641" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2641" s="17">
-        <v>45925.588194444441</v>
+        <v>45930.302083333336</v>
       </c>
       <c r="C2641" s="2">
-        <v>748835</v>
+        <v>9895</v>
       </c>
       <c r="D2641" s="2">
-        <v>750026</v>
+        <v>10313</v>
       </c>
       <c r="E2641" s="1">
         <f t="shared" si="46"/>
-        <v>1191</v>
+        <v>418</v>
       </c>
       <c r="F2641" s="2">
-        <v>68.489999999999995</v>
+        <v>35.229999999999997</v>
       </c>
       <c r="G2641" s="2">
-        <v>400</v>
+        <v>206.1</v>
       </c>
       <c r="H2641" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2641" s="26">
+        <v>7</v>
+      </c>
+      <c r="I2641" s="12">
         <v>45901</v>
       </c>
       <c r="J2641" s="2" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="K2641" s="2" t="s">
-        <v>27</v>
+        <v>205</v>
+      </c>
+      <c r="L2641" s="28" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="2642" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2642" s="17">
-        <v>45925.589583333334</v>
+        <v>45930.432638888888</v>
       </c>
       <c r="C2642" s="2">
-        <v>9083</v>
+        <v>12533</v>
       </c>
       <c r="D2642" s="2">
-        <v>9536</v>
+        <v>12943</v>
       </c>
       <c r="E2642" s="1">
         <f t="shared" si="46"/>
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="F2642" s="2">
-        <v>13</v>
+        <v>38.56</v>
       </c>
       <c r="G2642" s="2">
-        <v>75.14</v>
+        <v>230.97</v>
       </c>
       <c r="H2642" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2642" s="26">
+        <v>7</v>
+      </c>
+      <c r="I2642" s="12">
         <v>45901</v>
       </c>
       <c r="J2642" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K2642" s="2" t="s">
-        <v>122</v>
+        <v>172</v>
+      </c>
+      <c r="L2642" s="28" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="2643" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2643" s="17">
-        <v>45925.637499999997</v>
+        <v>45930.491666666669</v>
       </c>
       <c r="C2643" s="2">
-        <v>459137</v>
+        <v>11795</v>
       </c>
       <c r="D2643" s="2">
-        <v>461828</v>
+        <v>12299</v>
       </c>
       <c r="E2643" s="1">
         <f t="shared" si="46"/>
-        <v>2691</v>
+        <v>504</v>
       </c>
       <c r="F2643" s="2">
-        <v>159.61000000000001</v>
-      </c>
-      <c r="G2643" s="16">
-        <v>1021.56</v>
+        <v>38.29</v>
+      </c>
+      <c r="G2643" s="2">
+        <v>240.89</v>
       </c>
       <c r="H2643" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2643" s="26">
+        <v>7</v>
+      </c>
+      <c r="I2643" s="12">
         <v>45901</v>
       </c>
       <c r="J2643" s="2" t="s">
-        <v>310</v>
+        <v>46</v>
       </c>
       <c r="K2643" s="2" t="s">
-        <v>71</v>
+        <v>218</v>
+      </c>
+      <c r="L2643" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="2644" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2644" s="17">
-        <v>45925.645138888889</v>
-      </c>
-      <c r="C2644" s="2">
-        <v>453830</v>
-      </c>
-      <c r="D2644" s="2">
-        <v>454253</v>
+        <v>45930.522222222222</v>
       </c>
       <c r="E2644" s="1">
         <f t="shared" si="46"/>
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="F2644" s="2">
-        <v>135.65</v>
+        <v>32.57</v>
       </c>
       <c r="G2644" s="2">
-        <v>866.8</v>
+        <v>200</v>
       </c>
       <c r="H2644" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2644" s="26">
+      <c r="I2644" s="12">
         <v>45901</v>
       </c>
       <c r="J2644" s="2" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="K2644" s="2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2645" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2645" s="17">
-        <v>45925.691666666666</v>
+        <v>45930.604166666664</v>
       </c>
       <c r="C2645" s="2">
-        <v>6050</v>
+        <v>434245</v>
       </c>
       <c r="D2645" s="2">
-        <v>6450</v>
+        <v>434676</v>
       </c>
       <c r="E2645" s="1">
         <f t="shared" si="46"/>
-        <v>400</v>
-      </c>
-      <c r="F2645" s="2">
-        <v>30.44</v>
+        <v>431</v>
+      </c>
+      <c r="F2645" s="16">
+        <v>1373.21</v>
       </c>
       <c r="G2645" s="2">
-        <v>177.77</v>
+        <v>836.28</v>
       </c>
       <c r="H2645" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2645" s="26">
+        <v>16</v>
+      </c>
+      <c r="I2645" s="12">
         <v>45901</v>
       </c>
       <c r="J2645" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="K2645" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="L2645" s="28" t="s">
-        <v>320</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2646" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2646" s="17">
-        <v>45925.753472222219</v>
+        <v>45930.614583333336</v>
       </c>
       <c r="C2646" s="2">
-        <v>156490</v>
+        <v>434676</v>
       </c>
       <c r="D2646" s="2">
-        <v>157598</v>
+        <v>434750</v>
       </c>
       <c r="E2646" s="1">
         <f t="shared" si="46"/>
-        <v>1108</v>
+        <v>74</v>
       </c>
       <c r="F2646" s="2">
-        <v>377.87</v>
-      </c>
-      <c r="G2646" s="16">
-        <v>2301.23</v>
+        <v>68</v>
+      </c>
+      <c r="G2646" s="2">
+        <v>719.96</v>
       </c>
       <c r="H2646" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2646" s="26">
+      <c r="I2646" s="12">
         <v>45901</v>
       </c>
       <c r="J2646" s="2" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="K2646" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2647" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2647" s="17">
-        <v>45925.818749999999</v>
+        <v>45930.663194444445</v>
       </c>
       <c r="C2647" s="2">
-        <v>437531</v>
+        <v>462056</v>
       </c>
       <c r="D2647" s="2">
-        <v>437872</v>
+        <v>462644</v>
       </c>
       <c r="E2647" s="1">
         <f t="shared" si="46"/>
-        <v>341</v>
+        <v>588</v>
       </c>
       <c r="F2647" s="2">
-        <v>170.01</v>
+        <v>180.05</v>
       </c>
       <c r="G2647" s="16">
-        <v>1093.17</v>
+        <v>1132.55</v>
       </c>
       <c r="H2647" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2647" s="26">
+      <c r="I2647" s="12">
         <v>45901</v>
       </c>
       <c r="J2647" s="2" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="K2647" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2648" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2648" s="17">
-        <v>45925.869444444441</v>
+        <v>45930.68472222222</v>
       </c>
       <c r="C2648" s="2">
-        <v>10351</v>
+        <v>305379</v>
       </c>
       <c r="D2648" s="2">
-        <v>10801</v>
+        <v>305495</v>
       </c>
       <c r="E2648" s="1">
         <f t="shared" si="46"/>
-        <v>450</v>
+        <v>116</v>
       </c>
       <c r="F2648" s="2">
-        <v>41.09</v>
-      </c>
-      <c r="G2648" s="2">
-        <v>246.17</v>
+        <v>208.95</v>
+      </c>
+      <c r="G2648" s="16">
+        <v>1314.32</v>
       </c>
       <c r="H2648" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2648" s="26">
+        <v>14</v>
+      </c>
+      <c r="I2648" s="12">
         <v>45901</v>
       </c>
       <c r="J2648" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K2648" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L2648" s="29" t="s">
-        <v>323</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2649" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2649" s="17">
-        <v>45925.904166666667</v>
-      </c>
-      <c r="C2649" s="2">
-        <v>592022</v>
-      </c>
-      <c r="D2649" s="2">
-        <v>592426</v>
+        <v>45930.807638888888</v>
       </c>
       <c r="E2649" s="1">
         <f t="shared" si="46"/>
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="F2649" s="2">
-        <v>118.42</v>
+        <v>133.28</v>
       </c>
       <c r="G2649" s="2">
-        <v>692.76</v>
+        <v>838.35</v>
       </c>
       <c r="H2649" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2649" s="26">
+      <c r="I2649" s="12">
         <v>45901</v>
       </c>
       <c r="J2649" s="2" t="s">
-        <v>228</v>
+        <v>23</v>
       </c>
       <c r="K2649" s="2" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2650" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2650" s="18"/>
-      <c r="C2650" s="1"/>
-      <c r="D2650" s="1"/>
-      <c r="E2650" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2650" s="1"/>
-      <c r="G2650" s="10"/>
-      <c r="H2650" s="3"/>
-      <c r="J2650" s="7"/>
-      <c r="K2650" s="7"/>
+      <c r="B2650" s="23">
+        <v>45944</v>
+      </c>
+      <c r="F2650" s="2">
+        <v>180.19</v>
+      </c>
+      <c r="G2650" s="2">
+        <v>1133.44</v>
+      </c>
+      <c r="H2650" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2650" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2650" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2650" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="2651" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2651" s="18"/>
-      <c r="C2651" s="1"/>
-      <c r="D2651" s="1"/>
-      <c r="E2651" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2651" s="1"/>
-      <c r="G2651" s="10"/>
-      <c r="H2651" s="3"/>
-      <c r="J2651" s="7"/>
-      <c r="K2651" s="7"/>
+      <c r="B2651" s="23">
+        <v>45941</v>
+      </c>
+      <c r="F2651" s="2">
+        <v>38.04</v>
+      </c>
+      <c r="G2651" s="2">
+        <v>227.86</v>
+      </c>
+      <c r="H2651" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2651" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2651" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="K2651" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="2652" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2652" s="18"/>
-      <c r="C2652" s="1"/>
-      <c r="D2652" s="1"/>
-      <c r="E2652" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2652" s="1"/>
-      <c r="G2652" s="10"/>
-      <c r="H2652" s="3"/>
-      <c r="J2652" s="7"/>
-      <c r="K2652" s="7"/>
-    </row>
-    <row r="2653" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2653" s="18"/>
-      <c r="C2653" s="1"/>
-      <c r="D2653" s="1"/>
-      <c r="E2653" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2653" s="1"/>
-      <c r="G2653" s="10"/>
-      <c r="H2653" s="3"/>
-      <c r="J2653" s="7"/>
-      <c r="K2653" s="7"/>
-    </row>
-    <row r="2654" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2654" s="18"/>
-      <c r="C2654" s="1"/>
-      <c r="D2654" s="1"/>
-      <c r="E2654" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2654" s="1"/>
-      <c r="G2654" s="10"/>
-      <c r="H2654" s="3"/>
-      <c r="J2654" s="7"/>
-      <c r="K2654" s="7"/>
-    </row>
-    <row r="2655" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2655" s="17">
-        <v>45926.366666666669</v>
-      </c>
-      <c r="C2655" s="2">
-        <v>222131</v>
-      </c>
-      <c r="D2655" s="2">
-        <v>222637</v>
-      </c>
-      <c r="E2655" s="1">
-        <f t="shared" si="46"/>
-        <v>506</v>
-      </c>
-      <c r="F2655" s="2">
-        <v>447.75</v>
-      </c>
-      <c r="G2655" s="2">
-        <v>254.76</v>
-      </c>
-      <c r="H2655" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2655" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2655" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2655" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2656" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2656" s="17">
-        <v>45926.409722222219</v>
-      </c>
-      <c r="C2656" s="2">
-        <v>13402</v>
-      </c>
-      <c r="D2656" s="2">
-        <v>14043</v>
-      </c>
-      <c r="E2656" s="1">
-        <f t="shared" si="46"/>
-        <v>641</v>
-      </c>
-      <c r="F2656" s="2">
-        <v>38.07</v>
-      </c>
-      <c r="G2656" s="2">
-        <v>239.48</v>
-      </c>
-      <c r="H2656" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2656" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2656" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2656" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="2657" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2657" s="17">
-        <v>45926.415277777778</v>
-      </c>
-      <c r="C2657" s="2">
-        <v>149996</v>
-      </c>
-      <c r="D2657" s="2">
-        <v>150654</v>
-      </c>
-      <c r="E2657" s="1">
-        <f t="shared" si="46"/>
-        <v>658</v>
-      </c>
-      <c r="F2657" s="2">
-        <v>65.069999999999993</v>
-      </c>
-      <c r="G2657" s="2">
-        <v>399.55</v>
-      </c>
-      <c r="H2657" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2657" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2657" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="K2657" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2658" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2658" s="17">
-        <v>45926.425000000003</v>
-      </c>
-      <c r="C2658" s="2">
-        <v>750026</v>
-      </c>
-      <c r="D2658" s="2">
-        <v>750329</v>
-      </c>
-      <c r="E2658" s="1">
-        <f t="shared" si="46"/>
-        <v>303</v>
-      </c>
-      <c r="F2658" s="2">
-        <v>172.41</v>
-      </c>
-      <c r="G2658" s="16">
-        <v>1050</v>
-      </c>
-      <c r="H2658" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2658" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2658" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2658" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2659" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2659" s="17">
-        <v>45926.439583333333</v>
-      </c>
-      <c r="C2659" s="2">
-        <v>492582</v>
-      </c>
-      <c r="D2659" s="2">
-        <v>492843</v>
-      </c>
-      <c r="E2659" s="1">
-        <f t="shared" si="46"/>
-        <v>261</v>
-      </c>
-      <c r="F2659" s="2">
-        <v>26.62</v>
-      </c>
-      <c r="G2659" s="2">
-        <v>148.83000000000001</v>
-      </c>
-      <c r="H2659" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2659" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2659" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="K2659" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2660" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2660" s="17">
-        <v>45926.507638888892</v>
-      </c>
-      <c r="C2660" s="2">
-        <v>432929</v>
-      </c>
-      <c r="D2660" s="2">
-        <v>434038</v>
-      </c>
-      <c r="E2660" s="1">
-        <f t="shared" si="46"/>
-        <v>1109</v>
-      </c>
-      <c r="F2660" s="2">
-        <v>168.63</v>
-      </c>
-      <c r="G2660" s="16">
-        <v>1145</v>
-      </c>
-      <c r="H2660" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2660" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2660" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="K2660" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2661" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2661" s="17">
-        <v>45926.510416666664</v>
-      </c>
-      <c r="C2661" s="2">
-        <v>352434</v>
-      </c>
-      <c r="D2661" s="2">
-        <v>354029</v>
-      </c>
-      <c r="E2661" s="1">
-        <f t="shared" si="46"/>
-        <v>1595</v>
-      </c>
-      <c r="F2661" s="2">
-        <v>185.05</v>
-      </c>
-      <c r="G2661" s="16">
-        <v>1126.99</v>
-      </c>
-      <c r="H2661" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2661" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2661" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2661" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2662" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2662" s="17">
-        <v>45926.513888888891</v>
-      </c>
-      <c r="C2662" s="2">
-        <v>461871</v>
-      </c>
-      <c r="D2662" s="2">
-        <v>462388</v>
-      </c>
-      <c r="E2662" s="1">
-        <f t="shared" si="46"/>
-        <v>517</v>
-      </c>
-      <c r="F2662" s="2">
-        <v>131.37</v>
-      </c>
-      <c r="G2662" s="2">
-        <v>800.07</v>
-      </c>
-      <c r="H2662" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2662" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2662" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2662" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2663" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2663" s="17">
-        <v>45926.536111111112</v>
-      </c>
-      <c r="C2663" s="2">
-        <v>771221</v>
-      </c>
-      <c r="D2663" s="2">
-        <v>771930</v>
-      </c>
-      <c r="E2663" s="1">
-        <f t="shared" si="46"/>
-        <v>709</v>
-      </c>
-      <c r="F2663" s="2">
-        <v>150.11000000000001</v>
-      </c>
-      <c r="G2663" s="2">
-        <v>974.21</v>
-      </c>
-      <c r="H2663" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2663" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2663" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2663" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2664" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2664" s="17">
-        <v>45926.607638888891</v>
-      </c>
-      <c r="C2664" s="2">
-        <v>804443</v>
-      </c>
-      <c r="D2664" s="2">
-        <v>804995</v>
-      </c>
-      <c r="E2664" s="1">
-        <f t="shared" si="46"/>
-        <v>552</v>
-      </c>
-      <c r="F2664" s="2">
-        <v>163.38999999999999</v>
-      </c>
-      <c r="G2664" s="2">
-        <v>995.05</v>
-      </c>
-      <c r="H2664" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2664" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2664" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2664" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2665" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2665" s="17">
-        <v>45926.793749999997</v>
-      </c>
-      <c r="C2665" s="2">
-        <v>10247</v>
-      </c>
-      <c r="D2665" s="2">
-        <v>10701</v>
-      </c>
-      <c r="E2665" s="1">
-        <f t="shared" si="46"/>
-        <v>454</v>
-      </c>
-      <c r="F2665" s="2">
-        <v>49.2</v>
-      </c>
-      <c r="G2665" s="2">
-        <v>280</v>
-      </c>
-      <c r="H2665" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2665" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2665" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2665" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="L2665" s="28" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="2666" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2666" s="18"/>
-      <c r="C2666" s="1"/>
-      <c r="D2666" s="1"/>
-      <c r="E2666" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2666" s="1"/>
-      <c r="G2666" s="10"/>
-      <c r="H2666" s="3"/>
-      <c r="J2666" s="7"/>
-      <c r="K2666" s="7"/>
-    </row>
-    <row r="2667" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2667" s="18"/>
-      <c r="C2667" s="1"/>
-      <c r="D2667" s="1"/>
-      <c r="E2667" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2667" s="1"/>
-      <c r="G2667" s="10"/>
-      <c r="H2667" s="3"/>
-      <c r="J2667" s="7"/>
-      <c r="K2667" s="7"/>
-    </row>
-    <row r="2668" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2668" s="18"/>
-      <c r="C2668" s="1"/>
-      <c r="D2668" s="1"/>
-      <c r="E2668" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2668" s="1"/>
-      <c r="G2668" s="10"/>
-      <c r="H2668" s="3"/>
-      <c r="J2668" s="7"/>
-      <c r="K2668" s="7"/>
-    </row>
-    <row r="2669" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2669" s="18"/>
-      <c r="C2669" s="1"/>
-      <c r="D2669" s="1"/>
-      <c r="E2669" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2669" s="1"/>
-      <c r="G2669" s="10"/>
-      <c r="H2669" s="3"/>
-      <c r="J2669" s="7"/>
-      <c r="K2669" s="7"/>
-    </row>
-    <row r="2670" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2670" s="18"/>
-      <c r="C2670" s="1"/>
-      <c r="D2670" s="1"/>
-      <c r="E2670" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2670" s="1"/>
-      <c r="G2670" s="10"/>
-      <c r="H2670" s="3"/>
-      <c r="J2670" s="7"/>
-      <c r="K2670" s="7"/>
-    </row>
-    <row r="2671" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2671" s="17">
-        <v>45929.240972222222</v>
-      </c>
-      <c r="C2671" s="2">
-        <v>76414</v>
-      </c>
-      <c r="D2671" s="2">
-        <v>77930</v>
-      </c>
-      <c r="E2671" s="1">
-        <f t="shared" si="46"/>
-        <v>1516</v>
-      </c>
-      <c r="F2671" s="2">
-        <v>1.61</v>
-      </c>
-      <c r="G2671" s="2">
-        <v>10</v>
-      </c>
-      <c r="H2671" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2671" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2671" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2671" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2672" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2672" s="17">
-        <v>45929.245833333334</v>
-      </c>
-      <c r="C2672" s="2">
-        <v>77930</v>
-      </c>
-      <c r="D2672" s="2">
-        <v>77930</v>
-      </c>
-      <c r="E2672" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2672" s="2">
-        <v>69.25</v>
-      </c>
-      <c r="G2672" s="2">
-        <v>395.58</v>
-      </c>
-      <c r="H2672" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2672" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2672" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K2672" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2673" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2673" s="17">
-        <v>45929.270138888889</v>
-      </c>
-      <c r="C2673" s="2">
-        <v>116141</v>
-      </c>
-      <c r="D2673" s="2">
-        <v>117290</v>
-      </c>
-      <c r="E2673" s="1">
-        <f t="shared" si="46"/>
-        <v>1149</v>
-      </c>
-      <c r="F2673" s="2">
-        <v>556.04</v>
-      </c>
-      <c r="G2673" s="16">
-        <v>3497.5</v>
-      </c>
-      <c r="H2673" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2673" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2673" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2673" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2674" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2674" s="17">
-        <v>45929.275000000001</v>
-      </c>
-      <c r="C2674" s="2">
-        <v>434038</v>
-      </c>
-      <c r="D2674" s="2">
-        <v>434245</v>
-      </c>
-      <c r="E2674" s="1">
-        <f t="shared" si="46"/>
-        <v>207</v>
-      </c>
-      <c r="F2674" s="2">
-        <v>53.39</v>
-      </c>
-      <c r="G2674" s="2">
-        <v>325.14999999999998</v>
-      </c>
-      <c r="H2674" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2674" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2674" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2674" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2675" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2675" s="17">
-        <v>45929.283333333333</v>
-      </c>
-      <c r="C2675" s="2">
-        <v>461828</v>
-      </c>
-      <c r="D2675" s="2">
-        <v>462056</v>
-      </c>
-      <c r="E2675" s="1">
-        <f t="shared" si="46"/>
-        <v>228</v>
-      </c>
-      <c r="F2675" s="2">
-        <v>65.95</v>
-      </c>
-      <c r="G2675" s="2">
-        <v>414.83</v>
-      </c>
-      <c r="H2675" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2675" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2675" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2675" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2676" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2676" s="17">
-        <v>45929.317361111112</v>
-      </c>
-      <c r="C2676" s="2">
-        <v>7202</v>
-      </c>
-      <c r="D2676" s="2">
-        <v>7367</v>
-      </c>
-      <c r="E2676" s="1">
-        <f t="shared" si="46"/>
-        <v>165</v>
-      </c>
-      <c r="F2676" s="2">
-        <v>12.09</v>
-      </c>
-      <c r="G2676" s="2">
-        <v>77.19</v>
-      </c>
-      <c r="H2676" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2676" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2676" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2676" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="L2676" s="28" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2677" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2677" s="17">
-        <v>45929.367361111108</v>
-      </c>
-      <c r="C2677" s="2">
-        <v>150654</v>
-      </c>
-      <c r="D2677" s="2">
-        <v>151023</v>
-      </c>
-      <c r="E2677" s="1">
-        <f t="shared" si="46"/>
-        <v>369</v>
-      </c>
-      <c r="F2677" s="2">
-        <v>20</v>
-      </c>
-      <c r="G2677" s="2">
-        <v>105</v>
-      </c>
-      <c r="H2677" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2677" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2677" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="K2677" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2678" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2678" s="17">
-        <v>45929.375694444447</v>
-      </c>
-      <c r="C2678" s="2">
-        <v>592426</v>
-      </c>
-      <c r="D2678" s="2">
-        <v>593033</v>
-      </c>
-      <c r="E2678" s="1">
-        <f t="shared" si="46"/>
-        <v>607</v>
-      </c>
-      <c r="F2678" s="2">
-        <v>74.7</v>
-      </c>
-      <c r="G2678" s="2">
-        <v>481.11</v>
-      </c>
-      <c r="H2678" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2678" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2678" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2678" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2679" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2679" s="17">
-        <v>45929.382638888892</v>
-      </c>
-      <c r="C2679" s="2">
-        <v>14329</v>
-      </c>
-      <c r="D2679" s="2">
-        <v>14813</v>
-      </c>
-      <c r="E2679" s="1">
-        <f t="shared" si="46"/>
-        <v>484</v>
-      </c>
-      <c r="F2679" s="2">
-        <v>44.7</v>
-      </c>
-      <c r="G2679" s="2">
-        <v>258.85000000000002</v>
-      </c>
-      <c r="H2679" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2679" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2679" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2679" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L2679" s="28" t="s">
+      <c r="B2652" s="23">
+        <v>45941</v>
+      </c>
+      <c r="F2652" s="2">
+        <v>200</v>
+      </c>
+      <c r="G2652" s="2">
+        <v>1128</v>
+      </c>
+      <c r="H2652" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2652" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2652" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="K2652" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2659" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2659" s="28"/>
+    </row>
+    <row r="2670" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2670" s="28"/>
+    </row>
+    <row r="2673" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2673" s="28" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="2680" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2680" s="17">
-        <v>45929.595138888886</v>
-      </c>
-      <c r="C2680" s="2">
-        <v>6647</v>
-      </c>
-      <c r="D2680" s="2">
-        <v>7065</v>
-      </c>
-      <c r="E2680" s="1">
-        <f t="shared" si="46"/>
-        <v>418</v>
-      </c>
-      <c r="F2680" s="2">
-        <v>40.479999999999997</v>
-      </c>
-      <c r="G2680" s="2">
-        <v>242.49</v>
-      </c>
-      <c r="H2680" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2680" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2680" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2680" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="L2680" s="28" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2681" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2681" s="17">
-        <v>45930.302083333336</v>
-      </c>
-      <c r="C2681" s="2">
-        <v>9895</v>
-      </c>
-      <c r="D2681" s="2">
-        <v>10313</v>
-      </c>
-      <c r="E2681" s="1">
-        <f t="shared" si="46"/>
-        <v>418</v>
-      </c>
-      <c r="F2681" s="2">
-        <v>35.229999999999997</v>
-      </c>
-      <c r="G2681" s="2">
-        <v>206.1</v>
-      </c>
-      <c r="H2681" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2681" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2681" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="K2681" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="L2681" s="28" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2682" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2682" s="17">
-        <v>45930.432638888888</v>
-      </c>
-      <c r="C2682" s="2">
-        <v>12533</v>
-      </c>
-      <c r="D2682" s="2">
-        <v>12943</v>
-      </c>
-      <c r="E2682" s="1">
-        <f t="shared" si="46"/>
-        <v>410</v>
-      </c>
-      <c r="F2682" s="2">
-        <v>38.56</v>
-      </c>
-      <c r="G2682" s="2">
-        <v>230.97</v>
-      </c>
-      <c r="H2682" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2682" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2682" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2682" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2682" s="28" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="2683" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2683" s="17">
-        <v>45930.491666666669</v>
-      </c>
-      <c r="C2683" s="2">
-        <v>11795</v>
-      </c>
-      <c r="D2683" s="2">
-        <v>12299</v>
-      </c>
-      <c r="E2683" s="1">
-        <f t="shared" si="46"/>
-        <v>504</v>
-      </c>
-      <c r="F2683" s="2">
-        <v>38.29</v>
-      </c>
-      <c r="G2683" s="2">
-        <v>240.89</v>
-      </c>
-      <c r="H2683" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2683" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2683" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K2683" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="L2683" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2684" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2684" s="17">
-        <v>45930.522222222222</v>
-      </c>
-      <c r="E2684" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2684" s="2">
-        <v>32.57</v>
-      </c>
-      <c r="G2684" s="2">
-        <v>200</v>
-      </c>
-      <c r="H2684" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2684" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2684" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="K2684" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2685" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2685" s="17">
-        <v>45930.604166666664</v>
-      </c>
-      <c r="C2685" s="2">
-        <v>434245</v>
-      </c>
-      <c r="D2685" s="2">
-        <v>434676</v>
-      </c>
-      <c r="E2685" s="1">
-        <f t="shared" si="46"/>
-        <v>431</v>
-      </c>
-      <c r="F2685" s="16">
-        <v>1373.21</v>
-      </c>
-      <c r="G2685" s="2">
-        <v>836.28</v>
-      </c>
-      <c r="H2685" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2685" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2685" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2685" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2686" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2686" s="17">
-        <v>45930.614583333336</v>
-      </c>
-      <c r="C2686" s="2">
-        <v>434676</v>
-      </c>
-      <c r="D2686" s="2">
-        <v>434750</v>
-      </c>
-      <c r="E2686" s="1">
-        <f t="shared" si="46"/>
-        <v>74</v>
-      </c>
-      <c r="F2686" s="2">
-        <v>68</v>
-      </c>
-      <c r="G2686" s="2">
-        <v>719.96</v>
-      </c>
-      <c r="H2686" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2686" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2686" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2686" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2687" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2687" s="17">
-        <v>45930.663194444445</v>
-      </c>
-      <c r="C2687" s="2">
-        <v>462056</v>
-      </c>
-      <c r="D2687" s="2">
-        <v>462644</v>
-      </c>
-      <c r="E2687" s="1">
-        <f t="shared" si="46"/>
-        <v>588</v>
-      </c>
-      <c r="F2687" s="2">
-        <v>180.05</v>
-      </c>
-      <c r="G2687" s="16">
-        <v>1132.55</v>
-      </c>
-      <c r="H2687" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2687" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2687" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2687" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2688" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2688" s="17">
-        <v>45930.68472222222</v>
-      </c>
-      <c r="C2688" s="2">
-        <v>305379</v>
-      </c>
-      <c r="D2688" s="2">
-        <v>305495</v>
-      </c>
-      <c r="E2688" s="1">
-        <f t="shared" si="46"/>
-        <v>116</v>
-      </c>
-      <c r="F2688" s="2">
-        <v>208.95</v>
-      </c>
-      <c r="G2688" s="16">
-        <v>1314.32</v>
-      </c>
-      <c r="H2688" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2688" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2688" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2688" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2689" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2689" s="17">
-        <v>45930.807638888888</v>
-      </c>
-      <c r="E2689" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2689" s="2">
-        <v>133.28</v>
-      </c>
-      <c r="G2689" s="2">
-        <v>838.35</v>
-      </c>
-      <c r="H2689" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2689" s="12">
-        <v>45901</v>
-      </c>
-      <c r="J2689" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2689" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="2690" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2690" s="18"/>
-      <c r="C2690" s="1"/>
-      <c r="D2690" s="1"/>
-      <c r="E2690" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2690" s="1"/>
-      <c r="G2690" s="10"/>
-      <c r="K2690" s="7"/>
-    </row>
-    <row r="2691" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2691" s="18"/>
-      <c r="C2691" s="1"/>
-      <c r="D2691" s="1"/>
-      <c r="E2691" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2691" s="1"/>
-      <c r="G2691" s="10"/>
-      <c r="K2691" s="7"/>
-    </row>
-    <row r="2692" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2692" s="18"/>
-      <c r="C2692" s="1"/>
-      <c r="D2692" s="1"/>
-      <c r="E2692" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2692" s="1"/>
-      <c r="G2692" s="10"/>
-      <c r="K2692" s="7"/>
-    </row>
-    <row r="2693" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2693" s="18"/>
-      <c r="C2693" s="1"/>
-      <c r="D2693" s="1"/>
-      <c r="E2693" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2693" s="1"/>
-      <c r="G2693" s="10"/>
-      <c r="K2693" s="7"/>
-    </row>
-    <row r="2694" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2694" s="18"/>
-      <c r="C2694" s="1"/>
-      <c r="D2694" s="1"/>
-      <c r="E2694" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2694" s="1"/>
-      <c r="G2694" s="10"/>
-      <c r="K2694" s="7"/>
-    </row>
-    <row r="2695" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2695" s="18"/>
-      <c r="C2695" s="1"/>
-      <c r="D2695" s="1"/>
-      <c r="E2695" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2695" s="1"/>
-      <c r="G2695" s="10"/>
-      <c r="K2695" s="7"/>
-    </row>
-    <row r="2696" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2696" s="18"/>
-      <c r="C2696" s="1"/>
-      <c r="D2696" s="1"/>
-      <c r="E2696" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2696" s="1"/>
-      <c r="G2696" s="10"/>
-      <c r="K2696" s="7"/>
-    </row>
-    <row r="2697" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2697" s="18"/>
-      <c r="C2697" s="1"/>
-      <c r="D2697" s="1"/>
-      <c r="E2697" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2697" s="1"/>
-      <c r="G2697" s="10"/>
-      <c r="K2697" s="7"/>
-    </row>
-    <row r="2698" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2698" s="18"/>
-      <c r="C2698" s="1"/>
-      <c r="D2698" s="1"/>
-      <c r="E2698" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2698" s="1"/>
-      <c r="G2698" s="10"/>
-      <c r="K2698" s="7"/>
-    </row>
-    <row r="2699" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2699" s="18"/>
-      <c r="C2699" s="1"/>
-      <c r="D2699" s="1"/>
-      <c r="E2699" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2699" s="1"/>
-      <c r="G2699" s="10"/>
-      <c r="K2699" s="7"/>
-    </row>
-    <row r="2700" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2700" s="18"/>
-      <c r="C2700" s="1"/>
-      <c r="D2700" s="1"/>
-      <c r="E2700" s="1">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="F2700" s="1"/>
-      <c r="G2700" s="10"/>
-      <c r="K2700" s="7"/>
-    </row>
-    <row r="2701" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2701" s="18"/>
-      <c r="C2701" s="1"/>
-      <c r="D2701" s="1"/>
-      <c r="E2701" s="1">
-        <f t="shared" ref="E2701:E2764" si="47">D2701-C2701</f>
-        <v>0</v>
-      </c>
-      <c r="F2701" s="1"/>
-      <c r="G2701" s="10"/>
-      <c r="K2701" s="7"/>
-    </row>
-    <row r="2702" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2702" s="18"/>
-      <c r="C2702" s="1"/>
-      <c r="D2702" s="1"/>
-      <c r="E2702" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2702" s="1"/>
-      <c r="G2702" s="10"/>
-      <c r="K2702" s="7"/>
-    </row>
-    <row r="2703" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2703" s="18"/>
-      <c r="C2703" s="1"/>
-      <c r="D2703" s="1"/>
-      <c r="E2703" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2703" s="1"/>
-      <c r="G2703" s="10"/>
-      <c r="K2703" s="7"/>
-    </row>
-    <row r="2704" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2704" s="18"/>
-      <c r="C2704" s="1"/>
-      <c r="D2704" s="1"/>
-      <c r="E2704" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2704" s="1"/>
-      <c r="G2704" s="10"/>
-      <c r="K2704" s="7"/>
-    </row>
-    <row r="2705" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2705" s="18"/>
-      <c r="C2705" s="1"/>
-      <c r="D2705" s="1"/>
-      <c r="E2705" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2705" s="1"/>
-      <c r="G2705" s="10"/>
-      <c r="K2705" s="7"/>
-    </row>
-    <row r="2706" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2706" s="18"/>
-      <c r="C2706" s="1"/>
-      <c r="D2706" s="1"/>
-      <c r="E2706" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2706" s="1"/>
-      <c r="G2706" s="10"/>
-      <c r="K2706" s="7"/>
-    </row>
-    <row r="2707" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2707" s="18"/>
-      <c r="C2707" s="1"/>
-      <c r="D2707" s="1"/>
-      <c r="E2707" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2707" s="1"/>
-      <c r="G2707" s="10"/>
-      <c r="K2707" s="7"/>
-    </row>
-    <row r="2708" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2708" s="18"/>
-      <c r="C2708" s="1"/>
-      <c r="D2708" s="1"/>
-      <c r="E2708" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2708" s="1"/>
-      <c r="G2708" s="10"/>
-      <c r="K2708" s="7"/>
-    </row>
-    <row r="2709" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2709" s="18"/>
-      <c r="C2709" s="1"/>
-      <c r="D2709" s="1"/>
-      <c r="E2709" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2709" s="1"/>
-      <c r="G2709" s="10"/>
-      <c r="K2709" s="7"/>
-    </row>
-    <row r="2710" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2710" s="18"/>
-      <c r="C2710" s="1"/>
-      <c r="D2710" s="1"/>
-      <c r="E2710" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2710" s="1"/>
-      <c r="G2710" s="10"/>
-      <c r="K2710" s="7"/>
-    </row>
-    <row r="2711" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2711" s="18"/>
-      <c r="C2711" s="1"/>
-      <c r="D2711" s="1"/>
-      <c r="E2711" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2711" s="1"/>
-      <c r="G2711" s="10"/>
-      <c r="K2711" s="7"/>
-    </row>
-    <row r="2712" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2712" s="18"/>
-      <c r="C2712" s="1"/>
-      <c r="D2712" s="1"/>
-      <c r="E2712" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2712" s="1"/>
-      <c r="G2712" s="10"/>
-      <c r="K2712" s="7"/>
-    </row>
-    <row r="2713" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2713" s="18"/>
-      <c r="C2713" s="1"/>
-      <c r="D2713" s="1"/>
-      <c r="E2713" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2713" s="1"/>
-      <c r="G2713" s="10"/>
-      <c r="K2713" s="7"/>
-    </row>
-    <row r="2714" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2714" s="18"/>
-      <c r="C2714" s="1"/>
-      <c r="D2714" s="1"/>
-      <c r="E2714" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2714" s="1"/>
-      <c r="G2714" s="10"/>
-      <c r="K2714" s="7"/>
-    </row>
-    <row r="2715" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2715" s="18"/>
-      <c r="C2715" s="1"/>
-      <c r="D2715" s="1"/>
-      <c r="E2715" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2715" s="1"/>
-      <c r="G2715" s="10"/>
-      <c r="K2715" s="7"/>
-    </row>
-    <row r="2716" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2716" s="18"/>
-      <c r="C2716" s="1"/>
-      <c r="D2716" s="1"/>
-      <c r="E2716" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2716" s="1"/>
-      <c r="G2716" s="10"/>
-      <c r="K2716" s="7"/>
-    </row>
-    <row r="2717" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2717" s="18"/>
-      <c r="C2717" s="1"/>
-      <c r="D2717" s="1"/>
-      <c r="E2717" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2717" s="1"/>
-      <c r="G2717" s="10"/>
-      <c r="K2717" s="7"/>
-    </row>
-    <row r="2718" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2718" s="18"/>
-      <c r="C2718" s="1"/>
-      <c r="D2718" s="1"/>
-      <c r="E2718" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2718" s="1"/>
-      <c r="G2718" s="10"/>
-      <c r="K2718" s="7"/>
-    </row>
-    <row r="2719" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2719" s="18"/>
-      <c r="C2719" s="1"/>
-      <c r="D2719" s="1"/>
-      <c r="E2719" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2719" s="1"/>
-      <c r="G2719" s="10"/>
-      <c r="K2719" s="7"/>
-    </row>
-    <row r="2720" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2720" s="18"/>
-      <c r="C2720" s="1"/>
-      <c r="D2720" s="1"/>
-      <c r="E2720" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2720" s="1"/>
-      <c r="G2720" s="10"/>
-      <c r="K2720" s="7"/>
-    </row>
-    <row r="2721" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2721" s="18"/>
-      <c r="C2721" s="1"/>
-      <c r="D2721" s="1"/>
-      <c r="E2721" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2721" s="1"/>
-      <c r="G2721" s="10"/>
-      <c r="K2721" s="7"/>
-    </row>
-    <row r="2722" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2722" s="18"/>
-      <c r="C2722" s="1"/>
-      <c r="D2722" s="1"/>
-      <c r="E2722" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2722" s="1"/>
-      <c r="G2722" s="10"/>
-      <c r="K2722" s="7"/>
-    </row>
-    <row r="2723" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2723" s="18"/>
-      <c r="C2723" s="1"/>
-      <c r="D2723" s="1"/>
-      <c r="E2723" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2723" s="1"/>
-      <c r="G2723" s="10"/>
-      <c r="K2723" s="7"/>
-    </row>
-    <row r="2724" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2724" s="18"/>
-      <c r="C2724" s="1"/>
-      <c r="D2724" s="1"/>
-      <c r="E2724" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2724" s="1"/>
-      <c r="G2724" s="10"/>
-      <c r="K2724" s="7"/>
-    </row>
-    <row r="2725" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2725" s="18"/>
-      <c r="C2725" s="1"/>
-      <c r="D2725" s="1"/>
-      <c r="E2725" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2725" s="1"/>
-      <c r="G2725" s="10"/>
-      <c r="K2725" s="7"/>
-    </row>
-    <row r="2726" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2726" s="18"/>
-      <c r="C2726" s="1"/>
-      <c r="D2726" s="1"/>
-      <c r="E2726" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2726" s="1"/>
-      <c r="G2726" s="10"/>
-      <c r="K2726" s="7"/>
-    </row>
-    <row r="2727" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2727" s="18"/>
-      <c r="C2727" s="1"/>
-      <c r="D2727" s="1"/>
-      <c r="E2727" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2727" s="1"/>
-      <c r="G2727" s="10"/>
-      <c r="K2727" s="7"/>
-    </row>
-    <row r="2728" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2728" s="18"/>
-      <c r="C2728" s="1"/>
-      <c r="D2728" s="1"/>
-      <c r="E2728" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2728" s="1"/>
-      <c r="G2728" s="10"/>
-      <c r="K2728" s="7"/>
-    </row>
-    <row r="2729" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2729" s="18"/>
-      <c r="C2729" s="1"/>
-      <c r="D2729" s="1"/>
-      <c r="E2729" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2729" s="1"/>
-      <c r="G2729" s="10"/>
-      <c r="K2729" s="7"/>
-    </row>
-    <row r="2730" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2730" s="18"/>
-      <c r="C2730" s="1"/>
-      <c r="D2730" s="1"/>
-      <c r="E2730" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2730" s="1"/>
-      <c r="G2730" s="10"/>
-      <c r="K2730" s="7"/>
-    </row>
-    <row r="2731" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2731" s="18"/>
-      <c r="C2731" s="1"/>
-      <c r="D2731" s="1"/>
-      <c r="E2731" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2731" s="1"/>
-      <c r="G2731" s="10"/>
-      <c r="K2731" s="7"/>
-    </row>
-    <row r="2732" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2732" s="18"/>
-      <c r="C2732" s="1"/>
-      <c r="D2732" s="1"/>
-      <c r="E2732" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2732" s="1"/>
-      <c r="G2732" s="10"/>
-      <c r="K2732" s="7"/>
-    </row>
-    <row r="2733" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2733" s="18"/>
-      <c r="C2733" s="1"/>
-      <c r="D2733" s="1"/>
-      <c r="E2733" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2733" s="1"/>
-      <c r="G2733" s="10"/>
-      <c r="K2733" s="7"/>
-    </row>
-    <row r="2734" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2734" s="18"/>
-      <c r="C2734" s="1"/>
-      <c r="D2734" s="1"/>
-      <c r="E2734" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2734" s="1"/>
-      <c r="G2734" s="10"/>
-      <c r="K2734" s="7"/>
-    </row>
-    <row r="2735" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2735" s="18"/>
-      <c r="C2735" s="1"/>
-      <c r="D2735" s="1"/>
-      <c r="E2735" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2735" s="1"/>
-      <c r="G2735" s="10"/>
-      <c r="K2735" s="7"/>
-    </row>
-    <row r="2736" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2736" s="18"/>
-      <c r="C2736" s="1"/>
-      <c r="D2736" s="1"/>
-      <c r="E2736" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2736" s="1"/>
-      <c r="G2736" s="10"/>
-      <c r="K2736" s="7"/>
-    </row>
-    <row r="2737" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2737" s="18"/>
-      <c r="C2737" s="1"/>
-      <c r="D2737" s="1"/>
-      <c r="E2737" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2737" s="1"/>
-      <c r="G2737" s="10"/>
-      <c r="K2737" s="7"/>
-    </row>
-    <row r="2738" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2738" s="18"/>
-      <c r="C2738" s="1"/>
-      <c r="D2738" s="1"/>
-      <c r="E2738" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2738" s="1"/>
-      <c r="G2738" s="10"/>
-      <c r="K2738" s="7"/>
-    </row>
-    <row r="2739" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2739" s="18"/>
-      <c r="C2739" s="1"/>
-      <c r="D2739" s="1"/>
-      <c r="E2739" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2739" s="1"/>
-      <c r="G2739" s="10"/>
-      <c r="K2739" s="7"/>
-    </row>
-    <row r="2740" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2740" s="18"/>
-      <c r="C2740" s="1"/>
-      <c r="D2740" s="1"/>
-      <c r="E2740" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2740" s="1"/>
-      <c r="G2740" s="10"/>
-      <c r="K2740" s="7"/>
-    </row>
-    <row r="2741" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2741" s="18"/>
-      <c r="C2741" s="1"/>
-      <c r="D2741" s="1"/>
-      <c r="E2741" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2741" s="1"/>
-      <c r="G2741" s="10"/>
-      <c r="K2741" s="7"/>
-    </row>
-    <row r="2742" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2742" s="18"/>
-      <c r="C2742" s="1"/>
-      <c r="D2742" s="1"/>
-      <c r="E2742" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2742" s="1"/>
-      <c r="G2742" s="10"/>
-      <c r="K2742" s="7"/>
-    </row>
-    <row r="2743" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2743" s="18"/>
-      <c r="C2743" s="1"/>
-      <c r="D2743" s="1"/>
-      <c r="E2743" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2743" s="1"/>
-      <c r="G2743" s="10"/>
-      <c r="K2743" s="7"/>
-    </row>
-    <row r="2744" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2744" s="18"/>
-      <c r="C2744" s="1"/>
-      <c r="D2744" s="1"/>
-      <c r="E2744" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2744" s="1"/>
-      <c r="G2744" s="10"/>
-      <c r="K2744" s="7"/>
-    </row>
-    <row r="2745" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2745" s="18"/>
-      <c r="C2745" s="1"/>
-      <c r="D2745" s="1"/>
-      <c r="E2745" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2745" s="1"/>
-      <c r="G2745" s="10"/>
-      <c r="K2745" s="7"/>
-    </row>
-    <row r="2746" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2746" s="18"/>
-      <c r="C2746" s="1"/>
-      <c r="D2746" s="1"/>
-      <c r="E2746" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2746" s="1"/>
-      <c r="G2746" s="10"/>
-      <c r="K2746" s="7"/>
-    </row>
-    <row r="2747" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2747" s="18"/>
-      <c r="C2747" s="1"/>
-      <c r="D2747" s="1"/>
-      <c r="E2747" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2747" s="1"/>
-      <c r="G2747" s="10"/>
-      <c r="K2747" s="7"/>
-    </row>
-    <row r="2748" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2748" s="18"/>
-      <c r="C2748" s="1"/>
-      <c r="D2748" s="1"/>
-      <c r="E2748" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2748" s="1"/>
-      <c r="G2748" s="10"/>
-      <c r="K2748" s="7"/>
-    </row>
-    <row r="2749" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2749" s="18"/>
-      <c r="C2749" s="1"/>
-      <c r="D2749" s="1"/>
-      <c r="E2749" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2749" s="1"/>
-      <c r="G2749" s="10"/>
-      <c r="K2749" s="7"/>
-    </row>
-    <row r="2750" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2750" s="18"/>
-      <c r="C2750" s="1"/>
-      <c r="D2750" s="1"/>
-      <c r="E2750" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2750" s="1"/>
-      <c r="G2750" s="10"/>
-      <c r="K2750" s="7"/>
-    </row>
-    <row r="2751" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2751" s="18"/>
-      <c r="C2751" s="1"/>
-      <c r="D2751" s="1"/>
-      <c r="E2751" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2751" s="1"/>
-      <c r="G2751" s="10"/>
-      <c r="K2751" s="7"/>
-    </row>
-    <row r="2752" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2752" s="18"/>
-      <c r="C2752" s="1"/>
-      <c r="D2752" s="1"/>
-      <c r="E2752" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2752" s="1"/>
-      <c r="G2752" s="10"/>
-      <c r="K2752" s="7"/>
-    </row>
-    <row r="2753" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2753" s="18"/>
-      <c r="C2753" s="1"/>
-      <c r="D2753" s="1"/>
-      <c r="E2753" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2753" s="1"/>
-      <c r="G2753" s="10"/>
-      <c r="K2753" s="7"/>
-    </row>
-    <row r="2754" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2754" s="18"/>
-      <c r="C2754" s="1"/>
-      <c r="D2754" s="1"/>
-      <c r="E2754" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2754" s="1"/>
-      <c r="G2754" s="10"/>
-      <c r="K2754" s="7"/>
-    </row>
-    <row r="2755" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2755" s="18"/>
-      <c r="C2755" s="1"/>
-      <c r="D2755" s="1"/>
-      <c r="E2755" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2755" s="1"/>
-      <c r="G2755" s="10"/>
-      <c r="K2755" s="7"/>
-    </row>
-    <row r="2756" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2756" s="18"/>
-      <c r="C2756" s="1"/>
-      <c r="D2756" s="1"/>
-      <c r="E2756" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2756" s="1"/>
-      <c r="G2756" s="10"/>
-      <c r="K2756" s="7"/>
-    </row>
-    <row r="2757" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2757" s="18"/>
-      <c r="C2757" s="1"/>
-      <c r="D2757" s="1"/>
-      <c r="E2757" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2757" s="1"/>
-      <c r="G2757" s="10"/>
-      <c r="K2757" s="7"/>
-    </row>
-    <row r="2758" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2758" s="18"/>
-      <c r="C2758" s="1"/>
-      <c r="D2758" s="1"/>
-      <c r="E2758" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2758" s="1"/>
-      <c r="G2758" s="10"/>
-      <c r="K2758" s="7"/>
-    </row>
-    <row r="2759" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2759" s="18"/>
-      <c r="C2759" s="1"/>
-      <c r="D2759" s="1"/>
-      <c r="E2759" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2759" s="1"/>
-      <c r="G2759" s="10"/>
-      <c r="K2759" s="7"/>
-    </row>
-    <row r="2760" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2760" s="18"/>
-      <c r="C2760" s="1"/>
-      <c r="D2760" s="1"/>
-      <c r="E2760" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2760" s="1"/>
-      <c r="G2760" s="10"/>
-      <c r="K2760" s="7"/>
-    </row>
-    <row r="2761" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2761" s="18"/>
-      <c r="C2761" s="1"/>
-      <c r="D2761" s="1"/>
-      <c r="E2761" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2761" s="1"/>
-      <c r="G2761" s="10"/>
-      <c r="K2761" s="7"/>
-    </row>
-    <row r="2762" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2762" s="18"/>
-      <c r="C2762" s="1"/>
-      <c r="D2762" s="1"/>
-      <c r="E2762" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2762" s="1"/>
-      <c r="G2762" s="10"/>
-      <c r="K2762" s="7"/>
-    </row>
-    <row r="2763" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2763" s="18"/>
-      <c r="C2763" s="1"/>
-      <c r="D2763" s="1"/>
-      <c r="E2763" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2763" s="1"/>
-      <c r="G2763" s="10"/>
-      <c r="K2763" s="7"/>
-    </row>
-    <row r="2764" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2764" s="18"/>
-      <c r="C2764" s="1"/>
-      <c r="D2764" s="1"/>
-      <c r="E2764" s="1">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="F2764" s="1"/>
-      <c r="G2764" s="10"/>
-      <c r="K2764" s="7"/>
-    </row>
-    <row r="2765" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2765" s="18"/>
-      <c r="C2765" s="1"/>
-      <c r="D2765" s="1"/>
-      <c r="E2765" s="1">
-        <f t="shared" ref="E2765:E2828" si="48">D2765-C2765</f>
-        <v>0</v>
-      </c>
-      <c r="F2765" s="1"/>
-      <c r="G2765" s="10"/>
-      <c r="K2765" s="7"/>
-    </row>
-    <row r="2766" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2766" s="18"/>
-      <c r="C2766" s="1"/>
-      <c r="D2766" s="1"/>
-      <c r="E2766" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2766" s="1"/>
-      <c r="G2766" s="10"/>
-      <c r="K2766" s="7"/>
-    </row>
-    <row r="2767" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2767" s="18"/>
-      <c r="C2767" s="1"/>
-      <c r="D2767" s="1"/>
-      <c r="E2767" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2767" s="1"/>
-      <c r="G2767" s="10"/>
-      <c r="K2767" s="7"/>
-    </row>
-    <row r="2768" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2768" s="18"/>
-      <c r="C2768" s="1"/>
-      <c r="D2768" s="1"/>
-      <c r="E2768" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2768" s="1"/>
-      <c r="G2768" s="10"/>
-      <c r="K2768" s="7"/>
-    </row>
-    <row r="2769" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2769" s="18"/>
-      <c r="C2769" s="1"/>
-      <c r="D2769" s="1"/>
-      <c r="E2769" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2769" s="1"/>
-      <c r="G2769" s="10"/>
-      <c r="K2769" s="7"/>
-    </row>
-    <row r="2770" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2770" s="18"/>
-      <c r="C2770" s="1"/>
-      <c r="D2770" s="1"/>
-      <c r="E2770" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2770" s="1"/>
-      <c r="G2770" s="10"/>
-      <c r="K2770" s="7"/>
-    </row>
-    <row r="2771" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2771" s="18"/>
-      <c r="C2771" s="1"/>
-      <c r="D2771" s="1"/>
-      <c r="E2771" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2771" s="1"/>
-      <c r="G2771" s="10"/>
-      <c r="K2771" s="7"/>
-    </row>
-    <row r="2772" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2772" s="18"/>
-      <c r="C2772" s="1"/>
-      <c r="D2772" s="1"/>
-      <c r="E2772" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2772" s="1"/>
-      <c r="G2772" s="10"/>
-      <c r="K2772" s="7"/>
-    </row>
-    <row r="2773" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2773" s="18"/>
-      <c r="C2773" s="1"/>
-      <c r="D2773" s="1"/>
-      <c r="E2773" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2773" s="1"/>
-      <c r="G2773" s="10"/>
-      <c r="K2773" s="7"/>
-    </row>
-    <row r="2774" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2774" s="18"/>
-      <c r="C2774" s="1"/>
-      <c r="D2774" s="1"/>
-      <c r="E2774" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2774" s="1"/>
-      <c r="G2774" s="10"/>
-      <c r="K2774" s="7"/>
-    </row>
-    <row r="2775" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2775" s="18"/>
-      <c r="C2775" s="1"/>
-      <c r="D2775" s="1"/>
-      <c r="E2775" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2775" s="1"/>
-      <c r="G2775" s="10"/>
-      <c r="K2775" s="7"/>
-    </row>
-    <row r="2776" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2776" s="18"/>
-      <c r="C2776" s="1"/>
-      <c r="D2776" s="1"/>
-      <c r="E2776" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2776" s="1"/>
-      <c r="G2776" s="10"/>
-      <c r="K2776" s="7"/>
-    </row>
-    <row r="2777" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2777" s="18"/>
-      <c r="C2777" s="1"/>
-      <c r="D2777" s="1"/>
-      <c r="E2777" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2777" s="1"/>
-      <c r="G2777" s="10"/>
-      <c r="K2777" s="7"/>
-    </row>
-    <row r="2778" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2778" s="18"/>
-      <c r="C2778" s="1"/>
-      <c r="D2778" s="1"/>
-      <c r="E2778" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2778" s="1"/>
-      <c r="G2778" s="10"/>
-      <c r="K2778" s="7"/>
-    </row>
-    <row r="2779" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2779" s="18"/>
-      <c r="C2779" s="1"/>
-      <c r="D2779" s="1"/>
-      <c r="E2779" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2779" s="1"/>
-      <c r="G2779" s="10"/>
-      <c r="K2779" s="7"/>
-    </row>
-    <row r="2780" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2780" s="18"/>
-      <c r="C2780" s="1"/>
-      <c r="D2780" s="1"/>
-      <c r="E2780" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2780" s="1"/>
-      <c r="G2780" s="10"/>
-      <c r="K2780" s="7"/>
-    </row>
-    <row r="2781" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2781" s="18"/>
-      <c r="C2781" s="1"/>
-      <c r="D2781" s="1"/>
-      <c r="E2781" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2781" s="1"/>
-      <c r="G2781" s="10"/>
-      <c r="K2781" s="7"/>
-    </row>
-    <row r="2782" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2782" s="18"/>
-      <c r="C2782" s="1"/>
-      <c r="D2782" s="1"/>
-      <c r="E2782" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2782" s="1"/>
-      <c r="G2782" s="10"/>
-      <c r="K2782" s="7"/>
-    </row>
-    <row r="2783" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2783" s="18"/>
-      <c r="C2783" s="1"/>
-      <c r="D2783" s="1"/>
-      <c r="E2783" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2783" s="1"/>
-      <c r="G2783" s="10"/>
-      <c r="K2783" s="7"/>
-    </row>
-    <row r="2784" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2784" s="18"/>
-      <c r="C2784" s="1"/>
-      <c r="D2784" s="1"/>
-      <c r="E2784" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2784" s="1"/>
-      <c r="G2784" s="10"/>
-      <c r="K2784" s="7"/>
-    </row>
-    <row r="2785" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2785" s="18"/>
-      <c r="C2785" s="1"/>
-      <c r="D2785" s="1"/>
-      <c r="E2785" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2785" s="1"/>
-      <c r="G2785" s="10"/>
-      <c r="K2785" s="7"/>
-    </row>
-    <row r="2786" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2786" s="18"/>
-      <c r="C2786" s="1"/>
-      <c r="D2786" s="1"/>
-      <c r="E2786" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2786" s="1"/>
-      <c r="G2786" s="10"/>
-      <c r="K2786" s="7"/>
-    </row>
-    <row r="2787" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2787" s="18"/>
-      <c r="C2787" s="1"/>
-      <c r="D2787" s="1"/>
-      <c r="E2787" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2787" s="1"/>
-      <c r="G2787" s="10"/>
-      <c r="K2787" s="7"/>
-    </row>
-    <row r="2788" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2788" s="18"/>
-      <c r="C2788" s="1"/>
-      <c r="D2788" s="1"/>
-      <c r="E2788" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2788" s="1"/>
-      <c r="G2788" s="10"/>
-      <c r="K2788" s="7"/>
-    </row>
-    <row r="2789" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2789" s="18"/>
-      <c r="C2789" s="1"/>
-      <c r="D2789" s="1"/>
-      <c r="E2789" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2789" s="1"/>
-      <c r="G2789" s="10"/>
-      <c r="K2789" s="7"/>
-    </row>
-    <row r="2790" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2790" s="18"/>
-      <c r="C2790" s="1"/>
-      <c r="D2790" s="1"/>
-      <c r="E2790" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2790" s="1"/>
-      <c r="G2790" s="10"/>
-      <c r="K2790" s="7"/>
-    </row>
-    <row r="2791" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2791" s="18"/>
-      <c r="C2791" s="1"/>
-      <c r="D2791" s="1"/>
-      <c r="E2791" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2791" s="1"/>
-      <c r="G2791" s="10"/>
-      <c r="K2791" s="7"/>
-    </row>
-    <row r="2792" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2792" s="18"/>
-      <c r="C2792" s="1"/>
-      <c r="D2792" s="1"/>
-      <c r="E2792" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2792" s="1"/>
-      <c r="G2792" s="10"/>
-      <c r="K2792" s="7"/>
-    </row>
-    <row r="2793" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2793" s="18"/>
-      <c r="C2793" s="1"/>
-      <c r="D2793" s="1"/>
-      <c r="E2793" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2793" s="1"/>
-      <c r="G2793" s="10"/>
-      <c r="K2793" s="7"/>
-    </row>
-    <row r="2794" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2794" s="18"/>
-      <c r="C2794" s="1"/>
-      <c r="D2794" s="1"/>
-      <c r="E2794" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2794" s="1"/>
-      <c r="G2794" s="10"/>
-      <c r="K2794" s="7"/>
-    </row>
-    <row r="2795" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2795" s="18"/>
-      <c r="C2795" s="1"/>
-      <c r="D2795" s="1"/>
-      <c r="E2795" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2795" s="1"/>
-      <c r="G2795" s="10"/>
-      <c r="K2795" s="7"/>
-    </row>
-    <row r="2796" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2796" s="18"/>
-      <c r="C2796" s="1"/>
-      <c r="D2796" s="1"/>
-      <c r="E2796" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2796" s="1"/>
-      <c r="G2796" s="10"/>
-      <c r="K2796" s="7"/>
-    </row>
-    <row r="2797" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2797" s="18"/>
-      <c r="C2797" s="1"/>
-      <c r="D2797" s="1"/>
-      <c r="E2797" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2797" s="1"/>
-      <c r="G2797" s="10"/>
-      <c r="K2797" s="7"/>
-    </row>
-    <row r="2798" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2798" s="18"/>
-      <c r="C2798" s="1"/>
-      <c r="D2798" s="1"/>
-      <c r="E2798" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2798" s="1"/>
-      <c r="G2798" s="10"/>
-      <c r="K2798" s="7"/>
-    </row>
-    <row r="2799" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2799" s="18"/>
-      <c r="C2799" s="1"/>
-      <c r="D2799" s="1"/>
-      <c r="E2799" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2799" s="1"/>
-      <c r="G2799" s="10"/>
-      <c r="K2799" s="7"/>
-    </row>
-    <row r="2800" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2800" s="18"/>
-      <c r="C2800" s="1"/>
-      <c r="D2800" s="1"/>
-      <c r="E2800" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2800" s="1"/>
-      <c r="G2800" s="10"/>
-      <c r="K2800" s="7"/>
-    </row>
-    <row r="2801" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2801" s="18"/>
-      <c r="C2801" s="1"/>
-      <c r="D2801" s="1"/>
-      <c r="E2801" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2801" s="1"/>
-      <c r="G2801" s="10"/>
-      <c r="K2801" s="7"/>
-    </row>
-    <row r="2802" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2802" s="18"/>
-      <c r="C2802" s="1"/>
-      <c r="D2802" s="1"/>
-      <c r="E2802" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2802" s="1"/>
-      <c r="G2802" s="10"/>
-      <c r="K2802" s="7"/>
-    </row>
-    <row r="2803" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2803" s="18"/>
-      <c r="C2803" s="1"/>
-      <c r="D2803" s="1"/>
-      <c r="E2803" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2803" s="1"/>
-      <c r="G2803" s="10"/>
-      <c r="K2803" s="7"/>
-    </row>
-    <row r="2804" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2804" s="18"/>
-      <c r="C2804" s="1"/>
-      <c r="D2804" s="1"/>
-      <c r="E2804" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2804" s="1"/>
-      <c r="G2804" s="10"/>
-      <c r="K2804" s="7"/>
-    </row>
-    <row r="2805" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2805" s="18"/>
-      <c r="C2805" s="1"/>
-      <c r="D2805" s="1"/>
-      <c r="E2805" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2805" s="1"/>
-      <c r="G2805" s="10"/>
-      <c r="K2805" s="7"/>
-    </row>
-    <row r="2806" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2806" s="18"/>
-      <c r="C2806" s="1"/>
-      <c r="D2806" s="1"/>
-      <c r="E2806" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2806" s="1"/>
-      <c r="G2806" s="10"/>
-      <c r="K2806" s="7"/>
-    </row>
-    <row r="2807" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2807" s="18"/>
-      <c r="C2807" s="1"/>
-      <c r="D2807" s="1"/>
-      <c r="E2807" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2807" s="1"/>
-      <c r="G2807" s="10"/>
-      <c r="K2807" s="7"/>
-    </row>
-    <row r="2808" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2808" s="18"/>
-      <c r="C2808" s="1"/>
-      <c r="D2808" s="1"/>
-      <c r="E2808" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2808" s="1"/>
-      <c r="G2808" s="10"/>
-      <c r="K2808" s="7"/>
-    </row>
-    <row r="2809" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2809" s="18"/>
-      <c r="C2809" s="1"/>
-      <c r="D2809" s="1"/>
-      <c r="E2809" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2809" s="1"/>
-      <c r="G2809" s="10"/>
-      <c r="K2809" s="7"/>
-    </row>
-    <row r="2810" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2810" s="18"/>
-      <c r="C2810" s="1"/>
-      <c r="D2810" s="1"/>
-      <c r="E2810" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2810" s="1"/>
-      <c r="G2810" s="10"/>
-      <c r="K2810" s="7"/>
-    </row>
-    <row r="2811" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2811" s="18"/>
-      <c r="C2811" s="1"/>
-      <c r="D2811" s="1"/>
-      <c r="E2811" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2811" s="1"/>
-      <c r="G2811" s="10"/>
-      <c r="K2811" s="7"/>
-    </row>
-    <row r="2812" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2812" s="18"/>
-      <c r="C2812" s="1"/>
-      <c r="D2812" s="1"/>
-      <c r="E2812" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2812" s="1"/>
-      <c r="G2812" s="10"/>
-      <c r="K2812" s="7"/>
-    </row>
-    <row r="2813" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2813" s="18"/>
-      <c r="C2813" s="1"/>
-      <c r="D2813" s="1"/>
-      <c r="E2813" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2813" s="1"/>
-      <c r="G2813" s="10"/>
-      <c r="K2813" s="7"/>
-    </row>
-    <row r="2814" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2814" s="18"/>
-      <c r="C2814" s="1"/>
-      <c r="D2814" s="1"/>
-      <c r="E2814" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2814" s="1"/>
-      <c r="G2814" s="10"/>
-      <c r="K2814" s="7"/>
-    </row>
-    <row r="2815" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2815" s="18"/>
-      <c r="C2815" s="1"/>
-      <c r="D2815" s="1"/>
-      <c r="E2815" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2815" s="1"/>
-      <c r="G2815" s="10"/>
-      <c r="K2815" s="7"/>
-    </row>
-    <row r="2816" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2816" s="18"/>
-      <c r="C2816" s="1"/>
-      <c r="D2816" s="1"/>
-      <c r="E2816" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2816" s="1"/>
-      <c r="G2816" s="10"/>
-      <c r="K2816" s="7"/>
-    </row>
-    <row r="2817" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2817" s="18"/>
-      <c r="C2817" s="1"/>
-      <c r="D2817" s="1"/>
-      <c r="E2817" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2817" s="1"/>
-      <c r="G2817" s="10"/>
-      <c r="K2817" s="7"/>
-    </row>
-    <row r="2818" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2818" s="18"/>
-      <c r="C2818" s="1"/>
-      <c r="D2818" s="1"/>
-      <c r="E2818" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2818" s="1"/>
-      <c r="G2818" s="10"/>
-      <c r="K2818" s="7"/>
-    </row>
-    <row r="2819" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2819" s="18"/>
-      <c r="C2819" s="1"/>
-      <c r="D2819" s="1"/>
-      <c r="E2819" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2819" s="1"/>
-      <c r="G2819" s="10"/>
-      <c r="K2819" s="7"/>
-    </row>
-    <row r="2820" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2820" s="18"/>
-      <c r="C2820" s="1"/>
-      <c r="D2820" s="1"/>
-      <c r="E2820" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2820" s="1"/>
-      <c r="G2820" s="10"/>
-      <c r="K2820" s="7"/>
-    </row>
-    <row r="2821" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2821" s="18"/>
-      <c r="C2821" s="1"/>
-      <c r="D2821" s="1"/>
-      <c r="E2821" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2821" s="1"/>
-      <c r="G2821" s="10"/>
-      <c r="K2821" s="7"/>
-    </row>
-    <row r="2822" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2822" s="18"/>
-      <c r="C2822" s="1"/>
-      <c r="D2822" s="1"/>
-      <c r="E2822" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2822" s="1"/>
-      <c r="G2822" s="10"/>
-      <c r="K2822" s="7"/>
-    </row>
-    <row r="2823" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2823" s="18"/>
-      <c r="C2823" s="1"/>
-      <c r="D2823" s="1"/>
-      <c r="E2823" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2823" s="1"/>
-      <c r="G2823" s="10"/>
-      <c r="K2823" s="7"/>
-    </row>
-    <row r="2824" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2824" s="18"/>
-      <c r="C2824" s="1"/>
-      <c r="D2824" s="1"/>
-      <c r="E2824" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2824" s="1"/>
-      <c r="G2824" s="10"/>
-      <c r="K2824" s="7"/>
-    </row>
-    <row r="2825" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2825" s="18"/>
-      <c r="C2825" s="1"/>
-      <c r="D2825" s="1"/>
-      <c r="E2825" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2825" s="1"/>
-      <c r="G2825" s="10"/>
-      <c r="K2825" s="7"/>
-    </row>
-    <row r="2826" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2826" s="18"/>
-      <c r="C2826" s="1"/>
-      <c r="D2826" s="1"/>
-      <c r="E2826" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2826" s="1"/>
-      <c r="G2826" s="10"/>
-      <c r="K2826" s="7"/>
-    </row>
-    <row r="2827" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2827" s="18"/>
-      <c r="C2827" s="1"/>
-      <c r="D2827" s="1"/>
-      <c r="E2827" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2827" s="1"/>
-      <c r="G2827" s="10"/>
-      <c r="K2827" s="7"/>
-    </row>
-    <row r="2828" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2828" s="18"/>
-      <c r="C2828" s="1"/>
-      <c r="D2828" s="1"/>
-      <c r="E2828" s="1">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="F2828" s="1"/>
-      <c r="G2828" s="10"/>
-      <c r="K2828" s="7"/>
-    </row>
-    <row r="2829" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2829" s="18"/>
-      <c r="C2829" s="1"/>
-      <c r="D2829" s="1"/>
-      <c r="E2829" s="1">
-        <f t="shared" ref="E2829:E2848" si="49">D2829-C2829</f>
-        <v>0</v>
-      </c>
-      <c r="F2829" s="1"/>
-      <c r="G2829" s="10"/>
-      <c r="K2829" s="7"/>
-    </row>
-    <row r="2830" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2830" s="18"/>
-      <c r="C2830" s="1"/>
-      <c r="D2830" s="1"/>
-      <c r="E2830" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2830" s="1"/>
-      <c r="G2830" s="10"/>
-      <c r="K2830" s="7"/>
-    </row>
-    <row r="2831" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2831" s="18"/>
-      <c r="C2831" s="1"/>
-      <c r="D2831" s="1"/>
-      <c r="E2831" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2831" s="1"/>
-      <c r="G2831" s="10"/>
-      <c r="K2831" s="7"/>
-    </row>
-    <row r="2832" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2832" s="18"/>
-      <c r="C2832" s="1"/>
-      <c r="D2832" s="1"/>
-      <c r="E2832" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2832" s="1"/>
-      <c r="G2832" s="10"/>
-      <c r="K2832" s="7"/>
-    </row>
-    <row r="2833" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2833" s="18"/>
-      <c r="C2833" s="1"/>
-      <c r="D2833" s="1"/>
-      <c r="E2833" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2833" s="1"/>
-      <c r="G2833" s="10"/>
-      <c r="K2833" s="7"/>
-    </row>
-    <row r="2834" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2834" s="18"/>
-      <c r="C2834" s="1"/>
-      <c r="D2834" s="1"/>
-      <c r="E2834" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2834" s="1"/>
-      <c r="G2834" s="10"/>
-      <c r="K2834" s="7"/>
-    </row>
-    <row r="2835" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2835" s="18"/>
-      <c r="C2835" s="1"/>
-      <c r="D2835" s="1"/>
-      <c r="E2835" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2835" s="1"/>
-      <c r="G2835" s="10"/>
-      <c r="K2835" s="7"/>
-    </row>
-    <row r="2836" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2836" s="18"/>
-      <c r="C2836" s="1"/>
-      <c r="D2836" s="1"/>
-      <c r="E2836" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2836" s="1"/>
-      <c r="G2836" s="10"/>
-      <c r="K2836" s="7"/>
-    </row>
-    <row r="2837" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2837" s="18"/>
-      <c r="C2837" s="1"/>
-      <c r="D2837" s="1"/>
-      <c r="E2837" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2837" s="1"/>
-      <c r="G2837" s="10"/>
-      <c r="K2837" s="7"/>
-    </row>
-    <row r="2838" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2838" s="18"/>
-      <c r="C2838" s="1"/>
-      <c r="D2838" s="1"/>
-      <c r="E2838" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2838" s="1"/>
-      <c r="G2838" s="10"/>
-      <c r="K2838" s="7"/>
-    </row>
-    <row r="2839" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2839" s="18"/>
-      <c r="C2839" s="1"/>
-      <c r="D2839" s="1"/>
-      <c r="E2839" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2839" s="1"/>
-      <c r="G2839" s="10"/>
-      <c r="K2839" s="7"/>
-    </row>
-    <row r="2840" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2840" s="18"/>
-      <c r="C2840" s="1"/>
-      <c r="D2840" s="1"/>
-      <c r="E2840" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2840" s="1"/>
-      <c r="G2840" s="10"/>
-      <c r="K2840" s="7"/>
-    </row>
-    <row r="2841" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2841" s="18"/>
-      <c r="C2841" s="1"/>
-      <c r="D2841" s="1"/>
-      <c r="E2841" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2841" s="1"/>
-      <c r="G2841" s="10"/>
-      <c r="K2841" s="7"/>
-    </row>
-    <row r="2842" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2842" s="18"/>
-      <c r="C2842" s="1"/>
-      <c r="D2842" s="1"/>
-      <c r="E2842" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2842" s="1"/>
-      <c r="G2842" s="10"/>
-      <c r="K2842" s="7"/>
-    </row>
-    <row r="2843" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2843" s="18"/>
-      <c r="C2843" s="1"/>
-      <c r="D2843" s="1"/>
-      <c r="E2843" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2843" s="1"/>
-      <c r="G2843" s="10"/>
-      <c r="K2843" s="7"/>
-    </row>
-    <row r="2844" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2844" s="18"/>
-      <c r="C2844" s="1"/>
-      <c r="D2844" s="1"/>
-      <c r="E2844" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2844" s="1"/>
-      <c r="G2844" s="10"/>
-      <c r="K2844" s="7"/>
-    </row>
-    <row r="2845" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2845" s="18"/>
-      <c r="C2845" s="1"/>
-      <c r="D2845" s="1"/>
-      <c r="E2845" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2845" s="1"/>
-      <c r="G2845" s="10"/>
-      <c r="K2845" s="7"/>
-    </row>
-    <row r="2846" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2846" s="18"/>
-      <c r="C2846" s="1"/>
-      <c r="D2846" s="1"/>
-      <c r="E2846" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2846" s="1"/>
-      <c r="G2846" s="10"/>
-      <c r="K2846" s="7"/>
-    </row>
-    <row r="2847" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2847" s="18"/>
-      <c r="C2847" s="1"/>
-      <c r="D2847" s="1"/>
-      <c r="E2847" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2847" s="1"/>
-      <c r="G2847" s="10"/>
-      <c r="K2847" s="7"/>
-    </row>
-    <row r="2848" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2848" s="18"/>
-      <c r="C2848" s="1"/>
-      <c r="D2848" s="1"/>
-      <c r="E2848" s="1">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="F2848" s="1"/>
-      <c r="G2848" s="10"/>
-      <c r="K2848" s="7"/>
-    </row>
-    <row r="2849" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2849" s="23">
-        <v>45944</v>
-      </c>
-      <c r="F2849" s="2">
-        <v>180.19</v>
-      </c>
-      <c r="G2849" s="2">
-        <v>1133.44</v>
-      </c>
-      <c r="H2849" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2849" s="12">
-        <v>45931</v>
-      </c>
-      <c r="J2849" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2849" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2850" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2850" s="23">
-        <v>45941</v>
-      </c>
-      <c r="F2850" s="2">
-        <v>38.04</v>
-      </c>
-      <c r="G2850" s="2">
-        <v>227.86</v>
-      </c>
-      <c r="H2850" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2850" s="12">
-        <v>45931</v>
-      </c>
-      <c r="J2850" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="K2850" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2851" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B2851" s="23">
-        <v>45941</v>
-      </c>
-      <c r="F2851" s="2">
-        <v>200</v>
-      </c>
-      <c r="G2851" s="2">
-        <v>1128</v>
-      </c>
-      <c r="H2851" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2851" s="12">
-        <v>45931</v>
-      </c>
-      <c r="J2851" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K2851" s="2" t="s">
-        <v>36</v>
-      </c>
+    <row r="2674" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2674" s="28"/>
+    </row>
+    <row r="2675" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2675" s="28"/>
+    </row>
+    <row r="2676" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L2676" s="28"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:L2851" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:L2845" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="988" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E36DC13-89CF-4EB3-AC1C-22199B2A65C6}"/>
+  <xr:revisionPtr revIDLastSave="990" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F7E4FB6-AD86-4141-A6D9-9D62AAB87473}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="990" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F7E4FB6-AD86-4141-A6D9-9D62AAB87473}"/>
+  <xr:revisionPtr revIDLastSave="1169" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11AD6616-EAAF-49F5-B597-951874DF896B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8230" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8298" uniqueCount="340">
   <si>
     <t>Data</t>
   </si>
@@ -1054,6 +1054,12 @@
   <si>
     <t>PAREBEM POSTO NITEROI</t>
   </si>
+  <si>
+    <t>HJF5G06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REDE DOM PEDRO DE POSTOS </t>
+  </si>
 </sst>
 </file>
 
@@ -87037,24 +87043,541 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2659" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2653" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2653" s="23">
+        <v>45945</v>
+      </c>
+      <c r="F2653" s="2">
+        <v>56.716000000000001</v>
+      </c>
+      <c r="G2653" s="2">
+        <v>347.1</v>
+      </c>
+      <c r="H2653" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2653" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2653" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2653" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2654" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2654" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2654" s="2">
+        <v>134.29</v>
+      </c>
+      <c r="G2654" s="2">
+        <v>858.11</v>
+      </c>
+      <c r="H2654" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2654" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2654" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K2654" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2655" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2655" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2655" s="2">
+        <v>100.94</v>
+      </c>
+      <c r="G2655" s="2">
+        <v>593.53</v>
+      </c>
+      <c r="H2655" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2655" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2655" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2655" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2656" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2656" s="23">
+        <v>45948</v>
+      </c>
+      <c r="F2656" s="2">
+        <v>99.33</v>
+      </c>
+      <c r="G2656" s="2">
+        <v>600</v>
+      </c>
+      <c r="H2656" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2656" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2656" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2656" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2657" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2657" s="23">
+        <v>45945</v>
+      </c>
+      <c r="F2657" s="2">
+        <v>201.63</v>
+      </c>
+      <c r="G2657" s="2">
+        <v>1268.26</v>
+      </c>
+      <c r="H2657" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2657" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2657" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2657" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2658" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2658" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2658" s="2">
+        <v>231.483</v>
+      </c>
+      <c r="G2658" s="2">
+        <v>1361.12</v>
+      </c>
+      <c r="H2658" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2658" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2658" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2658" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2659" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2659" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2659" s="2">
+        <v>126.08199999999999</v>
+      </c>
+      <c r="G2659" s="2">
+        <v>741.36</v>
+      </c>
+      <c r="H2659" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2659" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2659" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2659" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="L2659" s="28"/>
     </row>
-    <row r="2670" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2660" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2660" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2660" s="2">
+        <v>170.85</v>
+      </c>
+      <c r="G2660" s="2">
+        <v>1108.82</v>
+      </c>
+      <c r="H2660" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2660" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2660" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2660" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2661" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2661" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2661" s="2">
+        <v>85.617999999999995</v>
+      </c>
+      <c r="G2661" s="2">
+        <v>500</v>
+      </c>
+      <c r="H2661" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2661" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2661" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2661" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2662" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2662" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2662" s="2">
+        <v>146.61099999999999</v>
+      </c>
+      <c r="G2662" s="2">
+        <v>867.88</v>
+      </c>
+      <c r="H2662" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2662" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2662" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K2662" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2663" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2663" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2663" s="2">
+        <v>163.71</v>
+      </c>
+      <c r="G2663" s="2">
+        <v>1029.75</v>
+      </c>
+      <c r="H2663" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2663" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2663" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2663" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2664" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2664" s="23">
+        <v>45945</v>
+      </c>
+      <c r="F2664" s="2">
+        <v>199.06</v>
+      </c>
+      <c r="G2664" s="2">
+        <v>1244.03</v>
+      </c>
+      <c r="H2664" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2664" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2664" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K2664" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2665" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2665" s="23">
+        <v>45947</v>
+      </c>
+      <c r="F2665" s="2">
+        <v>114.09099999999999</v>
+      </c>
+      <c r="G2665" s="2">
+        <v>670.85</v>
+      </c>
+      <c r="H2665" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2665" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2665" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2665" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2666" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2666" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2666" s="2">
+        <v>175.32</v>
+      </c>
+      <c r="G2666" s="2">
+        <v>1127.28</v>
+      </c>
+      <c r="H2666" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2666" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2666" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2666" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2667" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2667" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2667" s="2">
+        <v>82.78</v>
+      </c>
+      <c r="G2667" s="2">
+        <v>500</v>
+      </c>
+      <c r="H2667" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2667" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2667" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2667" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2668" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2668" s="23">
+        <v>45946</v>
+      </c>
+      <c r="F2668" s="2">
+        <v>169.85</v>
+      </c>
+      <c r="G2668" s="2">
+        <v>983.43</v>
+      </c>
+      <c r="H2668" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2668" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2668" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="K2668" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2669" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2669" s="23">
+        <v>45916</v>
+      </c>
+      <c r="F2669" s="2">
+        <v>141.97</v>
+      </c>
+      <c r="G2669" s="2">
+        <v>864.6</v>
+      </c>
+      <c r="H2669" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2669" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2669" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2669" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2670" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2670" s="23">
+        <v>45922</v>
+      </c>
+      <c r="F2670" s="2">
+        <v>114.96</v>
+      </c>
+      <c r="G2670" s="2">
+        <v>700.11</v>
+      </c>
+      <c r="H2670" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2670" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2670" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K2670" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="L2670" s="28"/>
     </row>
-    <row r="2673" spans="12:12" x14ac:dyDescent="0.25">
-      <c r="L2673" s="28" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="2674" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2671" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2671" s="23">
+        <v>45926</v>
+      </c>
+      <c r="F2671" s="2">
+        <v>168.63</v>
+      </c>
+      <c r="G2671" s="2">
+        <v>1145</v>
+      </c>
+      <c r="H2671" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2671" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2671" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2671" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2672" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2672" s="23">
+        <v>45944</v>
+      </c>
+      <c r="F2672" s="2">
+        <v>160.96199999999999</v>
+      </c>
+      <c r="G2672" s="2">
+        <v>936.8</v>
+      </c>
+      <c r="H2672" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2672" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2672" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2672" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2673" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2673" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2673" s="2">
+        <v>49.68</v>
+      </c>
+      <c r="G2673" s="2">
+        <v>297.61</v>
+      </c>
+      <c r="H2673" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2673" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2673" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2673" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L2673" s="28"/>
+    </row>
+    <row r="2674" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2674" s="23">
+        <v>45929</v>
+      </c>
+      <c r="F2674" s="2">
+        <v>135.947</v>
+      </c>
+      <c r="G2674" s="2">
+        <v>814.32</v>
+      </c>
+      <c r="H2674" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2674" s="12">
+        <v>45901</v>
+      </c>
+      <c r="J2674" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2674" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="L2674" s="28"/>
     </row>
-    <row r="2675" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2675" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2675" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2675" s="2">
+        <v>143.85499999999999</v>
+      </c>
+      <c r="G2675" s="2">
+        <v>845.87</v>
+      </c>
+      <c r="H2675" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2675" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2675" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2675" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="L2675" s="28"/>
     </row>
-    <row r="2676" spans="12:12" x14ac:dyDescent="0.25">
+    <row r="2676" spans="2:12" x14ac:dyDescent="0.25">
       <c r="L2676" s="28"/>
     </row>
   </sheetData>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1169" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11AD6616-EAAF-49F5-B597-951874DF896B}"/>
+  <xr:revisionPtr revIDLastSave="1221" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010094F3-BE04-4A58-9790-266317330345}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8298" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8319" uniqueCount="341">
   <si>
     <t>Data</t>
   </si>
@@ -1060,6 +1060,9 @@
   <si>
     <t xml:space="preserve">REDE DOM PEDRO DE POSTOS </t>
   </si>
+  <si>
+    <t>POSTO CURINGA</t>
+  </si>
 </sst>
 </file>
 
@@ -1601,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2676"/>
+  <dimension ref="B1:L2682"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -87578,7 +87581,166 @@
       <c r="L2675" s="28"/>
     </row>
     <row r="2676" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2676" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2676" s="2">
+        <v>46.508000000000003</v>
+      </c>
+      <c r="G2676" s="2">
+        <v>273.45999999999998</v>
+      </c>
+      <c r="H2676" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2676" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2676" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2676" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="L2676" s="28"/>
+    </row>
+    <row r="2677" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2677" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2677" s="2">
+        <v>139.63999999999999</v>
+      </c>
+      <c r="G2677" s="2">
+        <v>878.35</v>
+      </c>
+      <c r="H2677" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2677" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2677" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2677" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2678" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2678" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2678" s="2">
+        <v>109.88200000000001</v>
+      </c>
+      <c r="G2678" s="2">
+        <v>646.1</v>
+      </c>
+      <c r="H2678" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2678" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2678" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2678" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2679" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2679" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2679" s="2">
+        <v>138.20699999999999</v>
+      </c>
+      <c r="G2679" s="2">
+        <v>798.83</v>
+      </c>
+      <c r="H2679" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2679" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2679" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K2679" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2680" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2680" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2680" s="2">
+        <v>166.52</v>
+      </c>
+      <c r="G2680" s="2">
+        <v>1064.06</v>
+      </c>
+      <c r="H2680" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2680" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2680" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K2680" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2681" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2681" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2681" s="2">
+        <v>161.041</v>
+      </c>
+      <c r="G2681" s="2">
+        <v>946.92</v>
+      </c>
+      <c r="H2681" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2681" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2681" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2681" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2682" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2682" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2682" s="2">
+        <v>186.97</v>
+      </c>
+      <c r="G2682" s="2">
+        <v>1176.0899999999999</v>
+      </c>
+      <c r="H2682" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2682" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2682" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2682" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:L2845" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1221" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{010094F3-BE04-4A58-9790-266317330345}"/>
+  <xr:revisionPtr revIDLastSave="1237" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95ED65FD-2498-41FB-A140-EC21A3C728FE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8319" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8325" uniqueCount="341">
   <si>
     <t>Data</t>
   </si>
@@ -1604,7 +1604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2682"/>
+  <dimension ref="B1:L2684"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -87742,6 +87742,52 @@
         <v>38</v>
       </c>
     </row>
+    <row r="2683" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2683" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2683" s="2">
+        <v>325.92</v>
+      </c>
+      <c r="G2683" s="2">
+        <v>2050.06</v>
+      </c>
+      <c r="H2683" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2683" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2683" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2683" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2684" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2684" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2684" s="2">
+        <v>206.45</v>
+      </c>
+      <c r="G2684" s="2">
+        <v>1298.5899999999999</v>
+      </c>
+      <c r="H2684" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2684" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2684" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2684" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:L2845" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1237" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95ED65FD-2498-41FB-A140-EC21A3C728FE}"/>
+  <xr:revisionPtr revIDLastSave="1383" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64E3E173-CF34-4C60-BC3F-F67414732361}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2845</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$2:$L$2849</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8325" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8382" uniqueCount="342">
   <si>
     <t>Data</t>
   </si>
@@ -1063,6 +1063,9 @@
   <si>
     <t>POSTO CURINGA</t>
   </si>
+  <si>
+    <t>POSTO NICODEMOS</t>
+  </si>
 </sst>
 </file>
 
@@ -1604,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2684"/>
+  <dimension ref="B1:L2703"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -87788,8 +87791,445 @@
         <v>35</v>
       </c>
     </row>
+    <row r="2685" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2685" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2685" s="2">
+        <v>53.05</v>
+      </c>
+      <c r="G2685" s="2">
+        <v>333.7</v>
+      </c>
+      <c r="H2685" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2685" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2685" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2685" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2686" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2686" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2686" s="2">
+        <v>74.510000000000005</v>
+      </c>
+      <c r="G2686" s="2">
+        <v>483.57</v>
+      </c>
+      <c r="H2686" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2686" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2686" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2686" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2687" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2687" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2687" s="2">
+        <v>123.343</v>
+      </c>
+      <c r="G2687" s="2">
+        <v>725.25</v>
+      </c>
+      <c r="H2687" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2687" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2687" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2687" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2688" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2688" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2688" s="2">
+        <v>161.69</v>
+      </c>
+      <c r="G2688" s="2">
+        <v>1101.7</v>
+      </c>
+      <c r="H2688" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2688" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2688" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2688" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2689" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2689" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2689" s="2">
+        <v>167.35</v>
+      </c>
+      <c r="G2689" s="2">
+        <v>1052.6600000000001</v>
+      </c>
+      <c r="H2689" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2689" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2689" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2689" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2690" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2690" s="23">
+        <v>45951</v>
+      </c>
+      <c r="F2690" s="2">
+        <v>152</v>
+      </c>
+      <c r="G2690" s="2">
+        <v>986.48</v>
+      </c>
+      <c r="H2690" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2690" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2690" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2690" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2691" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2691" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2691" s="2">
+        <v>85.34</v>
+      </c>
+      <c r="G2691" s="2">
+        <v>553.85</v>
+      </c>
+      <c r="H2691" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2691" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2691" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2691" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2692" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2692" s="23">
+        <v>45953</v>
+      </c>
+      <c r="F2692" s="2">
+        <v>181.48</v>
+      </c>
+      <c r="G2692" s="2">
+        <v>1177.81</v>
+      </c>
+      <c r="H2692" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2692" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2692" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2692" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2693" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2693" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2693" s="2">
+        <v>96.855000000000004</v>
+      </c>
+      <c r="G2693" s="2">
+        <v>569.51</v>
+      </c>
+      <c r="H2693" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2693" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2693" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2693" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2694" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2694" s="23">
+        <v>45944</v>
+      </c>
+      <c r="F2694" s="2">
+        <v>164.39</v>
+      </c>
+      <c r="G2694" s="2">
+        <v>1066.8900000000001</v>
+      </c>
+      <c r="H2694" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2694" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2694" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2694" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2695" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2695" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2695" s="2">
+        <v>218.76</v>
+      </c>
+      <c r="G2695" s="2">
+        <v>1367.26</v>
+      </c>
+      <c r="H2695" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2695" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2695" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K2695" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2696" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2696" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2696" s="2">
+        <v>158.16399999999999</v>
+      </c>
+      <c r="G2696" s="2">
+        <v>994.85</v>
+      </c>
+      <c r="H2696" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2696" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2696" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2696" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2697" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2697" s="23">
+        <v>45953</v>
+      </c>
+      <c r="F2697" s="2">
+        <v>23.87</v>
+      </c>
+      <c r="G2697" s="2">
+        <v>150.18</v>
+      </c>
+      <c r="H2697" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2697" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2697" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2697" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2698" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2698" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2698" s="2">
+        <v>124.42</v>
+      </c>
+      <c r="G2698" s="2">
+        <v>795.04</v>
+      </c>
+      <c r="H2698" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2698" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2698" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="K2698" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2699" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2699" s="23">
+        <v>45950</v>
+      </c>
+      <c r="F2699" s="2">
+        <v>188.376</v>
+      </c>
+      <c r="G2699" s="2">
+        <v>1298.5899999999999</v>
+      </c>
+      <c r="H2699" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2699" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2699" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2699" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2700" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2700" s="23">
+        <v>45952</v>
+      </c>
+      <c r="F2700" s="2">
+        <v>156.523</v>
+      </c>
+      <c r="G2700" s="2">
+        <v>920.35</v>
+      </c>
+      <c r="H2700" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2700" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2700" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2700" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2701" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2701" s="23">
+        <v>45953</v>
+      </c>
+      <c r="F2701" s="2">
+        <v>64.227999999999994</v>
+      </c>
+      <c r="G2701" s="2">
+        <v>377.65</v>
+      </c>
+      <c r="H2701" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2701" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2701" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="K2701" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2702" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2702" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2702" s="2">
+        <v>398.97</v>
+      </c>
+      <c r="G2702" s="2">
+        <v>2509.58</v>
+      </c>
+      <c r="H2702" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2702" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2702" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2702" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2703" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2703" s="23">
+        <v>45954</v>
+      </c>
+      <c r="F2703" s="2">
+        <v>27.9</v>
+      </c>
+      <c r="G2703" s="2">
+        <v>89.01</v>
+      </c>
+      <c r="H2703" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2703" s="12">
+        <v>45931</v>
+      </c>
+      <c r="J2703" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2703" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:L2845" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
+  <autoFilter ref="B2:L2849" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data/combustivel.xlsx
+++ b/data/combustivel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jrferragens-my.sharepoint.com/personal/jhonatan_veiga_jrferragens_com/Documents/01/HTML/DASHBOARD/DASHBOARD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1383" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64E3E173-CF34-4C60-BC3F-F67414732361}"/>
+  <xr:revisionPtr revIDLastSave="1387" documentId="8_{99301734-F318-4AB5-A368-7B22515FFAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324BDC0D-7ED1-48C8-BE60-A0517B0A5DE9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3C74772-B78D-41DC-AF47-91104267B3E5}"/>
   </bookViews>
@@ -1607,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}">
-  <dimension ref="B1:L2703"/>
+  <dimension ref="B1:L2704"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" style="2" customWidth="1"/>
@@ -88228,6 +88228,9 @@
         <v>25</v>
       </c>
     </row>
+    <row r="2704" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2704" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="B2:L2849" xr:uid="{35CF32DB-1C2A-4D45-8F6F-18BE3AEB45FF}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
